--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -5,26 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenh\Dropbox\mine\עבודה\MatchMe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A7FFAA-2E88-4688-917F-7D065A18558A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03373798-5046-4661-90D1-CC15F1D119CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId1"/>
-    <sheet name="מאפיינים - כללי" sheetId="1" r:id="rId2"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId3"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId4"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId5"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId6"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId7"/>
+    <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId2"/>
+    <sheet name="מאפיינים - כללי" sheetId="1" r:id="rId3"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId4"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId5"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId6"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId7"/>
     <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId8"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId9"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId9"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId10"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId11"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="457">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -263,13 +265,7 @@
     <t>ילדותיות</t>
   </si>
   <si>
-    <t>קשיחות ערכית / שמרנות</t>
-  </si>
-  <si>
     <t>value_rigidity</t>
-  </si>
-  <si>
-    <t>שמרנות ערכית</t>
   </si>
   <si>
     <t>אהבה לבעלי חיים</t>
@@ -404,15 +400,6 @@
     <t>Height</t>
   </si>
   <si>
-    <t>סגנון עצמי</t>
-  </si>
-  <si>
-    <t>סגנון</t>
-  </si>
-  <si>
-    <t>self_style</t>
-  </si>
-  <si>
     <t>סטטוס משתמש</t>
   </si>
   <si>
@@ -509,12 +496,6 @@
     <t xml:space="preserve">קבוע </t>
   </si>
   <si>
-    <t>להשלים אפשרויות</t>
-  </si>
-  <si>
-    <t>בחירה מרובה: להשלים</t>
-  </si>
-  <si>
     <t>אלגוריתם</t>
   </si>
   <si>
@@ -645,12 +626,6 @@
   </si>
   <si>
     <t>AI</t>
-  </si>
-  <si>
-    <t>גבר &gt; אישה</t>
-  </si>
-  <si>
-    <t>מסנן רק עבור סטרייטים. במידה וחשוב למשתמש - חישוב מיוחד. להשלים.</t>
   </si>
   <si>
     <t>חישוב ציון מאפיינים פנימיים  (אחרי מסננים)</t>
@@ -786,18 +761,9 @@
     <t>מעל 180</t>
   </si>
   <si>
-    <t>ספורטיבי / טבעי</t>
-  </si>
-  <si>
-    <t>ספורטיבי, שרירי</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
-    <t>מטופחת, קלילה</t>
-  </si>
-  <si>
     <t>בהירה</t>
   </si>
   <si>
@@ -811,9 +777,6 @@
   </si>
   <si>
     <t>ודאות*משקל</t>
-  </si>
-  <si>
-    <t>מטופחת, ספורטיבי</t>
   </si>
   <si>
     <t>החישוב היה צריך לצאת יותר גבוה לדעתי... לראות איך מתקננים את זה</t>
@@ -1182,9 +1145,6 @@
     <t>גבוהה מאוד, גבוהה, בינונית, נמוכה (מראה טבעי)</t>
   </si>
   <si>
-    <t>LookStyle</t>
-  </si>
-  <si>
     <t>BodyType</t>
   </si>
   <si>
@@ -1207,12 +1167,6 @@
   </si>
   <si>
     <t>יכול גם לסנן אם קריטי למשתמש במידת ודאות רבה (אולי רק עבור רזה/חטוב)</t>
-  </si>
-  <si>
-    <t>טופס + AI לגבי מה הוא רוצה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור לי לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין של מבנה גוף וטיפוח נגיד. </t>
   </si>
   <si>
     <t>initial_attraction_signal</t>
@@ -1314,13 +1268,13 @@
     <t>לפי הגדרת התאמות טיפוסים שנעשה ברמת שניה</t>
   </si>
   <si>
-    <t xml:space="preserve">רק על טיפוסים ספציפיים שלא הולכים אחד עם השני. רמה ראשונה - לא הולכים בכלל, מסנן לכולם. רמה שניה - פחות מתאימים, נסנן רק למשתמשים שרגישים לסגנון. </t>
-  </si>
-  <si>
     <t>אהבת הארץ וציונות</t>
   </si>
   <si>
     <t>צמחונות</t>
+  </si>
+  <si>
+    <t>היפיות</t>
   </si>
   <si>
     <t>מוסר עבודה</t>
@@ -1387,70 +1341,239 @@
     <t>ציון המשתמש += 20</t>
   </si>
   <si>
+    <t>בהמשך אולי נעשה את זה יותר מדויק</t>
+  </si>
+  <si>
+    <t>נשיות / גבריות</t>
+  </si>
+  <si>
+    <t>GenderMatched</t>
+  </si>
+  <si>
+    <t>שאלות עבור הAI</t>
+  </si>
+  <si>
+    <t>איך היית מתאר את שגרת הטיפוח שלך? או משהו בסגנון כדי להבין עד כמה המשתמש מטופח/בכושר וכו'</t>
+  </si>
+  <si>
+    <t>איך היית מתאר את הטעם שלך בנשים/גברים? מה חשוב לך? ככל שיותר תפרט נמצא לך התאמה מדויקת יותר :)</t>
+  </si>
+  <si>
+    <t>איך היית מתאר את המראה שלך באופן כללי? ככל שתתן פירוט אמין ומדויק יותר נוכל למצוא לך התאמות עם משיכה חזקה יותר</t>
+  </si>
+  <si>
+    <t>גדול מ85</t>
+  </si>
+  <si>
+    <t>קטן מ60 (או 0.6? )</t>
+  </si>
+  <si>
+    <t>תאריך עדכון מאפיינים אחרון</t>
+  </si>
+  <si>
+    <t>שמרנות/פרימיטיביות</t>
+  </si>
+  <si>
+    <t>לפי בחירת משתמש</t>
+  </si>
+  <si>
+    <t>30 לכל כיוון</t>
+  </si>
+  <si>
+    <t>ערכים אפשריים - נשי/גברי לגבר ונשית/גברית לאישה</t>
+  </si>
+  <si>
+    <t>יכול גם לסנן עבור גייז אם קריטי במידת ודאות רבה</t>
+  </si>
+  <si>
+    <t>אזורים</t>
+  </si>
+  <si>
+    <t>תל אביב</t>
+  </si>
+  <si>
+    <t>שרון</t>
+  </si>
+  <si>
+    <t>שפלה</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>אזורים קרובים</t>
+  </si>
+  <si>
+    <t>שפלה, שרון</t>
+  </si>
+  <si>
+    <t>תל אביב, נתניה</t>
+  </si>
+  <si>
+    <t>.....</t>
+  </si>
+  <si>
+    <t>אזור</t>
+  </si>
+  <si>
+    <t>ערים</t>
+  </si>
+  <si>
+    <t>סגנונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סגנון </t>
+  </si>
+  <si>
+    <t>מתאים לסגנון</t>
+  </si>
+  <si>
+    <t>לא מתאים לסגנון</t>
+  </si>
+  <si>
+    <t>חנון</t>
+  </si>
+  <si>
+    <t>קפליניסט</t>
+  </si>
+  <si>
+    <t>ביביסט</t>
+  </si>
+  <si>
+    <t>מלומד</t>
+  </si>
+  <si>
+    <t>סובייטי</t>
+  </si>
+  <si>
+    <t>תל אביבי</t>
+  </si>
+  <si>
+    <t>היפסטר</t>
+  </si>
+  <si>
+    <t>חיית מסיבות</t>
+  </si>
+  <si>
+    <t>המעורב חברתית</t>
+  </si>
+  <si>
+    <t>צופיפניק</t>
+  </si>
+  <si>
+    <t>ערס/ית</t>
+  </si>
+  <si>
+    <t>היפי/ת</t>
+  </si>
+  <si>
+    <t>פירוט לAI</t>
+  </si>
+  <si>
+    <t>היפסטריות</t>
+  </si>
+  <si>
+    <t>עממיות</t>
+  </si>
+  <si>
+    <t>חנוניות</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">ספורטיבי, מטופח... </t>
+      <t xml:space="preserve">רק על טיפוסים ספציפיים שלא הולכים אחד עם השני. רמה ראשונה - לא הולכים בכלל, מסנן לכולם. רמה שניה - פחות מתאימים, נסנן רק למשתמשים שרגישים לסגנון.   </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>להשלים</t>
+      <t>כרגע להוריד מהMVP</t>
     </r>
   </si>
   <si>
-    <t>בהמשך אולי נעשה את זה יותר מדויק</t>
-  </si>
-  <si>
-    <t>נשיות / גבריות</t>
-  </si>
-  <si>
-    <t>GenderMatched</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">רלוונטי רק עבור גייז. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-ערכים אפשריים - נשי/גברי לגבר ונשית/גברית לאישה</t>
-    </r>
-  </si>
-  <si>
-    <t>אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור הי לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין בה מבנה גוף וטיפוח נגיד.</t>
-  </si>
-  <si>
-    <t>אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור  ג לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין ,  מבנה גוף וטיפוח נגיד.</t>
-  </si>
-  <si>
-    <t>אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור ונ לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין נו מבנה גוף וטיפוח נגיד.</t>
-  </si>
-  <si>
-    <t>אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור  א לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין ,  מבנה גוף וטיפוח נגיד.</t>
-  </si>
-  <si>
-    <t>אפשרויות מרובות. להחליט בכלל אם להכניס. זה רק אם זה יעזור 
-ע לקלוט מאפיינים שבאמת רלוונטיים ולא נעים לשאול כמו מבנה גוף. אולי במקום למלא את זה - זה ישמש את הAI לנתח את המאפיין  
- מבנה גוף וטיפוח נגיד.</t>
+    <t>סגנון תל אביבי</t>
+  </si>
+  <si>
+    <t>סגנון סובייטי</t>
+  </si>
+  <si>
+    <t>צריך אולי להוסיף ערך מינימום ערך רצוי, ערך אפשרי ואז יכול להיות חצי תואם תוצאה</t>
+  </si>
+  <si>
+    <t>שלב</t>
+  </si>
+  <si>
+    <t>משימה</t>
+  </si>
+  <si>
+    <t>הערות ופירוט</t>
+  </si>
+  <si>
+    <t>ניהול</t>
+  </si>
+  <si>
+    <t>מעבר לגיט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מסמך אפיון </t>
+  </si>
+  <si>
+    <t>אקסל  אפיון מפורט</t>
+  </si>
+  <si>
+    <t>בוצע</t>
+  </si>
+  <si>
+    <t>קיים בDocs של הפרויקט</t>
+  </si>
+  <si>
+    <t>קיים בתיקיית dropbox. כשמושלם להעביר לDocs</t>
+  </si>
+  <si>
+    <t>בניית DB</t>
+  </si>
+  <si>
+    <t>אלגוריתם התאמות</t>
+  </si>
+  <si>
+    <t>סינון</t>
+  </si>
+  <si>
+    <t>בביצוע</t>
+  </si>
+  <si>
+    <t>לעשות מאפיין של זמן המתנה, מאפיין של עדיפות מערכת עם הסבר איך מחשבים. (אולי המאפיינים כבר קיימים ורק צריך להוסיף את הלוגיקה.
+אחרי זה לכתוב אפיון ברור ולהריץ</t>
+  </si>
+  <si>
+    <t>ציון פנימי</t>
+  </si>
+  <si>
+    <t>ציון חיצוני</t>
+  </si>
+  <si>
+    <t>לביצוע</t>
+  </si>
+  <si>
+    <t>מובייל</t>
+  </si>
+  <si>
+    <t>טופס הרשמה בסיסי</t>
+  </si>
+  <si>
+    <t>עובד בweb , במובייל עצמו רץ אבל לא רושם בגלל בעיית נטוורק</t>
+  </si>
+  <si>
+    <t>אלגוריתם שידוכים</t>
+  </si>
+  <si>
+    <t>את המשקל לגבי הצד השני והודאות אין צורך להזין אם לא עלה ספונטנית בשיחה וזוהתה חשיבות יתר לאותו מאפיין. המשקל יתווסף למשקל הדיפולטי של אותו מאפיין.</t>
+  </si>
+  <si>
+    <t>את הערך הרצוי נרצה להוציא בודאות זהה לודאות הנדרשת מהערך האישי</t>
   </si>
 </sst>
 </file>
@@ -1552,7 +1675,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1562,6 +1685,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1578,7 +1707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1661,9 +1790,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1673,7 +1799,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1953,6 +2081,474 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="50.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C7" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B8" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6">
+      <c r="A9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" t="s">
+        <v>446</v>
+      </c>
+      <c r="D10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="42.5546875" customWidth="1"/>
+    <col min="5" max="5" width="62.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="C4" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.8">
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2">
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="14" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>422</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1969,7 +2565,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1982,508 +2578,490 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="43.2">
       <c r="A7" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="72">
       <c r="A8" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="100.8">
       <c r="A10" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="43.2">
       <c r="A11" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="28.8">
+    <row r="12" spans="1:9" ht="72">
       <c r="A12" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="31"/>
+      <c r="I12" s="30" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="43.2">
+      <c r="A13" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="72">
-      <c r="A13" s="11" t="s">
+      <c r="H13" s="11"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="115.2">
+      <c r="A14" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B14" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H13" s="31"/>
-      <c r="I13" s="30" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.2">
-      <c r="A14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="11" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="G14" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="28.8">
+      <c r="A15" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" ht="115.2">
-      <c r="A15" s="11" t="s">
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="32"/>
-    </row>
-    <row r="16" spans="1:9" ht="28.8">
-      <c r="A16" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>123</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>156</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="11" t="s">
-        <v>326</v>
+        <v>119</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="32"/>
+      <c r="I16" s="30" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>8</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C17" s="11"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="30" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" ht="86.4">
       <c r="A18" s="11" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>292</v>
+      </c>
       <c r="G18" s="11" t="s">
-        <v>127</v>
+        <v>353</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" ht="86.4">
+      <c r="I18" s="30"/>
+    </row>
+    <row r="19" spans="1:9" ht="57.6">
       <c r="A19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>305</v>
+        <v>150</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="H19" s="11"/>
+        <v>352</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>354</v>
+      </c>
       <c r="I19" s="30"/>
     </row>
     <row r="20" spans="1:9" ht="57.6">
       <c r="A20" s="11" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>348</v>
+        <v>144</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>157</v>
+      <c r="E20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>370</v>
-      </c>
-      <c r="I20" s="30"/>
-    </row>
-    <row r="21" spans="1:9" ht="57.6">
+        <v>315</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8">
       <c r="A23" s="11" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="11" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="11" t="s">
-        <v>321</v>
+        <v>125</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="11" t="s">
-        <v>132</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -2491,9 +3069,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -2508,12 +3086,12 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="28" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="27.6">
@@ -2533,19 +3111,19 @@
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.2">
@@ -2556,7 +3134,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D5" s="2">
         <v>0.7</v>
@@ -2571,13 +3149,13 @@
         <v>8</v>
       </c>
       <c r="H5" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.8">
@@ -2588,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D6" s="2">
         <v>0.6</v>
@@ -2603,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.8">
@@ -2629,7 +3207,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2658,13 +3236,13 @@
     </row>
     <row r="9" spans="1:10" ht="82.8">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="D9" s="2">
         <v>0.7</v>
@@ -2676,16 +3254,16 @@
         <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.8">
@@ -2711,7 +3289,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8">
@@ -2737,7 +3315,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2769,10 +3347,10 @@
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="D13" s="2">
         <v>0.4</v>
@@ -2907,10 +3485,10 @@
         <v>8</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2960,8 +3538,8 @@
         <v>8</v>
       </c>
       <c r="I20" s="2"/>
-      <c r="J20" s="36" t="s">
-        <v>391</v>
+      <c r="J20" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3060,7 +3638,7 @@
         <v>63</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="D25" s="2">
         <v>0.6</v>
@@ -3098,13 +3676,13 @@
     </row>
     <row r="27" spans="1:10" ht="28.8">
       <c r="A27" s="3" t="s">
-        <v>70</v>
+        <v>393</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>68</v>
+        <v>393</v>
       </c>
       <c r="D27" s="2">
         <v>0.6</v>
@@ -3117,7 +3695,7 @@
       </c>
       <c r="G27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="J27" t="s">
         <v>20</v>
@@ -3125,13 +3703,13 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2">
         <v>0.6</v>
@@ -3147,10 +3725,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="3" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="D29" s="2">
         <v>0.3</v>
@@ -3158,14 +3736,17 @@
       <c r="E29" s="2">
         <v>3</v>
       </c>
+      <c r="F29" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="D30" s="2">
         <v>0.4</v>
@@ -3173,13 +3754,16 @@
       <c r="E30" s="2">
         <v>4</v>
       </c>
+      <c r="F30" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="27.6">
       <c r="A31" s="3" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="D31" s="2">
         <v>0.2</v>
@@ -3187,13 +3771,16 @@
       <c r="E31" s="2">
         <v>2</v>
       </c>
+      <c r="F31" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="D32" s="2">
         <v>0.2</v>
@@ -3201,13 +3788,16 @@
       <c r="E32" s="2">
         <v>2</v>
       </c>
+      <c r="F32" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="33" spans="1:10" ht="27.6">
-      <c r="A33" s="34" t="s">
-        <v>383</v>
+      <c r="A33" s="33" t="s">
+        <v>367</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="D33" s="2">
         <v>0.5</v>
@@ -3215,16 +3805,19 @@
       <c r="E33" s="2">
         <v>4</v>
       </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="28.8">
       <c r="A34" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D34" s="2">
         <v>0.2</v>
@@ -3234,22 +3827,16 @@
         <v>9</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="D35" s="2">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="2">
         <v>4</v>
@@ -3257,106 +3844,196 @@
       <c r="F35" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" ht="27.6">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="D36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D37" s="2">
         <v>0.4</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" ht="27.6">
-      <c r="A37" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D37">
-        <v>0.4</v>
-      </c>
-      <c r="E37" s="2"/>
+      <c r="E37" s="2">
+        <v>6</v>
+      </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="41.4">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="D38" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="41.4">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="D39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E42" s="2">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" ht="27.6">
+      <c r="A43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" ht="27.6">
+      <c r="A44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D44">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="41.4">
+      <c r="A45" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I45" s="19"/>
+      <c r="J45" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="41.4">
+      <c r="A46" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D46" s="2">
         <v>0.1</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3" t="s">
+      <c r="E46" s="2"/>
+      <c r="F46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J39" s="35"/>
+      <c r="G46" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J46" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -3373,10 +4050,10 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="27.6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="41.4">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
@@ -3384,7 +4061,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>5</v>
@@ -3396,56 +4073,54 @@
         <v>4</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>294</v>
+        <v>151</v>
+      </c>
+      <c r="F3" s="36">
+        <v>90</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="28.8">
+      <c r="H3" t="s">
+        <v>395</v>
+      </c>
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -3454,90 +4129,91 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>188</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="72">
+        <v>394</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="28.8">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
+        <v>324</v>
+      </c>
+      <c r="C5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>399</v>
+        <v>319</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="28.8">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>332</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3549,96 +4225,76 @@
         <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>328</v>
+      </c>
+      <c r="B10" t="s">
+        <v>330</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E10">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" t="s">
-        <v>336</v>
+        <v>8</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.8">
       <c r="A11" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="B11" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="43.2">
-      <c r="A12" t="s">
-        <v>401</v>
-      </c>
-      <c r="B12" t="s">
-        <v>402</v>
-      </c>
-      <c r="C12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12">
-        <v>0.5</v>
-      </c>
-      <c r="F12">
-        <v>80</v>
-      </c>
-      <c r="G12" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>403</v>
+        <v>396</v>
+      </c>
+      <c r="L11" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -3646,7 +4302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -3666,12 +4322,15 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>206</v>
+        <v>197</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="27.6">
@@ -3679,44 +4338,47 @@
         <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8">
       <c r="C5" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="14" t="s">
-        <v>207</v>
+        <v>198</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="41.4">
@@ -3724,52 +4386,52 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="43.2">
       <c r="C10" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -3794,7 +4456,7 @@
     </row>
     <row r="13" spans="1:10" ht="15.6">
       <c r="A13" s="23" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -3937,7 +4599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -3954,50 +4616,50 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="14" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="K2" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="L2" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="57.6">
       <c r="A3" s="14" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="K3" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8">
@@ -4011,29 +4673,29 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <f>MIN(A4 * 5, 100)</f>
+        <f t="shared" ref="D4:D12" si="0">MIN(A4 * 5, 100)</f>
         <v>35</v>
       </c>
       <c r="E4">
-        <f>MAX(0, 100 - B4 * 10)</f>
+        <f t="shared" ref="E4:E12" si="1">MAX(0, 100 - B4 * 10)</f>
         <v>50</v>
       </c>
       <c r="F4">
-        <f>MAX(0, 100 - C4 * 10)</f>
+        <f t="shared" ref="F4:F12" si="2">MAX(0, 100 - C4 * 10)</f>
         <v>80</v>
       </c>
       <c r="G4">
-        <f>0.4*D4+0.2*E4+0.4*F4</f>
+        <f t="shared" ref="G4:G12" si="3">0.4*D4+0.2*E4+0.4*F4</f>
         <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="43.2">
@@ -4047,23 +4709,23 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <f>MIN(A5 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="E5">
-        <f>MAX(0, 100 - B5 * 10)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="F5">
-        <f>MAX(0, 100 - C5 * 10)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="G5">
-        <f>0.4*D5+0.2*E5+0.4*F5</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28.8">
@@ -4077,26 +4739,26 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <f>MIN(A6 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="E6">
-        <f>MAX(0, 100 - B6 * 10)</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="F6">
-        <f>MAX(0, 100 - C6 * 10)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="G6">
-        <f>0.4*D6+0.2*E6+0.4*F6</f>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4110,23 +4772,23 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <f>MIN(A7 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="E7">
-        <f>MAX(0, 100 - B7 * 10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>MAX(0, 100 - C7 * 10)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="G7">
-        <f>0.4*D7+0.2*E7+0.4*F7</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8">
@@ -4140,26 +4802,26 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <f>MIN(A8 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="E8">
-        <f>MAX(0, 100 - B8 * 10)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="F8">
-        <f>MAX(0, 100 - C8 * 10)</f>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="G8">
-        <f>0.4*D8+0.2*E8+0.4*F8</f>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="27">
@@ -4173,26 +4835,26 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <f>MIN(A9 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="E9">
-        <f>MAX(0, 100 - B9 * 10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>MAX(0, 100 - C9 * 10)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="G9">
-        <f>0.4*D9+0.2*E9+0.4*F9</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="L9" s="33" t="s">
-        <v>362</v>
+        <v>347</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4206,19 +4868,19 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <f>MIN(A10 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E10">
-        <f>MAX(0, 100 - B10 * 10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>MAX(0, 100 - C10 * 10)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G10">
-        <f>0.4*D10+0.2*E10+0.4*F10</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -4233,26 +4895,26 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <f>MIN(A11 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="E11">
-        <f>MAX(0, 100 - B11 * 10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F11">
-        <f>MAX(0, 100 - C11 * 10)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G11">
-        <f>0.4*D11+0.2*E11+0.4*F11</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4266,19 +4928,19 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <f>MIN(A12 * 5, 100)</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="E12">
-        <f>MAX(0, 100 - B12 * 10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F12">
-        <f>MAX(0, 100 - C12 * 10)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G12">
-        <f>0.4*D12+0.2*E12+0.4*F12</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
@@ -4287,9 +4949,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
-  <dimension ref="B1:M22"/>
+  <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
@@ -4300,23 +4962,23 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1" s="19" t="s">
         <v>190</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -4329,253 +4991,209 @@
         <v>7</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="5" t="s">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="C5" s="5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>85</v>
+      </c>
+      <c r="G5" s="5">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5">
         <v>0.8</v>
-      </c>
-      <c r="F5" s="5">
-        <v>90</v>
-      </c>
-      <c r="G5" s="5">
-        <v>72</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.9</v>
       </c>
       <c r="I5" s="15">
         <f>SQRT(H5*E5)</f>
-        <v>0.84852813742385713</v>
+        <v>0.69282032302755092</v>
       </c>
       <c r="J5" s="15">
         <f>(C5+F5)/2</f>
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K5" s="15">
         <f>I5*J5</f>
-        <v>76.367532368147138</v>
+        <v>58.889727457341827</v>
       </c>
       <c r="L5" s="5">
         <f>100-ABS(G5-D5)</f>
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <f>L5*K5</f>
-        <v>5880.2999923473299</v>
+        <v>5888.9727457341824</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D6" s="5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>80</v>
+      </c>
+      <c r="G6" s="5">
+        <v>60</v>
+      </c>
+      <c r="H6" s="5">
         <v>0.6</v>
-      </c>
-      <c r="F6" s="5">
-        <v>85</v>
-      </c>
-      <c r="G6" s="5">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.8</v>
       </c>
       <c r="I6" s="15">
         <f>SQRT(H6*E6)</f>
-        <v>0.69282032302755092</v>
+        <v>0.54772255750516607</v>
       </c>
       <c r="J6" s="15">
         <f>(C6+F6)/2</f>
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="K6" s="15">
         <f>I6*J6</f>
-        <v>58.889727457341827</v>
+        <v>38.340579025361627</v>
       </c>
       <c r="L6" s="5">
         <f>100-ABS(G6-D6)</f>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M6">
         <f>L6*K6</f>
-        <v>5888.9727457341824</v>
+        <v>3450.6521122825466</v>
       </c>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="5">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5">
+        <v>90</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5">
         <v>24</v>
       </c>
-      <c r="C7" s="5">
-        <v>60</v>
-      </c>
-      <c r="D7" s="5">
-        <v>50</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="H7" s="5">
         <v>0.5</v>
-      </c>
-      <c r="F7" s="5">
-        <v>80</v>
-      </c>
-      <c r="G7" s="5">
-        <v>60</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.6</v>
       </c>
       <c r="I7" s="15">
         <f>SQRT(H7*E7)</f>
-        <v>0.54772255750516607</v>
+        <v>0.3872983346207417</v>
       </c>
       <c r="J7" s="15">
         <f>(C7+F7)/2</f>
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K7" s="15">
         <f>I7*J7</f>
-        <v>38.340579025361627</v>
+        <v>9.6824583655185421</v>
       </c>
       <c r="L7" s="5">
         <f>100-ABS(G7-D7)</f>
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="M7">
         <f>L7*K7</f>
-        <v>3450.6521122825466</v>
+        <v>329.2035844276304</v>
       </c>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="5">
-        <v>30</v>
-      </c>
-      <c r="D8" s="5">
-        <v>90</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="5">
-        <v>20</v>
-      </c>
-      <c r="G8" s="5">
-        <v>24</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.5</v>
-      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="15">
-        <f>SQRT(H8*E8)</f>
-        <v>0.3872983346207417</v>
-      </c>
-      <c r="J8" s="15">
-        <f>(C8+F8)/2</f>
-        <v>25</v>
-      </c>
-      <c r="K8" s="15">
-        <f>I8*J8</f>
-        <v>9.6824583655185421</v>
-      </c>
-      <c r="L8" s="5">
-        <f>100-ABS(G8-D8)</f>
-        <v>34</v>
-      </c>
-      <c r="M8">
-        <f>L8*K8</f>
-        <v>329.2035844276304</v>
+        <f>SUM(I5:I7)</f>
+        <v>1.6278412151534587</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13">
+        <f>SUM(K5:K7)/5</f>
+        <v>21.382552969644401</v>
+      </c>
+      <c r="L8" s="13">
+        <f>SUM(L5:L7)/5</f>
+        <v>44.8</v>
+      </c>
+      <c r="M8" s="14">
+        <f>SUM(M5:M7)/SUM(K5:K7)</f>
+        <v>90.436613964390943</v>
       </c>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="5">
-        <v>50</v>
-      </c>
-      <c r="D9" s="5">
-        <v>40</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="F9" s="5">
-        <v>50</v>
-      </c>
-      <c r="G9" s="5">
-        <v>60</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="15">
-        <f>SQRT(H9*E9)</f>
-        <v>0.56568542494923812</v>
-      </c>
-      <c r="J9" s="15">
-        <f>(C9+F9)/2</f>
-        <v>50</v>
-      </c>
-      <c r="K9" s="15">
-        <f>I9*J9</f>
-        <v>28.284271247461906</v>
-      </c>
-      <c r="L9" s="5">
-        <f>100-ABS(G9-D9)</f>
-        <v>80</v>
-      </c>
-      <c r="M9">
-        <f>L9*K9</f>
-        <v>2262.7416997969526</v>
-      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <f>I8/5</f>
+        <v>0.32556824303069176</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="5"/>
@@ -4585,20 +5203,10 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="15">
-        <f>SUM(I5:I9)</f>
-        <v>3.0420547775265541</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="13">
-        <f>SUM(L5:L9)/5</f>
-        <v>76.2</v>
-      </c>
-      <c r="M10" s="14">
-        <f>SUM(M5:M9)/SUM(K5:K9)</f>
-        <v>84.191177492150587</v>
-      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="5"/>
@@ -4608,384 +5216,640 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <f>I10/5</f>
-        <v>0.60841095550531077</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
+    <row r="12" spans="2:13" ht="28.8">
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="2:13" ht="28.8">
+      <c r="B13" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="5">
+        <v>70</v>
+      </c>
+      <c r="D13" s="5">
+        <v>80</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F13" s="5">
+        <v>80</v>
+      </c>
+      <c r="G13" s="5">
+        <v>72</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" ref="I13:I18" si="0">SQRT(H13*E13)</f>
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" ref="J13:J18" si="1">(C13+F13)/2</f>
+        <v>75</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" ref="K13:K18" si="2">I13*J13</f>
+        <v>67.5</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" ref="L13:L18" si="3">100-ABS(G13-D13)</f>
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M18" si="4">L13*K13</f>
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
       <c r="B14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>170</v>
+        <v>13</v>
+      </c>
+      <c r="C14" s="5">
+        <v>80</v>
+      </c>
+      <c r="D14" s="5">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F14" s="5">
+        <v>80</v>
+      </c>
+      <c r="G14" s="5">
+        <v>90</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>0.2449489742783178</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="2"/>
+        <v>19.595917942265423</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="4"/>
+        <v>587.87753826796268</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="5" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="C15" s="5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D15" s="5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E15" s="5">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G15" s="5">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H15" s="5">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" ref="I15:I20" si="0">SQRT(H15*E15)</f>
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>0.54772255750516607</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" ref="J15:J20" si="1">(C15+F15)/2</f>
-        <v>75</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="K15" s="15">
-        <f t="shared" ref="K15:K20" si="2">I15*J15</f>
-        <v>67.5</v>
+        <f t="shared" si="2"/>
+        <v>27.386127875258303</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" ref="L15:L20" si="3">100-ABS(G15-D15)</f>
-        <v>92</v>
+        <f t="shared" si="3"/>
+        <v>90</v>
       </c>
       <c r="M15">
-        <f t="shared" ref="M15:M20" si="4">L15*K15</f>
-        <v>6210</v>
+        <f t="shared" si="4"/>
+        <v>2464.7515087732472</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C16" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D16" s="5">
+        <v>100</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>100</v>
+      </c>
+      <c r="G16" s="5">
         <v>20</v>
       </c>
-      <c r="E16" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="F16" s="5">
-        <v>80</v>
-      </c>
-      <c r="G16" s="5">
-        <v>90</v>
-      </c>
       <c r="H16" s="5">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>0.2449489742783178</v>
+        <v>1</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K16" s="15">
         <f t="shared" si="2"/>
-        <v>19.595917942265423</v>
+        <v>100</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M16">
         <f t="shared" si="4"/>
-        <v>587.87753826796268</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="5">
+        <v>100</v>
+      </c>
+      <c r="D17" s="5">
+        <v>66</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>100</v>
+      </c>
+      <c r="G17" s="5">
         <v>24</v>
       </c>
-      <c r="C17" s="5">
-        <v>50</v>
-      </c>
-      <c r="D17" s="5">
-        <v>50</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="H17" s="5">
         <v>0.5</v>
-      </c>
-      <c r="F17" s="5">
-        <v>50</v>
-      </c>
-      <c r="G17" s="5">
-        <v>60</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0.6</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>0.54772255750516607</v>
+        <v>0.3872983346207417</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K17" s="15">
         <f t="shared" si="2"/>
-        <v>27.386127875258303</v>
+        <v>38.729833462074168</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="M17">
         <f t="shared" si="4"/>
-        <v>2464.7515087732472</v>
+        <v>2246.3303408003017</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C18" s="5">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E18" s="5">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F18" s="5">
         <v>100</v>
       </c>
       <c r="G18" s="5">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H18" s="5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.56568542494923812</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K18" s="15">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>33.941125496954285</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M18">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>2715.2900397563426</v>
       </c>
     </row>
     <row r="19" spans="2:13">
-      <c r="B19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="5">
-        <v>100</v>
-      </c>
-      <c r="D19" s="5">
-        <v>66</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="F19" s="5">
-        <v>100</v>
-      </c>
-      <c r="G19" s="5">
-        <v>24</v>
-      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
       <c r="H19" s="5">
-        <v>0.5</v>
+        <f>SUM(H13:H18)/5</f>
+        <v>0.78</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>0.3872983346207417</v>
-      </c>
-      <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="K19" s="15">
-        <f t="shared" si="2"/>
-        <v>38.729833462074168</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="4"/>
-        <v>2246.3303408003017</v>
+        <f>SUM(I13:I18)</f>
+        <v>3.6456552913534637</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="13">
+        <f>SUM(L13:L18)/5</f>
+        <v>74</v>
+      </c>
+      <c r="M19" s="14">
+        <f>SUM(M13:M18)/SUM(K13:K18)</f>
+        <v>56.500364466750881</v>
       </c>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="5">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5">
-        <v>40</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="F20" s="5">
-        <v>100</v>
-      </c>
-      <c r="G20" s="5">
-        <v>60</v>
-      </c>
-      <c r="H20" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>0.56568542494923812</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="K20" s="15">
-        <f t="shared" si="2"/>
-        <v>33.941125496954285</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="4"/>
-        <v>2715.2900397563426</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5">
-        <f>SUM(H15:H20)/5</f>
-        <v>0.78</v>
-      </c>
-      <c r="I21" s="15">
-        <f>SUM(I15:I20)</f>
-        <v>3.6456552913534637</v>
-      </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="13">
-        <f>SUM(L15:L20)/5</f>
-        <v>74</v>
-      </c>
-      <c r="M21" s="14">
-        <f>SUM(M15:M20)/SUM(K15:K20)</f>
-        <v>56.500364466750881</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5">
-        <f>I21/5</f>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5">
+        <f>I19/5</f>
         <v>0.72913105827069269</v>
       </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="5"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="43.2">
+      <c r="A6" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="5">
+        <v>95</v>
+      </c>
+      <c r="E7" s="5">
+        <v>185</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <f>F7*D7</f>
+        <v>95</v>
+      </c>
+      <c r="I7">
+        <f>D7*F7*G7</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <f>F8*D8</f>
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:I11" si="0">D8*F8*G8</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9">
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <f>F9*D9</f>
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10">
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <f>F10*D10</f>
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11">
+        <v>0.6</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>F11*D11</f>
+        <v>18</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="D12">
+        <f>SUM(D7:D11)</f>
+        <v>335</v>
+      </c>
+      <c r="F12">
+        <f>SUM(F7:F11)</f>
+        <v>3.4</v>
+      </c>
+      <c r="H12">
+        <f>SUM(H7:H11)</f>
+        <v>233</v>
+      </c>
+      <c r="I12" s="25">
+        <f>SUM(I7:I11)/H12</f>
+        <v>9.2274678111587978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="20" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>432</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5003,109 +5867,109 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="L3" s="14" t="s">
         <v>246</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="I4" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="K4" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="L4" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="L5" s="19" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="27" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="L11" s="14" t="s">
         <v>246</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -5122,13 +5986,13 @@
         <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="H12" s="29">
         <v>46075</v>
@@ -5148,7 +6012,7 @@
         <v>67.599999999999994</v>
       </c>
       <c r="N12" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -5201,505 +6065,6 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="14"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" customWidth="1"/>
-    <col min="8" max="8" width="32.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="43.2">
-      <c r="A6" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" s="5">
-        <v>95</v>
-      </c>
-      <c r="E7" s="5">
-        <v>185</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <f>D7*F7*G7</f>
-        <v>950</v>
-      </c>
-      <c r="I7">
-        <f>F7*D7</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <f t="shared" ref="H8:H13" si="0">D8*F8*G8</f>
-        <v>400</v>
-      </c>
-      <c r="I8">
-        <f t="shared" ref="I8:I13" si="1">F8*D8</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D9">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>239</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>425</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>165</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11">
-        <v>0.8</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12">
-        <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12">
-        <v>0.5</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>236</v>
-      </c>
-      <c r="F13">
-        <v>0.6</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="D14">
-        <f>SUM(D7:D13)</f>
-        <v>500</v>
-      </c>
-      <c r="F14">
-        <f>SUM(F7:F13)</f>
-        <v>5.3999999999999995</v>
-      </c>
-      <c r="H14" s="25">
-        <f>SUM(H7:H13)/I14</f>
-        <v>7.474874371859296</v>
-      </c>
-      <c r="I14">
-        <f>SUM(I7:I13)</f>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="20" t="s">
-        <v>242</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="42.5546875" customWidth="1"/>
-    <col min="5" max="5" width="62.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="D1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="C4" s="14" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="C7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" t="s">
-        <v>290</v>
-      </c>
-      <c r="E7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.8">
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.2">
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="C12" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="C13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" t="s">
-        <v>295</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="C14" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>283</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03373798-5046-4661-90D1-CC15F1D119CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D008A3-A6F4-4235-B1A3-895B7DD02642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="459">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -1545,10 +1545,6 @@
     <t>בביצוע</t>
   </si>
   <si>
-    <t>לעשות מאפיין של זמן המתנה, מאפיין של עדיפות מערכת עם הסבר איך מחשבים. (אולי המאפיינים כבר קיימים ורק צריך להוסיף את הלוגיקה.
-אחרי זה לכתוב אפיון ברור ולהריץ</t>
-  </si>
-  <si>
     <t>ציון פנימי</t>
   </si>
   <si>
@@ -1574,6 +1570,15 @@
   </si>
   <si>
     <t>את הערך הרצוי נרצה להוציא בודאות זהה לודאות הנדרשת מהערך האישי</t>
+  </si>
+  <si>
+    <t>סוכן מנתח</t>
+  </si>
+  <si>
+    <t>סוכן משוחח</t>
+  </si>
+  <si>
+    <t>סוכנים</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -2159,7 +2164,7 @@
         <v>444</v>
       </c>
       <c r="B7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
         <v>440</v>
@@ -2170,35 +2175,52 @@
         <v>444</v>
       </c>
       <c r="B8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" t="s">
         <v>449</v>
       </c>
-      <c r="C8" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="57.6">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C9" t="s">
-        <v>446</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>447</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B10" t="s">
         <v>451</v>
-      </c>
-      <c r="B10" t="s">
-        <v>452</v>
       </c>
       <c r="C10" t="s">
         <v>446</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C11" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4330,7 +4352,7 @@
         <v>197</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="27.6">
@@ -4378,7 +4400,7 @@
         <v>198</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="41.4">

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D008A3-A6F4-4235-B1A3-895B7DD02642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9937C9-878E-421E-A58D-E547D96BEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="482">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -91,54 +92,27 @@
     <t>רגיש</t>
   </si>
   <si>
-    <t>cognitive_profile</t>
-  </si>
-  <si>
-    <t>פרופיל קוגניטיבי</t>
-  </si>
-  <si>
-    <t>Vibe</t>
-  </si>
-  <si>
     <t>סחיות</t>
   </si>
   <si>
-    <t>יציבות רגשית כללית</t>
-  </si>
-  <si>
     <t>emotional_stability</t>
   </si>
   <si>
     <t>יציבות רגשית</t>
   </si>
   <si>
-    <t>נטייה לחרדה/דרמטיות</t>
-  </si>
-  <si>
-    <t>Neuroticism</t>
-  </si>
-  <si>
-    <t>נוירוטיות</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
     <t>פלט בטוח</t>
   </si>
   <si>
-    <t>חשיבות המשפחה בחיים</t>
-  </si>
-  <si>
     <t>family_orientation</t>
   </si>
   <si>
     <t>משפחתיות</t>
   </si>
   <si>
-    <t>אהבה ליציאות, מסיבות, בילויים</t>
-  </si>
-  <si>
     <t>party_orientation</t>
   </si>
   <si>
@@ -157,9 +131,6 @@
     <t>מופנמות/מוחצנות</t>
   </si>
   <si>
-    <t>רמת אנרגיה כללית</t>
-  </si>
-  <si>
     <t>energy_level</t>
   </si>
   <si>
@@ -184,18 +155,12 @@
     <t>רצינות</t>
   </si>
   <si>
-    <t>שטותניקיות בקטע גופי</t>
-  </si>
-  <si>
     <t>goophiness</t>
   </si>
   <si>
     <t>שטותניקיות</t>
   </si>
   <si>
-    <t>רמת דתיות</t>
-  </si>
-  <si>
     <t>Religiosity</t>
   </si>
   <si>
@@ -208,18 +173,12 @@
     <t>self_awareness</t>
   </si>
   <si>
-    <t xml:space="preserve">הומור וקלילות.   </t>
-  </si>
-  <si>
     <t>Humor</t>
   </si>
   <si>
     <t>הומור</t>
   </si>
   <si>
-    <t>מעורבות פוליטית</t>
-  </si>
-  <si>
     <t>political_orientation</t>
   </si>
   <si>
@@ -256,9 +215,6 @@
     <t>פתיחות</t>
   </si>
   <si>
-    <t xml:space="preserve">מידת ילדותיות לעומת בגרות </t>
-  </si>
-  <si>
     <t>Childishness</t>
   </si>
   <si>
@@ -293,9 +249,6 @@
   </si>
   <si>
     <t>שיעור אישור</t>
-  </si>
-  <si>
-    <t>רמת בוטות</t>
   </si>
   <si>
     <t>bluntness_score</t>
@@ -1048,9 +1001,6 @@
     <t>SexuallIdentity</t>
   </si>
   <si>
-    <t>טרנס/אמיני - לחשוב מה עוד נכנס פה</t>
-  </si>
-  <si>
     <t>מסנן</t>
   </si>
   <si>
@@ -1259,12 +1209,6 @@
     <t>לפי הגדרת התאמות טיפוסים שנעשה</t>
   </si>
   <si>
-    <t xml:space="preserve">עד כמה המשתמש "סחי"  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מדד קוגניטיבי פנימי כללי להתאמה מחשבתית (אינטליגנציה כללית). </t>
-  </si>
-  <si>
     <t>לפי הגדרת התאמות טיפוסים שנעשה ברמת שניה</t>
   </si>
   <si>
@@ -1283,13 +1227,7 @@
     <t>"ילד טוב"</t>
   </si>
   <si>
-    <t>ציונות, אהבת המדינה</t>
-  </si>
-  <si>
     <t>ימניות/שמאלניות</t>
-  </si>
-  <si>
-    <t>כמה שיותר ימני - דירוג גבוה יותר</t>
   </si>
   <si>
     <t>כמה שיותר צמחוני - דירוג גבוה יותר. טבעוני יהיה הגבוה ביותר</t>
@@ -1320,24 +1258,9 @@
     <t>לא בטוח שרלוונטי, כי אולי הai לא מספיק טוב בלזהות.</t>
   </si>
   <si>
-    <t>דברים שעלולים להוות דיל ברייקרס אצל הצד השני. למשל - מישהו שגר עם ההורים.</t>
-  </si>
-  <si>
-    <t>זיהוי רעילות - אלימות, גזענות וכל מה שאתה מזהה כרעיל</t>
-  </si>
-  <si>
-    <t>האם באמת מחפש שידוכים או שבא להטריל את המערכת</t>
-  </si>
-  <si>
-    <t>פתיחות לרעיונות וחוויות, לא במובן של פתיחות רגשית.</t>
-  </si>
-  <si>
     <t>extovert</t>
   </si>
   <si>
-    <t>ככל שהמוחצנות גבוהה - נתן ציון גבוה יותר</t>
-  </si>
-  <si>
     <t>ציון המשתמש += 20</t>
   </si>
   <si>
@@ -1474,9 +1397,6 @@
   </si>
   <si>
     <t>עממיות</t>
-  </si>
-  <si>
-    <t>חנוניות</t>
   </si>
   <si>
     <r>
@@ -1579,6 +1499,157 @@
   </si>
   <si>
     <t>סוכנים</t>
+  </si>
+  <si>
+    <t>קבוצה</t>
+  </si>
+  <si>
+    <t>אינטליגנציה רגשית</t>
+  </si>
+  <si>
+    <t>פרופיל קוגנטיבי</t>
+  </si>
+  <si>
+    <t>אינטליגנציה מחשבתית</t>
+  </si>
+  <si>
+    <t>IQ</t>
+  </si>
+  <si>
+    <t>אנחנו רוצים להעריך פה בגדול עד כמה המשתמש אינטילגנטי. במובן הפשוט של המילה כמו שאתה מבין איך להעריך אינטלגנציה. לא אינטלגנציה רגשית, רק מחשבתית. תרגיש חופשי להבין את זה מהנוסח של המשתמש ומורכבות המחשבה שלו. שים לב - אין צורך להיות "פוליטיקלי קורקט" ולמצע את הציונים. תן ציון באמת כפי שנראה לך, גם אם הוא נמוך.    
+לגבי המשקל עבור המשתמש - אם אתה חושב שלמשתמש מאוד חשוב מישהו חכם - תן משקל גבוה, אחרת אין צורך להזין.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מידת אינטילגנציה רגשית. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">יציבות רגשית כללית. עד כמה המשתמש נוטה למצבי רוח קיצוניים, למצבי רוח שליליים, חרדה וכו'. </t>
+  </si>
+  <si>
+    <t>מאפיינים שלא נכנסו בינתיים לMVP, להתעלם:</t>
+  </si>
+  <si>
+    <t>הטיפוס המסיבתי</t>
+  </si>
+  <si>
+    <t>FunImportance</t>
+  </si>
+  <si>
+    <t>האם מדובר בטיפוס המסיבתי? שיוצא למסיבות כל הזמן, עושה הרבה סטוצים, וייב בלייני מסיבתי</t>
+  </si>
+  <si>
+    <t>עד כמה הבנאדם פשוט אוהב לעשות כיף. זה לא חייב להיות סוג ספציפי של כיף, אבל נגיד - אוהב לבלות עם חברים, לצאת למסעדות, לטייל בחו"ל, לצאת לברים.. בכלל כמה חשוב לו לעשות כיף ולבלות, האם זה ממש ערך בשבילו לצאת וליהנות מהחיים? כמה שהוא יותר אוהב ומעריך כיף ובילויים נקבל פה ציון גבוה יותר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עד כמה המשתמש קשור למשפחת המוצא שלו. שים לב - לא מדובר בעד כמה המשתמש רוצה משפחה וילדים משלו, אלא על כמה שהוא קשור למשפחת המוצא, להורים בעיקר, כמה שהמשפחה היא חלק חשוב ונוכח בחיים שלו. </t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש "סחי"  . ככל שהוא יותר סחי נתן ציון גבוה יותר. שים לב - סחיות זה גם עד כמה המשתמש סוג של בסיסי - אוהב דברים של מיינסטרים מוגזם וכו'. אלא גם כמה הדעות שלו ותחומי העניין שלו הם ממוצעים ונורמטיבים, עד כמה הוא "עם העדר". עד כמה היית מגדיר אותו בינוני ורגיל בגדול.  חשוב שתבחין בין מיינסטרים ישראלי למיינסטרים כללי. למשל - לאהוב הארי פוטר זה דבר מאוד מיינסטרימי כביכול, זה ספר מאוד פופולרי אבל בתכל'ס זה בדרך כלל יותר של חנונים ופחות מיינסטרים בישראל. שים לב לזה.  ככל שהבנאדם סחי יותר - יקבל פה ציון גבוה יותר.</t>
+  </si>
+  <si>
+    <t>האם הבנאדם מופנם או מוחצן? ככל שהמוחצנות גבוהה - נתן ציון גבוה יותר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רמת אנרגיה כללית. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שטותניקיות בקטע goophi. שים לב - לא מדובר פה על קלילות ועל הומור סטנדרטיים אלא על אנשים עם נטיה לשטויות מהסוג המביך. למשל כאלה שעושים את ריקוד הרובוט. מן גופיות חנונית כזאת. זו הכוונה. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רמת דתיות. מי שדתי ברמה של שמירת שבת, כלומר ממש דתי בהגדרה יהיה בטווח ה90 עד 100. מעבר לזה יש לנו טווח בין חילוני גמור למסורתי קצת לדתי קצת וכו'. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הומור וקלילות.   הומור קצת קשה לנטר, אז תתייחס בעיקר לכמה חשוב למשתמש חוש הומור, בדרך כלל זה מעיד על החוש הומור שלו עצמו. או אם הוא מעיד באופן ישיר שהוא בעל חוש הומור. קלילות אפשר לנסות להעריך לפי איך שאתה מבין </t>
+  </si>
+  <si>
+    <t>מעורבות פוליטית. עד כמה זה חשוב למשתמש? עד כמה הוא מחזיק בדעות פוליטיות נוקשות וחי פוליטיקה?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מעורבות חברתית. עד כמה המשתמש הוא הטיפוס המעורב, כזה שהולך להפגנות, מתעסק בתיקון חברתי, מתנדב, עד כמה אכפת לו מנושאים חברתיים בוערים וכו'. </t>
+  </si>
+  <si>
+    <t>שמרנות/פרימיטיביות. אל תפחד להעריך פה. לא להיות פוליטיקלי קורקט. לנסות להבין כמה הבנאדם מחזיק בדעות שמרניות. ככל שיותר שמרן/פרימיטיבי - ציון גבוה יותר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מידת ילדותיות לעומת בגרות. ככל שיותר ילדותי - ציון גבוה יותר. </t>
+  </si>
+  <si>
+    <t>פתיחות לרעיונות וחוויות, לא במובן של פתיחות רגשית. במובן של פתיחות לחוויות חדשות, לרעיונות חדשים, צורות חיים שונות וכו'. ככל שהפתיחות גבוהה יותר - ציון גבוה יותר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אהבה לבעלי חיים. ככל שהמשתמש אוהב יותר בעלי חיים - יקבל ציון גבוה יותר. שים לב - לא סתם לנטר אם שמעת מילה על בעלי חיים, שים לב למה שהמשתמש באמת אומר.  למשל מישהו שמפחד מכלבים יכול לציין את זה ואז יקבל ציון נמוך. מישהו שאומר שיש לו כלב - יקבל ציון גבוה. </t>
+  </si>
+  <si>
+    <t>ציונות, אהבת המדינה. עד כמה ציונות זה ערך עבור המשתמש?</t>
+  </si>
+  <si>
+    <t>כמה שיותר ימני - דירוג גבוה יותר. אם המשתמש מעיד על עצמו שאין לו נטייה פוליטית חזקה אפשר פחות להתעכב על הסעיף הזה. אם הוא מאוד פוליטי - קריטי לדעת לאיזה צד.</t>
+  </si>
+  <si>
+    <t>היפסטריות. כלומר - סגנון אינדי, אולי התנשאות קלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כמה המשתמש חי את התל אביביות שלו, או גם אם הוא לא תל אביבי - כמה הוא בסגנון התל אביבי של יציאות, בילויים. או לחילופין - כמה הוא פריפריאלי באופי. ככל שפחות פריפריאלי יקבל פה ציון גבוה יותר. </t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש עממי. ככל שעממי יותר יקבל ציון גבוה יותר. זה יכול להתבטא במוזיקה ווייב מזרחי או בכל מה שאתה מבין כעממיות</t>
+  </si>
+  <si>
+    <t>גיקיות</t>
+  </si>
+  <si>
+    <t>גיקיות. לאו דווקא חנון במובן של ילד טוב וחכם. אלא גיק - כלומר בקטע של מחשבים, פנטזיה וכל מה שקשור בגיקיות</t>
+  </si>
+  <si>
+    <t>סגנון היפי</t>
+  </si>
+  <si>
+    <t>סגנון רוסי. זה יכול להתבטא באנליטיות גבוהה, בחינוך נוקשה או כל מה שאתה מתאר כסובייטי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רמת בוטות. אם אתה לא מזהה בוטות אצל המשתמש אחרי כל השאלות כנראה שאפשר להגיד במידה גבוהה שיש לו בוטות נמוכה. </t>
+  </si>
+  <si>
+    <t>זיהוי רעילות - אלימות, גזענות וכל מה שאתה מזהה כרעיל. חשוב לזהות רק את מי שבאמת רעיל. אם אחרי כל השאלות לא זיהית רעילות מיוחדת - זה אומר שהמשתמש כנראה לא רגיל.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">האם באמת מחפש שידוכים או שבא להטריל את המערכת. אם אתה רואה תשובות שנראות לך הזויות, סותרות, לא כנות או סתם לא לעניין. </t>
+  </si>
+  <si>
+    <t>האם סביר שהמשתמש הוא טרנס או א-מיני? האם העיד על עצמו שיש לו זהות מינית מיוחדת? אם לא קיבלת שום אינדיקציה כזאת מהמשתמש אחרי כל השאלות - כנראה שאין .</t>
+  </si>
+  <si>
+    <t>דברים שעלולים להוות דיל ברייקרס אצל הצד השני. האם זיהית אחד מהדברים הבאים: גר עם ההורים, גרוש פלוס ילדים, יש לו בעל חיים, שונא בעלי חיים. או כל דבר שאתה חושב שיכול להיות דיל ברייקר אצל משתמשים מסוימים. אם זיהית משהו כזה - פה לא ניתן ציון, אלא הערכה טקסטואלית.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש בעל חזות גברית/נשית</t>
+  </si>
+  <si>
+    <t>סגנון</t>
+  </si>
+  <si>
+    <t>פרופיל רגשי</t>
+  </si>
+  <si>
+    <t>אורח חיים</t>
+  </si>
+  <si>
+    <t>וייב</t>
+  </si>
+  <si>
+    <t>ערכים</t>
+  </si>
+  <si>
+    <t>כללי</t>
+  </si>
+  <si>
+    <t>Mainstreamness</t>
+  </si>
+  <si>
+    <t>EQ</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1805,8 +1876,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2098,129 +2170,129 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="35" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="C2" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B4" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="B6" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="C6" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="B8" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="C8" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="C10" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="D10" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="B11" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="C11" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="B12" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -2240,149 +2312,149 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="14" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="C3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="C4" s="14" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="C5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="C7" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8">
       <c r="C8" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="C9" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2">
       <c r="C10" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" s="14" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="C14" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E14" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="C16" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2402,137 +2474,137 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="14" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="B5" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="14" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="14" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="14" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2547,22 +2619,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -2587,7 +2659,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2600,490 +2672,490 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="11" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="11" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="11" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="11" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="43.2">
       <c r="A7" s="11" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="72">
       <c r="A8" s="11" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="G8" s="11" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="11" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="100.8">
       <c r="A10" s="11" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="11" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="43.2">
       <c r="A11" s="11" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="72">
       <c r="A12" s="11" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="30" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="43.2">
       <c r="A13" s="11" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="11" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" ht="115.2">
       <c r="A14" s="11" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="11" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" ht="28.8">
       <c r="A15" s="11" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="11" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="11" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="30" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="11" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="11" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="86.4">
       <c r="A18" s="11" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="30"/>
     </row>
     <row r="19" spans="1:9" ht="57.6">
       <c r="A19" s="11" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="I19" s="30"/>
     </row>
     <row r="20" spans="1:9" ht="57.6">
       <c r="A20" s="11" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="11" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="11" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.8">
       <c r="A23" s="11" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="11" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="11" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="11" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="11" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="12" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="11" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="11" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -3093,30 +3165,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
     <col min="2" max="2" width="20.5546875" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.77734375" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="40.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="53.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="27.6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -3124,929 +3197,1096 @@
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>83</v>
-      </c>
       <c r="G4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>182</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2">
+        <v>167</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="110.4">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>435</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F5" s="2">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F6" s="2">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" spans="1:11" ht="124.2">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="2">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.8">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B7" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.6</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F7" s="2">
         <v>7</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.8">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="E7" s="2">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="H7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28.8">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.7</v>
       </c>
-      <c r="E8" s="2">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2">
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="82.8">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="55.2">
       <c r="A9" s="3" t="s">
-        <v>355</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.7</v>
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="E9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8">
+      <c r="J9" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28.8">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>441</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.6</v>
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="E10" s="2">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>21</v>
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.8">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="69">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.6</v>
+        <v>442</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="E11" s="2">
-        <v>6</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>8</v>
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="H11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="27.6">
       <c r="A12" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.5</v>
+        <v>355</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>447</v>
       </c>
       <c r="E12" s="2">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="27.6">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.4</v>
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>8</v>
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="H13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="2">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2">
         <v>0.5</v>
       </c>
-      <c r="E14" s="2">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="2">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.5</v>
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
+        <v>0.6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="41.4">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.6</v>
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="E16" s="2">
-        <v>5</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>8</v>
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="H16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.6</v>
+        <v>36</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E17" s="2">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" ht="28.8">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="55.2">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.7</v>
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>451</v>
       </c>
       <c r="E18" s="2">
-        <v>6</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="27.6">
       <c r="A19" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.7</v>
+        <v>39</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="E19" s="2">
-        <v>9</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>8</v>
+        <v>0.6</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="H19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="41.4">
       <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="2">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="41.4">
+      <c r="A23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C24" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F24" s="2">
+        <v>7</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="41.4">
+      <c r="A25" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F25" s="2">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="69">
+      <c r="A26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="41.4">
+      <c r="A28" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="27.6">
+      <c r="A31" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" s="2">
         <v>0.5</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F31" s="2">
         <v>4</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="s">
+    </row>
+    <row r="32" spans="1:11" ht="28.8">
+      <c r="A32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F33" s="2">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="55.2">
+      <c r="A34" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="2">
+    </row>
+    <row r="35" spans="1:11" ht="27.6">
+      <c r="A35" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="27.6">
+      <c r="A36" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F36" s="2">
+        <v>4</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="27.6">
+      <c r="A38" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="27.6">
+      <c r="A40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>4</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" ht="41.4">
+      <c r="A41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" ht="41.4">
+      <c r="A42" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E42">
+        <v>0.4</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="41.4">
+      <c r="A43" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J43" s="19"/>
+      <c r="K43" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="69">
+      <c r="A44" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K44" s="34"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="36" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="69">
+      <c r="A48" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F48" s="2">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F49" s="2">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="55.2">
+      <c r="A50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E50" s="2">
         <v>0.6</v>
       </c>
-      <c r="E21" s="2">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="F50" s="2">
+        <v>5</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E22" s="2">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E24" s="2">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="27.6">
-      <c r="A25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E25" s="2">
-        <v>6</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E26" s="2">
-        <v>7</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" ht="28.8">
-      <c r="A27" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E27" s="2">
-        <v>7</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="I27" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E28" s="2">
-        <v>5</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E29" s="2">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E30" s="2">
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="27.6">
-      <c r="A31" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="27.6">
-      <c r="A33" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E33" s="2">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="28.8">
-      <c r="A34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E35" s="2">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E36" s="2">
-        <v>3</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>6</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="2">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E39" s="2">
-        <v>3</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E40" s="2">
-        <v>3</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="E42" s="2">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" ht="27.6">
-      <c r="A43" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" ht="27.6">
-      <c r="A44" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D44">
-        <v>0.4</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="41.4">
-      <c r="A45" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="41.4">
-      <c r="A46" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J46" s="34"/>
+      <c r="J50" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4072,7 +4312,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="16" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="41.4">
@@ -4083,7 +4323,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>5</v>
@@ -4095,54 +4335,60 @@
         <v>4</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="36">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F3">
         <v>90</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="I3" s="19"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>163</v>
+      </c>
+      <c r="D4" t="s">
+        <v>472</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -4151,19 +4397,19 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" ht="28.8">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -4175,21 +4421,21 @@
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4201,18 +4447,18 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4224,18 +4470,18 @@
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4247,15 +4493,15 @@
         <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E9">
         <v>0.3</v>
@@ -4267,18 +4513,18 @@
         <v>9</v>
       </c>
       <c r="K9" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B10" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -4290,18 +4536,21 @@
         <v>8</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.8">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>164</v>
+      </c>
+      <c r="D11" t="s">
+        <v>473</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -4313,10 +4562,10 @@
         <v>9</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="L11" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4344,15 +4593,15 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>454</v>
+        <v>181</v>
+      </c>
+      <c r="E3" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="27.6">
@@ -4360,47 +4609,47 @@
         <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8">
       <c r="C5" s="5" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>455</v>
+        <v>182</v>
+      </c>
+      <c r="E8" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="41.4">
@@ -4408,52 +4657,52 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="43.2">
       <c r="C10" s="5" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -4478,7 +4727,7 @@
     </row>
     <row r="13" spans="1:10" ht="15.6">
       <c r="A13" s="23" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -4638,50 +4887,50 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="14" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="K2" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="L2" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="57.6">
       <c r="A3" s="14" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="K3" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8">
@@ -4711,13 +4960,13 @@
         <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="43.2">
@@ -4747,7 +4996,7 @@
         <v>50</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28.8">
@@ -4777,10 +5026,10 @@
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4810,7 +5059,7 @@
         <v>22</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8">
@@ -4840,10 +5089,10 @@
         <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="27">
@@ -4873,10 +5122,10 @@
         <v>22</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4933,10 +5182,10 @@
         <v>14</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4984,23 +5233,23 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="14" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -5013,42 +5262,42 @@
         <v>7</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5">
         <v>85</v>
@@ -5091,7 +5340,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" s="5">
         <v>60</v>
@@ -5134,7 +5383,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5">
         <v>30</v>
@@ -5248,42 +5497,42 @@
         <v>7</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="5" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C13" s="5">
         <v>70</v>
@@ -5326,7 +5575,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5">
         <v>80</v>
@@ -5369,7 +5618,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5">
         <v>50</v>
@@ -5412,7 +5661,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="5" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5">
         <v>100</v>
@@ -5455,7 +5704,7 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C17" s="5">
         <v>100</v>
@@ -5498,7 +5747,7 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="5" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C18" s="5">
         <v>20</v>
@@ -5599,14 +5848,14 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="14" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="26" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -5622,7 +5871,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="20" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -5639,7 +5888,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5651,42 +5900,42 @@
     </row>
     <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="22" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="D7" s="5">
         <v>95</v>
@@ -5711,19 +5960,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D8">
         <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>0.5</v>
@@ -5742,19 +5991,19 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D9">
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F9">
         <v>0.8</v>
@@ -5773,19 +6022,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D10">
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F10">
         <v>0.5</v>
@@ -5804,19 +6053,19 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F11">
         <v>0.6</v>
@@ -5853,17 +6102,17 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="19" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="20" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5889,109 +6138,109 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="14" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="I4" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="K4" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="L4" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="L5" s="19" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="27" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="14" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -6008,13 +6257,13 @@
         <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="F12" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="H12" s="29">
         <v>46075</v>
@@ -6034,7 +6283,7 @@
         <v>67.599999999999994</v>
       </c>
       <c r="N12" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:14">

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9937C9-878E-421E-A58D-E547D96BEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A4FBEA-5140-4840-BC18-3E5E251AB18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="טופס הזנה" sheetId="8" r:id="rId10"/>
     <sheet name="טבלאות דאטה" sheetId="11" r:id="rId11"/>
     <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId12"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="524">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -137,18 +138,12 @@
     <t>אנרגטיות</t>
   </si>
   <si>
-    <t>נטייה אנליטית</t>
-  </si>
-  <si>
     <t>analytical_tendency</t>
   </si>
   <si>
     <t>אנליטיות</t>
   </si>
   <si>
-    <t>רצינות כלפי החיים</t>
-  </si>
-  <si>
     <t>Seriousness</t>
   </si>
   <si>
@@ -191,18 +186,12 @@
     <t>social_involvement</t>
   </si>
   <si>
-    <t>גישה חיובית</t>
-  </si>
-  <si>
     <t>Positivity</t>
   </si>
   <si>
     <t>חיוביות</t>
   </si>
   <si>
-    <t>לבביות וחום אנושי</t>
-  </si>
-  <si>
     <t>Warmth</t>
   </si>
   <si>
@@ -231,9 +220,6 @@
   </si>
   <si>
     <t>שימוש פנימי</t>
-  </si>
-  <si>
-    <t>רגישות למראה חיצוני</t>
   </si>
   <si>
     <t>appearance_sensitivity</t>
@@ -1230,15 +1216,6 @@
     <t>ימניות/שמאלניות</t>
   </si>
   <si>
-    <t>כמה שיותר צמחוני - דירוג גבוה יותר. טבעוני יהיה הגבוה ביותר</t>
-  </si>
-  <si>
-    <t>עד כמה המשתמש "ילד טוב" - נשמע לחוקים, לא מרדן, לא מעגל פינות וכו'.</t>
-  </si>
-  <si>
-    <t>מוסר עבודה גבוה</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">מסנן. רק למי שחולק אותה זהות. או מי שהגדיר "לא משנה" במגדר רצוי (אחרי וידוא עם המשתמש). </t>
     </r>
@@ -1516,16 +1493,6 @@
     <t>IQ</t>
   </si>
   <si>
-    <t>אנחנו רוצים להעריך פה בגדול עד כמה המשתמש אינטילגנטי. במובן הפשוט של המילה כמו שאתה מבין איך להעריך אינטלגנציה. לא אינטלגנציה רגשית, רק מחשבתית. תרגיש חופשי להבין את זה מהנוסח של המשתמש ומורכבות המחשבה שלו. שים לב - אין צורך להיות "פוליטיקלי קורקט" ולמצע את הציונים. תן ציון באמת כפי שנראה לך, גם אם הוא נמוך.    
-לגבי המשקל עבור המשתמש - אם אתה חושב שלמשתמש מאוד חשוב מישהו חכם - תן משקל גבוה, אחרת אין צורך להזין.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מידת אינטילגנציה רגשית. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">יציבות רגשית כללית. עד כמה המשתמש נוטה למצבי רוח קיצוניים, למצבי רוח שליליים, חרדה וכו'. </t>
-  </si>
-  <si>
     <t>מאפיינים שלא נכנסו בינתיים לMVP, להתעלם:</t>
   </si>
   <si>
@@ -1535,93 +1502,12 @@
     <t>FunImportance</t>
   </si>
   <si>
-    <t>האם מדובר בטיפוס המסיבתי? שיוצא למסיבות כל הזמן, עושה הרבה סטוצים, וייב בלייני מסיבתי</t>
-  </si>
-  <si>
-    <t>עד כמה הבנאדם פשוט אוהב לעשות כיף. זה לא חייב להיות סוג ספציפי של כיף, אבל נגיד - אוהב לבלות עם חברים, לצאת למסעדות, לטייל בחו"ל, לצאת לברים.. בכלל כמה חשוב לו לעשות כיף ולבלות, האם זה ממש ערך בשבילו לצאת וליהנות מהחיים? כמה שהוא יותר אוהב ומעריך כיף ובילויים נקבל פה ציון גבוה יותר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">עד כמה המשתמש קשור למשפחת המוצא שלו. שים לב - לא מדובר בעד כמה המשתמש רוצה משפחה וילדים משלו, אלא על כמה שהוא קשור למשפחת המוצא, להורים בעיקר, כמה שהמשפחה היא חלק חשוב ונוכח בחיים שלו. </t>
-  </si>
-  <si>
-    <t>עד כמה המשתמש "סחי"  . ככל שהוא יותר סחי נתן ציון גבוה יותר. שים לב - סחיות זה גם עד כמה המשתמש סוג של בסיסי - אוהב דברים של מיינסטרים מוגזם וכו'. אלא גם כמה הדעות שלו ותחומי העניין שלו הם ממוצעים ונורמטיבים, עד כמה הוא "עם העדר". עד כמה היית מגדיר אותו בינוני ורגיל בגדול.  חשוב שתבחין בין מיינסטרים ישראלי למיינסטרים כללי. למשל - לאהוב הארי פוטר זה דבר מאוד מיינסטרימי כביכול, זה ספר מאוד פופולרי אבל בתכל'ס זה בדרך כלל יותר של חנונים ופחות מיינסטרים בישראל. שים לב לזה.  ככל שהבנאדם סחי יותר - יקבל פה ציון גבוה יותר.</t>
-  </si>
-  <si>
-    <t>האם הבנאדם מופנם או מוחצן? ככל שהמוחצנות גבוהה - נתן ציון גבוה יותר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">רמת אנרגיה כללית. </t>
-  </si>
-  <si>
     <t xml:space="preserve">שטותניקיות בקטע goophi. שים לב - לא מדובר פה על קלילות ועל הומור סטנדרטיים אלא על אנשים עם נטיה לשטויות מהסוג המביך. למשל כאלה שעושים את ריקוד הרובוט. מן גופיות חנונית כזאת. זו הכוונה. </t>
   </si>
   <si>
-    <t xml:space="preserve">רמת דתיות. מי שדתי ברמה של שמירת שבת, כלומר ממש דתי בהגדרה יהיה בטווח ה90 עד 100. מעבר לזה יש לנו טווח בין חילוני גמור למסורתי קצת לדתי קצת וכו'. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הומור וקלילות.   הומור קצת קשה לנטר, אז תתייחס בעיקר לכמה חשוב למשתמש חוש הומור, בדרך כלל זה מעיד על החוש הומור שלו עצמו. או אם הוא מעיד באופן ישיר שהוא בעל חוש הומור. קלילות אפשר לנסות להעריך לפי איך שאתה מבין </t>
-  </si>
-  <si>
-    <t>מעורבות פוליטית. עד כמה זה חשוב למשתמש? עד כמה הוא מחזיק בדעות פוליטיות נוקשות וחי פוליטיקה?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מעורבות חברתית. עד כמה המשתמש הוא הטיפוס המעורב, כזה שהולך להפגנות, מתעסק בתיקון חברתי, מתנדב, עד כמה אכפת לו מנושאים חברתיים בוערים וכו'. </t>
-  </si>
-  <si>
-    <t>שמרנות/פרימיטיביות. אל תפחד להעריך פה. לא להיות פוליטיקלי קורקט. לנסות להבין כמה הבנאדם מחזיק בדעות שמרניות. ככל שיותר שמרן/פרימיטיבי - ציון גבוה יותר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מידת ילדותיות לעומת בגרות. ככל שיותר ילדותי - ציון גבוה יותר. </t>
-  </si>
-  <si>
-    <t>פתיחות לרעיונות וחוויות, לא במובן של פתיחות רגשית. במובן של פתיחות לחוויות חדשות, לרעיונות חדשים, צורות חיים שונות וכו'. ככל שהפתיחות גבוהה יותר - ציון גבוה יותר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אהבה לבעלי חיים. ככל שהמשתמש אוהב יותר בעלי חיים - יקבל ציון גבוה יותר. שים לב - לא סתם לנטר אם שמעת מילה על בעלי חיים, שים לב למה שהמשתמש באמת אומר.  למשל מישהו שמפחד מכלבים יכול לציין את זה ואז יקבל ציון נמוך. מישהו שאומר שיש לו כלב - יקבל ציון גבוה. </t>
-  </si>
-  <si>
-    <t>ציונות, אהבת המדינה. עד כמה ציונות זה ערך עבור המשתמש?</t>
-  </si>
-  <si>
-    <t>כמה שיותר ימני - דירוג גבוה יותר. אם המשתמש מעיד על עצמו שאין לו נטייה פוליטית חזקה אפשר פחות להתעכב על הסעיף הזה. אם הוא מאוד פוליטי - קריטי לדעת לאיזה צד.</t>
-  </si>
-  <si>
-    <t>היפסטריות. כלומר - סגנון אינדי, אולי התנשאות קלה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כמה המשתמש חי את התל אביביות שלו, או גם אם הוא לא תל אביבי - כמה הוא בסגנון התל אביבי של יציאות, בילויים. או לחילופין - כמה הוא פריפריאלי באופי. ככל שפחות פריפריאלי יקבל פה ציון גבוה יותר. </t>
-  </si>
-  <si>
-    <t>עד כמה המשתמש עממי. ככל שעממי יותר יקבל ציון גבוה יותר. זה יכול להתבטא במוזיקה ווייב מזרחי או בכל מה שאתה מבין כעממיות</t>
-  </si>
-  <si>
     <t>גיקיות</t>
   </si>
   <si>
-    <t>גיקיות. לאו דווקא חנון במובן של ילד טוב וחכם. אלא גיק - כלומר בקטע של מחשבים, פנטזיה וכל מה שקשור בגיקיות</t>
-  </si>
-  <si>
-    <t>סגנון היפי</t>
-  </si>
-  <si>
-    <t>סגנון רוסי. זה יכול להתבטא באנליטיות גבוהה, בחינוך נוקשה או כל מה שאתה מתאר כסובייטי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">רמת בוטות. אם אתה לא מזהה בוטות אצל המשתמש אחרי כל השאלות כנראה שאפשר להגיד במידה גבוהה שיש לו בוטות נמוכה. </t>
-  </si>
-  <si>
-    <t>זיהוי רעילות - אלימות, גזענות וכל מה שאתה מזהה כרעיל. חשוב לזהות רק את מי שבאמת רעיל. אם אחרי כל השאלות לא זיהית רעילות מיוחדת - זה אומר שהמשתמש כנראה לא רגיל.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">האם באמת מחפש שידוכים או שבא להטריל את המערכת. אם אתה רואה תשובות שנראות לך הזויות, סותרות, לא כנות או סתם לא לעניין. </t>
-  </si>
-  <si>
-    <t>האם סביר שהמשתמש הוא טרנס או א-מיני? האם העיד על עצמו שיש לו זהות מינית מיוחדת? אם לא קיבלת שום אינדיקציה כזאת מהמשתמש אחרי כל השאלות - כנראה שאין .</t>
-  </si>
-  <si>
-    <t>דברים שעלולים להוות דיל ברייקרס אצל הצד השני. האם זיהית אחד מהדברים הבאים: גר עם ההורים, גרוש פלוס ילדים, יש לו בעל חיים, שונא בעלי חיים. או כל דבר שאתה חושב שיכול להיות דיל ברייקר אצל משתמשים מסוימים. אם זיהית משהו כזה - פה לא ניתן ציון, אלא הערכה טקסטואלית.</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -1650,13 +1536,1677 @@
   </si>
   <si>
     <t>EQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רמת אנרגיה כללית. האם מדובר בבנאדם קופצני שצריך כל הזמן לעשות דברים, לדבר, לצאת וכו' או בבנאדם אם וייב יותר צ'יל ורגוע. ככל שרמת האנרגיה גבוהה יותר נתן ציון גבוה יותר. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רמת בוטות. אם אתה לא מזהה בוטות אצל המשתמש אחרי 10 שאלות כנראה שאפשר להגיד במידה גבוהה שיש לו בוטות נמוכה. </t>
+  </si>
+  <si>
+    <t>הערכת אינטליגנציה רגשית.
+מטרת התכונה:
+להעריך עד כמה המשתמש מבין רגשות של אחרים ומנהל אינטראקציות רגשיות בצורה בוגרת.
+אין להתייחס למודעות עצמית (נמדדת בנפרד).
+---
+איך להעריך:
+התבסס על:
+- הבנת רגשות של אחרים (אמפתיה)
+- תגובות רגשיות מותאמות (לא קיצוניות / לא אדישות)
+- יכולת להבין מצבים בין-אישיים
+- מורכבות רגשית (לא שחור/לבן)
+---
+הבחנה חשובה:
+נחמדות / חום / חברותיות ≠ אינטליגנציה רגשית
+---
+סקאלה:
+0–20:
+חוסר הבנה של רגשות אחרים, תגובות קיצוניות / לא מותאמות
+20–40:
+הבנה נמוכה, תגובות רגשיות שטחיות
+40–60:
+ממוצע — מבין מצבים בסיסיים
+60–75:
+טוב — אמפתיה ותגובות מותאמות
+75–90:
+גבוה — הבנה עמוקה של אנשים ומצבים רגשיים
+90–100:
+גבוה מאוד — הבנה מורכבת ועדינה של רגשות ודינמיקות
+---
+חוקים:
+- אל תבלבל בין נחמדות לאינטליגנציה רגשית
+- אם אין שיח רגשי → תן ציון עם confidence נמוך
+- אם יש הבנה רגשית מורכבת → תן ציון גבוה בהתאם
+- אם המשתמש מדבר על מערכות יחסים או קונפליקטים בצורה עמוקה → העלה את הציון</t>
+  </si>
+  <si>
+    <t>הערכת סחיות (מידת מיינסטרים וקונפורמיות).
+מטרת התכונה:
+להעריך עד כמה המשתמש נוטה למיינסטרים, לנורמות מקובלות ולגישה "רגילה" לחיים, לעומת ייחודיות, פתיחות וסטייה מהנורמה.
+---
+איך להעריך:
+התבסס על:
+- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
+- עד כמה הדעות שלו נפוצות ונורמטיביות
+- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
+- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)
+---
+הגדרה:
+סחיות = שילוב של מיינסטרים + קונפורמיות + גישה נורמטיבית לחיים
+---
+סקאלה:
+0–20:
+מאוד לא סחי — ייחודי, לא שגרתי, פתוח, לא הולך עם העדר
+20–40:
+די לא סחי — יש ייחודיות ופתיחות, לא מאוד נורמטיבי
+40–60:
+אמצע — שילוב בין מיינסטרים לייחודיות
+60–80:
+די סחי — נוטה למיינסטרים, גישה די נורמטיבית
+80–100:
+מאוד סחי — מיינסטרים מאוד, דעות שגרתיות, גישה קונבנציונלית לחיים
+---
+חוקים:
+- יש להעריך לפי הקשר תרבותי ישראלי
+- תחביבים בלבד לא מספיקים — חשוב גם גישה לחיים ודעות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך
+- אם המשתמש מציג חשיבה עצמאית או חריגה → הורד ציון
+- אם המשתמש מדגיש "נורמלי", "רגיל", "מסודר", "קלאסי" → העלה ציון
+- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון</t>
+  </si>
+  <si>
+    <t>הערכת יציבות רגשית.
+מטרת התכונה:
+להעריך עד כמה עולמו הרגשי של המשתמש יציב ומאוזן, לעומת נטייה למצבי רוח קיצוניים, רגשות שליליים חזקים, חרדה, דכדוך, דרמה רגשית או סערות נפשיות.
+התכונה הזו נועדה לשקף לא רק שליטה עצמית, אלא גם את רמת התנודתיות והעומס הרגשי הכללי של האדם.
+---
+איך להעריך:
+התבסס על:
+- נטייה למצבי רוח קיצוניים או משתנים
+- נטייה לרגשות שליליים חזקים (דכדוך, פסימיות, כובד, ייאוש)
+- נטייה לחרדה, לחץ, overthinking או חוסר שקט נפשי
+- דרמה רגשית / תגובתיות גבוהה
+- עד כמה העולם הרגשי מרגיש יציב וקל לעומת סוער וכבד
+---
+הבחנות חשובות:
+- רגישות ≠ חוסר יציבות  
+  אדם יכול להיות רגיש אך יציב.
+- עומק רגשי ≠ חוסר יציבות  
+  אדם עמוק רגשית לא בהכרח נוטה לדרמה, דיכאון או קיצוניות.
+- כאן חשוב במיוחד לזהות נטייה לקצוות רגשיים, כובד רגשי, חרדתיות, ודפוסים של דרמה או תנודתיות.
+---
+סקאלה:
+0–20:
+מאוד לא יציב — סערות רגשיות, דרמה גבוהה, תנודתיות חזקה, הרבה כובד או קיצוניות
+20–40:
+די לא יציב — נטייה בולטת למצבי רוח שליליים, חרדה, דרמה או תגובות לא מאוזנות
+40–60:
+בינוני — יש סימנים מסוימים לתנודתיות, שליליות או עומס רגשי, אבל לא בצורה קיצונית
+60–75:
+די יציב — רגשות יחסית מאוזנים, מעט דרמה, מעט תנודתיות
+75–90:
+יציב מאוד — רגוע, מאוזן, לא נוטה למצבי קיצון או כובד רגשי
+90–100:
+יציבות גבוהה מאוד — שלווה, עקביות רגשית, מעט מאוד חרדה / דרמה / שליליות
+---
+חוקים:
+- אם יש ביטויים של חרדה, דיכאון, כובד רגשי, דרמה או תנודתיות → הורד ציון
+- אם המשתמש מציג עולם רגשי רגוע, מאוזן וקל יחסית → העלה ציון
+- אם המשתמש מדבר על קונפליקטים, משברים או רגשות קשים — השתמש בזה כסיגנל מרכזי
+- אם אין מידע רגשי ברור → תן ציון עם confidence נמוך
+- אל תבלבל בין רגישות או עומק רגשי לבין חוסר יציבות</t>
+  </si>
+  <si>
+    <t>הערכת משפחתיות כלפי משפחת המוצא.
+מטרת התכונה:
+להעריך עד כמה משפחת המוצא של המשתמש (ובעיקר ההורים והמשפחה הקרובה) תופסת מקום מרכזי, נוכח ומשפיע בחייו.
+לא מדובר ברצון להקים משפחה וילדים משלו, אלא במידת הקרבה, המעורבות והמרכזיות של משפחת המוצא בחיים בפועל.
+---
+איך להעריך:
+התבסס על:
+- מידת הקרבה להורים ולמשפחה הקרובה
+- תדירות המפגשים / הקשר
+- עד כמה המשפחה נוכחת בשגרה
+- עד כמה המשפחה משפיעה על החלטות, סדרי עדיפויות ואורח חיים
+- עד כמה המשתמש רואה במשפחתיות חלק מרכזי מחייו, לעומת רצון בחיים נפרדים ועצמאיים יותר
+---
+הבחנות חשובות:
+- לא למדוד כאן רצון למשפחה וילדים בעתיד
+- לא למדוד כאן רק אהבה או כבוד למשפחה
+- מה שחשוב הוא עד כמה משפחת המוצא היא כוח נוכח, משמעותי ומשפיע בחיים
+---
+סקאלה:
+0–20:
+מעט משפחתי — קשר מועט / מרוחק, רצון ברור לחיים נפרדים מהמשפחה
+20–40:
+די לא משפחתי — המשפחה קיימת אך לא מאוד נוכחת או מרכזית
+40–60:
+בינוני — קשר טוב, אך המשפחה לא מאוד דומיננטית
+60–80:
+די משפחתי — קשר קרוב, המשפחה נוכחת ומשמעותית בחיים
+80–100:
+מאוד משפחתי — המשפחה מאוד מרכזית, הרבה קשר/מפגשים, השפעה ברורה על אורח החיים
+---
+חוקים:
+- אם המשתמש מתאר הרבה מפגשים משפחתיים, קשר הדוק או מעורבות גבוהה של המשפחה → העלה ציון
+- אם המשתמש מתאר צורך במרחק, עצמאות או תחושת כבדות סביב המשפחה → הורד ציון
+- אם יש רק אזכור כללי של "אני אוהב את המשפחה שלי" בלי מידע על נוכחות בפועל → תן ציון מתון עם confidence נמוך
+- יש להעריך לא רק רגש, אלא גם את המקום המעשי של המשפחה בחיי היומיום</t>
+  </si>
+  <si>
+    <t>הערכת נהנתנות (אהבה לבילויים וחוויות).
+מטרת התכונה:
+להעריך עד כמה המשתמש נהנה, מחפש ומעריך חוויות מהנות בחיים — כמו בילויים, מסעדות, טיולים, יציאות, וחוויות חדשות — ועד כמה זה חלק מרכזי מהערכים ואורח החיים שלו.
+---
+איך להעריך:
+התבסס על:
+- עד כמה חשוב לו "ליהנות מהחיים"
+- רצון לחוויות (טיולים, אוכל, בילויים, יציאות)
+- עד כמה הוא מחפש אקטיבית חוויות ולא רק זורם אם יש
+- עד כמה זה בא לידי ביטוי בפועל (ולא רק בדיבור)
+- תיאורים של אורח חיים עשיר בחוויות לעומת שגרה שקטה וביתית
+---
+הבחנות חשובות:
+- לא מדובר במסיבות דווקא — זה כולל כל סוג של בילוי וחוויה
+- לא למדוד כאן טיפוס מסיבתי
+- לא למדוד כאן מוחצנות — אדם יכול להיות מופנם ונהנתן
+- לא למדוד כאן רק אמירות כלליות — חשוב גם ביטוי בפועל
+---
+סקאלה:
+0–20:
+לא נהנתן — כמעט ולא מחפש בילויים או חוויות, נוטה לשגרה ביתית
+20–40:
+די לא נהנתן — מעט עניין בבילויים וחוויות
+40–60:
+בינוני — נהנה לפעמים, אבל זה לא מרכזי בחיים
+60–80:
+די נהנתן — אוהב חוויות ובילויים כחלק משמעותי מהחיים
+80–100:
+מאוד נהנתן — מחפש אקטיבית חוויות, בילויים והנאה, זה ערך מרכזי באורח החיים
+---
+חוקים:
+- אם המשתמש מדגיש רצון ליהנות, לבלות, לחוות → העלה ציון
+- אם המשתמש מתאר אורח חיים פעיל של בילויים, טיולים, אוכל וכו' → העלה ציון משמעותית
+- אם המשתמש מתאר אדישות או חוסר עניין בבילויים → הורד ציון
+- אם מדובר רק באמירה כללית ("אוהב ליהנות") בלי ביטוי בפועל → תן ציון בינוני עם confidence נמוך
+- אם המשתמש מחפש חוויות אקטיבית ולא רק זורם → העלה ציון</t>
+  </si>
+  <si>
+    <t>הערכת מופנמות / מוחצנות כסגנון ביטוי.
+מטרת התכונה:
+להעריך את סגנון הביטוי והנוכחות של המשתמש — עד כמה הוא אקספרסיבי, מוחצן ותופס מקום, לעומת שקט, רגוע ומופנם.
+ציון גבוה = סגנון מוחצן (אקספרסיבי)
+ציון נמוך = סגנון מופנם (שקט)
+---
+איך להעריך:
+התבסס על:
+- סגנון הדיבור (ישיר, פתוח, מרובה לעומת מדוד ושקט)
+- רמת האקספרסיביות (כמה מבטא את עצמו כלפי חוץ)
+- "ווליום" אנרגטי — מורגש, דומיננטי, יוזם לעומת שקט ונוכח בעדינות
+- עד כמה נראה שהוא תופס מקום חברתית לעומת משתלב ברקע
+- קצב ואופי הביטוי (מהיר/זורם/יוזם לעומת רגוע/מאופק)
+---
+הבחנות חשובות:
+- זה לא מודד צורך חברתי — אדם יכול להיות מופנם מאוד ועדיין מאוד אוהב אנשים  
+- זה לא מודד נהנתנות  
+- זה לא מודד טיפוס מסיבתי  
+- זה לא מודד אינטליגנציה חברתית  
+- מדובר בסגנון נוכחות וביטוי בלבד
+---
+סקאלה:
+0–20:
+מופנם מאוד — שקט, מאופק, לא תופס מקום, ביטוי מינימלי
+20–40:
+די מופנם — רגוע, פחות אקספרסיבי, נוכחות עדינה
+40–60:
+אמצע — שילוב בין שקט לאקספרסיביות
+60–80:
+די מוחצן — אקספרסיבי, נוכח, מבטא את עצמו בקלות
+80–100:
+מוחצן מאוד — בולט, דומיננטי, "מורגש", ווליום גבוה
+---
+חוקים:
+- אם המשתמש נשמע שקט, מאופק או מינימליסטי בביטוי → הורד ציון
+- אם המשתמש נשמע אקספרסיבי, פתוח, יוזם ודומיננטי → העלה ציון
+- לא להסיק מוחצנות רק מזה שהוא אוהב אנשים או בילויים
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת נטייה אנליטית.
+מטרת התכונה:
+להעריך עד כמה המשתמש נוטה לחשיבה אנליטית — כלומר פירוק, ניתוח והבנה לוגית של דברים — לעומת חשיבה אינטואיטיבית או זורמת.
+---
+איך להעריך:
+התבסס על:
+- האם המשתמש מפרק רעיונות ומסביר אותם
+- שימוש בהיגיון, מבנה או שלבים
+- נטייה לנתח מצבים ולא רק לתאר אותם
+- סגנון חשיבה מסודר לעומת אינטואיטיבי/זורם
+---
+הבחנות חשובות:
+- לא למדוד כאן אינטליגנציה כללית
+- אדם יכול להיות חכם אך לא אנליטי
+- אדם יכול להיות אנליטי בלי להיות עמוק רגשית
+---
+סקאלה:
+0–20:
+לא אנליטי — חשיבה אינטואיטיבית, זורמת, ללא ניתוח
+20–40:
+מעט אנליטי — יש מעט מבנה אך בעיקר אינטואיציה
+40–60:
+בינוני — שילוב בין ניתוח לאינטואיציה
+60–80:
+די אנליטי — נוטה לפרק, להסביר ולחשוב בצורה לוגית
+80–100:
+מאוד אנליטי — מפרק, מנתח, חושב בצורה מבנית ועקבית
+---
+חוקים:
+- אם המשתמש מסביר דברים בשלבים או מפרק רעיונות → העלה ציון
+- אם החשיבה בעיקר אינטואיטיבית/תחושתית → הורד ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>אינטלקטואליות</t>
+  </si>
+  <si>
+    <t>הערכת אינטלקטואליות.
+מטרת התכונה:
+להעריך עד כמה המשתמש נוטה לשיח רעיוני, עומק מחשבתי והתעניינות בנושאים מופשטים, לעומת שיח פרקטי, יומיומי ופשוט.
+---
+איך להעריך:
+התבסס על:
+- רמת העומק של השיח
+- עיסוק ברעיונות, תפיסות או ניתוחים
+- סגנון ביטוי (עשיר, מורכב, מופשט לעומת פשוט וישיר)
+- נטייה לשיח פילוסופי, פסיכולוגי או רעיוני
+- שימוש בהבחנות, הסברים ורמות חשיבה שונות
+---
+הבחנות חשובות:
+- לא למדוד כאן אינטליגנציה בלבד  
+  אדם יכול להיות חכם אך לא אינטלקטואלי  
+- לא למדוד כאן רק אנליטיות  
+  אנליטיות = פירוק  
+  אינטלקטואליות = עומק ושיח רעיוני  
+- לא למדוד רק ניסוח טכני (עברית יפה)  
+  אלא עומק וסוג החשיבה
+---
+סקאלה:
+0–20:
+לא אינטלקטואלי — שיח פשוט, פרקטי, ללא עומק רעיוני
+20–40:
+מעט אינטלקטואלי — יש מעט עומק, אבל לרוב שיח יומיומי
+40–60:
+בינוני — שילוב בין שיח פרקטי לרעיוני
+60–80:
+די אינטלקטואלי — עיסוק ברעיונות, עומק ושיח מורכב
+80–100:
+מאוד אינטלקטואלי — עומק גבוה, שיח מופשט, הבחנות מורכבות
+---
+חוקים:
+- אם השיח כולל רעיונות, הבחנות ועומק → העלה ציון
+- אם השיח פרקטי בלבד → הורד ציון
+- אם יש ניסוח יפה אבל ללא עומק → לא לתת ציון גבוה
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת רצינות לגבי החיים.
+מטרת התכונה:
+להעריך עד כמה המשתמש ניגש לחיים בצורה אחראית, ממוקדת ומחויבת — עם שאיפות, מסגרת ועשייה — לעומת גישה קלילה, זורמת ופחות מחויבת.
+לא מדובר ברצינות בזוגיות, אלא בגישה כללית לחיים.
+---
+איך להעריך:
+התבסס על:
+- רמת האחריות והמחויבות (עבודה, סדר, התנהלות)
+- קיומן של מטרות או שאיפות ברורות
+- עד כמה המשתמש שם דגש על "לעשות מה שצריך"
+- התייחסות לחיים כמשהו שצריך לנהל ולהתקדם בו
+- לעומת גישה זורמת, קלילה, פחות מתוכננת או פחות מחויבת
+---
+הבחנות חשובות:
+- לא מדובר בכובד או חוסר הומור  
+- אדם יכול להיות קליל ונעים ועדיין מאוד רציני לגבי החיים  
+- לא למדוד כאן אינטליגנציה או עומק  
+- לא למדוד נהנתנות  
+---
+סקאלה:
+0–20:
+לא רציני — גישה מאוד זורמת, ללא מסגרת, מעט אחריות או שאיפות
+20–40:
+די לא רציני — פחות ממוקד, פחות מחויב, גישה קלילה לחיים
+40–60:
+בינוני — שילוב בין קלילות לאחריות
+60–80:
+די רציני — אחראי, עם כיוון ושאיפות, מתנהל בצורה מסודרת
+80–100:
+מאוד רציני — מחויב מאוד, ממוקד, עם מטרות ברורות ודגש חזק על עשייה והתקדמות
+---
+חוקים:
+- אם המשתמש מדבר על מטרות, קריירה, התקדמות או אחריות → העלה ציון
+- אם המשתמש מתאר גישה זורמת מאוד או חוסר כיוון → הורד ציון
+- אם יש גם קלילות וגם אחריות → שמור על ציון בינוני-גבוה בהתאם לאיזון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת רמת דתיות.
+מטרת התכונה:
+להעריך עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
+---
+איך להעריך:
+התבסס על:
+- שמירת שבת (סיגנל חזק מאוד)
+- שמירת כשרות / מנהגים דתיים
+- אמונה והזדהות כדתית / חילונית / מסורתית
+- עד כמה הדת משפיעה על אורח החיים בפועל
+- תיאורים של אורח חיים דתי לעומת חילוני
+---
+הבחנות חשובות:
+- שמירת שבת היא אינדיקציה מרכזית לדתיות גבוהה
+- לא להסתמך רק על הגדרה מילולית ("אני מסורתי") אלא גם על אורח החיים בפועל
+- יש להעריך את הרצף בין חילוני, מסורתי ודתי
+---
+סקאלה:
+0–20:
+חילוני לגמרי — אין כמעט קשר לדת או למסורת
+20–40:
+חילוני עם נגיעה מסורתית קלה
+40–60:
+מסורתי — יש חיבור מסוים למסורת, אך לא מחויבות מלאה
+60–80:
+מסורתי-דתי — חלק מהפרקטיקות הדתיות כן מתקיימות
+80–90:
+דתי — אורח חיים דתי ברור
+90–100:
+דתי מאוד — שמירת שבת, אורח חיים דתי מלא
+---
+חוקים:
+- אם יש שמירת שבת → הציון צריך להיות גבוה (90+)
+- אם המשתמש מתאר אורח חיים חילוני → הציון צריך להיות נמוך
+- אם יש סתירה בין הגדרה להתנהגות → לתת עדיפות להתנהגות בפועל
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת חשיבות והזדהות עם הומור.
+מטרת התכונה:
+להעריך עד כמה הומור הוא חלק מהזהות של המשתמש ועד כמה הוא חשוב לו — הן אצל עצמו והן אצל בן/בת זוג.
+לא מדובר בניסיון למדוד עד כמה המשתמש באמת מצחיק, אלא עד כמה הומור הוא ערך או מאפיין מרכזי עבורו.
+---
+איך להעריך:
+התבסס על:
+- אמירות ישירות ("יש לי חוש הומור", "אני מאוד ציני", "חשוב לי הומור")
+- הדגשה של הומור כמרכיב חשוב בזוגיות
+- אזכורים חוזרים של הומור או קלילות
+- סגנון ביטוי שמעיד על קלילות או משחקיות (כאשר ברור)
+---
+הבחנות חשובות:
+- לא לנסות להעריך בפועל עד כמה המשתמש מצחיק  
+- להתבסס בעיקר על הצהרות, ערכים ודגש שהמשתמש נותן להומור  
+- "קלילות" נמדדת בתכונות אחרות — כאן הפוקוס הוא על הומור
+---
+סקאלה:
+0–20:
+אין התייחסות להומור, לא נראה חשוב
+20–40:
+מעט חשיבות להומור
+40–60:
+בינוני — הומור קיים אך לא מרכזי
+60–80:
+די חשוב — הומור הוא חלק משמעותי
+80–100:
+מאוד חשוב — הומור הוא ערך מרכזי וזהותי
+---
+חוקים:
+- אם המשתמש מצהיר שחוש הומור חשוב לו → העלה ציון
+- אם המשתמש מציג את עצמו כאדם עם חוש הומור → העלה ציון
+- אם הומור מוזכר כמה פעמים או בהדגשה → העלה ציון משמעותית
+- אם אין אזכור כלל → שמור על ציון נמוך עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת מעורבות פוליטית.
+מטרת התכונה:
+להעריך עד כמה פוליטיקה מהווה חלק מרכזי ומשמעותי בחיי המשתמש — ברמת העניין, המעורבות והחשיבות שהוא נותן לנושא.
+---
+איך להעריך:
+התבסס על:
+- עד כמה המשתמש מתעניין או עוסק בפוליטיקה
+- עד כמה פוליטיקה היא חלק מהשיח שלו
+- עד כמה זה חשוב לו או מגדיר אותו
+- עד כמה הוא מבטא דעות פוליטיות באופן ברור
+- עד כמה הנושא תופס מקום בחיים ובזהות שלו
+---
+הבחנות חשובות:
+- לא למדוד כאן שמאל/ימין או עמדות ספציפיות
+- ניתן לקחת בחשבון גם נוקשות או עוצמת הדעות, אך רק כחלק מהמעורבות הכוללת
+- אדם יכול להחזיק בדעות אך לא להיות מעורב — וזה צריך לקבל ציון נמוך יותר
+---
+סקאלה:
+0–20:
+לא מעורב — כמעט ואין עניין בפוליטיקה
+20–40:
+מעורבות נמוכה — מעט עניין, לא מרכזי
+40–60:
+בינוני — יש עניין, אך לא דומיננטי
+60–80:
+מעורב — פוליטיקה היא חלק משמעותי מהשיח והעניין
+80–100:
+מעורב מאוד — פוליטיקה היא חלק מרכזי בזהות ובחיים
+---
+חוקים:
+- אם המשתמש מדגיש חוסר עניין בפוליטיקה → הורד ציון
+- אם המשתמש מדבר על פוליטיקה כחלק מרכזי מהחיים → העלה ציון
+- אם יש דעות חזקות אך מעט עיסוק בפועל → תן ציון בינוני
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת מעורבות חברתית (אקטיביזם).
+מטרת התכונה:
+להעריך עד כמה המשתמש מעורב, אקטיבי ופועל בנושאים חברתיים — כמו התנדבות, פעילות חברתית, מחאה או עיסוק בתיקון חברתי — ועד כמה זה חלק מהזהות וסגנון החיים שלו.
+---
+איך להעריך:
+התבסס על:
+- מעורבות בפעילות חברתית (התנדבות, ארגונים, יוזמות)
+- השתתפות במחאות, הפגנות או עשייה ציבורית
+- עיסוק פעיל בנושאים חברתיים (לא רק דעה)
+- עד כמה זה חלק מהזהות והחיים
+- עד כמה אכפת לו מנושאים חברתיים באופן שמוביל לפעולה
+---
+הבחנות חשובות:
+- לא מדובר רק בדעות פוליטיות
+- אדם יכול להיות פוליטי אך לא מעורב חברתית
+- התכונה מודדת עשייה ומעורבות בפועל, לא רק עניין או דעה
+- אכפתיות ללא פעולה → ציון בינוני בלבד
+---
+סקאלה:
+0–20:
+לא מעורב — אין עניין או עשייה חברתית
+20–40:
+מעורבות נמוכה — אכפתיות כללית אך ללא עשייה
+40–60:
+בינוני — עניין מסוים ולעיתים מעורבות
+60–80:
+מעורב — משתתף או פועל באופן די קבוע
+80–100:
+מאוד מעורב — אקטיביזם ברור, עשייה חברתית כחלק מהזהות והחיים
+---
+חוקים:
+- אם המשתמש מתאר עשייה בפועל (התנדבות, הפגנות וכו') → העלה ציון משמעותית
+- אם יש רק עניין או דעה ללא פעולה → תן ציון בינוני
+- אם המשתמש מדגיש אדישות לנושאים חברתיים → הורד ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת מודעות עצמית.
+מטרת התכונה:
+להעריך עד כמה המשתמש מבין את עצמו — רגשות, דפוסים, חוזקות וחולשות — ויכול לדבר עליהם בצורה מודעת.
+---
+איך להעריך:
+התבסס על:
+- יכולת לתאר את עצמו באופן מדויק
+- מודעות לדפוסים, חוזקות או חולשות
+- רפלקציה על חוויות או התנהגות
+---
+הבחנות חשובות:
+- לא למדוד כאן אינטליגנציה או ניסוח טוב
+- ניסוח יפה ≠ מודעות עצמית
+- ניתוח כללי ≠ הבנה של עצמי
+---
+חוקים:
+- אם אין רפלקציה אישית ברורה → לא לתת ציון גבוה
+- אם יש תיאור עצמי עמוק או מודע → העלה ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת גישה חיובית (אופטימיות).
+מטרת התכונה:
+להעריך עד כמה המשתמש נוטה לגישה חיובית, אופטימית וקלילה לחיים, לעומת גישה שלילית, ביקורתית או פסימית.
+---
+איך להעריך:
+התבסס על:
+- סגנון כללי של התבטאות (חיובי לעומת שלילי)
+- נטייה לראות את הטוב או להתמקד בקושי
+- גישה למצבים (אופטימית לעומת פסימית)
+- טון רגשי כללי — קליל/חיובי לעומת כבד/ביקורתי
+---
+הבחנות חשובות:
+- לא מדובר ביציבות רגשית  
+  אדם יכול להיות יציב אך שלילי  
+- לא מדובר בעומק או אינטליגנציה  
+- לא מדובר בקלילות בלבד  
+---
+סקאלה:
+0–20:
+גישה שלילית — פסימיות, ביקורתיות, כובד
+20–40:
+די שלילי — נטייה לראות בעיות וקושי
+40–60:
+בינוני — שילוב בין חיובי לשלילי
+60–80:
+די חיובי — גישה נעימה ואופטימית
+80–100:
+מאוד חיובי — אופטימי, קליל, רואה טוב
+---
+חוקים:
+- אם המשתמש מתבטא בצורה חיובית, אופטימית או קלילה → העלה ציון
+- אם המשתמש מדגיש קושי, שליליות או ביקורת → הורד ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת לבביות וחום אנושי.
+מטרת התכונה:
+להעריך עד כמה המשתמש חם, נעים, מפרגן ומקרין יחס חיובי ואוהב כלפי אחרים.
+---
+איך להעריך:
+התבסס על:
+- סגנון התקשורת (חם, נעים, מפרגן לעומת קר או ענייני)
+- שימוש במחמאות או שפה חיובית כלפי אחרים
+- תחושת קרבה, רכות או פתיחות בין-אישית
+- עד כמה המשתמש משדר "לב טוב" ויחס אוהב
+---
+הבחנות חשובות:
+- לא מדובר בכמות אינטראקציות (זה חברתיות)
+- לא מדובר באופטימיות כללית (זה גישה חיובית)
+- לא מדובר באינטליגנציה רגשית
+- אדם יכול להיות מופנם ועדיין מאוד לבבי
+- אדם יכול להיות מוחצן אך לא לבבי
+---
+סקאלה:
+0–20:
+קר מאוד — מרוחק, ענייני, ללא חום
+20–40:
+די קר — מעט חום, תקשורת יותר טכנית
+40–60:
+בינוני — תקשורת נעימה אך לא מאוד חמה
+60–80:
+די לבבי — חם, נעים, מפרגן
+80–100:
+מאוד לבבי — חם מאוד, מלא אהבה, מחמאות ואנרגיה חיובית כלפי אחרים
+---
+חוקים:
+- אם המשתמש מבטא חום, פרגון או רכות → העלה ציון
+- אם התקשורת קרה, עניינית או מרוחקת → הורד ציון
+- לא להסיק לבביות רק מזה שהמשתמש חברותי
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת פתיחות (Openness).
+מטרת התכונה:
+להעריך עד כמה המשתמש פתוח לרעיונות, חוויות וסגנונות חיים שונים — ועד כמה הוא נמשך אקטיבית להתנסות ולחוות דברים חדשים, גם אם הם מחוץ לאזור הנוחות.
+לא מדובר בפתיחות רגשית.
+---
+איך להעריך:
+התבסס על:
+- סקרנות ורצון לנסות דברים חדשים
+- פתיחות לרעיונות, תפיסות וסגנונות חיים שונים
+- נכונות לצאת מאזור הנוחות
+- משיכה לחוויות חדשות או לא שגרתיות
+- עד כמה חוויות והתנסות הן ערך שמניע את המשתמש
+- willingness להיכנס למצבים לא מוכרים או לא שגרתיים מתוך רצון לחוות
+---
+הבחנות חשובות:
+- לא מדובר באינטלקטואליות (עומק שיח)
+- לא מדובר בסחיות (נורמטיביות)
+- אדם יכול להיות לא סחי אך לא פתוח
+- אדם יכול להיות פתוח גם אם הוא לא אינטלקטואלי
+- חשוב למדוד גם פתיחות מחשבתית וגם פתיחות חווייתית בפועל
+---
+סקאלה:
+0–20:
+סגור מאוד — נצמד למוכר, נמנע משינוי או חוויות חדשות
+20–40:
+די סגור — מעט פתיחות, מעדיף אזור נוחות
+40–60:
+בינוני — פתוח חלקית, אך עם גבולות ברורים
+60–80:
+די פתוח — סקרן, פתוח להתנסות ולרעיונות חדשים
+80–100:
+מאוד פתוח — מחפש חוויות, פתוח מאוד לשונות, מוכן לצאת מאזור נוחות ולהתנסות בדברים חדשים
+---
+חוקים:
+- אם המשתמש מבטא רצון לחוות, להתנסות או לחפש חוויות → העלה ציון
+- אם המשתמש מוכן להיכנס למצבים לא שגרתיים מתוך סקרנות או רצון לחוות → העלה ציון משמעותית
+- אם המשתמש מבטא קבלה או סקרנות כלפי סגנונות חיים שונים → העלה ציון
+- אם המשתמש מבטא הסתייגות משונות או היצמדות למה שמוכר → הורד ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת וייב ילדותי לעומת בוגר.
+מטרת התכונה:
+להעריך את הסגנון והוייב הכללי של המשתמש — עד כמה הוא נוטה לוייב ילדותי (playful, חמוד, נאיבי בסגנון) לעומת וייב בוגר יותר.
+ציון גבוה = יותר וייב ילדותי  
+ציון נמוך = יותר וייב בוגר
+---
+איך להעריך:
+התבסס על:
+- טון וסגנון הביטוי
+- סוג ההומור או הווייב הכללי
+- תחומי עניין או טעמים בעלי אופי ילדותי לעומת בוגר
+- תחושת "חמידות", נאיביות או playful באנרגיה הכללית
+- לעומת תחושת סגנון בוגר ומבוסס יותר
+---
+הבחנות חשובות:
+- לא מדובר באחריות או בגרות תפקודית  
+- אדם יכול להיות מאוד אחראי וחכם אך עם וייב ילדותי  
+- לא מדובר באינטליגנציה או עומק  
+- לא מדובר ברצינות לחיים  
+- מדובר בסגנון, טעם ותחושה כללית בלבד
+---
+סקאלה:
+0–20:
+וייב בוגר מאוד — סגנון בוגר, טעם ותחושה מבוססים
+20–40:
+די בוגר — מעט אלמנטים ילדותיים
+40–60:
+בינוני — שילוב בין ילדותי לבוגר
+60–80:
+די ילדותי — וייב playful, חמוד או נאיבי
+80–100:
+מאוד ילדותי — סגנון ילדי ברור, playful מאוד
+---
+חוקים:
+- אם יש תחושה כללית של playful, חמידות או אלמנטים ילדותיים → העלה ציון
+- אם הסגנון מרגיש בוגר, מאופק או "grown-up" → הורד ציון
+- לא להסיק ילדותיות מהומור בלבד
+- לא להסיק ילדותיות מחוסר אחריות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת שמרנות ערכית-חברתית.
+מטרת התכונה:
+להעריך עד כמה המשתמש מחזיק בגישה שמרנית לעומת ליברלית/פתוחה בנושאים של זוגיות, מגדר ונורמות חברתיות.
+ציון גבוה = שמרני  
+ציון נמוך = ליברלי / מתירני
+---
+איך להעריך:
+התבסס על:
+- תפיסות לגבי תפקידי מגדר (מסורתיים לעומת שוויוניים)
+- גישה לזוגיות ומערכות יחסים
+- פתיחות או התנגדות לנורמות לא שגרתיות
+- עמדות לגבי חופש אישי מול מסגרת מסורתית
+- שיפוטיות מול קבלה של אורח חיים שונה
+---
+הבחנות חשובות:
+- לא מדובר בפוליטיקה (שמאל/ימין)
+- לא מדובר בדתיות (זו תכונה נפרדת)
+- יש להתמקד בגישה הערכית והחברתית בפועל
+- ניתן להסיק גם באופן עקיף — אך לשקף זאת ב-confidence
+---
+סקאלה:
+0–20:
+ליברלי מאוד — פתוח מאוד, שוויוני, מקבל מגוון רחב של סגנונות חיים
+20–40:
+די ליברלי — פתוח יחסית, מעט גבולות
+40–60:
+בינוני — שילוב בין גישות
+60–80:
+די שמרני — מחזיק בגישות מסורתיות יותר
+80–100:
+מאוד שמרני — תפיסות מסורתיות ברורות, פחות פתוח לשונות
+---
+חוקים:
+- אם יש אמירות ברורות על תפקידי מגדר, גבולות או נורמות → העלה ציון בהתאם
+- אם יש ביטוי לפתיחות, שוויון או קבלה → הורד ציון
+- אם יש שיפוטיות כלפי סגנונות חיים שונים → העלה ציון
+- אם אין מספיק מידע → תן ציון עם confidence נמוך
+- אין למצע ציונים ללא סיבה — אך גם אין לנחש ללא בסיס</t>
+  </si>
+  <si>
+    <t>הערכת ציונות ואהבת המדינה.
+מטרת התכונה:
+להעריך עד כמה המשתמש מחובר רגשית וערכית למדינה — כולל תחושת שייכות, אהבת הארץ והזדהות עם רעיון הציונות.
+---
+איך להעריך:
+התבסס על:
+- אמירות על אהבת הארץ או המדינה
+- הזדהות כציוני
+- תחושת שייכות, גאווה או משמעות הקשורה למדינה
+- התייחסות ערכית לחיים בארץ
+---
+הבחנות חשובות:
+- לא מדובר בפוליטיקה או עמדות ספציפיות
+- יש להבחין בין אזכור כללי לבין ערך משמעותי
+- ניתן לזהות גם אדישות או ריחוק רגשי
+---
+סקאלה:
+0–20:
+אין חיבור — אדישות או ניתוק מהמדינה
+20–40:
+חיבור נמוך — מעט שייכות, לא ערך מרכזי
+40–60:
+בינוני — חיבור מסוים אך לא משמעותי
+60–80:
+די מחובר — אהבה והזדהות עם המדינה
+80–100:
+מאוד מחובר — ציונות ואהבת הארץ כערך מרכזי
+---
+חוקים:
+- אם המשתמש מדגיש שהמדינה/ציונות חשובים לו → העלה ציון
+- אם יש ביטויי אהבה, שייכות או גאווה → העלה ציון
+- אם המשתמש מתאר את הקשר למדינה כחלק מהזהות שלו → העלה ציון משמעותית
+- אם המשתמש מבטא ריחוק, אדישות או ביקורת עמוקה → הורד ציון
+- לא להסיק מהזכרת ישראל בלבד
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת צמחונות / טבעונות.
+מטרת התכונה:
+להעריך את הרגלי התזונה של המשתמש ביחס לצריכת בעלי חיים — החל מאכילת בשר רגילה ועד צמחונות או טבעונות.
+ציון גבוה = יותר צמחוני/טבעוני  
+ציון נמוך = אוכל בשר באופן רגיל
+---
+איך להעריך:
+התבסס על:
+- הצהרה מפורשת (צמחוני / טבעוני)
+- תיאור הרגלי אכילה בפועל
+- הימנעות ממוצרים מן החי
+---
+הבחנות חשובות:
+- יש להסתמך על מידע מפורש בלבד
+- לא להסיק מתכונות אחרות או ערכים כלליים
+- העדפה בלבד (למשל "אוהב אוכל צמחוני") ≠ צמחונות
+---
+סקאלה:
+0–20:
+אוכל בשר באופן רגיל
+20–40:
+מעט הפחתה בצריכת בשר
+40–60:
+נוטה לצמחונות אך לא עקבי
+60–80:
+צמחוני
+80–100:
+טבעוני
+---
+חוקים:
+- אם המשתמש מציין שהוא צמחוני → ציון גבוה (60–80)
+- אם המשתמש מציין שהוא טבעוני → ציון גבוה מאוד (80–100)
+- אם אין הצהרה ברורה → לא להסיק או לתת ציון עם confidence נמוך מאוד
+- לא להסיק מתזונה בריאה או ערכים בלבד</t>
+  </si>
+  <si>
+    <t>הערכת מוסר עבודה.
+מטרת התכונה:
+להעריך עד כמה המשתמש רציני, מחויב ומשקיע בעבודה או בעשייה שלו — ועד כמה יש לו גישה של התמדה, אחריות ורצון לעשות דברים כמו שצריך.
+---
+איך להעריך:
+התבסס על:
+- יחס לעבודה, קריירה או עשייה
+- מידת האחריות והמחויבות
+- השקעה, התמדה וחריצות
+- שאיפה לעשות דברים היטב ולא רק "לסמן וי"
+- גישה של משמעת עצמית והתמדה לאורך זמן
+---
+הבחנות חשובות:
+- לא מדובר רק בשאפתנות  
+  אדם יכול להיות שאפתן אך עם מוסר עבודה נמוך  
+- לא מדובר רק ברצינות כללית לחיים  
+  כאן הפוקוס הוא על עבודה, עשייה והתמדה בפועל  
+- לא מדובר בהצלחה חיצונית או סטטוס  
+  אלא באופן שבו האדם ניגש לעבודה ומחזיק מחויבות
+---
+סקאלה:
+0–20:
+מוסר עבודה נמוך מאוד — חוסר התמדה, חוסר מחויבות, גישה רופפת
+20–40:
+די נמוך — מעט אחריות או השקעה, נוטה לזרום
+40–60:
+בינוני — מתפקד ועושה מה שצריך, אך לא מאוד משקיע
+60–80:
+די גבוה — אחראי, מתמיד, משקיע בעבודה ובעשייה
+80–100:
+גבוה מאוד — חרוץ, מחויב מאוד, משקיע ודורש מעצמו
+---
+חוקים:
+- אם המשתמש מדבר על התמדה, השקעה, מחויבות או משמעת עצמית → העלה ציון
+- אם המשתמש מתאר את עצמו כעצלן, לא עקבי או חסר משמעת → הורד ציון
+- אם יש שאיפות אבל מעט עדות לעשייה בפועל → אל תיתן ציון גבוה מדי
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת נטייה לציות למסגרות (״ילד טוב״).
+מטרת התכונה:
+להעריך עד כמה המשתמש נוטה לפעול לפי חוקים, מסגרות ונורמות — לעומת גישה גמישה יותר, שבה חוקים הם בגדר המלצה וניתן לעגל פינות.
+ציון גבוה = יותר "ילד טוב" (ציות גבוה)  
+ציון נמוך = יותר גמיש/מרדן
+---
+איך להעריך:
+התבסס על:
+- יחס לחוקים ולמסגרות
+- נטייה "לעשות את הדבר הנכון"
+- כבוד לסמכות או כללים
+- לעומת נוחות לעגל פינות או לחרוג מהכללים
+- גישה של ציות לעומת גישה חופשית/מרדנית
+---
+הבחנות חשובות:
+- לא מדובר במוסר או טוב/רע
+- לא מדובר בפשע או עבירות חמורות
+- אדם יכול להיות חכם, מוסרי ואחראי אך לא "ילד טוב"
+- מדובר בסגנון התנהלות מול חוקים ומסגרות
+---
+סקאלה:
+0–20:
+מאוד לא "ילד טוב" — גישה חופשית, נוטה לעגל פינות, לא מחויב לכללים
+20–40:
+די גמיש — חוקים נתפסים כהמלצה
+40–60:
+בינוני — שילוב בין ציות לגמישות
+60–80:
+די "ילד טוב" — נוטה לפעול לפי הכללים
+80–100:
+מאוד "ילד טוב" — מציית, הולך לפי חוקים ומסגרות
+---
+חוקים:
+- אם המשתמש מדגיש חשיבות של כללים, סדר או "לעשות נכון" → העלה ציון
+- אם המשתמש מבטא גישה של גמישות, עקיפת חוקים או "לזרום" עם הכללים → הורד ציון
+- לא להסיק ממוסר או אינטליגנציה
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת רגישות למראה חיצוני.
+מטרת התכונה:
+להעריך עד כמה המראה החיצוני של בן/בת זוג הוא גורם חשוב ומשמעותי עבור המשתמש.
+---
+איך להעריך:
+התבסס על:
+- עד כמה המשתמש מדבר על מראה חיצוני
+- קיומן של דרישות או העדפות ברורות
+- נוקשות או גמישות לגבי מראה
+- האם מראה מוצג כדיל ברייקר או כגורם מרכזי
+- חזרתיות — האם הנושא עולה כמה פעמים
+---
+הבחנות חשובות:
+- לא למדוד מה הטעם (למשל גובה/שיער), אלא כמה זה חשוב
+- אזכור בודד של מראה ≠ רגישות גבוהה
+- יש להבחין בין העדפה ("נחמד אם") לבין דרישה ("חייב/ת")
+- יש להתחשב בטון — נוקשות מול גמישות
+---
+סקאלה:
+0–20:
+לא חשוב — כמעט ואין חשיבות למראה
+20–40:
+חשיבות נמוכה — העדפות קלות בלבד
+40–60:
+בינוני — יש חשיבות, אך לא מרכזית
+60–80:
+די חשוב — מראה הוא גורם משמעותי
+80–100:
+חשוב מאוד — דרישות ברורות, דיל ברייקרים, נוקשות גבוהה
+---
+חוקים:
+- אם המשתמש נותן דרישות חד משמעיות או דיל ברייקרים → העלה ציון משמעותית
+- אם המשתמש חוזר על הנושא או מדגיש אותו → העלה ציון
+- אם יש רק העדפות כלליות → שמור על ציון בינוני
+- אם אין אזכור → תן ציון נמוך עם confidence נמוך
+- לא להסיק מציון גבוה על סמך אזכור אחד בלבד
+---
+חיזוק:
+אם המשתמש מבטא דרישות ברורות או נוקשות לגבי מראה → שקול גם להעלות weight_for_match</t>
+  </si>
+  <si>
+    <t>הערכת היפסטריות (סגנון אינדי/אלטרנטיבי).
+מטרת התכונה:
+להעריך עד כמה המשתמש משדר סגנון וטעם תרבותי אלטרנטיבי, אינדי או "היפסטרי" — כלומר העדפה לדברים לא מיינסטרימיים, נישתיים או ייחודיים.
+---
+איך להעריך:
+התבסס על:
+- טעם תרבותי (מוזיקה, קולנוע, בילויים) לא מיינסטרימי
+- העדפה לדברים נישתיים או פחות פופולריים
+- סגנון אישי שמדגיש ייחודיות או אלטרנטיביות
+- וייב של "אני לא כמו כולם"
+- לעיתים גם נימה של מודעות לסטייל או ייחודיות
+---
+הבחנות חשובות:
+- לא מדובר רק ב"לא סחי" — אך לעיתים יש חפיפה
+- לא מדובר באינטלקטואליות — אך לעיתים יכולה להיות קורלציה
+- אדם יכול להיות לא מיינסטרים אך לא היפסטר
+- מדובר בסגנון תרבותי ואסתטי ספציפי
+---
+סקאלה:
+0–20:
+לא היפסטרי — טעם מיינסטרימי לחלוטין
+20–40:
+מעט אלטרנטיבי — נגיעות קלות של אינדי
+40–60:
+בינוני — שילוב בין מיינסטרים לאלטרנטיבי
+60–80:
+די היפסטרי — טעם וסגנון נישתי וברור
+80–100:
+מאוד היפסטרי — וייב אינדי מובהק, טעם ייחודי ולא מיינסטרימי
+---
+חוקים:
+- אם המשתמש מדגיש טעם ייחודי או לא מיינסטרימי → העלה ציון
+- אם יש וייב ברור של אינדי/אלטרנטיבי → העלה ציון
+- ניתן להשתמש בקורלציות מתכונות אחרות (כמו לא סחי או אינטלקטואליות) כסיגנל חלש בלבד כאשר אין מידע ישיר
+- אין להסיק היפסטריות מתכונה אחת בלבד
+- יש להעדיף סיגנלים ישירים של סגנון וטעם על פני הסקות עקיפות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך
+---
+חיזוק:
+יש להעריך את הסגנון הכללי והוייב של המשתמש, ולא להסתמך על פריט או תחביב בודד</t>
+  </si>
+  <si>
+    <t>הערכת וייב תל אביבי.
+מטרת התכונה:
+להעריך עד כמה המשתמש מתחבר לסגנון החיים, התרבות והוייב המזוהים עם תל אביב — או לחלופין עד כמה הוא מרגיש מנותק או אפילו אנטגוניסטי אליו.
+---
+איך להעריך:
+התבסס על:
+- יחס ישיר לתל אביב (אהבה / חיבור / הסתייגות)
+- הזדהות עם סגנון החיים המזוהה עם תל אביב
+- העדפה או דחייה של בילויים, סגנון חברתי ותרבות המזוהים עם העיר
+- תחושת "זה אני" לעומת "זה לא מדבר אליי בכלל"
+---
+הבחנות חשובות:
+- לא מדובר בכמה המשתמש עירוני או יוצא לבלות
+- אדם יכול להיות מאוד עירוני אך לא להתחבר לוייב התל אביבי
+- אדם יכול לא לגור בתל אביב ועדיין להזדהות איתה מאוד
+- מדובר בהזדהות תרבותית־סגנונית ספציפית
+---
+סקאלה:
+0–20:
+אנטי תל אביבי — חוסר חיבור ברור או אפילו דחייה
+20–40:
+די לא מתחבר — לא מזדהה עם הסגנון
+40–60:
+בינוני — אדישות או חיבור חלקי
+60–80:
+די מתחבר — אוהב את הסגנון והוייב
+80–100:
+מאוד תל אביבי — הזדהות חזקה, "זה אני"
+---
+חוקים:
+- אם המשתמש מבטא אהבה או חיבור לתל אביב או לוייב שלה → העלה ציון
+- אם המשתמש מבטא חוסר חיבור או אנטגוניזם → הורד ציון משמעותית
+- יש להעריך הזדהות תרבותית, לא רק התנהגות
+- ניתן להשתמש בקורלציות (נהנתנות, פתיחות וכו') כסיגנל חלש בלבד
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת סגנון מזרחי (עממיות תרבותית־סגנונית).
+מטרת התכונה:
+להעריך עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן.
+ציון גבוה = סגנון מזרחי מובהק  
+ציון נמוך = סגנון פחות מזרחי / יותר סלקטיבי או נישתי
+---
+איך להעריך:
+התבסס על:
+- טעם מוזיקלי (למשל חיבור למוזיקה מזרחית או פופולרית)
+- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
+- וייב כללי של חום, פתיחות ונגישות
+- חיבור לתרבות פופולרית רחבה
+- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
+- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
+---
+הבחנות חשובות:
+- לא מדובר בעדה או רקע אישי בפועל
+- מדובר בסגנון תרבותי בלבד
+- אדם יכול להיות מכל רקע ולהיות בעל סגנון מזרחי או לא
+- לא מדובר באינטליגנציה, קלילות או נהנתנות
+- לא מדובר רק במיינסטרים — אלא בסגנון תרבותי ספציפי
+---
+סקאלה:
+0–20:
+לא מזרחי — סגנון נישתי, סלקטיבי או מובחן מאוד
+20–40:
+מעט מזרחי — נגיעות קלות של סגנון עממי
+40–60:
+בינוני — שילוב בין סגנונות
+60–80:
+די מזרחי — סגנון עממי ברור
+80–100:
+מאוד מזרחי — וייב מובהק של סגנון מזרחי
+---
+חוקים:
+- אם המשתמש משדר סגנון עממי, פתוח, מחובר לתרבות פופולרית → העלה ציון
+- אם יש אינדיקציות לטעם וסגנון המזוהים עם וייב מזרחי → העלה ציון
+- אם המשתמש משדר סגנון נישתי, סלקטיבי או מובחן → הורד ציון
+- ניתן להשתמש במספר אינדיקציות (מוזיקה, שפה, וייב) יחד — לא מאפיין אחד בלבד
+- לא להסיק על בסיס עדה
+- יש להעריך את הוייב הכללי
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת גיקיות (חיבור לתרבות גיקית).
+מטרת התכונה:
+להעריך עד כמה המשתמש מתחבר לעולמות תוכן המזוהים עם תרבות גיקית — כמו טכנולוגיה, גיימינג, מדע בדיוני, פנטזיה, קומיקס או תחומי עניין דומים.
+ציון גבוה = יותר גיק  
+ציון נמוך = לא גיק
+---
+איך להעריך:
+התבסס על:
+- תחומי עניין (משחקי מחשב, פנטזיה, מד״ב, קומיקס, אנימה וכו')
+- חיבור לטכנולוגיה מעבר לשימוש רגיל
+- אזכורים של עולמות תוכן גיקיים
+- העדפה לפעילויות הקשורות לעולמות אלו
+---
+הבחנות חשובות:
+- לא מדובר באינטליגנציה או אנליטיות
+- לא מדובר ב"חנוניות" כללית
+- אדם יכול להיות חכם מאוד אך לא גיק
+- אדם יכול להיות גיקי מאוד אך לא "חנון"
+- מדובר בתחומי עניין וסגנון תרבותי בלבד
+---
+סקאלה:
+0–20:
+לא גיק — אין חיבור לעולמות תוכן גיקיים
+20–40:
+מעט גיק — נגיעות קלות
+40–60:
+בינוני — תחומי עניין מסוימים
+60–80:
+די גיק — חיבור ברור לתרבות גיקית
+80–100:
+מאוד גיק — עולמות תוכן גיקיים הם חלק מרכזי
+---
+חוקים:
+- אם המשתמש מציין תחומי עניין גיקיים ברורים → העלה ציון
+- אם מדובר בתחביב מרכזי → העלה ציון משמעותית
+- לא להסיק מגיקיות על אינטליגנציה
+- לא להסיק מהיותו מופנם או חנון
+- יש להעדיף תחומי עניין מפורשים על פני הסקות עקיפות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת היפיות (סגנון רוחני־אלטרנטיבי).
+מטרת התכונה:
+להעריך עד כמה המשתמש מתחבר לסגנון חיים רוחני, אלטרנטיבי או "היפי" — הכולל עניין ברוחניות, סדנאות, התפתחות אישית, טבע ואורח חיים פחות קונבנציונלי.
+ציון גבוה = יותר היפי  
+ציון נמוך = לא היפי
+---
+איך להעריך:
+התבסס על:
+- עניין ברוחניות או התפתחות אישית
+- השתתפות או עניין בסדנאות, ריטריטים או חוויות רוחניות
+- חיבור לטבע ואורח חיים "זורם" או לא קונבנציונלי
+- וייב של חופש, רוחניות או חיפוש משמעות
+- תחומי עניין המזוהים עם סגנון היפי
+---
+הבחנות חשובות:
+- לא מדובר בפתיחות כללית
+- לא מדובר בנהנתנות
+- לא מדובר באינטלקטואליות
+- אדם יכול להיות פתוח אך לא היפי
+- מדובר בסגנון חיים ותרבות ספציפיים
+---
+סקאלה:
+0–20:
+לא היפי — אין חיבור לעולם הרוחני/אלטרנטיבי
+20–40:
+מעט היפי — נגיעות קלות
+40–60:
+בינוני — עניין מסוים
+60–80:
+די היפי — חיבור ברור לעולם הרוחני/אלטרנטיבי
+80–100:
+מאוד היפי — זהות וסגנון חיים היפי מובהק
+---
+חוקים:
+- אם המשתמש מציין עניין ברור ברוחניות או סדנאות → העלה ציון
+- אם מדובר בחלק משמעותי מהחיים → העלה ציון משמעותית
+- לא להסיק מתכונה אחת בלבד
+- ניתן להשתמש בקורלציות (פתיחות, סגנון חיים) כסיגנל חלש בלבד
+- יש להעדיף אינדיקציות ישירות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת סגנון תרבותי־רוסי (יוצאי ברה״מ).
+מטרת התכונה:
+להעריך עד כמה המשתמש משדר סגנון תרבותי המזוהה עם יוצאי ברית המועצות לשעבר — מבחינת וייב, סגנון חברתי ותרבותי — או עד כמה הוא אינו מזוהה עם סגנון זה.
+ציון גבוה = סגנון רוסי מובהק  
+ציון נמוך = לא מזוהה עם הסגנון
+---
+איך להעריך:
+התבסס על:
+- זהות מוצהרת (למשל: רוסי/אוקראיני וכו') — סיגנל חזק
+- חיבור או הזדהות עם התרבות
+- וייב וסגנון כללי (חברתי, תקשורתי, תרבותי)
+- תחושת שייכות או חיבור לקהילה
+---
+הבחנות חשובות:
+- לא מדובר רק במוצא, אלא גם בסגנון
+- אדם יכול להיות ממוצא רוסי אך לא להזדהות עם הסגנון
+- אדם יכול לא להיות ממוצא רוסי אך לאמץ סגנון כזה
+- מדובר בהתרשמות כללית — לא בתכונות אופי ספציפיות
+---
+סקאלה:
+0–20:
+לא מזוהה כלל עם הסגנון
+20–40:
+מעט זיקה
+40–60:
+בינוני — חלק מהמאפיינים קיימים
+60–80:
+די מזוהה — סגנון ברור
+80–100:
+מאוד מזוהה — סגנון מובהק או זהות מוצהרת
+---
+חוקים:
+- אם המשתמש מציין מוצא רוסי/אוקראיני → העלה ציון משמעותית
+- אם יש גם הזדהות תרבותית → העלה ציון עוד יותר
+- אם יש רק וייב ללא מידע ישיר → ניתן להסיק בזהירות עם confidence נמוך
+- לא להסיק על בסיס סטריאוטיפים בלבד
+- יש להעדיף מידע ישיר על פני התרשמות
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>זיהוי רעילות (התנהגות מסוכנת).
+מטרת התכונה:
+לזהות משתמשים שמבטאים רמות גבוהות של רעילות, תוקפנות או התנהגות שעלולה להיות בעייתית במערכת — לצורך ניטור ובקרה בלבד.
+תכונה זו אינה מיועדת להתאמה אלא להערכת סיכון.
+---
+איך להעריך:
+התבסס על:
+- שיח אלים או תוקפני
+- ביטויי שנאה (גזענות, שנאת נשים, הכללות פוגעניות וכו')
+- זלזול או הקטנה של אחרים
+- תפיסות בעייתיות לגבי זוגיות (שליטה, חוסר כבוד, החפצה)
+- אגרסיביות או נוקשות חריגה בשיח
+---
+הבחנות חשובות:
+- לא כל דעה לא פופולרית היא רעילות
+- לא כל ישירות היא רעילות
+- יש להבחין בין הומור לבין כוונה אמיתית
+- יש להעריך לפי דפוס ולא לפי אמירה בודדת (אלא אם היא חמורה במיוחד)
+---
+סקאלה:
+0–20:
+אין סימני רעילות — שיח תקין
+20–40:
+מעט סימנים — ניואנסים קלים בלבד
+40–60:
+גבולי — יש אינדיקציות, אך לא חד משמעיות
+60–80:
+רעילות גבוהה — דפוסים ברורים של שיח בעייתי
+80–100:
+רעילות חמורה — ביטויים חריפים של אלימות, שנאה או התנהגות מסוכנת
+---
+חוקים:
+- יש להסתמך על דפוסים חוזרים ולא על אמירה בודדת (אלא אם היא חמורה מאוד)
+- אם יש ביטוי קיצוני (אלימות, גזענות ברורה וכו') → העלה ציון משמעותית
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך
+---
+חיזוק (קריטי):
+יש לזהות רעילות רק כאשר יש אינדיקציות ברורות — אין להסיק רעילות על בסיס רמזים חלשים בלבד
+---
+כלל כיסוי (חשוב):
+אם לאחר מספר אינטראקציות (כ־10–12 שאלות) לא זוהו אינדיקציות לרעילות —
+יש להניח שהמשתמש אינו רעיל, ולהחזיר ציון נמוך עם confidence סביר (לא null)
+אין להשאיר את התכונה ריקה כאשר יש מספיק מידע כללי על השיחה</t>
+  </si>
+  <si>
+    <t>זיהוי טרוליות.
+מטרת התכונה:
+לזהות האם המשתמש באמת מחפש שידוך ומשתף פעולה עם המערכת, או שמא הוא עונה בצורה לא כנה, ממציא, משחק עם המערכת או מטריל אותה.
+תכונה זו מיועדת לניטור ובקרה פנימיים בלבד, ואינה חלק מציון ההתאמה.
+---
+איך להעריך:
+התבסס על:
+- תשובות שנראות מופרכות או לא אמינות במכוון
+- סתירות חוזרות ומהותיות
+- תשובות לא ענייניות או לא קשורות
+- תחושה שהמשתמש "משחק" עם המערכת במקום לענות בכנות
+- זלזול עקבי בתהליך או בפורמט
+- תשובות אבסורדיות, ציניות או מופרעות באופן שחוזר על עצמו
+---
+הבחנות חשובות:
+- לא כל תשובה מוזרה היא טרוליות
+- לא כל הומור הוא טרוליות
+- לא כל חוסר עקביות הוא טרוליות
+- יש להבחין בין בלבול, חוסר ריכוז או סגנון מיוחד — לבין כוונה ברורה לא לשתף פעולה
+---
+סקאלה:
+0–20:
+אין סימני טרוליות — נראה משתף פעולה וכנה
+20–40:
+מעט סימנים — קלילות, בלבול או חוסר רצינות מסוים
+40–60:
+גבולי — יש אינדיקציות, אך לא חד משמעיות
+60–80:
+טרוליות גבוהה — דפוס ברור של תשובות לא כנות/מופרכות/לא ענייניות
+80–100:
+טרוליות חמורה — נראה באופן ברור שהמשתמש מטריל את המערכת
+---
+חוקים:
+- יש להסתמך על דפוס חוזר ולא על תשובה אחת בודדת
+- אם יש סתירות מהותיות חוזרות, תשובות מופרכות או זלזול עקבי → העלה ציון משמעותית
+- אם המשתמש מוזר אך עדיין נראה כנה ומשתף פעולה → לא לתת ציון גבוה
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך
+---
+חיזוק (קריטי):
+יש לזהות טרוליות רק כאשר יש אינדיקציות ברורות — אין להסיק טרוליות על בסיס תשובה אחת מוזרה, הומור, או חוסר עקביות קל בלבד
+---
+כלל כיסוי (חשוב):
+אם לאחר מספר אינטראקציות (כ־10–12 שאלות) לא זוהו אינדיקציות ברורות לטרוליות —
+יש להניח שהמשתמש אינו טרול, ולהחזיר ציון נמוך עם confidence סביר (לא null)
+אין להשאיר את התכונה ריקה כאשר יש מספיק מידע כללי על השיחה</t>
+  </si>
+  <si>
+    <t>זיהוי דיל ברייקרס פוטנציאליים.
+מטרת התכונה:
+לזהות מאפיינים משמעותיים אצל המשתמש שעלולים להוות דיל ברייקר עבור חלק מהאנשים — לצורך התאמה טובה יותר והימנעות מחוסר התאמה.
+אין לתת ציון.
+יש להחזיר:
+1. רשימה של דיל ברייקרס מתוך רשימה מוגדרת בלבד
+2. תיאור טקסטואלי קצר (אם יש מה להוסיף)
+---
+רשימת דיל ברייקרס אפשריים:
+- lives_with_parents (גר עם ההורים)
+- divorced (גרוש/ה)
+- has_children (יש ילדים)
+- has_pets (יש לו בעל חיים)
+- dislikes_pets (שונא/לא מסתדר עם בעלי חיים)
+---
+איך להעריך:
+התבסס על מידע מפורש שהמשתמש נתן במהלך השיחה.
+---
+הבחנות חשובות:
+- מדובר בדיל ברייקרס פוטנציאליים בלבד — לא בהכרח בעיה
+- יש להחזיר רק מאפיינים משמעותיים וברורים
+- אין להוסיף פריטים שלא מופיעים ברשימה
+- אין לנחש או להסיק ללא בסיס ברור
+---
+חוקים:
+- אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
+- אין צורך ביותר ממאפיין אחד — גם אחד מספיק
+- אם אין אינדיקציה ברורה → להחזיר ריק
+- אין להחזיר ערכים על בסיס השערה
+---
+תיאור טקסטואלי:
+אם רלוונטי, ניתן להוסיף משפט קצר שמסביר את ההקשר (למשל: "גר עם ההורים כרגע" או "יש כלב בבית")</t>
+  </si>
+  <si>
+    <t>יתרונות אפשריים</t>
+  </si>
+  <si>
+    <t>זיהוי יתרונות פוטנציאליים.
+מטרת התכונה:
+לזהות מאפיינים אצל המשתמש שיכולים להוות יתרון עבור חלק מהאנשים — לצורך התאמה טובה יותר והדגשת נקודות חיוביות.
+אין לתת ציון.
+יש להחזיר:
+1. רשימה של יתרונות מתוך רשימה מוגדרת בלבד
+2. תיאור טקסטואלי קצר (אם יש מה להוסיף)
+---
+רשימת יתרונות אפשריים:
+- has_pets (יש לו בעל חיים)
+- has_children (יש ילדים)
+- divorced (גרוש/ה)
+- plays_music (מנגן)
+- into_fitness (עוסק בבריאות וכושר)
+- high_income (הכנסה גבוהה)
+- high_education (השכלה גבוהה)
+---
+איך להעריך:
+התבסס על מידע מפורש שהמשתמש נתן במהלך השיחה.
+---
+הבחנות חשובות:
+- מדובר ביתרונות פוטנציאליים בלבד — לא בהכרח יתרון עבור כולם
+- יש להחזיר רק מאפיינים ברורים ומשמעותיים
+- אין להוסיף פריטים שלא מופיעים ברשימה
+- אין לנחש או להסיק ללא בסיס ברור
+---
+חוקים:
+- אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
+- אין צורך ביותר ממאפיין אחד — גם אחד מספיק
+- אם אין אינדיקציה ברורה → להחזיר ריק
+- אין להחזיר ערכים על בסיס השערה
+---
+תיאור טקסטואלי:
+אם רלוונטי, ניתן להוסיף משפט קצר שמסביר את ההקשר (למשל: "מנגן בגיטרה" או "מתאמן באופן קבוע")</t>
+  </si>
+  <si>
+    <t>שימוש פנימי - יתרונות אפשריים לבדיקה</t>
+  </si>
+  <si>
+    <t>יוקרה תעסוקתית</t>
+  </si>
+  <si>
+    <t>מעל המשתמש או -20</t>
+  </si>
+  <si>
+    <t>מראה</t>
+  </si>
+  <si>
+    <t>זהות</t>
+  </si>
+  <si>
+    <t>האם יש משהו נוסף לגבי הזהות שלך שחשוב שנדע...?  בנוסח שכתבנו.</t>
+  </si>
+  <si>
+    <t>סוגי בדיקות</t>
+  </si>
+  <si>
+    <t>משתמשים שאני מכירה טוב ולראות את הניתוח</t>
+  </si>
+  <si>
+    <t>זוגות קיימים ולבדוק את ההתאמה ביניהם</t>
+  </si>
+  <si>
+    <t>חוויית משתמש של משתמשים רנדומליים - האם השיחה זרמה, האם חפר מדי, האם היו משלמים על דבר כזה וכו'</t>
+  </si>
+  <si>
+    <t>מקרי קצה</t>
+  </si>
+  <si>
+    <t>משתמשים שעונים תשובות קצרות מדי</t>
+  </si>
+  <si>
+    <t>טרנס - ישיר או מרומז</t>
+  </si>
+  <si>
+    <t>א-מיני ישיר או מרומז</t>
+  </si>
+  <si>
+    <t>מכורים למין/סמים, BDSM</t>
+  </si>
+  <si>
+    <t>לחשוב אם בכלל זה רלוונטי לנו</t>
+  </si>
+  <si>
+    <t>טרולים</t>
+  </si>
+  <si>
+    <t>סוגים שונים של אנשים אם נצליח להביא</t>
+  </si>
+  <si>
+    <t>רלוונטי אולי רק לזוגות כי אני לא אדע אם הניתוח טוב אלא אם אני מכירה אישית</t>
+  </si>
+  <si>
+    <t>שיחה עם הצ'אט</t>
+  </si>
+  <si>
+    <t>בוצע, לבדוק בנייד</t>
+  </si>
+  <si>
+    <t>העלאת תמונות</t>
+  </si>
+  <si>
+    <t>בוצע, לבדוק</t>
+  </si>
+  <si>
+    <t>יצירת כרטיס התאמה</t>
+  </si>
+  <si>
+    <t>דירוגים</t>
+  </si>
+  <si>
+    <t>נוטיפיקציית התאמה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מובייל </t>
+  </si>
+  <si>
+    <t>עיצוב, חוויית משתמש וכו'</t>
+  </si>
+  <si>
+    <t>אריזה לאפליקציה אמיתית</t>
+  </si>
+  <si>
+    <t>מנויים תשלומים וכו'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אבטחת מידע </t>
+  </si>
+  <si>
+    <t>אבטחה - AI מול המשתמש</t>
+  </si>
+  <si>
+    <t>בדיקות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניהול </t>
+  </si>
+  <si>
+    <t>אנליזה</t>
+  </si>
+  <si>
+    <t>כמה משתמשים יש, כמה קיבלו התאמה, זמן המתנה ממוצע וכו'</t>
+  </si>
+  <si>
+    <t>הערכת אינטליגנציה מחשבתית (לא רגשית).
+מטרת התכונה:
+להעריך את רמת החשיבה הקוגניטיבית של המשתמש — יכולת ניסוח, מורכבות מחשבה, עומק, והיגיון.
+אין להתייחס לאינטליגנציה רגשית.
+---
+איך להעריך:
+השתמש בסיגנלים הבאים:
+- מורכבות ניסוח (פשוט / מורכב)
+- עומק רעיוני (שטחי / מעמיק)
+- יכולת הבחנה בין רעיונות
+- חשיבה לוגית ועקבית
+- יכולת להסביר או לנתח דברים
+---
+סקאלה (חובה להשתמש בקצוות כשמתאים):
+0–20:
+חשיבה מאוד בסיסית, תשובות שטחיות מאוד, בלבול, חוסר היגיון
+20–40:
+פשוט, מוגבל, מעט עומק, ניסוח בסיסי
+40–60:
+ממוצע — תקשורת תקינה אבל ללא עומק מיוחד
+60–75:
+מעל הממוצע — חשיבה ברורה, ניסוח טוב, מעט עומק
+75–90:
+גבוה — ניסוח מדויק, חשיבה מורכבת, הבחנות טובות
+90–100:
+גבוה מאוד — עומק חריג, הפשטה, ניתוח, חשיבה חדה במיוחד
+---
+חוקים חשובים:
+- אין להימנע מציונים נמוכים אם זה מה שנראה
+- אם השיחה פשוטה/שטחית → הציון צריך להיות נמוך
+- אל תמשוך לממוצע
+- אם יש מעט מידע → תן ציון עם confidence נמוך, אבל עדיין תעריך
+---
+משקל עבור התאמה:
+יש להגדיר weight_for_match רק אם המשתמש מביע חשיבות לאינטליגנציה אצל בן/בת זוג.
+אינדיקציות:
+- "חשוב לי מישהו חכם"
+- "צריך שיהיה ברמה שלי"
+- "לא מסתדרת עם אנשים לא חכמים"
+אם אין סיגנל ברור → להשאיר null
+אין למצע ציונים. אם רמת החשיבה נראית נמוכה או גבוהה — יש לשקף זאת בצורה חדה.
+אין לתת ציון מעל הממוצע כברירת מחדל.</t>
+  </si>
+  <si>
+    <t>יוקרה תעסוקתית - הערכת רמת השכלה ומסלול מקצועי.
+מטרת התכונה:
+להעריך את רמת ההשכלה והמסלול המקצועי של המשתמש — כולל סוג העיסוק, רמת מקצועיות והישגים — כמדד כללי לסגנון חיים, תחומי עניין והתאמה אפשרית.
+ציון גבוה = השכלה/מקצוע ברמה גבוהה יותר  
+ציון נמוך = פחות השכלה פורמלית או מקצוע פחות דורש הכשרה
+לדוגמה - רופאים, מהנדסי תוכנה, טייסים וכו' - יקבלו ציונים גבוהים במיוחד. לעומת זאת - ירקן / עובד מאפייה - משהו פשוט כזה - יקבל ציון נמוך. 
+---
+איך להעריך:
+התבסס על:
+- השכלה פורמלית (תואר, תחום לימודים)
+- סוג המקצוע
+- רמת מומחיות או בכירות
+- תחום עיסוק (למשל: הייטק, רפואה, הנדסה וכו')
+- תיאורים של הקריירה או המסלול המקצועי
+---
+הבחנות חשובות:
+- לא מדובר באינטליגנציה
+- לא מדובר בערך אישי של האדם
+- מדובר במדד של השכלה ומסלול מקצועי בלבד
+---
+סקאלה:
+0–20:
+ללא השכלה פורמלית או מקצוע שאינו דורש הכשרה
+20–40:
+הכשרה בסיסית / מקצוע כללי
+40–60:
+השכלה או מקצוע בינוני
+60–80:
+השכלה גבוהה או מקצוע מקצועי
+80–100:
+השכלה גבוהה מאוד או מקצוע ברמת מומחיות/יוקרה גבוהה
+---
+אין למצע ציונים.
+מקצועות הדורשים השכלה גבוהה או הכשרה מקצועית משמעותית (כגון הייטק, רפואה, הנדסה וכו') → ציון גבוה.
+מקצועות ללא השכלה פורמלית או מסלול מקצועי ברור → ציון נמוך.
+יש להשתמש בטווח רחב של הסקאלה כאשר יש סיגנל ברור.
+חוקים:
+- אם המשתמש מציין תואר, לימודים מתקדמים או מקצוע מקצועי → העלה ציון
+- אם יש תיאור של תפקיד בכיר או מומחיות → העלה ציון משמעותית
+- אין להסיק מקצוע או השכלה ללא מידע מפורש
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת נטייה פוליטית.
+מטרת התכונה:
+להעריך את מיקומו של המשתמש על הציר הפוליטי — משמאל לימין — בהתאם לעמדות או רמזים פוליטיים שהוא מבטא.
+ציון נמוך = שמאל  
+ציון גבוה = ימין
+---
+איך להעריך:
+התבסס על:
+- אמירות פוליטיות מפורשות
+- הזדהות עם מחנות או עמדות
+- רמזים עקיפים אך ברורים לעמדות פוליטיות
+- נושאים ערכיים עם זיקה פוליטית ברורה
+---
+הבחנות חשובות:
+- לא מדובר ברמת מעורבות פוליטית (זו תכונה נפרדת)
+- לא להסיק נטייה פוליטית מתכונות אחרות (דתיות, שמרנות וכו')
+- אם אין אינדיקציה ברורה → עדיף לא לנחש
+---
+סקאלה:
+0–20:
+שמאל קיצוני
+20–40:
+שמאל מתון
+40–60:
+מרכז
+60–80:
+ימין מתון
+80–100:
+ימין קיצוני
+---
+אם המשתמש מציין עמדה פוליטית במפורש — יש להשתמש בה ישירות.
+אם אין שום אזכור לפוליטיקה — אין להסיק כלל ויש להשאיר את התכונה ללא ערך.
+אין להסיק עמדה פוליטית על בסיס סגנון, ערכים או תחומי עניין.
+___
+חוקים:
+- אם המשתמש מבטא עמדה פוליטית ברורה → תן ציון בהתאם
+- אם יש רמזים עקיפים אך עקביים → ניתן להסיק עם confidence נמוך יותר
+- אם אין מספיק מידע → השאר null או תן ציון עם confidence נמוך מאוד
+- לא למצע ציונים כאשר יש אינדיקציה ברורה
+- אין להסיק נטייה פוליטית מתכונות אחרות בלבד</t>
+  </si>
+  <si>
+    <t>הערכת טיפוס מסיבתי (סגנון חיי לילה).
+מטרת התכונה:
+להעריך עד כמה סגנון החיים של המשתמש כולל חיי לילה, מסיבות, ליינים ותרבות בילוי מסיבתית, ועד כמה זה חלק מרכזי בזהות ובשגרה שלו.
+לא מדובר בכמה הוא נהנה ממסיבות באופן כללי, אלא האם זה סגנון חיים קבוע ומשמעותי.
+---
+איך להעריך:
+התבסס על:
+- תדירות יציאה למסיבות / חיי לילה
+- עד כמה זה חלק קבוע מהשגרה
+- זיקה לליינים, מועדונים, סצנה
+- סוג הסביבה החברתית (חיי לילה לעומת בילויים אחרים)
+- שפה שמעידה על סגנון חיים מסיבתי
+---
+הבחנות חשובות:
+- אדם יכול ליהנות ממסיבות אך לא להיות טיפוס מסיבתי  
+- התכונה מודדת סגנון חיים, לא העדפה נקודתית  
+---
+סקאלה:
+0–20:
+לא מסיבתי בכלל — לא חלק מהחיים, כמעט ולא יוצא למסיבות
+20–40:
+מעט מסיבתי — יוצא לפעמים, לא חלק משמעותי מהשגרה
+40–60:
+בינוני — משלב מסיבות מדי פעם כחלק מהחיים
+60–80:
+די מסיבתי — חיי לילה משמעותיים, יוצא הרבה
+80–100:
+מאוד מסיבתי — סגנון חיים מסיבתי, מסיבות וליינים הם חלק מרכזי מהזהות והשגרה
+---
+חוקים:
+- אם מדובר ביציאות מדי פעם בלבד → לא לתת ציון גבוה
+- אם זה נראה כמו חלק קבוע מהחיים → העלה ציון
+- אם המשתמש מתאר ליינים, סצנה, יציאות תכופות → העלה ציון משמעותית
+- אם אין מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>הערכת אהבה לבעלי חיים.
+מטרת התכונה:
+להעריך עד כמה המשתמש אוהב, מחובר ונוח עם בעלי חיים — ועד כמה נוכחות של בעלי חיים מתאימה לו בחיים.
+---
+איך להעריך:
+התבסס על:
+- אהבה מפורשת לבעלי חיים
+- קיום חיית מחמד בפועל (סיגנל חזק מאוד)
+- תיאורים של קשר רגשי לבעלי חיים
+- נכונות לחיות עם בעלי חיים
+- רתיעה, פחד או התנגדות לבעלי חיים
+---
+הבחנות חשובות:
+- לא להסיק אהבה רק מאזכור של בעלי חיים
+- יש להבין את ההקשר (חיובי / שלילי / ניטרלי)
+- אזכור שלילי (פחד, דיל ברייקר) → ציון נמוך
+- אזכור חיובי עם מעורבות (למשל יש כלב) → ציון גבוה
+יש להבין את ההקשר.
+פחד, סלידה או דיל ברייקר הקשור לבעלי חיים הם סיגנל חזק מאוד לציון נמוך עם confidence גבוה.
+אזכור של בעל חיים בלבד אינו סיגנל חיובי.
+---
+סקאלה:
+0–20:
+לא אוהב — רתיעה, פחד או התנגדות ברורה
+20–40:
+די לא אוהב — לא נוח עם בעלי חיים
+40–60:
+בינוני — ניטרלי, אין חיבור חזק
+60–80:
+די אוהב — חיבור חיובי לבעלי חיים
+80–100:
+מאוד אוהב — אהבה ברורה, לעיתים גם חיית מחמד בפועל
+---
+חוקים:
+- אם המשתמש מציין שיש לו חיית מחמד או קשר חזק לבעלי חיים → העלה ציון משמעותית
+- אם המשתמש מבטא פחד, רתיעה או דיל ברייקר → הורד ציון משמעותית
+- אם יש רק אזכור טכני של בעלי חיים → אל תסיק מכך ציון גבוה
+- יש להתחשב בכיוון האמירה (חיובי / שלילי)
+- אם אין מספיק מידע → תן ציון עם confidence נמוך</t>
+  </si>
+  <si>
+    <t>זיהוי זהות מגדרית/מינית מוצהרת.
+מטרת התכונה:
+לזהות האם המשתמש הצהיר באופן מפורש על זהות מגדרית או מינית שאינה סטנדרטית — לצורך התאמה מדויקת יותר והימנעות מחוסר התאמה.
+תכונה זו מיועדת לשימוש פנימי בלבד.
+---
+איך להעריך:
+התבסס על:
+- הצהרה מפורשת של המשתמש על זהות מגדרית (למשל טרנסג׳נדר, לא בינארי וכו')
+- הצהרה מפורשת על זהות מינית (למשל א-מיני וכו')
+- מידע ברור שהמשתמש בחר לשתף
+---
+הבחנות חשובות:
+- אין להסיק זהות מגדרית או מינית ללא הצהרה מפורשת
+- אין לנחש על בסיס סגנון, שפה או התנהגות
+- מדובר רק במה שהמשתמש בחר לשתף באופן ברור
+---
+סקאלה:
+0–20:
+אין אינדיקציה — לא נמסר מידע
+60–80:
+יש אינדיקציה מסוימת אך לא חד משמעית
+80–100:
+הצהרה מפורשת וברורה
+---
+חוקים:
+- רק הצהרה מפורשת → ציון גבוה
+- רמזים בלבד → לכל היותר ציון בינוני עם confidence נמוך
+- אין לנחש או להסיק באופן עקיף
+- אם אין מידע → אפשר לתת ציון נמוך בסבירות נמוכה.
+- אם אין מידע מתוך הרבה טקסט (נגיד בסיום השאלון) - אפשר לתת ציון נמוך בסבירות די גבוהה - נגיד 0.5
+---
+כלל כיסוי:
+אם לאחר השיחה לא התקבלה שום הצהרה מפורשת —
+יש להניח שאין מידע רלוונטי, ולא להסיק דבר</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1750,6 +3300,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <charset val="177"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1783,7 +3358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1878,6 +3453,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2159,7 +3744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -2170,129 +3755,228 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="35" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D4" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>515</v>
+      </c>
+      <c r="B5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D5" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B6" t="s">
-        <v>418</v>
-      </c>
-      <c r="C6" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B7" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C7" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B8" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>426</v>
+        <v>409</v>
+      </c>
+      <c r="B9" t="s">
+        <v>413</v>
       </c>
       <c r="C9" t="s">
-        <v>413</v>
-      </c>
-      <c r="D9" s="5"/>
+        <v>414</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>423</v>
-      </c>
-      <c r="B10" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
-      </c>
-      <c r="D10" t="s">
-        <v>425</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="B11" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C11" t="s">
-        <v>419</v>
+        <v>411</v>
+      </c>
+      <c r="D11" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B12" t="s">
-        <v>430</v>
+        <v>421</v>
+      </c>
+      <c r="C12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" t="s">
+        <v>411</v>
+      </c>
+      <c r="D14" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C15" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B16" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>423</v>
+      </c>
+      <c r="B17" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B18" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>415</v>
+      </c>
+      <c r="B19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>508</v>
+      </c>
+      <c r="B20" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -2312,149 +3996,149 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="14" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="C4" s="14" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="C5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="C7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8">
       <c r="C8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="C9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2">
       <c r="C10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" s="14" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D13" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="C14" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E14" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E15" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="C16" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D16" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -2474,137 +4158,137 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="14" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B3" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B5" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B6" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="14" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="14" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="14" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -2614,27 +4298,121 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>361</v>
+      <c r="A3" s="14" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="14" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="37.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="14" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="14" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +4437,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2672,490 +4450,490 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="43.2">
       <c r="A7" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="72">
       <c r="A8" s="11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="11" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="100.8">
       <c r="A10" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="43.2">
       <c r="A11" s="11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="72">
       <c r="A12" s="11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H12" s="31"/>
       <c r="I12" s="30" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="43.2">
       <c r="A13" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" ht="115.2">
       <c r="A14" s="11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" ht="28.8">
       <c r="A15" s="11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="30" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="86.4">
       <c r="A18" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="30"/>
     </row>
     <row r="19" spans="1:9" ht="57.6">
       <c r="A19" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I19" s="30"/>
     </row>
     <row r="20" spans="1:9" ht="57.6">
       <c r="A20" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="11" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="11" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.8">
       <c r="A23" s="11" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="11" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="11" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3165,13 +4943,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" style="38" customWidth="1"/>
     <col min="3" max="3" width="17.109375" customWidth="1"/>
-    <col min="4" max="4" width="53.6640625" customWidth="1"/>
+    <col min="4" max="4" width="71.33203125" style="5" customWidth="1"/>
     <col min="7" max="7" width="12.109375" customWidth="1"/>
     <col min="8" max="8" width="17.77734375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
@@ -3181,23 +4959,23 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="39" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
@@ -3209,33 +4987,33 @@
         <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="110.4">
-      <c r="A5" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>436</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="409.6">
+      <c r="A5" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>428</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>437</v>
+        <v>518</v>
       </c>
       <c r="E5" s="2">
         <v>0.7</v>
@@ -3253,24 +5031,24 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>481</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="409.6">
+      <c r="A6" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>443</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="E6" s="2">
         <v>0.6</v>
@@ -3278,59 +5056,59 @@
       <c r="F6" s="2">
         <v>7</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="21"/>
     </row>
-    <row r="7" spans="1:11" ht="124.2">
+    <row r="7" spans="1:11" ht="409.6">
       <c r="A7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="2">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="K7" s="21"/>
+    </row>
+    <row r="8" spans="1:11" ht="409.6">
+      <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="B8" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.6</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F8" s="2">
         <v>7</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="28.8">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>8</v>
@@ -3339,85 +5117,85 @@
         <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="55.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="409.6">
       <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E9" s="2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="28.8">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="409.6">
       <c r="A10" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E10" s="2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="69">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="409.6">
       <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>444</v>
+        <v>521</v>
       </c>
       <c r="E11" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>8</v>
@@ -3425,26 +5203,28 @@
       <c r="H11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" ht="27.6">
+      <c r="J11" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="409.6">
       <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>355</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>431</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E12" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -3454,24 +5234,24 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="409.6">
       <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>347</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>477</v>
+        <v>439</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E13" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F13" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>8</v>
@@ -3481,18 +5261,18 @@
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" ht="409.6">
       <c r="A14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="B14" s="40" t="s">
+        <v>25</v>
+      </c>
       <c r="C14" s="2" t="s">
-        <v>477</v>
+        <v>439</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>452</v>
       </c>
       <c r="E14" s="2">
         <v>0.5</v>
@@ -3508,51 +5288,41 @@
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" ht="409.6">
       <c r="A15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="B15" s="40"/>
       <c r="C15" s="2" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="409.6">
+      <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="2">
+      <c r="B16" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E16" s="2">
         <v>0.6</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F16" s="2">
         <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="41.4">
-      <c r="A16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="F16" s="2">
-        <v>6</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>8</v>
@@ -3560,31 +5330,26 @@
       <c r="H16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="409.6">
       <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>35</v>
+        <v>456</v>
       </c>
       <c r="E17" s="2">
         <v>0.7</v>
       </c>
       <c r="F17" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>8</v>
@@ -3592,26 +5357,31 @@
       <c r="H17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="55.2">
+      <c r="J17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="409.6">
       <c r="A18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E18" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>8</v>
@@ -3620,25 +5390,22 @@
         <v>8</v>
       </c>
       <c r="J18" s="2"/>
-      <c r="K18" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="27.6">
+    </row>
+    <row r="19" spans="1:11" ht="409.6">
       <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>478</v>
+        <v>439</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E19" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -3646,21 +5413,26 @@
       <c r="G19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" ht="41.4">
+      <c r="K19" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="409.6">
       <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E20" s="2">
         <v>0.6</v>
@@ -3669,48 +5441,48 @@
         <v>4</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>44</v>
+    <row r="21" spans="1:11" ht="409.6">
+      <c r="A21" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>459</v>
       </c>
       <c r="E21" s="2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" ht="409.6">
       <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>461</v>
       </c>
       <c r="E22" s="2">
         <v>0.4</v>
@@ -3719,29 +5491,29 @@
         <v>3</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="41.4">
+    <row r="23" spans="1:11" ht="409.6">
       <c r="A23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E23" s="2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F23" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>14</v>
@@ -3749,43 +5521,43 @@
       <c r="H23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" ht="409.6">
       <c r="A24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E24" s="2">
         <v>0.6</v>
       </c>
       <c r="F24" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="41.4">
-      <c r="A25" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
+    <row r="25" spans="1:11" ht="409.6">
+      <c r="A25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>478</v>
+        <v>437</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E25" s="2">
         <v>0.6</v>
@@ -3794,111 +5566,116 @@
         <v>7</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="J25" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="69">
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="409.6">
       <c r="A26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>359</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E26" s="2">
         <v>0.6</v>
       </c>
       <c r="F26" s="2">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="409.6">
+      <c r="A27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F27" s="2">
         <v>5</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F27" s="2">
-        <v>3</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="H27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="41.4">
+    <row r="28" spans="1:11" ht="409.6">
       <c r="A28" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E28" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" ht="409.6">
+      <c r="A29" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E29" s="2">
         <v>0.4</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F29" s="2">
         <v>4</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" ht="409.6">
       <c r="A30" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="E30" s="2">
         <v>0.2</v>
@@ -3910,160 +5687,160 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="27.6">
-      <c r="A31" s="33" t="s">
-        <v>348</v>
+    <row r="31" spans="1:11" ht="409.6">
+      <c r="A31" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>351</v>
+        <v>468</v>
       </c>
       <c r="E31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="409.6">
+      <c r="A32" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E32" s="2">
         <v>0.5</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F32" s="2">
         <v>4</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="28.8">
-      <c r="A32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" ht="409.6">
       <c r="A33" s="3" t="s">
-        <v>400</v>
+        <v>54</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E33" s="2">
         <v>0.2</v>
       </c>
-      <c r="F33" s="2">
-        <v>4</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="55.2">
+      <c r="H33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" ht="409.6">
       <c r="A34" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="E34" s="2">
         <v>0.2</v>
       </c>
       <c r="F34" s="2">
+        <v>4</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="409.6">
+      <c r="A35" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="2">
         <v>3</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="27.6">
-      <c r="A35" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="E35" s="2">
+    <row r="36" spans="1:11" ht="409.6">
+      <c r="A36" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E36" s="2">
         <v>0.4</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="2">
         <v>6</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="27.6">
-      <c r="A36" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="E36" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F36" s="2">
-        <v>4</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" ht="409.6">
       <c r="A37" s="3" t="s">
-        <v>346</v>
+        <v>433</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="E37" s="2">
         <v>0.2</v>
       </c>
       <c r="F37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="27.6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="409.6">
       <c r="A38" s="3" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E38" s="2">
         <v>0.2</v>
@@ -4072,48 +5849,68 @@
         <v>3</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="409.6">
+      <c r="A39" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="27.6">
+    <row r="40" spans="1:11" ht="409.6">
       <c r="A40" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>60</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="E40" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F40" s="2">
-        <v>4</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="2"/>
+      <c r="H40" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="1:11" ht="41.4">
+    <row r="41" spans="1:11" ht="409.6">
       <c r="A41" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>119</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>120</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E41" s="2">
+        <v>478</v>
+      </c>
+      <c r="E41">
         <v>0.4</v>
       </c>
       <c r="F41" s="2"/>
@@ -4121,137 +5918,156 @@
         <v>9</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" ht="41.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="409.6">
       <c r="A42" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>125</v>
+        <v>276</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>277</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E42">
+        <v>523</v>
+      </c>
+      <c r="E42" s="2">
         <v>0.4</v>
       </c>
-      <c r="F42" s="2"/>
       <c r="G42" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="41.4">
+        <v>278</v>
+      </c>
+      <c r="J42" s="19"/>
+      <c r="K42" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="409.6">
       <c r="A43" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>275</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="E43" s="2">
-        <v>0.4</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="69">
+        <v>279</v>
+      </c>
+      <c r="K43" s="34"/>
+    </row>
+    <row r="44" spans="1:11" ht="409.6">
       <c r="A44" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>471</v>
+        <v>441</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="E44" s="2">
         <v>0.1</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="3" t="s">
-        <v>9</v>
+      <c r="G44" t="s">
+        <v>14</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K44" s="34"/>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="36" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="69">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="36" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="69">
+      <c r="A47" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F47" s="2">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>339</v>
+        <v>21</v>
+      </c>
+      <c r="B48" s="40" t="s">
+        <v>20</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="3" t="s">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="E48" s="2">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F48" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="41.4">
       <c r="A49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="B49" s="40" t="s">
+        <v>29</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="3" t="s">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="E49" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F49" s="2">
         <v>5</v>
@@ -4262,23 +6078,26 @@
       <c r="H49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="55.2">
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" ht="41.4">
       <c r="A50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>439</v>
+      </c>
       <c r="D50" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E50" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>8</v>
@@ -4287,6 +6106,30 @@
         <v>8</v>
       </c>
       <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" ht="27.6">
+      <c r="A51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F51" s="2">
+        <v>4</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4312,7 +6155,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="16" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="41.4">
@@ -4323,7 +6166,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>5</v>
@@ -4335,36 +6178,36 @@
         <v>4</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4373,22 +6216,22 @@
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I3" s="19"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -4397,19 +6240,19 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" ht="28.8">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -4421,21 +6264,21 @@
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4447,18 +6290,18 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4470,18 +6313,18 @@
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4493,15 +6336,15 @@
         <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>0.3</v>
@@ -4513,18 +6356,18 @@
         <v>9</v>
       </c>
       <c r="K9" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>0.4</v>
@@ -4536,21 +6379,21 @@
         <v>8</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.8">
       <c r="A11" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -4562,10 +6405,10 @@
         <v>9</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="L11" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -4593,15 +6436,15 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="27.6">
@@ -4609,47 +6452,47 @@
         <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8">
       <c r="C5" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="14" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="41.4">
@@ -4657,52 +6500,52 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="43.2">
       <c r="C10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -4727,7 +6570,7 @@
     </row>
     <row r="13" spans="1:10" ht="15.6">
       <c r="A13" s="23" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -4887,50 +6730,50 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="14" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="K2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="57.6">
       <c r="A3" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>240</v>
-      </c>
       <c r="G3" s="14" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8">
@@ -4960,13 +6803,13 @@
         <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="43.2">
@@ -4996,7 +6839,7 @@
         <v>50</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28.8">
@@ -5026,10 +6869,10 @@
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5059,7 +6902,7 @@
         <v>22</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8">
@@ -5089,10 +6932,10 @@
         <v>64</v>
       </c>
       <c r="K8" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="27">
@@ -5122,10 +6965,10 @@
         <v>22</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5182,10 +7025,10 @@
         <v>14</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5233,23 +7076,23 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -5262,37 +7105,37 @@
         <v>7</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="I4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="K4" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="2:13">
@@ -5383,7 +7226,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="5">
         <v>30</v>
@@ -5497,42 +7340,42 @@
         <v>7</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="I12" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="K12" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C13" s="5">
         <v>70</v>
@@ -5661,7 +7504,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C16" s="5">
         <v>100</v>
@@ -5704,7 +7547,7 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5">
         <v>100</v>
@@ -5747,7 +7590,7 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5">
         <v>20</v>
@@ -5848,14 +7691,14 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="26" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -5871,7 +7714,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="20" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -5888,7 +7731,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5900,42 +7743,42 @@
     </row>
     <row r="6" spans="1:9" ht="43.2">
       <c r="A6" s="22" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="H6" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="I6" s="22" t="s">
         <v>196</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D7" s="5">
         <v>95</v>
@@ -5960,19 +7803,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D8">
         <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F8">
         <v>0.5</v>
@@ -5991,19 +7834,19 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D9">
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F9">
         <v>0.8</v>
@@ -6022,19 +7865,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D10">
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F10">
         <v>0.5</v>
@@ -6053,19 +7896,19 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F11">
         <v>0.6</v>
@@ -6102,17 +7945,17 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="19" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="20" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6138,109 +7981,109 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>227</v>
-      </c>
       <c r="J3" s="14" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="I4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="L5" s="19" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="27" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="14" t="s">
+      <c r="I11" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>227</v>
-      </c>
       <c r="J11" s="14" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -6257,13 +8100,13 @@
         <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H12" s="29">
         <v>46075</v>
@@ -6283,7 +8126,7 @@
         <v>67.599999999999994</v>
       </c>
       <c r="N12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:14">

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,27 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A4FBEA-5140-4840-BC18-3E5E251AB18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC03644-A9C4-41C7-AC93-92BA8928AC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
     <sheet name="פרטי משתמש" sheetId="3" r:id="rId2"/>
     <sheet name="מאפיינים - כללי" sheetId="1" r:id="rId3"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId4"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId5"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId6"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId7"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId8"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId9"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId10"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId11"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId12"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId13"/>
+    <sheet name="internal traits" sheetId="14" r:id="rId4"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId5"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId6"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId7"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId8"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId9"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId10"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId11"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId12"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId13"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="613">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3201,12 +3201,628 @@
 אם לאחר השיחה לא התקבלה שום הצהרה מפורשת —
 יש להניח שאין מידע רלוונטי, ולא להסיק דבר</t>
   </si>
+  <si>
+    <t>סקאלת ציונים</t>
+  </si>
+  <si>
+    <t>הסבר כללי</t>
+  </si>
+  <si>
+    <t>מה כן נחשב סיגנל</t>
+  </si>
+  <si>
+    <t>התבסס על:
+- השכלה פורמלית (תואר, תחום לימודים)
+- סוג המקצוע
+- רמת מומחיות או בכירות
+- תחום עיסוק (למשל: הייטק, רפואה, הנדסה וכו')
+- תיאורים של הקריירה או המסלול המקצועי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+הבחנות חשובות:
+- מדובר ביתרונות פוטנציאליים בלבד — לא בהכרח יתרון עבור כולם
+- יש להחזיר רק מאפיינים ברורים ומשמעותיים
+- אין להוסיף פריטים שלא מופיעים ברשימה
+- אין לנחש או להסיק ללא בסיס ברור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+התבסס על מידע מפורש שהמשתמש נתן במהלך השיחה.</t>
+  </si>
+  <si>
+    <t>זיהוי יתרונות פוטנציאליים.
+אין לתת ציון.
+יש להחזיר:
+1. רשימה של יתרונות מתוך רשימה מוגדרת בלבד
+2. תיאור טקסטואלי קצר (אם יש מה להוסיף)
+רשימת יתרונות אפשריים:
+- has_pets (יש לו בעל חיים)
+- has_children (יש ילדים)
+- divorced (גרוש/ה)
+- plays_music (מנגן)
+- into_fitness (עוסק בבריאות וכושר)
+- high_income (הכנסה גבוהה)
+- high_education (השכלה גבוהה)
+חוקים:
+- אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
+- אין צורך ביותר ממאפיין אחד — גם אחד מספיק
+- אם אין אינדיקציה ברורה → להחזיר ריק
+- אין להחזיר ערכים על בסיס השערה</t>
+  </si>
+  <si>
+    <t>נחמדות / חום / חברותיות ≠ אינטליגנציה רגשית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הבחנות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
+- עד כמה הדעות שלו נפוצות ונורמטיביות
+- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
+- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- רגישות ≠ חוסר יציבות  
+  אדם יכול להיות רגיש אך יציב.
+- עומק רגשי ≠ חוסר יציבות  
+  אדם עמוק רגשית לא בהכרח נוטה לדרמה, דיכאון או קיצוניות.
+</t>
+  </si>
+  <si>
+    <t>לא מדובר ברצון להקים משפחה וילדים משלו, אלא במידת הקרבה, המעורבות והמרכזיות של משפחת המוצא בחיים בפועל.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אדם יכול ליהנות ממסיבות אך לא להיות טיפוס מסיבתי  
+- התכונה מודדת סגנון חיים, לא העדפה נקודתית  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- תדירות יציאה למסיבות / חיי לילה
+- עד כמה זה חלק קבוע מהשגרה
+- זיקה לליינים, מועדונים, סצנה
+- סוג הסביבה החברתית (חיי לילה לעומת בילויים אחרים)
+- שפה שמעידה על סגנון חיים מסיבתי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- מידת הקרבה להורים ולמשפחה 
+- עד כמה המשפחה נוכחת בשגרה
+- עד כמה המשפחה משפיעה על החלטות, סדרי עדיפויות ואורח חיים
+- עד כמה המשתמש רואה במשפחתיות חלק מרכזי מחייו, לעומת רצון בחיים נפרדים ועצמאיים יותר</t>
+  </si>
+  <si>
+    <t>הערכת מופנמות / מוחצנות כסגנון ביטוי.
+התכונה מודדת את סגנון הביטוי והנוכחות של המשתמש — עד כמה הוא אקספרסיבי, מוחצן ותופס מקום, לעומת שקט, רגוע ומופנם.
+ציון גבוה = סגנון מוחצן (אקספרסיבי)
+ציון נמוך = סגנון מופנם (שקט)
+חוקים:
+- אם המשתמש נשמע שקט, מאופק או מינימליסטי בביטוי → הורד ציון
+- אם המשתמש נשמע אקספרסיבי, פתוח, יוזם ודומיננטי → העלה ציון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- סגנון הדיבור (ישיר, פתוח, מרובה לעומת מדוד ושקט)
+- רמת האקספרסיביות (כמה מבטא את עצמו כלפי חוץ)
+- "ווליום" אנרגטי — מורגש, דומיננטי, יוזם לעומת שקט ונוכח בעדינות
+- עד כמה נראה שהוא תופס מקום חברתית לעומת משתלב ברקע
+- קצב ואופי הביטוי (מהיר/זורם/יוזם לעומת רגוע/מאופק)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- זה לא מודד צורך חברתי — אדם יכול להיות מופנם מאוד ועדיין מאוד אוהב אנשים  
+- זה לא מודד נהנתנות  
+- זה לא מודד אינטליגנציה חברתית  
+- מדובר בסגנון נוכחות וביטוי בלבד
+- לא להסיק מוחצנות רק מזה שהוא אוהב אנשים או בילויים</t>
+  </si>
+  <si>
+    <t>:
+-לא מדובר במסיבות דווקא — זה כולל כל סוג של בילוי וחוויה
+- לא למדוד כאן מוחצנות — אדם יכול להיות מופנם ונהנתן
+- לא למדוד כאן רק אמירות כלליות — חשוב גם ביטוי בפועל</t>
+  </si>
+  <si>
+    <t>הערכת מודעות עצמית
+עד כמה המשתמש מבין את עצמו — רגשות, דפוסים, חוזקות וחולשות — ויכול לדבר עליהם בצורה מודעת..
+- אם אין רפלקציה אישית ברורה → לא לתת ציון גבוה
+- אם יש תיאור עצמי עמוק או מודע → העלה ציון</t>
+  </si>
+  <si>
+    <t>:
+- ניסוח יפה ≠ מודעות עצמית
+- ניתוח כללי ≠ הבנה של עצמי</t>
+  </si>
+  <si>
+    <t>הערכת חשיבות והזדהות עם הומור
+עד כמה הומור הוא חלק מהזהות של המשתמש ועד כמה הוא חשוב לו — הן אצל עצמו והן אצל בן/בת זוג.
+לא מדובר בניסיון למדוד עד כמה המשתמש באמת מצחיק, אלא עד כמה הומור הוא ערך או מאפיין מרכזי עבורו.
+חוקים:
+- אם המשתמש מצהיר שחוש הומור חשוב לו → העלה ציון
+- אם המשתמש מציג את עצמו כאדם עם חוש הומור → העלה ציון
+- אם הומור מוזכר כמה פעמים או בהדגשה → העלה ציון משמעותית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אמירות ישירות ("יש לי חוש הומור", "אני מאוד ציני", "חשוב לי הומור")
+- הדגשה של הומור כמרכיב חשוב בזוגיות
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה המשתמש מתעניין או עוסק בפוליטיקה
+- עד כמה פוליטיקה היא חלק מהשיח שלו
+- עד כמה הוא מבטא דעות פוליטיות באופן ברור
+- עד כמה הנושא תופס מקום בחיים ובזהות שלו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר ביציבות רגשית  
+  אדם יכול להיות יציב אך שלילי  
+- לא מדובר בעומק או אינטליגנציה  
+- לא מדובר בקלילות בלבד  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- סגנון התקשורת (חם, נעים, מפרגן לעומת קר או ענייני)
+- שימוש במחמאות או שפה חיובית כלפי אחרים
+- תחושת קרבה, רכות או פתיחות בין-אישית
+- עד כמה המשתמש משדר "לב טוב" ויחס אוהב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר בכמות אינטראקציות (זה חברתיות)
+- לא מדובר באופטימיות כללית (זה גישה חיובית)
+- לא מדובר באינטליגנציה רגשית
+- אדם יכול להיות מופנם ועדיין מאוד לבבי
+- אדם יכול להיות מוחצן אך לא לבבי</t>
+  </si>
+  <si>
+    <t>הערכת פתיחות (Openness).
+עד כמה המשתמש פתוח לרעיונות, חוויות וסגנונות חיים שונים — ועד כמה הוא נמשך אקטיבית להתנסות ולחוות דברים חדשים, גם אם הם מחוץ לאזור הנוחות.
+ חשוב למדוד גם פתיחות מחשבתית וגם פתיחות חווייתית בפועל
+חוקים:
+- אם המשתמש מבטא רצון לחוות, להתנסות או לחפש חוויות → העלה ציון- אם המשתמש מבטא קבלה או סקרנות כלפי סגנונות חיים שונים → העלה ציון
+- אם המשתמש מבטא הסתייגות משונות או היצמדות למה שמוכר → הורד ציון</t>
+  </si>
+  <si>
+    <t>:
+-  לא מדובר בפתיחות רגשית
+- לא מדובר באינטלקטואליות (עומק שיח)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר באחריות או בגרות תפקודית  
+- אדם יכול להיות מאוד אחראי וחכם אך עם וייב ילדותי  
+- לא מדובר באינטליגנציה או עומק  
+- לא מדובר ברצינות לחיים  
+- לא להסיק ילדותיות מחוסר אחריות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+הבחנות חשובות:
+- לא מדובר בפוליטיקה או עמדות ספציפיות
+- לא להסיק מהזכרת ישראל בלבד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אמירות פוליטיות מפורשות
+- הזדהות עם מחנות או עמדות
+- רמזים עקיפים אך ברורים לעמדות פוליטיות
+- נושאים ערכיים עם זיקה פוליטית ברורה
+ - פעילות בארגון בעל זיהוי פוליטי/מחאתי היא סיגנל חזק
+- ביקורת על הממשלה או תמיכה בממשלה תהווה סיגנל ברור</t>
+  </si>
+  <si>
+    <t>הערכת מוסר עבודה
+עד כמה המשתמש רציני, מחויב ומשקיע בעבודה או בעשייה שלו — ועד כמה יש לו גישה של התמדה, אחריות ורצון לעשות דברים כמו שצריך.
+חוקים:
+- אם המשתמש מדבר על התמדה, השקעה, מחויבות או משמעת עצמית → העלה ציון
+- אם המשתמש מתאר את עצמו כעצלן, לא עקבי או חסר משמעת → הורד ציון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- יחס לעבודה, קריירה או עשייה
+- מידת האחריות והמחויבות
+- השקעה, התמדה וחריצות
+- שאיפה לעשות דברים היטב ולא רק "לסמן וי"
+- גישה של משמעת עצמית והתמדה לאורך זמן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר במוסר או טוב/רע
+- לא מדובר בפשע או עבירות חמורות
+- אדם יכול להיות חכם, מוסרי ואחראי אך לא "ילד טוב"
+- מדובר בסגנון התנהלות מול חוקים ומסגרות
+-- לא להסיק ממוסר או אינטליגנציה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- טעם תרבותי (מוזיקה, קולנוע, בילויים) לא מיינסטרימי
+- העדפה לדברים נישתיים או פחות פופולריים
+- סגנון אישי שמדגיש ייחודיות או אלטרנטיביות
+ לעיתים גם נימה של מודעות לסטייל או ייחודיות</t>
+  </si>
+  <si>
+    <t>הערכת וייב תל אביבי
+עד כמה המשתמש מתחבר לסגנון החיים, התרבות והוייב המזוהים עם תל אביב .
+חוקים:
+- אם המשתמש מבטא אהבה או חיבור לתל אביב או לוייב שלה → העלה ציון
+- אם המשתמש מבטא חוסר חיבור או אנטגוניזם → הורד ציון משמעותית
+ המשתמש מבטא חיבור לפריפריה - הורד ציון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- יחס ישיר לתל אביב (אהבה / חיבור / הסתייגות)
+- הזדהות עם סגנון החיים המזוהה עם תל אביב
+- העדפה או דחייה של בילויים, סגנון חברתי ותרבות המזוהים עם העיר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר בכמה המשתמש עירוני או יוצא לבלות
+- אדם יכול לא לגור בתל אביב ועדיין להזדהות איתה מאוד
+- מדובר בהזדהות תרבותית־סגנונית ספציפית</t>
+  </si>
+  <si>
+    <t>:
+- טעם מוזיקלי (חיבור למוזיקה מזרחית)
+- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
+- וייב כללי של חום, פתיחות ונגישות
+- חיבור לתרבות פופולרית רחבה
+- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
+- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
+- זהות מוצהרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר באינטליגנציה, קלילות או נהנתנות
+- לא מדובר רק במיינסטרים — אלא בסגנון תרבותי ספציפי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- תחומי עניין (משחקי מחשב, פנטזיה, מד״ב, קומיקס, אנימה וכו')
+- חיבור לטכנולוגיה מעבר לשימוש רגיל
+- אזכורים של עולמות תוכן גיקיים
+- העדפה לפעילויות הקשורות לעולמות אלו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+השתתפות או עניין בסדנאות, ריטריטים או חוויות רוחניות
+- חיבור לטבע ואורח חיים "זורם" או לא קונבנציונלי
+- וייב של חופש, רוחניות או חיפוש משמעות
+- תחומי עניין המזוהים עם סגנון היפי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- זהות מוצהרת (למשל: רוסי/אוקראיני וכו') — סיגנל חזק
+- חיבור או הזדהות עם התרבות
+- וייב וסגנון כללי (חברתי, תקשורתי, תרבותי)
+- תחושת שייכות או חיבור לקהילה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- יש להבחין בין הומור לבין כוונה אמיתית
+- יש להעריך לפי דפוס ולא לפי אמירה בודדת (אלא אם היא חמורה במיוחד)</t>
+  </si>
+  <si>
+    <t>:
+- שיח אלים או תוקפני
+- ביטויי שנאה (גזענות, שנאת נשים, הכללות פוגעניות וכו')
+תפיסות בעייתיות לגבי זוגיות (שליטה, חוסר כבוד, החפצה)
+- אגרסיביות או נוקשות חריגה בשיח</t>
+  </si>
+  <si>
+    <t>ערכים ≠ שמרנות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר ברמת מעורבות פוליטית (זו תכונה נפרדת)
+- חשוב מאוד - כשיש סיגנל חזק אנחנו לא בהכרח מעלים את הציון! אנחנו מעלים או מורידים אותו בהתאם לכיוון הסיגנל.  לדוגמה: חברות באחים לנשק - סיגנל חזק לשמאל = הורדת ציון. לעומת חברות באם תרצו = סיגנל חזק לימין</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא כל תשובה מוזרה היא טרוליות
+- לא כל הומור הוא טרוליות
+- לא כל חוסר עקביות הוא טרוליות
+- יש להבחין בין בלבול, חוסר ריכוז או סגנון מיוחד — לבין כוונה ברורה לא לשתף פעולה</t>
+  </si>
+  <si>
+    <t>זיהוי דיל ברייקרס פוטנציאליים
+.
+ מאפיינים משמעותיים אצל המשתמש שעלולים להוות דיל ברייקר עבור חלק מהאנשים — לצורך התאמה טובה יותר והימנעות מחוסר התאמה.
+יש להחזיר:
+1. רשימה של דיל ברייקרס מתוך רשימה מוגדרת בלבד
+2. תיאור טקסטואלי קצר (אם יש מה להוסיף)---
+אין לתת ציון
+רשימת דיל ברייקרס אפשריים:
+- lives_with_parents (גר עם ההורים)
+- divorced (גרוש/ה)
+- has_children (יש ילדים)
+- has_pets (יש לו בעל חיים)
+- dislikes_pets (שונא/לא מסתדר עם בעלי חיים)
+חוקים:
+-אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
+- אם אין אינדיקציה ברורה → להחזיר ריק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אין להוסיף פריטים שלא מופיעים ברשימה
+- אין לנחש או להסיק ללא בסיס ברור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת אינטליגנציה מחשבתית (לא רגשית).
+עד כמה המשתמש חזק בהסקה לוגית, בעל כושר ניסוח ובכללי - אינטליגנט.
+אין למצע ציונים ואין לתת ציון מעל הממוצע כברירת מחדל
+יש להגדיר ולהעריך  weight_for_match  אם המשתמש מביע חשיבות לאינטליגנציה אצל בן/בת זוג. </t>
+  </si>
+  <si>
+    <t>הערכת אינטליגנציה רגשית.
+עד כמה המשתמש מבין רגשות של אחרים ומנהל אינטראקציות רגשיות בצורה בוגרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+רמת ההשכלה והמסלול המקצועי של המשתמש — כולל סוג העיסוק, רמת מקצועיות והישגים
+ .
+ציון גבוה = השכלה/מקצוע ברמה גבוהה יותר  
+ציון נמוך = פחות השכלה פורמלית או מקצוע פחות דורש הכשרה
+לדוגמה - רופאים, מהנדסי תוכנה, טייסים וכו' - יקבלו ציונים גבוהים במיוחד. לעומת זאת - ירקן / עובד מאפייה - משהו פשוט כזה - יקבל ציון נמוך. 
+מקצועות הדורשים השכלה גבוהה או הכשרה מקצועית משמעותית (כגון הייטק, רפואה, הנדסה וכו') → ציון גבוה.
+מקצועות ללא השכלה פורמלית או מסלול מקצועי ברור → ציון נמוך.
+אל תחשוש לתת ציון נמוך במידת הצורך. לא למצע ולא להגדיל סתם
+יש להגדיר ולהעריך weight_for_match  אם המשתמש מביע חשיבות למקצוע או להכשרה התעסוקתית או ל"מוצלחות" של הצד השני</t>
+  </si>
+  <si>
+    <t>הערכת יציבות רגשית.
+עד כמה עולמו הרגשי של המשתמש יציב ומאוזן, לעומת נטייה למצבי רוח קיצוניים, רגשות שליליים חזקים, חרדה, דכדוך, דרמה רגשית או סערות נפשיות.
+- חשוב במיוחד לזהות נטייה לקצוות רגשיים, כובד רגשי, חרדתיות, ודפוסים של דרמה או תנודתיות</t>
+  </si>
+  <si>
+    <t>הערכת נהנתנות (אהבה לבילויים וחוויות).
+עד כמה המשתמש נהנה, מחפש ומעריך חוויות מהנות בחיים — כמו בילויים, מסעדות, טיולים, יציאות, וחוויות חדשות — ועד כמה זה חלק מרכזי מהערכים ואורח החיים שלו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה חשוב לו "ליהנות מהחיים"
+- רצון לחוויות (טיולים, אוכל, בילויים, יציאות)
+- עד כמה הוא מחפש אקטיבית חוויות ולא רק זורם אם יש
+- תיאורים של אורח חיים עשיר בחוויות לעומת שגרה שקטה וביתית</t>
+  </si>
+  <si>
+    <t>הערכת רמת דתיות
+עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
+ יש להעריך את הרצף בין חילוני, מסורתי ודתי
+ככל שמידת הדתיות גבוהה יותר - נגדיר ציון גבוה יותר</t>
+  </si>
+  <si>
+    <t>הערכת משפחתיות כלפי משפחת המוצא.
+עד כמה משפחת המוצא של המשתמש (ובעיקר ההורים) תופסת מקום מרכזי, נוכח ומשפיע בחייו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- סקרנות ורצון לנסות דברים חדשים
+- פתיחות לרעיונות, תפיסות וסגנונות חיים שונים
+- משיכה לחוויות חדשות או לא שגרתיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה אנליטית.
+מודד עד כמה המשתמש נוטה לחשיבה אנליטית — כלומר פירוק, ניתוח והבנה לוגית של דברים — לעומת חשיבה אינטואיטיבית או זורמת.
+</t>
+  </si>
+  <si>
+    <t>הערכת רצינות לגבי החיים
+התכונה מודדת עד כמה המשתמש ניגש לחיים בצורה אחראית, ממוקדת ומחויבת — עם שאיפות, מסגרת ועשייה, ועושה "את מה שצריך" — לעומת גישה קלילה, זורמת ופחות מחויבת.
+אין קשר למידת הרצינות לגבי חיפוש קשר ווגם לא בהכרח לרצון להקים משפחה בעתיד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר בכובד או חוסר הומור  
+- אדם יכול להיות קליל ונעים ועדיין מאוד רציני לגבי החיים  
+- לא למדוד כאן אינטליגנציה או עומק  
+- לא מדובר ברצון לקשר רציני, אלא רצינות כלפי החיים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה פוליטית
+מיקומו של המשתמש על הציר הפוליטי — משמאל לימין — בהתאם לעמדות או רמזים פוליטיים שהוא מבטא.
+כאשר הסקאלה נעה בין שמאל קיצוני (0-10), שמאל (10-40), מרכז (40-60), ימין (60-90) וימין קיצוני (90-100)
+אם אין לך מושג לגבי נטיה פוליטית ולא הצלחת לנחש ממאפיינים אחרים או הוייב הכללי - נעדיף לתת ממוצע - 50.
+כך בחשבון שהממשלה הנוכחית היא ימנית, ולכן אם משתמש מביע ביקורת/תמיכה בה - נוריד/נעלה את הציון בהתאם
+. . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא למדוד כאן שמאל/ימין או עמדות ספציפיות
+</t>
+  </si>
+  <si>
+    <t>הערכת גישה חיובית (אופטימיות)
+עד כמה המשתמש נוטה לגישה חיובית, אופטימית וקלילה לחיים, לעומת גישה שלילית, ביקורתית או פסימית.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מעורבות פוליטית
+עד כמה פוליטיקה מהווה חלק מרכזי ומשמעותי בחיי המשתמש — ברמת העניין, המעורבות והחשיבות שהוא נותן לנושא
+אם אין לנו מושג לגבי מידת הפוליטיות ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מעורבות חברתית (אקטיביזם)
+עד כמה המשתמש מעורב, אקטיבי ופועל בנושאים חברתיים — כמו התנדבות, פעילות חברתית, מחאה או עיסוק בתיקון חברתי — ועד כמה זה חלק מהזהות וסגנון החיים שלו.
+אם אין לנו מושג לגבי מידת המעורבות החברתית ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
+  </si>
+  <si>
+    <t>הערכת לבביות וחום אנושי
+עד כמה המשתמש חם, נעים, מפרגן ומקרין יחס חיובי ואוהב כלפי אחרים.</t>
+  </si>
+  <si>
+    <t>הערכת טיפוס מסיבתי (סגנון חיי לילה).
+עד כמה סגנון החיים של המשתמש כולל חיי לילה, מסיבות, ליינים ותרבות בילוי מסיבתית, ועד כמה זה חלק מרכזי בזהות ובשגרה שלו.
+לא מדובר בכמה הוא נהנה ממסיבות באופן כללי, אלא האם זה סגנון חיים קבוע ומשמעותי.
+אם אין אינדיקציה מיוחדת על טיפוס מסיבתי ולא ניתן לנחש מהוייב והתכונות האחרות - נניח ציון נמוך עם סבירות נמוכה</t>
+  </si>
+  <si>
+    <t>הערכת אהבה לבעלי חיים
+עד כמה המשתמש אוהב, מחובר ונוח עם בעלי חיים — ועד כמה נוכחות של בעלי חיים מתאימה לו בחיים.
+- יש להבין את ההקשר (חיובי / שלילי / ניטרלי)
+- אזכור שלילי (פחד, דיל ברייקר) → ציון נמוך
+- אזכור חיובי עם מעורבות (למשל יש כלב) → ציון גבוה
+חוקים:
+- אם המשתמש מציין שיש לו חיית מחמד או קשר חזק לבעלי חיים → העלה ציון משמעותית
+- אם המשתמש מבטא פחד, רתיעה או דיל ברייקר → הורד ציון משמעותית
+- אם יש רק אזכור טכני של בעלי חיים → אל תסיק מכך ציון גבוה
+- יש להתחשב בכיוון האמירה (חיובי / שלילי)
+בהיעדר מידע מוחלט נניח ציון ממוצע - 50.</t>
+  </si>
+  <si>
+    <t>הערכת צמחונות / טבעונות
+הרגלי התזונה של המשתמש ביחס לצריכת בעלי חיים — החל מאכילת בשר רגילה ועד צמחונות או טבעונות.
+ציון גבוה = יותר צמחוני/טבעוני  
+ציון נמוך = אוכל בשר באופן רגיל
+חוקים:
+- אם המשתמש מציין חיבה מיוחדת לבשר - ציון נמוך מאוד
+- אם המשתמש מציין שהוא צמחוני או טבעוני - ציון גבוה מאוד.
+בהיעדר מידע מוחלט- נעדיף לנחש לכיוון האמצע</t>
+  </si>
+  <si>
+    <t>הערכת ציונות ואהבת המדינה
+עד כמה המשתמש מחובר רגשית וערכית למדינה — כולל תחושת שייכות, אהבת הארץ ורצון לפעול למען המדינה
+בהיעדר מידע מוחלט - נעדיף לנחש לכיוון האמצע</t>
+  </si>
+  <si>
+    <t>הערכת רגישות למראה חיצוני.
+עד כמה המראה החיצוני של בן/בת זוג הוא גורם חשוב ומשמעותי עבור המשתמש.
+- יש להבחין בין העדפה ("נחמד אם") לבין דרישה ("חייב/ת")
+- יש להתחשב בטון — נוקשות מול גמישות
+חוקים:
+- אם המשתמש נותן דרישות חד משמעיות או דיל ברייקרים → העלה ציון משמעותית
+- אם המשתמש חוזר על הנושא או מדגיש אותו → העלה ציון
+- אם יש רק העדפות כלליות → שמור על ציון בינוני
+בהיעדר מידע מוחלט - ננחש ציון בינוני</t>
+  </si>
+  <si>
+    <t>הערכת היפסטריות (סגנון אינדי/אלטרנטיבי
+עד כמה המשתמש משדר סגנון וטעם תרבותי אלטרנטיבי, אינדי או "היפסטרי" — כלומר העדפה לדברים לא מיינסטרימיים, נישתיים או ייחודיים
+בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה יחסית</t>
+  </si>
+  <si>
+    <t>הערכת גיקיות (חיבור לתרבות גיקית)
+עד כמה המשתמש מתחבר לעולמות תוכן המזוהים עם תרבות גיקית — כמו טכנולוגיה, גיימינג, מדע בדיוני, פנטזיה, קומיקס או תחומי עניין דומים.
+ציון גבוה = יותר גיק  
+ציון נמוך = לא גיק
+בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת היפיות (סגנון רוחני־אלטרנטיבי)
+עד כמה המשתמש מתחבר לסגנון חיים "היפי" — הכולל עניין ברוחניות, סדנאות, התפתחות אישית, טבע וטבעיות.
+ציון גבוה = יותר היפי  
+ציון נמוך = לא היפי
+בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה
+</t>
+  </si>
+  <si>
+    <t>הערכת סגנון תרבותי־רוסי (יוצאי ברה״מ)..
+ציון גבוה = סגנון רוסי מובהק  
+ציון נמוך = לא מזוהה עם הסגנון
+חוקים:
+- אם המשתמש מציין מוצא רוסי/אוקראיני → העלה ציון משמעותית
+- אם יש גם הזדהות תרבותית → העלה ציון עוד יותר
+בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זיהוי רעילות (התנהגות מסוכנת).
+המטרה לזהות משתמשים שמבטאים רמות גבוהות של רעילות, תוקפנות או התנהגות שעלולה להיות בעייתית במערכת — לצורך ניטור ובקרה בלבד
+תכונה זו אינה מיועדת להתאמה אלא להערכת סיכון 
+חוקים:
+- אם יש ביטוי קיצוני (אלימות, גזענות ברורה וכו') → העלה ציון משמעותית
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך.
+בהיעדר מידע מוחלט - נניח רעילות נמוכה בסבירות נמוכה. אם לאחר שיחה שלמה לא זיהינו רעילות - אפשר להניח גם רעילות נמוכה בסבירות בינונית.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זיהוי טרוליות.
+לזהות האם המשתמש באמת מחפש שידוך ומשתף פעולה עם המערכת, או שמא הוא עונה בצורה לא כנה, ממציא, משחק עם המערכת או מטריל אותה
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת סחיות (מידת מיינסטרים וקונפורמיות).
+הגדרה:
+סחיות = שילוב של מיינסטרים + קונפורמיות + גישה נורמטיבית לחיים
+עד כמה המשתמש נוטה למיינסטרים, לנורמות מקובלות ולגישה "רגילה" לחיים, לעומת ייחודיות, פתיחות וסטייה מהנורמה.
+חוקים:
+- יש להעריך לפי הקשר תרבותי ישראלי
+- אם המשתמש מציג חשיבה עצמאית או חריגה → הורד ציון
+- אם המשתמש מדגיש "נורמלי", "רגיל", "מסודר", "קלאסי" → העלה ציון
+- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת סגנון מזרחי (עממיות תרבותית־סגנונית)
+.
+ציון גבוה = סגנון מזרחי מובהק  
+ציון נמוך = סגנון פחות מזרחי / יותר סלקטיבי או נישתי
+עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן
+חוקים:
+- אם המשתמש משדר סגנון עממי, פתוח, מחובר לתרבות פופולרית → העלה ציון
+- אם יש אינדיקציות לטעם וסגנון המזוהים עם וייב מזרחי → העלה ציון
+- אם המשתמש משדר סגנון נישתי, סלקטיבי או מובחן → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת שמרנות ערכית-חברתית.
+עד כמה המשתמש מחזיק בגישה שמרנית ומיושנת לעומת ליברלית/פתוחה בנושאים של זוגיות, מגדר ונורמות חברתיות
+ציון גבוה = שמרני - פרימיטיבי  
+ציון נמוך = ליברלי / מתירני
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת אינטלקטואליות.
+עד כמה המשתמש נוטה לשיח רעיוני, עומק מחשבתי והתעניינות בנושאים מופשטים, לעומת שיח פרקטי, יומיומי ופשוט. עד כמה הוא עוסק בנושאים אינטלקטואלים - ספרים וכדומה
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת וייב ילדותי לעומת בוגר
+הסגנון והוייב הכללי של המשתמש — עד כמה הוא נוטה לוייב ילדותי (playful, חמוד, נאיבי בסגנון) לעומת וייב בוגר יותר..
+ציון גבוה = יותר וייב ילדותי  
+ציון נמוך = יותר וייב בוגר
+חוקים:
+- אם יש תחושה כללית של playful, חמידות או אלמנטים ילדותיים → העלה ציון
+- אם הסגנון מרגיש בוגר, מאופק או "grown-up" → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה לציות למסגרות (״ילד טוב״)
+עד כמה המשתמש נוטה לפעול לפי חוקים, מסגרות ונורמות — לעומת גישה גמישה יותר, שבה חוקים הם בגדר המלצה וניתן לעגל פינות.  
+ציון גבוה = יותר "ילד טוב" (ציות גבוה)  
+ציון נמוך = יותר גמיש/מרדן
+אם המשתמש נותן וייב של מישהו שבטח המורות ממש אהבו בבית הספר - העלה את הציון, אחרת - תוריד.
+בהיעדר מידע מוחלט - ננחש לפי הוייב והסגנון של המשתמש
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t>זיהוי זהות מגדרית לא סטנדרטית
+לזהות האם המשתמש הצהיר באופן מפורש על היותו טרנס/ית או א-מיני.
+חוקים:
+- רק הצהרה מפורשת → ציון גבוה
+- אם אין מידע מתוך הרבה טקסט (נגיד בסיום השאלון) - אפשר לתת ציון נמוך בסבירות די גבוהה - נגיד 0.5</t>
+  </si>
+  <si>
+    <t>זהויות מגדריות שונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אין להסיק זהות מגדרית או מינית ללא הצהרה מפורשת
+- אין לנחש על בסיס סגנון, שפה או התנהגות
+- מדובר רק במה שהמשתמש בחר לשתף באופן ברור
+- אין להסיק זהות על בסיס משיכה לגבר/אישה! אין קשר למשיכה, רק טרנס/ית או א-מיני. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3325,6 +3941,20 @@
       <family val="2"/>
       <charset val="177"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <charset val="177"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3358,7 +3988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3463,6 +4093,39 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3985,6 +4648,228 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="I4" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" t="s">
+        <v>238</v>
+      </c>
+      <c r="L4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="L5" s="19" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12">
+        <v>4541</v>
+      </c>
+      <c r="B12">
+        <v>221</v>
+      </c>
+      <c r="C12">
+        <v>844</v>
+      </c>
+      <c r="D12">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" s="29">
+        <v>46075</v>
+      </c>
+      <c r="I12">
+        <v>60</v>
+      </c>
+      <c r="J12">
+        <v>50</v>
+      </c>
+      <c r="K12">
+        <f>(J12+I12)/2</f>
+        <v>55</v>
+      </c>
+      <c r="L12">
+        <f>0.3*K12+0.7*D12</f>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="N12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="D13">
+        <v>90</v>
+      </c>
+      <c r="K13">
+        <v>55</v>
+      </c>
+      <c r="L13">
+        <f>0.3*K13+0.7*D13</f>
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="D14">
+        <v>90</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <f>0.3*K14+0.7*D14</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <f>0.3*K15+0.7*D15</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="D16">
+        <v>70</v>
+      </c>
+      <c r="K16">
+        <v>70</v>
+      </c>
+      <c r="L16">
+        <f>0.3*K16+0.7*D16</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4146,7 +5031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4296,7 +5181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4341,7 +5226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6137,6 +7022,1436 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
+  <dimension ref="A1:N51"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="52.5546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="29.5546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="59" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="17.77734375" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="C2" s="28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="27.6">
+      <c r="A4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="110.4">
+      <c r="A5" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="42">
+        <v>0.7</v>
+      </c>
+      <c r="I5" s="42">
+        <v>10</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="42">
+        <v>20</v>
+      </c>
+      <c r="M5" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="N5" s="44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="55.2">
+      <c r="A6" s="49" t="s">
+        <v>443</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>425</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="21"/>
+    </row>
+    <row r="7" spans="1:14" ht="317.39999999999998">
+      <c r="A7" s="40"/>
+      <c r="B7" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="N7" s="21"/>
+    </row>
+    <row r="8" spans="1:14" ht="262.2">
+      <c r="A8" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="96.6">
+      <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="262.2">
+      <c r="B10" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>563</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="138">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E11" s="33"/>
+      <c r="F11" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="N11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="110.4">
+      <c r="A12" s="40"/>
+      <c r="B12" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="138">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E13" s="45"/>
+      <c r="F13" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="110.4">
+      <c r="A14" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="124.2">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="E15" s="33"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="110.4">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="193.2">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" ht="248.4">
+      <c r="A18" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" ht="207">
+      <c r="A19" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="82.8">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" ht="124.2">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" ht="193.2">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="193.2">
+      <c r="B23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>571</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I23" s="2">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="110.4">
+      <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>547</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>588</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I24" s="2">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" ht="124.2">
+      <c r="A25" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:14" ht="82.8">
+      <c r="A26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" ht="138">
+      <c r="A27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I27" s="2">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" ht="151.80000000000001">
+      <c r="A28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I28" s="2">
+        <v>4</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="262.2">
+      <c r="A29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" ht="82.8">
+      <c r="B30" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" ht="193.2">
+      <c r="B31" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="207">
+      <c r="B32" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="207">
+      <c r="A33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:14" ht="124.2">
+      <c r="B34" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>559</v>
+      </c>
+      <c r="F34" s="33"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="151.80000000000001">
+      <c r="B35" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>565</v>
+      </c>
+      <c r="F35" s="33"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="165.6">
+      <c r="B36" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I36" s="2">
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="193.2">
+      <c r="A37" s="51"/>
+      <c r="B37" s="41" t="s">
+        <v>436</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I37" s="2">
+        <v>3</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="248.4">
+      <c r="A38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="110.4">
+      <c r="A39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39">
+        <v>0.4</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="138">
+      <c r="A40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="33" t="s">
+        <v>612</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M40" s="19"/>
+      <c r="N40" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="331.2">
+      <c r="A41" s="40" t="s">
+        <v>275</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="33" t="s">
+        <v>574</v>
+      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N41" s="34"/>
+    </row>
+    <row r="42" spans="1:14" ht="360">
+      <c r="B42" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="C44" s="36" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="69">
+      <c r="A45" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="I45" s="2">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="27.6">
+      <c r="A46" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I46" s="2">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="55.2">
+      <c r="A47" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I47" s="2">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="1:14" ht="41.4">
+      <c r="A48" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I48" s="2">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" ht="27.6">
+      <c r="A49" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" ht="151.80000000000001">
+      <c r="B50" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>557</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I50" s="2">
+        <v>2</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="165.6">
+      <c r="B51" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>561</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I51" s="2">
+        <v>3</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6416,7 +8731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6713,7 +9028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7063,7 +9378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7678,7 +9993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7961,226 +10276,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="10.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="I4" t="s">
-        <v>227</v>
-      </c>
-      <c r="K4" t="s">
-        <v>238</v>
-      </c>
-      <c r="L4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="L5" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12">
-        <v>4541</v>
-      </c>
-      <c r="B12">
-        <v>221</v>
-      </c>
-      <c r="C12">
-        <v>844</v>
-      </c>
-      <c r="D12">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" t="s">
-        <v>220</v>
-      </c>
-      <c r="G12" t="s">
-        <v>221</v>
-      </c>
-      <c r="H12" s="29">
-        <v>46075</v>
-      </c>
-      <c r="I12">
-        <v>60</v>
-      </c>
-      <c r="J12">
-        <v>50</v>
-      </c>
-      <c r="K12">
-        <f>(J12+I12)/2</f>
-        <v>55</v>
-      </c>
-      <c r="L12">
-        <f>0.3*K12+0.7*D12</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="N12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="D13">
-        <v>90</v>
-      </c>
-      <c r="K13">
-        <v>55</v>
-      </c>
-      <c r="L13">
-        <f>0.3*K13+0.7*D13</f>
-        <v>79.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="D14">
-        <v>90</v>
-      </c>
-      <c r="K14">
-        <v>20</v>
-      </c>
-      <c r="L14">
-        <f>0.3*K14+0.7*D14</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="D15">
-        <v>100</v>
-      </c>
-      <c r="K15">
-        <v>10</v>
-      </c>
-      <c r="L15">
-        <f>0.3*K15+0.7*D15</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="D16">
-        <v>70</v>
-      </c>
-      <c r="K16">
-        <v>70</v>
-      </c>
-      <c r="L16">
-        <f>0.3*K16+0.7*D16</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="14"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC03644-A9C4-41C7-AC93-92BA8928AC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3385E088-2784-4C42-8DF1-574559399A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="635">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3231,37 +3231,10 @@
 התבסס על מידע מפורש שהמשתמש נתן במהלך השיחה.</t>
   </si>
   <si>
-    <t>זיהוי יתרונות פוטנציאליים.
-אין לתת ציון.
-יש להחזיר:
-1. רשימה של יתרונות מתוך רשימה מוגדרת בלבד
-2. תיאור טקסטואלי קצר (אם יש מה להוסיף)
-רשימת יתרונות אפשריים:
-- has_pets (יש לו בעל חיים)
-- has_children (יש ילדים)
-- divorced (גרוש/ה)
-- plays_music (מנגן)
-- into_fitness (עוסק בבריאות וכושר)
-- high_income (הכנסה גבוהה)
-- high_education (השכלה גבוהה)
-חוקים:
-- אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
-- אין צורך ביותר ממאפיין אחד — גם אחד מספיק
-- אם אין אינדיקציה ברורה → להחזיר ריק
-- אין להחזיר ערכים על בסיס השערה</t>
-  </si>
-  <si>
     <t>נחמדות / חום / חברותיות ≠ אינטליגנציה רגשית</t>
   </si>
   <si>
     <t xml:space="preserve">הבחנות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
-- עד כמה הדעות שלו נפוצות ונורמטיביות
-- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
-- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -3408,15 +3381,6 @@
 - לא להסיק מהזכרת ישראל בלבד</t>
   </si>
   <si>
-    <t xml:space="preserve">
-- אמירות פוליטיות מפורשות
-- הזדהות עם מחנות או עמדות
-- רמזים עקיפים אך ברורים לעמדות פוליטיות
-- נושאים ערכיים עם זיקה פוליטית ברורה
- - פעילות בארגון בעל זיהוי פוליטי/מחאתי היא סיגנל חזק
-- ביקורת על הממשלה או תמיכה בממשלה תהווה סיגנל ברור</t>
-  </si>
-  <si>
     <t>הערכת מוסר עבודה
 עד כמה המשתמש רציני, מחויב ומשקיע בעבודה או בעשייה שלו — ועד כמה יש לו גישה של התמדה, אחריות ורצון לעשות דברים כמו שצריך.
 חוקים:
@@ -3467,21 +3431,6 @@
 - מדובר בהזדהות תרבותית־סגנונית ספציפית</t>
   </si>
   <si>
-    <t>:
-- טעם מוזיקלי (חיבור למוזיקה מזרחית)
-- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
-- וייב כללי של חום, פתיחות ונגישות
-- חיבור לתרבות פופולרית רחבה
-- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
-- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
-- זהות מוצהרת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- לא מדובר באינטליגנציה, קלילות או נהנתנות
-- לא מדובר רק במיינסטרים — אלא בסגנון תרבותי ספציפי</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 - תחומי עניין (משחקי מחשב, פנטזיה, מד״ב, קומיקס, אנימה וכו')
 - חיבור לטכנולוגיה מעבר לשימוש רגיל
@@ -3519,15 +3468,242 @@
   </si>
   <si>
     <t xml:space="preserve">
-- לא מדובר ברמת מעורבות פוליטית (זו תכונה נפרדת)
-- חשוב מאוד - כשיש סיגנל חזק אנחנו לא בהכרח מעלים את הציון! אנחנו מעלים או מורידים אותו בהתאם לכיוון הסיגנל.  לדוגמה: חברות באחים לנשק - סיגנל חזק לשמאל = הורדת ציון. לעומת חברות באם תרצו = סיגנל חזק לימין</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
 - לא כל תשובה מוזרה היא טרוליות
 - לא כל הומור הוא טרוליות
 - לא כל חוסר עקביות הוא טרוליות
 - יש להבחין בין בלבול, חוסר ריכוז או סגנון מיוחד — לבין כוונה ברורה לא לשתף פעולה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אין להוסיף פריטים שלא מופיעים ברשימה
+- אין לנחש או להסיק ללא בסיס ברור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת אינטליגנציה מחשבתית (לא רגשית).
+עד כמה המשתמש חזק בהסקה לוגית, בעל כושר ניסוח ובכללי - אינטליגנט.
+אין למצע ציונים ואין לתת ציון מעל הממוצע כברירת מחדל
+יש להגדיר ולהעריך  weight_for_match  אם המשתמש מביע חשיבות לאינטליגנציה אצל בן/בת זוג. </t>
+  </si>
+  <si>
+    <t>הערכת אינטליגנציה רגשית.
+עד כמה המשתמש מבין רגשות של אחרים ומנהל אינטראקציות רגשיות בצורה בוגרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+רמת ההשכלה והמסלול המקצועי של המשתמש — כולל סוג העיסוק, רמת מקצועיות והישגים
+ .
+ציון גבוה = השכלה/מקצוע ברמה גבוהה יותר  
+ציון נמוך = פחות השכלה פורמלית או מקצוע פחות דורש הכשרה
+לדוגמה - רופאים, מהנדסי תוכנה, טייסים וכו' - יקבלו ציונים גבוהים במיוחד. לעומת זאת - ירקן / עובד מאפייה - משהו פשוט כזה - יקבל ציון נמוך. 
+מקצועות הדורשים השכלה גבוהה או הכשרה מקצועית משמעותית (כגון הייטק, רפואה, הנדסה וכו') → ציון גבוה.
+מקצועות ללא השכלה פורמלית או מסלול מקצועי ברור → ציון נמוך.
+אל תחשוש לתת ציון נמוך במידת הצורך. לא למצע ולא להגדיל סתם
+יש להגדיר ולהעריך weight_for_match  אם המשתמש מביע חשיבות למקצוע או להכשרה התעסוקתית או ל"מוצלחות" של הצד השני</t>
+  </si>
+  <si>
+    <t>הערכת יציבות רגשית.
+עד כמה עולמו הרגשי של המשתמש יציב ומאוזן, לעומת נטייה למצבי רוח קיצוניים, רגשות שליליים חזקים, חרדה, דכדוך, דרמה רגשית או סערות נפשיות.
+- חשוב במיוחד לזהות נטייה לקצוות רגשיים, כובד רגשי, חרדתיות, ודפוסים של דרמה או תנודתיות</t>
+  </si>
+  <si>
+    <t>הערכת נהנתנות (אהבה לבילויים וחוויות).
+עד כמה המשתמש נהנה, מחפש ומעריך חוויות מהנות בחיים — כמו בילויים, מסעדות, טיולים, יציאות, וחוויות חדשות — ועד כמה זה חלק מרכזי מהערכים ואורח החיים שלו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה חשוב לו "ליהנות מהחיים"
+- רצון לחוויות (טיולים, אוכל, בילויים, יציאות)
+- עד כמה הוא מחפש אקטיבית חוויות ולא רק זורם אם יש
+- תיאורים של אורח חיים עשיר בחוויות לעומת שגרה שקטה וביתית</t>
+  </si>
+  <si>
+    <t>הערכת משפחתיות כלפי משפחת המוצא.
+עד כמה משפחת המוצא של המשתמש (ובעיקר ההורים) תופסת מקום מרכזי, נוכח ומשפיע בחייו.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- סקרנות ורצון לנסות דברים חדשים
+- פתיחות לרעיונות, תפיסות וסגנונות חיים שונים
+- משיכה לחוויות חדשות או לא שגרתיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה אנליטית.
+מודד עד כמה המשתמש נוטה לחשיבה אנליטית — כלומר פירוק, ניתוח והבנה לוגית של דברים — לעומת חשיבה אינטואיטיבית או זורמת.
+</t>
+  </si>
+  <si>
+    <t>הערכת רצינות לגבי החיים
+התכונה מודדת עד כמה המשתמש ניגש לחיים בצורה אחראית, ממוקדת ומחויבת — עם שאיפות, מסגרת ועשייה, ועושה "את מה שצריך" — לעומת גישה קלילה, זורמת ופחות מחויבת.
+אין קשר למידת הרצינות לגבי חיפוש קשר ווגם לא בהכרח לרצון להקים משפחה בעתיד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא מדובר בכובד או חוסר הומור  
+- אדם יכול להיות קליל ונעים ועדיין מאוד רציני לגבי החיים  
+- לא למדוד כאן אינטליגנציה או עומק  
+- לא מדובר ברצון לקשר רציני, אלא רצינות כלפי החיים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- לא למדוד כאן שמאל/ימין או עמדות ספציפיות
+</t>
+  </si>
+  <si>
+    <t>הערכת גישה חיובית (אופטימיות)
+עד כמה המשתמש נוטה לגישה חיובית, אופטימית וקלילה לחיים, לעומת גישה שלילית, ביקורתית או פסימית.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מעורבות פוליטית
+עד כמה פוליטיקה מהווה חלק מרכזי ומשמעותי בחיי המשתמש — ברמת העניין, המעורבות והחשיבות שהוא נותן לנושא
+אם אין לנו מושג לגבי מידת הפוליטיות ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מעורבות חברתית (אקטיביזם)
+עד כמה המשתמש מעורב, אקטיבי ופועל בנושאים חברתיים — כמו התנדבות, פעילות חברתית, מחאה או עיסוק בתיקון חברתי — ועד כמה זה חלק מהזהות וסגנון החיים שלו.
+אם אין לנו מושג לגבי מידת המעורבות החברתית ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
+  </si>
+  <si>
+    <t>הערכת לבביות וחום אנושי
+עד כמה המשתמש חם, נעים, מפרגן ומקרין יחס חיובי ואוהב כלפי אחרים.</t>
+  </si>
+  <si>
+    <t>הערכת טיפוס מסיבתי (סגנון חיי לילה).
+עד כמה סגנון החיים של המשתמש כולל חיי לילה, מסיבות, ליינים ותרבות בילוי מסיבתית, ועד כמה זה חלק מרכזי בזהות ובשגרה שלו.
+לא מדובר בכמה הוא נהנה ממסיבות באופן כללי, אלא האם זה סגנון חיים קבוע ומשמעותי.
+אם אין אינדיקציה מיוחדת על טיפוס מסיבתי ולא ניתן לנחש מהוייב והתכונות האחרות - נניח ציון נמוך עם סבירות נמוכה</t>
+  </si>
+  <si>
+    <t>הערכת אהבה לבעלי חיים
+עד כמה המשתמש אוהב, מחובר ונוח עם בעלי חיים — ועד כמה נוכחות של בעלי חיים מתאימה לו בחיים.
+- יש להבין את ההקשר (חיובי / שלילי / ניטרלי)
+- אזכור שלילי (פחד, דיל ברייקר) → ציון נמוך
+- אזכור חיובי עם מעורבות (למשל יש כלב) → ציון גבוה
+חוקים:
+- אם המשתמש מציין שיש לו חיית מחמד או קשר חזק לבעלי חיים → העלה ציון משמעותית
+- אם המשתמש מבטא פחד, רתיעה או דיל ברייקר → הורד ציון משמעותית
+- אם יש רק אזכור טכני של בעלי חיים → אל תסיק מכך ציון גבוה
+- יש להתחשב בכיוון האמירה (חיובי / שלילי)
+בהיעדר מידע מוחלט נניח ציון ממוצע - 50.</t>
+  </si>
+  <si>
+    <t>הערכת צמחונות / טבעונות
+הרגלי התזונה של המשתמש ביחס לצריכת בעלי חיים — החל מאכילת בשר רגילה ועד צמחונות או טבעונות.
+ציון גבוה = יותר צמחוני/טבעוני  
+ציון נמוך = אוכל בשר באופן רגיל
+חוקים:
+- אם המשתמש מציין חיבה מיוחדת לבשר - ציון נמוך מאוד
+- אם המשתמש מציין שהוא צמחוני או טבעוני - ציון גבוה מאוד.
+בהיעדר מידע מוחלט- נעדיף לנחש לכיוון האמצע</t>
+  </si>
+  <si>
+    <t>הערכת ציונות ואהבת המדינה
+עד כמה המשתמש מחובר רגשית וערכית למדינה — כולל תחושת שייכות, אהבת הארץ ורצון לפעול למען המדינה
+בהיעדר מידע מוחלט - נעדיף לנחש לכיוון האמצע</t>
+  </si>
+  <si>
+    <t>הערכת רגישות למראה חיצוני.
+עד כמה המראה החיצוני של בן/בת זוג הוא גורם חשוב ומשמעותי עבור המשתמש.
+- יש להבחין בין העדפה ("נחמד אם") לבין דרישה ("חייב/ת")
+- יש להתחשב בטון — נוקשות מול גמישות
+חוקים:
+- אם המשתמש נותן דרישות חד משמעיות או דיל ברייקרים → העלה ציון משמעותית
+- אם המשתמש חוזר על הנושא או מדגיש אותו → העלה ציון
+- אם יש רק העדפות כלליות → שמור על ציון בינוני
+בהיעדר מידע מוחלט - ננחש ציון בינוני</t>
+  </si>
+  <si>
+    <t>הערכת היפסטריות (סגנון אינדי/אלטרנטיבי
+עד כמה המשתמש משדר סגנון וטעם תרבותי אלטרנטיבי, אינדי או "היפסטרי" — כלומר העדפה לדברים לא מיינסטרימיים, נישתיים או ייחודיים
+בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה יחסית</t>
+  </si>
+  <si>
+    <t>הערכת גיקיות (חיבור לתרבות גיקית)
+עד כמה המשתמש מתחבר לעולמות תוכן המזוהים עם תרבות גיקית — כמו טכנולוגיה, גיימינג, מדע בדיוני, פנטזיה, קומיקס או תחומי עניין דומים.
+ציון גבוה = יותר גיק  
+ציון נמוך = לא גיק
+בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת היפיות (סגנון רוחני־אלטרנטיבי)
+עד כמה המשתמש מתחבר לסגנון חיים "היפי" — הכולל עניין ברוחניות, סדנאות, התפתחות אישית, טבע וטבעיות.
+ציון גבוה = יותר היפי  
+ציון נמוך = לא היפי
+בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה
+</t>
+  </si>
+  <si>
+    <t>הערכת סגנון תרבותי־רוסי (יוצאי ברה״מ)..
+ציון גבוה = סגנון רוסי מובהק  
+ציון נמוך = לא מזוהה עם הסגנון
+חוקים:
+- אם המשתמש מציין מוצא רוסי/אוקראיני → העלה ציון משמעותית
+- אם יש גם הזדהות תרבותית → העלה ציון עוד יותר
+בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זיהוי רעילות (התנהגות מסוכנת).
+המטרה לזהות משתמשים שמבטאים רמות גבוהות של רעילות, תוקפנות או התנהגות שעלולה להיות בעייתית במערכת — לצורך ניטור ובקרה בלבד
+תכונה זו אינה מיועדת להתאמה אלא להערכת סיכון 
+חוקים:
+- אם יש ביטוי קיצוני (אלימות, גזענות ברורה וכו') → העלה ציון משמעותית
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך.
+בהיעדר מידע מוחלט - נניח רעילות נמוכה בסבירות נמוכה. אם לאחר שיחה שלמה לא זיהינו רעילות - אפשר להניח גם רעילות נמוכה בסבירות בינונית.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זיהוי טרוליות.
+לזהות האם המשתמש באמת מחפש שידוך ומשתף פעולה עם המערכת, או שמא הוא עונה בצורה לא כנה, ממציא, משחק עם המערכת או מטריל אותה
+- אם אין אינדיקציות ברורות → שמור על ציון נמוך
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת שמרנות ערכית-חברתית.
+עד כמה המשתמש מחזיק בגישה שמרנית ומיושנת לעומת ליברלית/פתוחה בנושאים של זוגיות, מגדר ונורמות חברתיות
+ציון גבוה = שמרני - פרימיטיבי  
+ציון נמוך = ליברלי / מתירני
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת אינטלקטואליות.
+עד כמה המשתמש נוטה לשיח רעיוני, עומק מחשבתי והתעניינות בנושאים מופשטים, לעומת שיח פרקטי, יומיומי ופשוט. עד כמה הוא עוסק בנושאים אינטלקטואלים - ספרים וכדומה
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת וייב ילדותי לעומת בוגר
+הסגנון והוייב הכללי של המשתמש — עד כמה הוא נוטה לוייב ילדותי (playful, חמוד, נאיבי בסגנון) לעומת וייב בוגר יותר..
+ציון גבוה = יותר וייב ילדותי  
+ציון נמוך = יותר וייב בוגר
+חוקים:
+- אם יש תחושה כללית של playful, חמידות או אלמנטים ילדותיים → העלה ציון
+- אם הסגנון מרגיש בוגר, מאופק או "grown-up" → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה לציות למסגרות (״ילד טוב״)
+עד כמה המשתמש נוטה לפעול לפי חוקים, מסגרות ונורמות — לעומת גישה גמישה יותר, שבה חוקים הם בגדר המלצה וניתן לעגל פינות.  
+ציון גבוה = יותר "ילד טוב" (ציות גבוה)  
+ציון נמוך = יותר גמיש/מרדן
+אם המשתמש נותן וייב של מישהו שבטח המורות ממש אהבו בבית הספר - העלה את הציון, אחרת - תוריד.
+בהיעדר מידע מוחלט - ננחש לפי הוייב והסגנון של המשתמש
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t>זיהוי זהות מגדרית לא סטנדרטית
+לזהות האם המשתמש הצהיר באופן מפורש על היותו טרנס/ית או א-מיני.
+חוקים:
+- רק הצהרה מפורשת → ציון גבוה
+- אם אין מידע מתוך הרבה טקסט (נגיד בסיום השאלון) - אפשר לתת ציון נמוך בסבירות די גבוהה - נגיד 0.5</t>
+  </si>
+  <si>
+    <t>זהויות מגדריות שונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- אין להסיק זהות מגדרית או מינית ללא הצהרה מפורשת
+- אין לנחש על בסיס סגנון, שפה או התנהגות
+- מדובר רק במה שהמשתמש בחר לשתף באופן ברור
+- אין להסיק זהות על בסיס משיכה לגבר/אישה! אין קשר למשיכה, רק טרנס/ית או א-מיני. </t>
   </si>
   <si>
     <t>זיהוי דיל ברייקרס פוטנציאליים
@@ -3543,286 +3719,189 @@
 - has_children (יש ילדים)
 - has_pets (יש לו בעל חיים)
 - dislikes_pets (שונא/לא מסתדר עם בעלי חיים)
+- childfree (אל-הורי/ת – לא מעוניין/ת בילדים)
+- smoker (מעשנ/ת)
+- polyamorous (פוליאמורי/ת)
+- open_relationship (בזוגיות פתוחה)
 חוקים:
 -אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
 - אם אין אינדיקציה ברורה → להחזיר ריק</t>
   </si>
   <si>
-    <t xml:space="preserve">
-- אין להוסיף פריטים שלא מופיעים ברשימה
-- אין לנחש או להסיק ללא בסיס ברור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת אינטליגנציה מחשבתית (לא רגשית).
-עד כמה המשתמש חזק בהסקה לוגית, בעל כושר ניסוח ובכללי - אינטליגנט.
-אין למצע ציונים ואין לתת ציון מעל הממוצע כברירת מחדל
-יש להגדיר ולהעריך  weight_for_match  אם המשתמש מביע חשיבות לאינטליגנציה אצל בן/בת זוג. </t>
-  </si>
-  <si>
-    <t>הערכת אינטליגנציה רגשית.
-עד כמה המשתמש מבין רגשות של אחרים ומנהל אינטראקציות רגשיות בצורה בוגרת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-רמת ההשכלה והמסלול המקצועי של המשתמש — כולל סוג העיסוק, רמת מקצועיות והישגים
- .
-ציון גבוה = השכלה/מקצוע ברמה גבוהה יותר  
-ציון נמוך = פחות השכלה פורמלית או מקצוע פחות דורש הכשרה
-לדוגמה - רופאים, מהנדסי תוכנה, טייסים וכו' - יקבלו ציונים גבוהים במיוחד. לעומת זאת - ירקן / עובד מאפייה - משהו פשוט כזה - יקבל ציון נמוך. 
-מקצועות הדורשים השכלה גבוהה או הכשרה מקצועית משמעותית (כגון הייטק, רפואה, הנדסה וכו') → ציון גבוה.
-מקצועות ללא השכלה פורמלית או מסלול מקצועי ברור → ציון נמוך.
-אל תחשוש לתת ציון נמוך במידת הצורך. לא למצע ולא להגדיל סתם
-יש להגדיר ולהעריך weight_for_match  אם המשתמש מביע חשיבות למקצוע או להכשרה התעסוקתית או ל"מוצלחות" של הצד השני</t>
-  </si>
-  <si>
-    <t>הערכת יציבות רגשית.
-עד כמה עולמו הרגשי של המשתמש יציב ומאוזן, לעומת נטייה למצבי רוח קיצוניים, רגשות שליליים חזקים, חרדה, דכדוך, דרמה רגשית או סערות נפשיות.
-- חשוב במיוחד לזהות נטייה לקצוות רגשיים, כובד רגשי, חרדתיות, ודפוסים של דרמה או תנודתיות</t>
-  </si>
-  <si>
-    <t>הערכת נהנתנות (אהבה לבילויים וחוויות).
-עד כמה המשתמש נהנה, מחפש ומעריך חוויות מהנות בחיים — כמו בילויים, מסעדות, טיולים, יציאות, וחוויות חדשות — ועד כמה זה חלק מרכזי מהערכים ואורח החיים שלו.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- עד כמה חשוב לו "ליהנות מהחיים"
-- רצון לחוויות (טיולים, אוכל, בילויים, יציאות)
-- עד כמה הוא מחפש אקטיבית חוויות ולא רק זורם אם יש
-- תיאורים של אורח חיים עשיר בחוויות לעומת שגרה שקטה וביתית</t>
-  </si>
-  <si>
-    <t>הערכת רמת דתיות
-עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
- יש להעריך את הרצף בין חילוני, מסורתי ודתי
-ככל שמידת הדתיות גבוהה יותר - נגדיר ציון גבוה יותר</t>
-  </si>
-  <si>
-    <t>הערכת משפחתיות כלפי משפחת המוצא.
-עד כמה משפחת המוצא של המשתמש (ובעיקר ההורים) תופסת מקום מרכזי, נוכח ומשפיע בחייו.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- סקרנות ורצון לנסות דברים חדשים
-- פתיחות לרעיונות, תפיסות וסגנונות חיים שונים
-- משיכה לחוויות חדשות או לא שגרתיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת נטייה אנליטית.
-מודד עד כמה המשתמש נוטה לחשיבה אנליטית — כלומר פירוק, ניתוח והבנה לוגית של דברים — לעומת חשיבה אינטואיטיבית או זורמת.
-</t>
-  </si>
-  <si>
-    <t>הערכת רצינות לגבי החיים
-התכונה מודדת עד כמה המשתמש ניגש לחיים בצורה אחראית, ממוקדת ומחויבת — עם שאיפות, מסגרת ועשייה, ועושה "את מה שצריך" — לעומת גישה קלילה, זורמת ופחות מחויבת.
-אין קשר למידת הרצינות לגבי חיפוש קשר ווגם לא בהכרח לרצון להקים משפחה בעתיד</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- לא מדובר בכובד או חוסר הומור  
-- אדם יכול להיות קליל ונעים ועדיין מאוד רציני לגבי החיים  
-- לא למדוד כאן אינטליגנציה או עומק  
-- לא מדובר ברצון לקשר רציני, אלא רצינות כלפי החיים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת נטייה פוליטית
-מיקומו של המשתמש על הציר הפוליטי — משמאל לימין — בהתאם לעמדות או רמזים פוליטיים שהוא מבטא.
-כאשר הסקאלה נעה בין שמאל קיצוני (0-10), שמאל (10-40), מרכז (40-60), ימין (60-90) וימין קיצוני (90-100)
-אם אין לך מושג לגבי נטיה פוליטית ולא הצלחת לנחש ממאפיינים אחרים או הוייב הכללי - נעדיף לתת ממוצע - 50.
-כך בחשבון שהממשלה הנוכחית היא ימנית, ולכן אם משתמש מביע ביקורת/תמיכה בה - נוריד/נעלה את הציון בהתאם
-. . </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- לא למדוד כאן שמאל/ימין או עמדות ספציפיות
-</t>
-  </si>
-  <si>
-    <t>הערכת גישה חיובית (אופטימיות)
-עד כמה המשתמש נוטה לגישה חיובית, אופטימית וקלילה לחיים, לעומת גישה שלילית, ביקורתית או פסימית.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת מעורבות פוליטית
-עד כמה פוליטיקה מהווה חלק מרכזי ומשמעותי בחיי המשתמש — ברמת העניין, המעורבות והחשיבות שהוא נותן לנושא
-אם אין לנו מושג לגבי מידת הפוליטיות ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת מעורבות חברתית (אקטיביזם)
-עד כמה המשתמש מעורב, אקטיבי ופועל בנושאים חברתיים — כמו התנדבות, פעילות חברתית, מחאה או עיסוק בתיקון חברתי — ועד כמה זה חלק מהזהות וסגנון החיים שלו.
-אם אין לנו מושג לגבי מידת המעורבות החברתית ולא הצלחנו לנחש לפי הוייב והתכונות האחרות - נניח ציון נמוך יחסית במידת סבירות נמוכה </t>
-  </si>
-  <si>
-    <t>הערכת לבביות וחום אנושי
-עד כמה המשתמש חם, נעים, מפרגן ומקרין יחס חיובי ואוהב כלפי אחרים.</t>
-  </si>
-  <si>
-    <t>הערכת טיפוס מסיבתי (סגנון חיי לילה).
-עד כמה סגנון החיים של המשתמש כולל חיי לילה, מסיבות, ליינים ותרבות בילוי מסיבתית, ועד כמה זה חלק מרכזי בזהות ובשגרה שלו.
-לא מדובר בכמה הוא נהנה ממסיבות באופן כללי, אלא האם זה סגנון חיים קבוע ומשמעותי.
-אם אין אינדיקציה מיוחדת על טיפוס מסיבתי ולא ניתן לנחש מהוייב והתכונות האחרות - נניח ציון נמוך עם סבירות נמוכה</t>
-  </si>
-  <si>
-    <t>הערכת אהבה לבעלי חיים
-עד כמה המשתמש אוהב, מחובר ונוח עם בעלי חיים — ועד כמה נוכחות של בעלי חיים מתאימה לו בחיים.
-- יש להבין את ההקשר (חיובי / שלילי / ניטרלי)
-- אזכור שלילי (פחד, דיל ברייקר) → ציון נמוך
-- אזכור חיובי עם מעורבות (למשל יש כלב) → ציון גבוה
+    <t>זיהוי יתרונות פוטנציאליים.
+אין לתת ציון.
+יש להחזיר:
+1. רשימה של יתרונות מתוך רשימה מוגדרת בלבד
+2. תיאור טקסטואלי קצר (אם יש מה להוסיף)
+רשימת יתרונות אפשריים:
+- has_pets (יש לו בעל חיים)
+- has_children (יש ילדים)
+- divorced (גרוש/ה)
+- plays_music (מנגן)
+- high_income (הכנסה גבוהה)
+- high_education (השכלה גבוהה)
+childfree (אל-הורי/ת – לא מעוניין/ת בילדים)
+smoker (מעשנ/ת)
+polyamorous (פוליאמורי/ת)
+open_relationship (בזוגיות פתוחה)
 חוקים:
-- אם המשתמש מציין שיש לו חיית מחמד או קשר חזק לבעלי חיים → העלה ציון משמעותית
-- אם המשתמש מבטא פחד, רתיעה או דיל ברייקר → הורד ציון משמעותית
-- אם יש רק אזכור טכני של בעלי חיים → אל תסיק מכך ציון גבוה
-- יש להתחשב בכיוון האמירה (חיובי / שלילי)
-בהיעדר מידע מוחלט נניח ציון ממוצע - 50.</t>
-  </si>
-  <si>
-    <t>הערכת צמחונות / טבעונות
-הרגלי התזונה של המשתמש ביחס לצריכת בעלי חיים — החל מאכילת בשר רגילה ועד צמחונות או טבעונות.
-ציון גבוה = יותר צמחוני/טבעוני  
-ציון נמוך = אוכל בשר באופן רגיל
-חוקים:
-- אם המשתמש מציין חיבה מיוחדת לבשר - ציון נמוך מאוד
-- אם המשתמש מציין שהוא צמחוני או טבעוני - ציון גבוה מאוד.
-בהיעדר מידע מוחלט- נעדיף לנחש לכיוון האמצע</t>
-  </si>
-  <si>
-    <t>הערכת ציונות ואהבת המדינה
-עד כמה המשתמש מחובר רגשית וערכית למדינה — כולל תחושת שייכות, אהבת הארץ ורצון לפעול למען המדינה
-בהיעדר מידע מוחלט - נעדיף לנחש לכיוון האמצע</t>
-  </si>
-  <si>
-    <t>הערכת רגישות למראה חיצוני.
-עד כמה המראה החיצוני של בן/בת זוג הוא גורם חשוב ומשמעותי עבור המשתמש.
-- יש להבחין בין העדפה ("נחמד אם") לבין דרישה ("חייב/ת")
-- יש להתחשב בטון — נוקשות מול גמישות
-חוקים:
-- אם המשתמש נותן דרישות חד משמעיות או דיל ברייקרים → העלה ציון משמעותית
-- אם המשתמש חוזר על הנושא או מדגיש אותו → העלה ציון
-- אם יש רק העדפות כלליות → שמור על ציון בינוני
-בהיעדר מידע מוחלט - ננחש ציון בינוני</t>
-  </si>
-  <si>
-    <t>הערכת היפסטריות (סגנון אינדי/אלטרנטיבי
-עד כמה המשתמש משדר סגנון וטעם תרבותי אלטרנטיבי, אינדי או "היפסטרי" — כלומר העדפה לדברים לא מיינסטרימיים, נישתיים או ייחודיים
-בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה יחסית</t>
-  </si>
-  <si>
-    <t>הערכת גיקיות (חיבור לתרבות גיקית)
-עד כמה המשתמש מתחבר לעולמות תוכן המזוהים עם תרבות גיקית — כמו טכנולוגיה, גיימינג, מדע בדיוני, פנטזיה, קומיקס או תחומי עניין דומים.
-ציון גבוה = יותר גיק  
-ציון נמוך = לא גיק
-בהיעדר מידע מוחלט - נקבע לפי הוייב הכללי של המשתמש בסבירות נמוכה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת היפיות (סגנון רוחני־אלטרנטיבי)
-עד כמה המשתמש מתחבר לסגנון חיים "היפי" — הכולל עניין ברוחניות, סדנאות, התפתחות אישית, טבע וטבעיות.
-ציון גבוה = יותר היפי  
-ציון נמוך = לא היפי
-בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה
-</t>
-  </si>
-  <si>
-    <t>הערכת סגנון תרבותי־רוסי (יוצאי ברה״מ)..
-ציון גבוה = סגנון רוסי מובהק  
-ציון נמוך = לא מזוהה עם הסגנון
-חוקים:
-- אם המשתמש מציין מוצא רוסי/אוקראיני → העלה ציון משמעותית
-- אם יש גם הזדהות תרבותית → העלה ציון עוד יותר
-בהיעדר מידע מוחלט - ננסה לנחש לפי הוייב הכללי של המשתמש ואם אין לנו מושג - נניח רמה נמוכה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">זיהוי רעילות (התנהגות מסוכנת).
-המטרה לזהות משתמשים שמבטאים רמות גבוהות של רעילות, תוקפנות או התנהגות שעלולה להיות בעייתית במערכת — לצורך ניטור ובקרה בלבד
-תכונה זו אינה מיועדת להתאמה אלא להערכת סיכון 
-חוקים:
-- אם יש ביטוי קיצוני (אלימות, גזענות ברורה וכו') → העלה ציון משמעותית
-- אם אין אינדיקציות ברורות → שמור על ציון נמוך.
-בהיעדר מידע מוחלט - נניח רעילות נמוכה בסבירות נמוכה. אם לאחר שיחה שלמה לא זיהינו רעילות - אפשר להניח גם רעילות נמוכה בסבירות בינונית.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">זיהוי טרוליות.
-לזהות האם המשתמש באמת מחפש שידוך ומשתף פעולה עם המערכת, או שמא הוא עונה בצורה לא כנה, ממציא, משחק עם המערכת או מטריל אותה
-- אם אין אינדיקציות ברורות → שמור על ציון נמוך
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת סחיות (מידת מיינסטרים וקונפורמיות).
+- אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
+- אין צורך ביותר ממאפיין אחד — גם אחד מספיק
+- אם אין אינדיקציה ברורה → להחזיר ריק
+- אין להחזיר ערכים על בסיס השערה</t>
+  </si>
+  <si>
+    <t>קונפורמיות</t>
+  </si>
+  <si>
+    <t>Conformity</t>
+  </si>
+  <si>
+    <t>נטייה למיינסטרים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מידת מיינסטרים
 הגדרה:
 סחיות = שילוב של מיינסטרים + קונפורמיות + גישה נורמטיבית לחיים
 עד כמה המשתמש נוטה למיינסטרים, לנורמות מקובלות ולגישה "רגילה" לחיים, לעומת ייחודיות, פתיחות וסטייה מהנורמה.
 חוקים:
 - יש להעריך לפי הקשר תרבותי ישראלי
+- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת קונפורמיות
+עד כמה המשתמש נוטה לנורמות מקובלות ולגישה "רגילה" לחיים לעומת פתיחות וסטייה מהנורמה. 
+ככל שהמשתמש יותר קונפורמיסט - העלה ציון
 - אם המשתמש מציג חשיבה עצמאית או חריגה → הורד ציון
-- אם המשתמש מדגיש "נורמלי", "רגיל", "מסודר", "קלאסי" → העלה ציון
-- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה הדעות שלו נפוצות ונורמטיביות
+- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
+- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)</t>
+  </si>
+  <si>
+    <t>Oriental</t>
+  </si>
+  <si>
+    <t>מזרחיות</t>
   </si>
   <si>
     <t xml:space="preserve">הערכת סגנון מזרחי (עממיות תרבותית־סגנונית)
 .
 ציון גבוה = סגנון מזרחי מובהק  
 ציון נמוך = סגנון פחות מזרחי / יותר סלקטיבי או נישתי
-עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן
+עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון יותר אשכנזי
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">עד כמה המשתמש בסגנון עממי
+.
+ציון גבוה = עממי מאוד
+ציון נמוך = סגנון יותר סלקטיבי או נישתי
+עד כמה המשתמש משדר סגנון תרבותי־עממי בוייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן
 חוקים:
 - אם המשתמש משדר סגנון עממי, פתוח, מחובר לתרבות פופולרית → העלה ציון
-- אם יש אינדיקציות לטעם וסגנון המזוהים עם וייב מזרחי → העלה ציון
 - אם המשתמש משדר סגנון נישתי, סלקטיבי או מובחן → הורד ציון
 חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
   </si>
   <si>
-    <t xml:space="preserve">הערכת שמרנות ערכית-חברתית.
-עד כמה המשתמש מחזיק בגישה שמרנית ומיושנת לעומת ליברלית/פתוחה בנושאים של זוגיות, מגדר ונורמות חברתיות
-ציון גבוה = שמרני - פרימיטיבי  
-ציון נמוך = ליברלי / מתירני
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת אינטלקטואליות.
-עד כמה המשתמש נוטה לשיח רעיוני, עומק מחשבתי והתעניינות בנושאים מופשטים, לעומת שיח פרקטי, יומיומי ופשוט. עד כמה הוא עוסק בנושאים אינטלקטואלים - ספרים וכדומה
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת וייב ילדותי לעומת בוגר
-הסגנון והוייב הכללי של המשתמש — עד כמה הוא נוטה לוייב ילדותי (playful, חמוד, נאיבי בסגנון) לעומת וייב בוגר יותר..
-ציון גבוה = יותר וייב ילדותי  
-ציון נמוך = יותר וייב בוגר
-חוקים:
-- אם יש תחושה כללית של playful, חמידות או אלמנטים ילדותיים → העלה ציון
-- אם הסגנון מרגיש בוגר, מאופק או "grown-up" → הורד ציון
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. 
+    <t xml:space="preserve">:
+- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
+- וייב כללי של חום, פתיחות ונגישות
+- חיבור לתרבות פופולרית רחבה
+- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
 </t>
   </si>
   <si>
-    <t xml:space="preserve">הערכת נטייה לציות למסגרות (״ילד טוב״)
-עד כמה המשתמש נוטה לפעול לפי חוקים, מסגרות ונורמות — לעומת גישה גמישה יותר, שבה חוקים הם בגדר המלצה וניתן לעגל פינות.  
-ציון גבוה = יותר "ילד טוב" (ציות גבוה)  
-ציון נמוך = יותר גמיש/מרדן
-אם המשתמש נותן וייב של מישהו שבטח המורות ממש אהבו בבית הספר - העלה את הציון, אחרת - תוריד.
-בהיעדר מידע מוחלט - ננחש לפי הוייב והסגנון של המשתמש
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
-  </si>
-  <si>
-    <t>זיהוי זהות מגדרית לא סטנדרטית
-לזהות האם המשתמש הצהיר באופן מפורש על היותו טרנס/ית או א-מיני.
-חוקים:
-- רק הצהרה מפורשת → ציון גבוה
-- אם אין מידע מתוך הרבה טקסט (נגיד בסיום השאלון) - אפשר לתת ציון נמוך בסבירות די גבוהה - נגיד 0.5</t>
-  </si>
-  <si>
-    <t>זהויות מגדריות שונות</t>
-  </si>
-  <si>
     <t xml:space="preserve">
-- אין להסיק זהות מגדרית או מינית ללא הצהרה מפורשת
-- אין לנחש על בסיס סגנון, שפה או התנהגות
-- מדובר רק במה שהמשתמש בחר לשתף באופן ברור
-- אין להסיק זהות על בסיס משיכה לגבר/אישה! אין קשר למשיכה, רק טרנס/ית או א-מיני. </t>
+- טעם מוזיקלי 
+- סגנון שפה 
+- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
+- זהות מוצהרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מוצא  ≠ סגנון.
+המטרה לא לזהות האם המשתמש מזרחי או אשכנזי. אם זיהית שהוא מזרחי לפי צבע עור או הצהרה ברורה - זה יכול מעט מאוד להעלות ציון אבל הציון מדבר על הסגנון, לא על קביעת העדה. </t>
+  </si>
+  <si>
+    <t>broad_appeal</t>
+  </si>
+  <si>
+    <t>קרבה למשפחת המוצא</t>
+  </si>
+  <si>
+    <t>family_of_origin_closeness</t>
+  </si>
+  <si>
+    <t>serious_relationship_intent</t>
+  </si>
+  <si>
+    <t>מחפש קשר רציני</t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש מחפש קשר רציני.
+אם מחפש סטוצים בלבד -&gt; הורד ציון.</t>
+  </si>
+  <si>
+    <t>emotional_expressiveness</t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש עסוק ברגשות ונוטה לשיח רגשי.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת רמת דתיות
+עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
+ יש להעריך את הרצף בין חילוני, מסורתי ודתי
+ככל שמידת הדתיות גבוהה יותר - נגדיר ציון גבוה יותר
+אם המשתמש לא מדבר כלל על הדת אין להניח שהוא בהכרח חילוני, ניתן לתת ציון נמוך בסביבות ה40. </t>
+  </si>
+  <si>
+    <t>דרמטיות/תיאטרליות</t>
+  </si>
+  <si>
+    <t>ימין פוליטי</t>
+  </si>
+  <si>
+    <t>שמאל פוליטי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- הבעת תמיכה בממשלה
+- רמזים עקיפים אך ברורים לעמדות פוליטיות</t>
+  </si>
+  <si>
+    <t>הערכת נטייה פוליטית שמאלנית
+עד כמה המשתמש נוטה לדעות פוליטיות שמאלניות.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה פוליטית ימנית
+עד כמה המשתמש נוטה לדעות פוליטיות ימניות (ביבי, בן גביר וכו'). . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- ביקורת על הממשלה
+- הפגנות וחברות בארגונים המזוהים עם השמאל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- תשובות מופרכות
+- תשובות לא קשורות ומתחכמות</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,6 +4034,12 @@
       <family val="2"/>
       <charset val="177"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3988,7 +4073,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4127,6 +4212,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7023,7 +7109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="38" customWidth="1"/>
@@ -7067,7 +7153,7 @@
         <v>526</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>524</v>
@@ -7105,7 +7191,7 @@
         <v>427</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -7143,11 +7229,11 @@
         <v>425</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2">
@@ -7173,7 +7259,7 @@
         <v>483</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>527</v>
@@ -7196,21 +7282,21 @@
       </c>
       <c r="N7" s="21"/>
     </row>
-    <row r="8" spans="1:14" ht="262.2">
+    <row r="8" spans="1:14" ht="220.8">
       <c r="A8" s="2" t="s">
         <v>442</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
+      <c r="C8" s="37" t="s">
+        <v>606</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>533</v>
+        <v>609</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -7230,209 +7316,202 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="96.6">
+    <row r="9" spans="1:14" ht="151.80000000000001">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>605</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>436</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>604</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33" t="s">
-        <v>544</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="2">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="262.2">
+    <row r="10" spans="1:14" ht="96.6">
+      <c r="A10" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>393</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>563</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="E10" s="33"/>
       <c r="F10" s="33" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I10" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="138">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
+      <c r="A11" s="52" t="s">
+        <v>611</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>359</v>
+        <v>436</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>612</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="3" t="s">
-        <v>570</v>
+        <v>613</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>616</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>617</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="M11" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="N11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="110.4">
-      <c r="A12" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="220.8">
+      <c r="A12" t="s">
+        <v>618</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>453</v>
+        <v>436</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>393</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="E12" s="33"/>
+        <v>614</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>615</v>
+      </c>
       <c r="F12" s="33"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="M12" s="2"/>
+      <c r="H12" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="138">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="33" t="s">
-        <v>534</v>
+        <v>595</v>
+      </c>
+      <c r="E13" s="33"/>
+      <c r="F13" s="3" t="s">
+        <v>565</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="M13" s="2" t="s">
-        <v>165</v>
+        <v>348</v>
+      </c>
+      <c r="N13" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="110.4">
-      <c r="A14" s="2" t="s">
-        <v>431</v>
-      </c>
+      <c r="A14" s="40"/>
       <c r="B14" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>453</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>580</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>542</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="2">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="124.2">
+    <row r="15" spans="1:14" ht="138">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="3"/>
+        <v>571</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="33" t="s">
+        <v>532</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="2">
         <v>0.7</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>8</v>
@@ -7441,30 +7520,27 @@
         <v>8</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="110.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="193.2">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>582</v>
+        <v>46</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>549</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>535</v>
+        <v>575</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>550</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="2">
@@ -7476,342 +7552,338 @@
       <c r="J16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="193.2">
+      <c r="K16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="110.4">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>431</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>551</v>
+        <v>18</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>572</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:14" ht="248.4">
-      <c r="A18" s="49" t="s">
-        <v>47</v>
+    <row r="18" spans="1:14" ht="165.6">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>48</v>
+        <v>436</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="E18" s="33"/>
-      <c r="F18" s="33" t="s">
-        <v>553</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="2"/>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" ht="207">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.2">
       <c r="A19" s="2" t="s">
-        <v>347</v>
+        <v>624</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>541</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="2">
-        <v>2</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" ht="82.8">
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" ht="110.4">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>620</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>619</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+        <v>574</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>533</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" ht="124.2">
+      <c r="M20" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.2">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>621</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>585</v>
+        <v>622</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>623</v>
       </c>
       <c r="E21" s="33"/>
-      <c r="F21" s="33" t="s">
-        <v>586</v>
-      </c>
+      <c r="F21" s="33"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="I21" s="2">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:14" ht="193.2">
-      <c r="A22" s="2" t="s">
-        <v>35</v>
+    <row r="22" spans="1:14" ht="248.4">
+      <c r="A22" s="49" t="s">
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>36</v>
+        <v>437</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>48</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="F22" s="33"/>
+        <v>597</v>
+      </c>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33" t="s">
+        <v>551</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I22" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="K22" s="2"/>
       <c r="M22" s="2"/>
-      <c r="N22" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="193.2">
+    </row>
+    <row r="23" spans="1:14" ht="207">
+      <c r="A23" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="B23" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>344</v>
+        <v>22</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>587</v>
+        <v>537</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="2">
         <v>0.4</v>
       </c>
       <c r="I23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="110.4">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" ht="82.8">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>547</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>588</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="3"/>
       <c r="H24" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="2"/>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:14" ht="124.2">
-      <c r="A25" s="49" t="s">
-        <v>40</v>
+      <c r="A25" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>591</v>
+        <v>439</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
+      <c r="F25" s="33" t="s">
+        <v>578</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="2">
         <v>0.6</v>
       </c>
       <c r="I25" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="82.8">
+    <row r="26" spans="1:14" ht="193.2">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33" t="s">
-        <v>548</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="F26" s="33"/>
       <c r="G26" s="3"/>
       <c r="H26" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="2"/>
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" ht="138">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="N26" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="55.2">
       <c r="B27" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>44</v>
+        <v>628</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>592</v>
+        <v>632</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>549</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>550</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="F27" s="33"/>
       <c r="G27" s="3"/>
       <c r="H27" s="2">
         <v>0.4</v>
@@ -7820,68 +7892,53 @@
         <v>3</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" ht="151.80000000000001">
-      <c r="A28" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="55.2">
       <c r="B28" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>430</v>
+        <v>629</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>593</v>
+        <v>631</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>537</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>536</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="F28" s="33"/>
       <c r="G28" s="3"/>
       <c r="H28" s="2">
         <v>0.4</v>
       </c>
       <c r="I28" s="2">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="262.2">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" ht="124.2">
+      <c r="A29" s="49" t="s">
+        <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+        <v>440</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="3"/>
       <c r="H29" s="2">
         <v>0.6</v>
       </c>
       <c r="I29" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>14</v>
@@ -7890,71 +7947,89 @@
       <c r="M29" s="2"/>
     </row>
     <row r="30" spans="1:14" ht="82.8">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B30" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3" t="s">
-        <v>554</v>
+        <v>580</v>
+      </c>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33" t="s">
+        <v>546</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I30" s="2">
         <v>3</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K30" s="2"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="1:14" ht="193.2">
+    <row r="31" spans="1:14" ht="138">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B31" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>340</v>
+        <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+        <v>583</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>547</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>548</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="207">
+      <c r="K31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" ht="151.80000000000001">
+      <c r="A32" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="B32" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>343</v>
+        <v>436</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33" t="s">
-        <v>558</v>
+        <v>584</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>534</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I32" s="2">
         <v>4</v>
@@ -7962,489 +8037,639 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="207">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="262.2">
       <c r="A33" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+        <v>585</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="I33" s="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
       <c r="J33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="K33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="124.2">
+    <row r="34" spans="1:14" ht="193.2">
       <c r="B34" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>559</v>
-      </c>
-      <c r="F34" s="33"/>
+        <v>586</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="2">
         <v>0.2</v>
       </c>
       <c r="I34" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="151.80000000000001">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="207">
       <c r="B35" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>343</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>565</v>
-      </c>
-      <c r="F35" s="33"/>
+        <v>598</v>
+      </c>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33" t="s">
+        <v>555</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I35" s="2">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="165.6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="207">
+      <c r="A36" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="B36" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>341</v>
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="E36" s="33" t="s">
-        <v>566</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>588</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="3"/>
       <c r="H36" s="2">
         <v>0.2</v>
       </c>
-      <c r="I36" s="2">
-        <v>3</v>
-      </c>
+      <c r="I36" s="2"/>
       <c r="J36" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="193.2">
-      <c r="A37" s="51"/>
-      <c r="B37" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" ht="124.2">
+      <c r="B37" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C37" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>601</v>
+      <c r="C37" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>589</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>567</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>556</v>
+      </c>
+      <c r="F37" s="33"/>
       <c r="G37" s="3"/>
       <c r="H37" s="2">
         <v>0.2</v>
       </c>
       <c r="I37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="248.4">
-      <c r="A38" s="2" t="s">
-        <v>60</v>
-      </c>
+    <row r="38" spans="1:14" ht="151.80000000000001">
       <c r="B38" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>61</v>
+        <v>433</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>569</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>568</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="F38" s="33"/>
       <c r="G38" s="3"/>
       <c r="H38" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="I38" s="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="I38" s="2">
+        <v>4</v>
+      </c>
       <c r="J38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:14" ht="110.4">
-      <c r="A39" s="2" t="s">
-        <v>120</v>
-      </c>
+    </row>
+    <row r="39" spans="1:14" ht="165.6">
       <c r="B39" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33" t="s">
-        <v>572</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>561</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39">
-        <v>0.4</v>
-      </c>
-      <c r="I39" s="2"/>
+      <c r="H39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I39" s="2">
+        <v>3</v>
+      </c>
       <c r="J39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="138">
-      <c r="A40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="33" t="s">
-        <v>612</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="193.2">
+      <c r="A40" s="51"/>
+      <c r="B40" s="41" t="s">
+        <v>436</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="2">
-        <v>0.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="I40" s="2">
+        <v>3</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="M40" s="19"/>
-      <c r="N40" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="331.2">
-      <c r="A41" s="40" t="s">
-        <v>275</v>
+    </row>
+    <row r="41" spans="1:14" ht="248.4">
+      <c r="A41" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="33" t="s">
-        <v>574</v>
+        <v>593</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>563</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="N41" s="34"/>
-    </row>
-    <row r="42" spans="1:14" ht="360">
+        <v>52</v>
+      </c>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:14" ht="110.4">
+      <c r="A42" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B42" s="2" t="s">
         <v>441</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>634</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42">
+        <v>0.4</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="138">
+      <c r="A43" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M43" s="19"/>
+      <c r="N43" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="400.2">
+      <c r="A44" s="40" t="s">
+        <v>275</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N44" s="34"/>
+    </row>
+    <row r="45" spans="1:14" ht="388.8">
+      <c r="B45" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="D45" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H45" s="2">
         <v>0.1</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J45" t="s">
         <v>14</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
-      <c r="C44" s="36" t="s">
+    <row r="47" spans="1:14">
+      <c r="C47" s="36" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="69">
-      <c r="A45" s="40" t="s">
+    <row r="48" spans="1:14" ht="69">
+      <c r="A48" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="3" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="I45" s="2">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="27.6">
-      <c r="A46" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I46" s="2">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="55.2">
-      <c r="A47" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="I47" s="2">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="1:14" ht="41.4">
-      <c r="A48" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I48" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" ht="27.6">
+        <v>335</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="27.6">
       <c r="A49" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>437</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="3" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>445</v>
+        <v>19</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" ht="151.80000000000001">
-      <c r="B50" s="2" t="s">
-        <v>440</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="55.2">
+      <c r="A50" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
-        <v>342</v>
+        <v>30</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="E50" s="33" t="s">
-        <v>557</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="2">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I50" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="165.6">
+        <v>8</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" spans="1:13" ht="41.4">
+      <c r="A51" s="40" t="s">
+        <v>23</v>
+      </c>
       <c r="B51" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="E51" s="33" t="s">
-        <v>561</v>
-      </c>
-      <c r="F51" s="33" t="s">
-        <v>562</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I51" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="K51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="1:13" ht="27.6">
+      <c r="A52" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I52" s="2">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:13" ht="151.80000000000001">
+      <c r="B53" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>554</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I53" s="2">
+        <v>2</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="165.6">
+      <c r="B54" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>559</v>
+      </c>
+      <c r="G54" s="3"/>
+      <c r="H54" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I54" s="2">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="82.8">
+      <c r="B55" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G55" s="3"/>
+      <c r="H55" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I55" s="2">
+        <v>3</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="1:13" ht="27.6">
+      <c r="B56" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="110.4">
+      <c r="A57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>579</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I57" s="2">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="2"/>
+      <c r="M57" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3385E088-2784-4C42-8DF1-574559399A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C9467-23F2-4E6C-96B7-54042F82C3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="טבלאות דאטה" sheetId="11" r:id="rId12"/>
     <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId13"/>
     <sheet name="בדיקות" sheetId="13" r:id="rId14"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="675">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3896,12 +3897,144 @@
 - תשובות מופרכות
 - תשובות לא קשורות ומתחכמות</t>
   </si>
+  <si>
+    <t>נושא השאלה</t>
+  </si>
+  <si>
+    <t>ה"אנטי" מאץ'</t>
+  </si>
+  <si>
+    <t>"בואי ננסה תרגיל של התבוננות הפוכה: תתארי לי את הדמות שתרגישי איתה הכי פחות בנוח. מה בווייב שלו או באמונות שלו פשוט לא עובר אצלך?"</t>
+  </si>
+  <si>
+    <t>"בואי נהיה רגע חדות – מי הבחור שהכי לא מתאים לך? מה הדעות והאמונות שלו שפוסלות אותו על הסף?"</t>
+  </si>
+  <si>
+    <t>"לפעמים הדיוק מגיע דווקא מהמקום שלא מהדהד איתנו. תתארי לי אדם שהאנרגיה והאמונות שלו מרגישים לך הכי רחוקים מהשורש שלך. מי הוא היה?"</t>
+  </si>
+  <si>
+    <t>קשר אחרון</t>
+  </si>
+  <si>
+    <t>"ספרי לי קצת על הקשר האחרון שלך. מה הרגשת שעבד שם מבחינת החיבור, ואיפה הרגשת שזה כבר לא היה נכון עבורך?"</t>
+  </si>
+  <si>
+    <t>"בואי נלמד מהעבר – מה קרה במערכת היחסים האחרונה שלך? מה עבד בשטח ומה הייתה הנקודה שבה זה הפסיק לעבוד?"</t>
+  </si>
+  <si>
+    <t>"איזה שיעור הביא איתו הקשר האחרון שהיה לך? מה שם הרגיש זורם ובאיזה שלב הרגשת שהחיבור כבר לא מזין אתכם?"</t>
+  </si>
+  <si>
+    <t>מראה עצמי</t>
+  </si>
+  <si>
+    <t>"איך את תופסת את המראה שלך?"</t>
+  </si>
+  <si>
+    <t>"בואי נדבר על המראה שלך, איך היית מתארת אותו?"</t>
+  </si>
+  <si>
+    <t>"איך את מתארת את המעטפת החיצונית שלך, המראה שלך?"</t>
+  </si>
+  <si>
+    <t>מראה - העדפה</t>
+  </si>
+  <si>
+    <t>"וחשוב לי להבין – אילו איכויות חיצוניות בבן זוג גורמות לך להרגיש משיכה או קרבה?"</t>
+  </si>
+  <si>
+    <t>"מה הסטנדרטים שלך לגבי המראה של הצד השני? מה חייב להיות שם?"</t>
+  </si>
+  <si>
+    <t>"ואילו מאפיינים פיזיים בבן זוג מרגישים לך נכונים ומזמינים?"</t>
+  </si>
+  <si>
+    <t>זהות/דיל ברייקר</t>
+  </si>
+  <si>
+    <t>"האם יש משהו מהותי בזהות שלך, או פרט חשוב עלייך, שאת מרגישה שחשוב שאדע לפני שאני מחבר אותך למישהו?"</t>
+  </si>
+  <si>
+    <t>"יש משהו מהותי בזהות שלך או פרט קריטי שחובה לדעת עלייך לפני שאנחנו יוצאים לדרך עם התאמות?"</t>
+  </si>
+  <si>
+    <t>"האם יש משהו בזהות העמוקה שלך, או פרט מהותי עלייך, שחשוב שיקבל ביטוי לפני שאני מחבר בין הנשמה שלך לאחרת?"</t>
+  </si>
+  <si>
+    <t>מיליון דולר</t>
+  </si>
+  <si>
+    <t>"דמייני שמחר את זוכה במיליון דולר. מה הדבר הראשון שתעשי עם הכוח הזה?"</t>
+  </si>
+  <si>
+    <t>"בונוס רציני: זכית במיליון דולר. מה את עושה עם הכסף הזה מחר בבוקר?"</t>
+  </si>
+  <si>
+    <t>"זרימה של שפע הגיעה אליך – מיליון דולר. איך היית משתמשת בהם כדי להיטיב עם חייך?"</t>
+  </si>
+  <si>
+    <t>קוגניציה (קנאה)</t>
+  </si>
+  <si>
+    <t>"שאלה קצת אחרת: דמייני אדם שמעולם לא חווה את הרגש שקוראים לו 'קנאה'. איך היית מסבירה לו את המנגנון הזה, בלי להשתמש במילה עצמה?"</t>
+  </si>
+  <si>
+    <t>"אתגר קטן: תסבירי לי איך המנגנון של 'קנאה' עובד, אבל בלי להשתמש במילה 'קנאה'. איך היית מתארת את התהליך הזה למישהו שלא מכיר אותו?"</t>
+  </si>
+  <si>
+    <t>"בואי ננסה להעמיק במשהו אנושי: איך היית מתארת את התנועה הפנימית שקורה לנו כשאנחנו 'מקנאים', למישהו שמעולם לא הרגיש את זה? (בלי להשתמש במילה המפורשת)."</t>
+  </si>
+  <si>
+    <t>הפסיכולוג</t>
+  </si>
+  <si>
+    <t>הקואצ'רית</t>
+  </si>
+  <si>
+    <t>המנטור הרוחני</t>
+  </si>
+  <si>
+    <t>זהות כללית</t>
+  </si>
+  <si>
+    <t>אמפתי, רפלקטיבי, מתמקד בדפוסים רגשיים ובתהליכי עומק. משתמש במילים כמו: "התבוננות", "מסע", "דפוסים", "חיבור". תגובות הביניים שלו: "אני שומע אותך", "זה נשמע משמעותי</t>
+  </si>
+  <si>
+    <t>ישירה, אנרגטית, ממוקדת תוצאות ומטרות. משתמשת במילים כמו: "חדות", "סטנדרטים", "הצלחה", "דוגרי". תגובות הביניים שלה: "מעולה, בואי נתקדם", "חשוב להיות חדים על זה</t>
+  </si>
+  <si>
+    <t>שליו, מטאפורי, מתמקד בערכים, אינטואיציה וחיבור נשמתי. משתמש במילים כמו: "הדהוד", "שיעור", "שורש", "תדר". תגובות הביניים שלו: "אני מתחבר למה שאמרת", "תודה על השיתוף העמוק</t>
+  </si>
+  <si>
+    <t>שורת פתיחה</t>
+  </si>
+  <si>
+    <t>"היי חן, אני איתן. אני שמח ללוות אותך בתהליך הזה. 😊
+כדי שאוכל להבין באמת מי את ומה הלב שלך מחפש, אנחנו צריכים רגע לצלול פנימה ולהכיר לעומק. ככל שתשתפי ביותר פתיחות וכנות, כך נוכל לבנות תמונה מלאה ודיוק רגשי שיוביל אותנו לאדם הנכון עבורך.
+אם תרגישי שזה עמוס מדי, תמיד תוכלי לקחת נשימה, לעצור ולהמשיך כשיהיה לך נוח.
+חשוב שתדעי – השיחה הזו היא מרחב בטוח ופרטי לגמרי. התשובות שלך לא יפורסמו בשום מקום; הן נועדו רק כדי שאוכל להבין את הדפוסים והצרכים שלך ולמצוא לך חיבור אמיתי.
+מרגישה בנוח להתחיל?"</t>
+  </si>
+  <si>
+    <t>"היי חן, אני מאיה, המאמנת שלך למציאת זוגיות! מוכנה לצאת לדרך? 🚀
+המטרה שלנו היא למצוא לך התאמה מדויקת וחזקה, ובשביל זה אני צריכה את המידע הכי חד שיש. ככל שתהיי יותר דוגרי, מפורטת וכנה בתשובות שלך – כך נוכל להגיע לתוצאה טובה יותר ולמצוא מישהו שבאמת מתאים לסטנדרטים שלך.
+זכרי, אם השיחה מתארכת, אפשר לעצור הכל ולהמשיך בזמן אחר. אנחנו כאן כדי לעבוד בשבילך.
+מבחינת פרטיות – הכל נשאר 'בחדר האימונים' שלנו. התשובות שלך לא עוברות לפרופיל הציבורי, הן רק הכלי שלי לנתח את הנתונים ולעשות לך את המאץ' המושלם.
+יוצאות לדרך?"</t>
+  </si>
+  <si>
+    <t>"שלום חן, אני רפאל. אני כאן כדי להקשיב לך ולמהות שאת מביאה איתך. 🙏
+הדרך למציאת חיבור אמיתי עוברת דרך הקשבה פנימית ודיוק. ככל שתאפשרי לעצמך לענות מהמקום הכי עמוק, פתוח ואמיתי שלך – כך נוכל למצוא אדם שהתדר והערכים שלו מהדהדים עם שלך.
+תרגישי חופשיה לזרום עם התחושות שלך. אם תרגישי צורך בהפסקה, אפשר לעצור לרגע ולהמשיך כשהלב יהיה פנוי לכך שוב.
+חשוב שתדעי שהמילים שלך קדושות עבורי; הן נשארות בינינו בלבד ולא יפורסמו. הן נועדו אך ורק כדי לעזור לי לראות את הנשמה שלך ולחבר אותה לאדם הנכון.
+הלב פתוח להתחיל?"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4040,6 +4173,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -4061,7 +4201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4069,11 +4209,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4213,6 +4368,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5391,6 +5552,161 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="53.6640625" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27.6" thickBot="1">
+      <c r="A1" s="54" t="s">
+        <v>635</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>664</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>665</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="54" thickBot="1">
+      <c r="A2" s="54" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>668</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>669</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="172.8" thickBot="1">
+      <c r="A3" s="54" t="s">
+        <v>671</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>672</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>673</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="40.799999999999997" thickBot="1">
+      <c r="A4" s="53" t="s">
+        <v>636</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>637</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>638</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="40.799999999999997" thickBot="1">
+      <c r="A5" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>641</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>642</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.6" thickBot="1">
+      <c r="A6" s="53" t="s">
+        <v>644</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>645</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>646</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.6" thickBot="1">
+      <c r="A7" s="53" t="s">
+        <v>648</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>649</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>650</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.6" thickBot="1">
+      <c r="A8" s="53" t="s">
+        <v>652</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>653</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>654</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.6" thickBot="1">
+      <c r="A9" s="53" t="s">
+        <v>656</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>657</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>658</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="40.799999999999997" thickBot="1">
+      <c r="A10" s="53" t="s">
+        <v>660</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>661</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>662</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
@@ -8223,7 +8539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="193.2">
+    <row r="40" spans="1:14" ht="179.4">
       <c r="A40" s="51"/>
       <c r="B40" s="41" t="s">
         <v>436</v>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C9467-23F2-4E6C-96B7-54042F82C3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0690435-A4A5-4E4E-A613-2EDB26F761A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="My Tasks" sheetId="12" r:id="rId1"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId2"/>
-    <sheet name="מאפיינים - כללי" sheetId="1" r:id="rId3"/>
-    <sheet name="internal traits" sheetId="14" r:id="rId4"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId5"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId6"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId7"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId8"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId9"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId10"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId11"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId12"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId13"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId14"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId15"/>
+    <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
+    <sheet name="Current Tasks" sheetId="16" r:id="rId2"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId3"/>
+    <sheet name="מאפיינים - כללי" sheetId="1" r:id="rId4"/>
+    <sheet name="internal traits" sheetId="14" r:id="rId5"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId6"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId7"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId8"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId9"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId10"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId11"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId12"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId13"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId14"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId15"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="700">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -1473,12 +1474,6 @@
     <t>סוכן מנתח</t>
   </si>
   <si>
-    <t>סוכן משוחח</t>
-  </si>
-  <si>
-    <t>סוכנים</t>
-  </si>
-  <si>
     <t>קבוצה</t>
   </si>
   <si>
@@ -4009,25 +4004,106 @@
     <t>שורת פתיחה</t>
   </si>
   <si>
-    <t>"היי חן, אני איתן. אני שמח ללוות אותך בתהליך הזה. 😊
+    <t>"שלום חן 🙏
+הדרך למציאת חיבור אמיתי עוברת דרך הקשבה פנימית ודיוק. ככל שתאפשרי לעצמך לענות מהמקום הכי עמוק, פתוח ואמיתי שלך – כך נוכל למצוא אדם שהתדר והערכים שלו מהדהדים עם שלך.
+תרגישי חופשיה לזרום עם התחושות שלך. אם תרגישי צורך בהפסקה, אפשר לעצור לרגע ולהמשיך כשהלב יהיה פנוי לכך שוב.
+חשוב שתדעי שהמילים שלך קדושות עבורי; הן נשארות בינינו בלבד ולא יפורסמו. הן נועדו אך ורק כדי לעזור לי לראות את הנשמה שלך ולחבר אותה לאדם הנכון. אני כאן כדי להקשיב לך ולמהות שאת מביאה
+מוכנה להתחיל?"</t>
+  </si>
+  <si>
+    <t>"היי חן, אני המאמנת שלך למציאת זוגיות! מוכנה לצאת לדרך? 🚀
+המטרה שלנו היא למצוא לך התאמה מדויקת וחזקה, ובשביל זה אני צריכה את המידע הכי חד שיש. ככל שתהיי יותר דוגרי, מפורטת וכנה בתשובות שלך – כך נוכל להגיע לתוצאה טובה יותר ולמצוא מישהו שבאמת מתאים לסטנדרטים שלך.
+זכרי, אם השיחה מתארכת, אפשר לעצור הכל ולהמשיך בזמן אחר. אנחנו כאן כדי לעבוד בשבילך.
+מבחינת פרטיות – הכל נשאר 'בחדר האימונים' שלנו. התשובות שלך לא עוברות לפרופיל הציבורי, הן רק הכלי שלי לנתח את הנתונים ולעשות לך את המאץ' המושלם.
+יוצאות לדרך?"</t>
+  </si>
+  <si>
+    <t>"היי חן, אני שמח ללוות אותך בתהליך הזה. 😊
 כדי שאוכל להבין באמת מי את ומה הלב שלך מחפש, אנחנו צריכים רגע לצלול פנימה ולהכיר לעומק. ככל שתשתפי ביותר פתיחות וכנות, כך נוכל לבנות תמונה מלאה ודיוק רגשי שיוביל אותנו לאדם הנכון עבורך.
 אם תרגישי שזה עמוס מדי, תמיד תוכלי לקחת נשימה, לעצור ולהמשיך כשיהיה לך נוח.
 חשוב שתדעי – השיחה הזו היא מרחב בטוח ופרטי לגמרי. התשובות שלך לא יפורסמו בשום מקום; הן נועדו רק כדי שאוכל להבין את הדפוסים והצרכים שלך ולמצוא לך חיבור אמיתי.
 מרגישה בנוח להתחיל?"</t>
   </si>
   <si>
-    <t>"היי חן, אני מאיה, המאמנת שלך למציאת זוגיות! מוכנה לצאת לדרך? 🚀
-המטרה שלנו היא למצוא לך התאמה מדויקת וחזקה, ובשביל זה אני צריכה את המידע הכי חד שיש. ככל שתהיי יותר דוגרי, מפורטת וכנה בתשובות שלך – כך נוכל להגיע לתוצאה טובה יותר ולמצוא מישהו שבאמת מתאים לסטנדרטים שלך.
-זכרי, אם השיחה מתארכת, אפשר לעצור הכל ולהמשיך בזמן אחר. אנחנו כאן כדי לעבוד בשבילך.
-מבחינת פרטיות – הכל נשאר 'בחדר האימונים' שלנו. התשובות שלך לא עוברות לפרופיל הציבורי, הן רק הכלי שלי לנתח את הנתונים ולעשות לך את המאץ' המושלם.
-יוצאות לדרך?"</t>
-  </si>
-  <si>
-    <t>"שלום חן, אני רפאל. אני כאן כדי להקשיב לך ולמהות שאת מביאה איתך. 🙏
-הדרך למציאת חיבור אמיתי עוברת דרך הקשבה פנימית ודיוק. ככל שתאפשרי לעצמך לענות מהמקום הכי עמוק, פתוח ואמיתי שלך – כך נוכל למצוא אדם שהתדר והערכים שלו מהדהדים עם שלך.
-תרגישי חופשיה לזרום עם התחושות שלך. אם תרגישי צורך בהפסקה, אפשר לעצור לרגע ולהמשיך כשהלב יהיה פנוי לכך שוב.
-חשוב שתדעי שהמילים שלך קדושות עבורי; הן נשארות בינינו בלבד ולא יפורסמו. הן נועדו אך ורק כדי לעזור לי לראות את הנשמה שלך ולחבר אותה לאדם הנכון.
-הלב פתוח להתחיל?"</t>
+    <t>ניתוח לפי אקסל תכונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סוכן משוחח </t>
+  </si>
+  <si>
+    <t>שיחה ראשונית שוטפת</t>
+  </si>
+  <si>
+    <t>כרטיס התאמה</t>
+  </si>
+  <si>
+    <t>בחירת מלווה</t>
+  </si>
+  <si>
+    <t>אחרי MVP:</t>
+  </si>
+  <si>
+    <t>מעבר לג'מיני או מודל אחר</t>
+  </si>
+  <si>
+    <t>מודל משוחח</t>
+  </si>
+  <si>
+    <t>שואל את אותה שאלה לפעמים בחזרה לשיחה</t>
+  </si>
+  <si>
+    <t>חזרה לשיחה</t>
+  </si>
+  <si>
+    <t>לבחור שוב מלווה, ולהתנהג בהתאם - אם חדש -שיחה חדשה, אם ישן - כיף שחזרת ולהמשיך..</t>
+  </si>
+  <si>
+    <t>לסדר אלגוריתם חישוב חיצוני ובהתאם מודל מנתח</t>
+  </si>
+  <si>
+    <t>לעדכן אפיון של המודלים</t>
+  </si>
+  <si>
+    <t>אפיון</t>
+  </si>
+  <si>
+    <t>מנתח</t>
+  </si>
+  <si>
+    <t>אלגוריתם ומשוחח</t>
+  </si>
+  <si>
+    <t>לסדר ציון לשידוך ולוודא שהמשוחח עובד איתו</t>
+  </si>
+  <si>
+    <t>לעשות שאלת טיפוסים</t>
+  </si>
+  <si>
+    <t>משוחח</t>
+  </si>
+  <si>
+    <t>להוסיף דיל ברייקרס נוספים - חרדי, ערבי, דרוזי. מה עוד?</t>
+  </si>
+  <si>
+    <t>להוסיף תכונות חדשות, תכונות מודלים ולסדר משקלים וודאויות</t>
+  </si>
+  <si>
+    <t>קלסטרים של טיפוסים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חלוקה לפרופילים כפי שהגדרתי </t>
+  </si>
+  <si>
+    <t>תכונות מורכבות - סחיות, עממיות.. מה עוד?</t>
+  </si>
+  <si>
+    <t>לסיים בכללי</t>
+  </si>
+  <si>
+    <t>להגיע לפרסום של שלב א'.</t>
+  </si>
+  <si>
+    <t>לתת שורת סיכום טובה</t>
   </si>
 </sst>
 </file>
@@ -4228,7 +4304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4374,6 +4450,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4654,7 +4731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -4695,6 +4772,9 @@
       <c r="B3" t="s">
         <v>404</v>
       </c>
+      <c r="C3" t="s">
+        <v>411</v>
+      </c>
       <c r="D3" t="s">
         <v>406</v>
       </c>
@@ -4706,25 +4786,34 @@
       <c r="B4" t="s">
         <v>403</v>
       </c>
+      <c r="C4" t="s">
+        <v>414</v>
+      </c>
       <c r="D4" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" t="s">
         <v>515</v>
-      </c>
-      <c r="B5" t="s">
-        <v>516</v>
-      </c>
-      <c r="D5" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>408</v>
       </c>
+      <c r="C6" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
@@ -4755,7 +4844,7 @@
       <c r="B9" t="s">
         <v>413</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="14" t="s">
         <v>414</v>
       </c>
     </row>
@@ -4784,10 +4873,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B12" t="s">
-        <v>421</v>
+        <v>673</v>
       </c>
       <c r="C12" t="s">
         <v>411</v>
@@ -4795,27 +4884,18 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>423</v>
+        <v>674</v>
       </c>
       <c r="B13" t="s">
-        <v>422</v>
+        <v>675</v>
       </c>
       <c r="C13" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>415</v>
-      </c>
-      <c r="B14" t="s">
-        <v>501</v>
-      </c>
-      <c r="C14" t="s">
-        <v>411</v>
-      </c>
-      <c r="D14" t="s">
-        <v>502</v>
+        <v>677</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4823,10 +4903,13 @@
         <v>415</v>
       </c>
       <c r="B15" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C15" t="s">
-        <v>504</v>
+        <v>411</v>
+      </c>
+      <c r="D15" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4834,23 +4917,26 @@
         <v>415</v>
       </c>
       <c r="B16" t="s">
-        <v>510</v>
+        <v>501</v>
+      </c>
+      <c r="C16" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>415</v>
+        <v>676</v>
       </c>
       <c r="B18" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4858,35 +4944,53 @@
         <v>415</v>
       </c>
       <c r="B19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>415</v>
       </c>
       <c r="B20" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>511</v>
+        <v>506</v>
+      </c>
+      <c r="B21" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>514</v>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -4895,6 +4999,291 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="43.2">
+      <c r="A6" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="5">
+        <v>95</v>
+      </c>
+      <c r="E7" s="5">
+        <v>185</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <f>F7*D7</f>
+        <v>95</v>
+      </c>
+      <c r="I7">
+        <f>D7*F7*G7</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <f>F8*D8</f>
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:I11" si="0">D8*F8*G8</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9">
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <f>F9*D9</f>
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F10">
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <f>F10*D10</f>
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11">
+        <v>0.6</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>F11*D11</f>
+        <v>18</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="D12">
+        <f>SUM(D7:D11)</f>
+        <v>335</v>
+      </c>
+      <c r="F12">
+        <f>SUM(F7:F11)</f>
+        <v>3.4</v>
+      </c>
+      <c r="H12">
+        <f>SUM(H7:H11)</f>
+        <v>233</v>
+      </c>
+      <c r="I12" s="25">
+        <f>SUM(I7:I11)/H12</f>
+        <v>9.2274678111587978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5116,7 +5505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5278,7 +5667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5428,7 +5817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5440,7 +5829,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -5460,12 +5849,12 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5473,7 +5862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5483,63 +5872,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="14" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5552,7 +5941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5564,142 +5953,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.6" thickBot="1">
       <c r="A1" s="54" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B1" s="54" t="s">
+        <v>662</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>663</v>
+      </c>
+      <c r="D1" s="54" t="s">
         <v>664</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>665</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="54" thickBot="1">
       <c r="A2" s="54" t="s">
+        <v>665</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>666</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>667</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="D2" s="53" t="s">
         <v>668</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>669</v>
-      </c>
-      <c r="D2" s="53" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="172.8" thickBot="1">
       <c r="A3" s="54" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>672</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A4" s="53" t="s">
+        <v>634</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" s="53" t="s">
         <v>636</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="D4" s="53" t="s">
         <v>637</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>638</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A5" s="53" t="s">
+        <v>638</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>639</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>640</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="D5" s="53" t="s">
         <v>641</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>642</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.6" thickBot="1">
       <c r="A6" s="53" t="s">
+        <v>642</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>643</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>644</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="D6" s="53" t="s">
         <v>645</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>646</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.6" thickBot="1">
       <c r="A7" s="53" t="s">
+        <v>646</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>647</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>648</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="D7" s="53" t="s">
         <v>649</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>650</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.6" thickBot="1">
       <c r="A8" s="53" t="s">
+        <v>650</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>651</v>
+      </c>
+      <c r="C8" s="53" t="s">
         <v>652</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="D8" s="53" t="s">
         <v>653</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>654</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.6" thickBot="1">
       <c r="A9" s="53" t="s">
+        <v>654</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>655</v>
+      </c>
+      <c r="C9" s="53" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="D9" s="53" t="s">
         <v>657</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>658</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A10" s="53" t="s">
+        <v>658</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>659</v>
+      </c>
+      <c r="C10" s="53" t="s">
         <v>660</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="D10" s="53" t="s">
         <v>661</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>662</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -5708,6 +6097,150 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C1EE30-A7E2-4C7A-8C61-FDFDE8F0687C}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.21875" customWidth="1"/>
+    <col min="4" max="4" width="48.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>682</v>
+      </c>
+      <c r="B4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B5" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>687</v>
+      </c>
+      <c r="B6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B8" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>687</v>
+      </c>
+      <c r="B10" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>686</v>
+      </c>
+      <c r="B14" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" t="s">
+        <v>698</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6228,7 +6761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6262,7 +6795,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>5</v>
@@ -6291,16 +6824,16 @@
     </row>
     <row r="5" spans="1:11" ht="409.6">
       <c r="A5" s="37" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E5" s="2">
         <v>0.7</v>
@@ -6326,16 +6859,16 @@
     </row>
     <row r="6" spans="1:11" ht="409.6">
       <c r="A6" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E6" s="2">
         <v>0.6</v>
@@ -6353,14 +6886,14 @@
     </row>
     <row r="7" spans="1:11" ht="409.6">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E7" s="2">
         <v>0.7</v>
@@ -6374,7 +6907,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K7" s="21"/>
     </row>
@@ -6383,13 +6916,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E8" s="2">
         <v>0.6</v>
@@ -6415,10 +6948,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="2">
         <v>0.7</v>
@@ -6444,10 +6977,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E10" s="2">
         <v>0.6</v>
@@ -6467,16 +7000,16 @@
     </row>
     <row r="11" spans="1:11" ht="409.6">
       <c r="A11" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E11" s="2">
         <v>0.4</v>
@@ -6499,13 +7032,13 @@
         <v>18</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E12" s="2">
         <v>0.5</v>
@@ -6529,10 +7062,10 @@
         <v>347</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E13" s="2">
         <v>0.4</v>
@@ -6556,10 +7089,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E14" s="2">
         <v>0.5</v>
@@ -6577,14 +7110,14 @@
     </row>
     <row r="15" spans="1:11" ht="409.6">
       <c r="A15" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -6600,10 +7133,10 @@
         <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E16" s="2">
         <v>0.6</v>
@@ -6627,10 +7160,10 @@
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E17" s="2">
         <v>0.7</v>
@@ -6659,10 +7192,10 @@
         <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E18" s="2">
         <v>0.7</v>
@@ -6686,10 +7219,10 @@
         <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E19" s="2">
         <v>0.5</v>
@@ -6716,10 +7249,10 @@
         <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E20" s="2">
         <v>0.6</v>
@@ -6741,10 +7274,10 @@
         <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E21" s="2">
         <v>0.6</v>
@@ -6766,10 +7299,10 @@
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E22" s="2">
         <v>0.4</v>
@@ -6791,10 +7324,10 @@
         <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E23" s="2">
         <v>0.4</v>
@@ -6816,10 +7349,10 @@
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E24" s="2">
         <v>0.6</v>
@@ -6841,10 +7374,10 @@
         <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2">
         <v>0.6</v>
@@ -6866,10 +7399,10 @@
         <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E26" s="2">
         <v>0.6</v>
@@ -6896,10 +7429,10 @@
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E27" s="2">
         <v>0.6</v>
@@ -6918,10 +7451,10 @@
         <v>339</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E28" s="2">
         <v>0.2</v>
@@ -6939,10 +7472,10 @@
         <v>344</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E29" s="2">
         <v>0.4</v>
@@ -6959,10 +7492,10 @@
         <v>340</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2">
         <v>0.2</v>
@@ -6979,10 +7512,10 @@
         <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E31" s="2">
         <v>0.2</v>
@@ -6999,10 +7532,10 @@
         <v>343</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E32" s="2">
         <v>0.5</v>
@@ -7022,10 +7555,10 @@
         <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E33" s="2">
         <v>0.2</v>
@@ -7044,10 +7577,10 @@
         <v>392</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E34" s="2">
         <v>0.2</v>
@@ -7064,10 +7597,10 @@
         <v>395</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E35" s="2">
         <v>0.2</v>
@@ -7084,10 +7617,10 @@
         <v>393</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E36" s="2">
         <v>0.4</v>
@@ -7101,13 +7634,13 @@
     </row>
     <row r="37" spans="1:11" ht="409.6">
       <c r="A37" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E37" s="2">
         <v>0.2</v>
@@ -7124,10 +7657,10 @@
         <v>341</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E38" s="2">
         <v>0.2</v>
@@ -7144,10 +7677,10 @@
         <v>396</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E39" s="2">
         <v>0.2</v>
@@ -7167,10 +7700,10 @@
         <v>60</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E40" s="2">
         <v>0.4</v>
@@ -7192,10 +7725,10 @@
         <v>120</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E41">
         <v>0.4</v>
@@ -7216,10 +7749,10 @@
         <v>277</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E42" s="2">
         <v>0.4</v>
@@ -7243,10 +7776,10 @@
         <v>275</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E43" s="2">
         <v>0.1</v>
@@ -7262,13 +7795,13 @@
     </row>
     <row r="44" spans="1:11" ht="409.6">
       <c r="A44" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E44" s="2">
         <v>0.1</v>
@@ -7277,12 +7810,12 @@
         <v>14</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="36" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="69">
@@ -7351,7 +7884,7 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E49" s="2">
         <v>0.6</v>
@@ -7375,10 +7908,10 @@
         <v>23</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E50" s="2">
         <v>0.5</v>
@@ -7402,10 +7935,10 @@
         <v>58</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E51" s="2">
         <v>0.3</v>
@@ -7423,7 +7956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7457,22 +7990,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>3</v>
@@ -7498,16 +8031,16 @@
     </row>
     <row r="5" spans="1:14" ht="110.4">
       <c r="A5" s="47" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
@@ -7536,20 +8069,20 @@
     </row>
     <row r="6" spans="1:14" ht="55.2">
       <c r="A6" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="2">
@@ -7569,16 +8102,16 @@
     <row r="7" spans="1:14" ht="317.39999999999998">
       <c r="A7" s="40"/>
       <c r="B7" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -7594,25 +8127,25 @@
       <c r="K7" s="3"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N7" s="21"/>
     </row>
     <row r="8" spans="1:14" ht="220.8">
       <c r="A8" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>607</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>609</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -7634,19 +8167,19 @@
     </row>
     <row r="9" spans="1:14" ht="151.80000000000001">
       <c r="A9" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>608</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>610</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -7665,17 +8198,17 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E10" s="33"/>
       <c r="F10" s="33" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="2">
@@ -7694,22 +8227,22 @@
     </row>
     <row r="11" spans="1:14" ht="138">
       <c r="A11" s="52" t="s">
+        <v>609</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>612</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>613</v>
-      </c>
       <c r="E11" s="33" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2">
@@ -7724,19 +8257,19 @@
     </row>
     <row r="12" spans="1:14" ht="220.8">
       <c r="A12" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>393</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="3"/>
@@ -7755,17 +8288,17 @@
         <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>359</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E13" s="33"/>
       <c r="F13" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="2">
@@ -7788,13 +8321,13 @@
     <row r="14" spans="1:14" ht="110.4">
       <c r="A14" s="40"/>
       <c r="B14" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E14" s="33"/>
       <c r="F14" s="33"/>
@@ -7810,17 +8343,17 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E15" s="45"/>
       <c r="F15" s="33" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="2">
@@ -7844,19 +8377,19 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="2">
@@ -7873,22 +8406,22 @@
     </row>
     <row r="17" spans="1:14" ht="110.4">
       <c r="A17" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="2">
@@ -7910,13 +8443,13 @@
         <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="3"/>
@@ -7942,16 +8475,16 @@
     </row>
     <row r="19" spans="1:14" ht="43.2">
       <c r="A19" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="3"/>
@@ -7969,22 +8502,22 @@
     </row>
     <row r="20" spans="1:14" ht="110.4">
       <c r="A20" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="2">
@@ -8005,16 +8538,16 @@
     </row>
     <row r="21" spans="1:14" ht="43.2">
       <c r="A21" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D21" s="33" t="s">
         <v>621</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>623</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
@@ -8030,17 +8563,17 @@
         <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C22" s="48" t="s">
         <v>48</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E22" s="33"/>
       <c r="F22" s="33" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="2">
@@ -8060,19 +8593,19 @@
         <v>347</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>537</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="F23" s="33" t="s">
-        <v>539</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="2">
@@ -8094,13 +8627,13 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
@@ -8124,17 +8657,17 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E25" s="33"/>
       <c r="F25" s="33" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="2">
@@ -8156,16 +8689,16 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F26" s="33"/>
       <c r="G26" s="3"/>
@@ -8188,16 +8721,16 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="B27" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="E27" s="33" t="s">
         <v>628</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>630</v>
       </c>
       <c r="F27" s="33"/>
       <c r="G27" s="3"/>
@@ -8213,16 +8746,16 @@
     </row>
     <row r="28" spans="1:14" ht="55.2">
       <c r="B28" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="33" t="s">
         <v>631</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>633</v>
       </c>
       <c r="F28" s="33"/>
       <c r="G28" s="3"/>
@@ -8239,13 +8772,13 @@
         <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C29" s="48" t="s">
         <v>39</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -8267,17 +8800,17 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="2">
@@ -8297,19 +8830,19 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="2">
@@ -8329,19 +8862,19 @@
         <v>17</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="2">
@@ -8365,13 +8898,13 @@
         <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -8390,13 +8923,13 @@
     </row>
     <row r="34" spans="1:14" ht="193.2">
       <c r="B34" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>340</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -8413,17 +8946,17 @@
     </row>
     <row r="35" spans="1:14" ht="207">
       <c r="B35" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>343</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E35" s="33"/>
       <c r="F35" s="33" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="2">
@@ -8441,13 +8974,13 @@
         <v>53</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="33"/>
@@ -8466,16 +8999,16 @@
     </row>
     <row r="37" spans="1:14" ht="124.2">
       <c r="B37" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>392</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F37" s="33"/>
       <c r="G37" s="3"/>
@@ -8491,16 +9024,16 @@
     </row>
     <row r="38" spans="1:14" ht="151.80000000000001">
       <c r="B38" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F38" s="33"/>
       <c r="G38" s="3"/>
@@ -8516,16 +9049,16 @@
     </row>
     <row r="39" spans="1:14" ht="165.6">
       <c r="B39" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>341</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -8542,16 +9075,16 @@
     <row r="40" spans="1:14" ht="179.4">
       <c r="A40" s="51"/>
       <c r="B40" s="41" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C40" s="33" t="s">
         <v>396</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -8570,19 +9103,19 @@
         <v>60</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="2">
@@ -8602,19 +9135,19 @@
         <v>120</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F42" s="33" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42">
@@ -8633,17 +9166,17 @@
         <v>277</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="33" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="2">
@@ -8665,17 +9198,17 @@
         <v>275</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>274</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="33" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="2">
@@ -8692,19 +9225,19 @@
     </row>
     <row r="45" spans="1:14" ht="388.8">
       <c r="B45" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H45" s="2">
         <v>0.1</v>
@@ -8713,12 +9246,12 @@
         <v>14</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="C47" s="36" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="69">
@@ -8793,7 +9326,7 @@
         <v>30</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -8817,13 +9350,13 @@
         <v>23</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -8847,13 +9380,13 @@
         <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -8871,16 +9404,16 @@
     </row>
     <row r="53" spans="1:13" ht="151.80000000000001">
       <c r="B53" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>342</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -8896,19 +9429,19 @@
     </row>
     <row r="54" spans="1:13" ht="165.6">
       <c r="B54" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>395</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="F54" s="33" t="s">
         <v>557</v>
-      </c>
-      <c r="E54" s="33" t="s">
-        <v>558</v>
-      </c>
-      <c r="F54" s="33" t="s">
-        <v>559</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="2">
@@ -8923,17 +9456,17 @@
     </row>
     <row r="55" spans="1:13" ht="82.8">
       <c r="B55" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>339</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="2">
@@ -8949,10 +9482,10 @@
     </row>
     <row r="56" spans="1:13" ht="27.6">
       <c r="B56" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="110.4">
@@ -8960,19 +9493,19 @@
         <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="2">
@@ -8992,7 +9525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9063,7 +9596,7 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -9087,7 +9620,7 @@
         <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -9249,7 +9782,7 @@
         <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -9272,7 +9805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9569,7 +10102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9919,7 +10452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10532,289 +11065,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" customWidth="1"/>
-    <col min="9" max="9" width="32.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="43.2">
-      <c r="A6" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="5">
-        <v>95</v>
-      </c>
-      <c r="E7" s="5">
-        <v>185</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <f>F7*D7</f>
-        <v>95</v>
-      </c>
-      <c r="I7">
-        <f>D7*F7*G7</f>
-        <v>950</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F8">
-        <v>0.5</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <f>F8*D8</f>
-        <v>40</v>
-      </c>
-      <c r="I8">
-        <f t="shared" ref="I8:I11" si="0">D8*F8*G8</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9">
-        <v>0.8</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <f>F9*D9</f>
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10">
-        <f>F10*D10</f>
-        <v>40</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11">
-        <v>0.6</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <f>F11*D11</f>
-        <v>18</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="D12">
-        <f>SUM(D7:D11)</f>
-        <v>335</v>
-      </c>
-      <c r="F12">
-        <f>SUM(F7:F11)</f>
-        <v>3.4</v>
-      </c>
-      <c r="H12">
-        <f>SUM(H7:H11)</f>
-        <v>233</v>
-      </c>
-      <c r="I12" s="25">
-        <f>SUM(I7:I11)/H12</f>
-        <v>9.2274678111587978</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>397</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0690435-A4A5-4E4E-A613-2EDB26F761A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2522F8B-BB10-43B0-8D0B-5368C395BEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="710">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3702,6 +3702,368 @@
 - אין להסיק זהות על בסיס משיכה לגבר/אישה! אין קשר למשיכה, רק טרנס/ית או א-מיני. </t>
   </si>
   <si>
+    <t>קונפורמיות</t>
+  </si>
+  <si>
+    <t>Conformity</t>
+  </si>
+  <si>
+    <t>נטייה למיינסטרים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת מידת מיינסטרים
+הגדרה:
+סחיות = שילוב של מיינסטרים + קונפורמיות + גישה נורמטיבית לחיים
+עד כמה המשתמש נוטה למיינסטרים, לנורמות מקובלות ולגישה "רגילה" לחיים, לעומת ייחודיות, פתיחות וסטייה מהנורמה.
+חוקים:
+- יש להעריך לפי הקשר תרבותי ישראלי
+- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת קונפורמיות
+עד כמה המשתמש נוטה לנורמות מקובלות ולגישה "רגילה" לחיים לעומת פתיחות וסטייה מהנורמה. 
+ככל שהמשתמש יותר קונפורמיסט - העלה ציון
+- אם המשתמש מציג חשיבה עצמאית או חריגה → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- עד כמה הדעות שלו נפוצות ונורמטיביות
+- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
+- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)</t>
+  </si>
+  <si>
+    <t>Oriental</t>
+  </si>
+  <si>
+    <t>מזרחיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת סגנון מזרחי (עממיות תרבותית־סגנונית)
+.
+ציון גבוה = סגנון מזרחי מובהק  
+ציון נמוך = סגנון פחות מזרחי / יותר סלקטיבי או נישתי
+עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון יותר אשכנזי
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">עד כמה המשתמש בסגנון עממי
+.
+ציון גבוה = עממי מאוד
+ציון נמוך = סגנון יותר סלקטיבי או נישתי
+עד כמה המשתמש משדר סגנון תרבותי־עממי בוייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן
+חוקים:
+- אם המשתמש משדר סגנון עממי, פתוח, מחובר לתרבות פופולרית → העלה ציון
+- אם המשתמש משדר סגנון נישתי, סלקטיבי או מובחן → הורד ציון
+חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">:
+- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
+- וייב כללי של חום, פתיחות ונגישות
+- חיבור לתרבות פופולרית רחבה
+- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- טעם מוזיקלי 
+- סגנון שפה 
+- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
+- זהות מוצהרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מוצא  ≠ סגנון.
+המטרה לא לזהות האם המשתמש מזרחי או אשכנזי. אם זיהית שהוא מזרחי לפי צבע עור או הצהרה ברורה - זה יכול מעט מאוד להעלות ציון אבל הציון מדבר על הסגנון, לא על קביעת העדה. </t>
+  </si>
+  <si>
+    <t>broad_appeal</t>
+  </si>
+  <si>
+    <t>קרבה למשפחת המוצא</t>
+  </si>
+  <si>
+    <t>family_of_origin_closeness</t>
+  </si>
+  <si>
+    <t>serious_relationship_intent</t>
+  </si>
+  <si>
+    <t>מחפש קשר רציני</t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש מחפש קשר רציני.
+אם מחפש סטוצים בלבד -&gt; הורד ציון.</t>
+  </si>
+  <si>
+    <t>emotional_expressiveness</t>
+  </si>
+  <si>
+    <t>עד כמה המשתמש עסוק ברגשות ונוטה לשיח רגשי.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת רמת דתיות
+עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
+ יש להעריך את הרצף בין חילוני, מסורתי ודתי
+ככל שמידת הדתיות גבוהה יותר - נגדיר ציון גבוה יותר
+אם המשתמש לא מדבר כלל על הדת אין להניח שהוא בהכרח חילוני, ניתן לתת ציון נמוך בסביבות ה40. </t>
+  </si>
+  <si>
+    <t>דרמטיות/תיאטרליות</t>
+  </si>
+  <si>
+    <t>ימין פוליטי</t>
+  </si>
+  <si>
+    <t>שמאל פוליטי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- הבעת תמיכה בממשלה
+- רמזים עקיפים אך ברורים לעמדות פוליטיות</t>
+  </si>
+  <si>
+    <t>הערכת נטייה פוליטית שמאלנית
+עד כמה המשתמש נוטה לדעות פוליטיות שמאלניות.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערכת נטייה פוליטית ימנית
+עד כמה המשתמש נוטה לדעות פוליטיות ימניות (ביבי, בן גביר וכו'). . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- ביקורת על הממשלה
+- הפגנות וחברות בארגונים המזוהים עם השמאל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- תשובות מופרכות
+- תשובות לא קשורות ומתחכמות</t>
+  </si>
+  <si>
+    <t>נושא השאלה</t>
+  </si>
+  <si>
+    <t>ה"אנטי" מאץ'</t>
+  </si>
+  <si>
+    <t>"בואי ננסה תרגיל של התבוננות הפוכה: תתארי לי את הדמות שתרגישי איתה הכי פחות בנוח. מה בווייב שלו או באמונות שלו פשוט לא עובר אצלך?"</t>
+  </si>
+  <si>
+    <t>"בואי נהיה רגע חדות – מי הבחור שהכי לא מתאים לך? מה הדעות והאמונות שלו שפוסלות אותו על הסף?"</t>
+  </si>
+  <si>
+    <t>"לפעמים הדיוק מגיע דווקא מהמקום שלא מהדהד איתנו. תתארי לי אדם שהאנרגיה והאמונות שלו מרגישים לך הכי רחוקים מהשורש שלך. מי הוא היה?"</t>
+  </si>
+  <si>
+    <t>קשר אחרון</t>
+  </si>
+  <si>
+    <t>"ספרי לי קצת על הקשר האחרון שלך. מה הרגשת שעבד שם מבחינת החיבור, ואיפה הרגשת שזה כבר לא היה נכון עבורך?"</t>
+  </si>
+  <si>
+    <t>"בואי נלמד מהעבר – מה קרה במערכת היחסים האחרונה שלך? מה עבד בשטח ומה הייתה הנקודה שבה זה הפסיק לעבוד?"</t>
+  </si>
+  <si>
+    <t>"איזה שיעור הביא איתו הקשר האחרון שהיה לך? מה שם הרגיש זורם ובאיזה שלב הרגשת שהחיבור כבר לא מזין אתכם?"</t>
+  </si>
+  <si>
+    <t>מראה עצמי</t>
+  </si>
+  <si>
+    <t>"איך את תופסת את המראה שלך?"</t>
+  </si>
+  <si>
+    <t>"בואי נדבר על המראה שלך, איך היית מתארת אותו?"</t>
+  </si>
+  <si>
+    <t>"איך את מתארת את המעטפת החיצונית שלך, המראה שלך?"</t>
+  </si>
+  <si>
+    <t>מראה - העדפה</t>
+  </si>
+  <si>
+    <t>"וחשוב לי להבין – אילו איכויות חיצוניות בבן זוג גורמות לך להרגיש משיכה או קרבה?"</t>
+  </si>
+  <si>
+    <t>"מה הסטנדרטים שלך לגבי המראה של הצד השני? מה חייב להיות שם?"</t>
+  </si>
+  <si>
+    <t>"ואילו מאפיינים פיזיים בבן זוג מרגישים לך נכונים ומזמינים?"</t>
+  </si>
+  <si>
+    <t>זהות/דיל ברייקר</t>
+  </si>
+  <si>
+    <t>"האם יש משהו מהותי בזהות שלך, או פרט חשוב עלייך, שאת מרגישה שחשוב שאדע לפני שאני מחבר אותך למישהו?"</t>
+  </si>
+  <si>
+    <t>"יש משהו מהותי בזהות שלך או פרט קריטי שחובה לדעת עלייך לפני שאנחנו יוצאים לדרך עם התאמות?"</t>
+  </si>
+  <si>
+    <t>"האם יש משהו בזהות העמוקה שלך, או פרט מהותי עלייך, שחשוב שיקבל ביטוי לפני שאני מחבר בין הנשמה שלך לאחרת?"</t>
+  </si>
+  <si>
+    <t>מיליון דולר</t>
+  </si>
+  <si>
+    <t>"דמייני שמחר את זוכה במיליון דולר. מה הדבר הראשון שתעשי עם הכוח הזה?"</t>
+  </si>
+  <si>
+    <t>"בונוס רציני: זכית במיליון דולר. מה את עושה עם הכסף הזה מחר בבוקר?"</t>
+  </si>
+  <si>
+    <t>"זרימה של שפע הגיעה אליך – מיליון דולר. איך היית משתמשת בהם כדי להיטיב עם חייך?"</t>
+  </si>
+  <si>
+    <t>קוגניציה (קנאה)</t>
+  </si>
+  <si>
+    <t>"שאלה קצת אחרת: דמייני אדם שמעולם לא חווה את הרגש שקוראים לו 'קנאה'. איך היית מסבירה לו את המנגנון הזה, בלי להשתמש במילה עצמה?"</t>
+  </si>
+  <si>
+    <t>"אתגר קטן: תסבירי לי איך המנגנון של 'קנאה' עובד, אבל בלי להשתמש במילה 'קנאה'. איך היית מתארת את התהליך הזה למישהו שלא מכיר אותו?"</t>
+  </si>
+  <si>
+    <t>"בואי ננסה להעמיק במשהו אנושי: איך היית מתארת את התנועה הפנימית שקורה לנו כשאנחנו 'מקנאים', למישהו שמעולם לא הרגיש את זה? (בלי להשתמש במילה המפורשת)."</t>
+  </si>
+  <si>
+    <t>הפסיכולוג</t>
+  </si>
+  <si>
+    <t>הקואצ'רית</t>
+  </si>
+  <si>
+    <t>המנטור הרוחני</t>
+  </si>
+  <si>
+    <t>זהות כללית</t>
+  </si>
+  <si>
+    <t>אמפתי, רפלקטיבי, מתמקד בדפוסים רגשיים ובתהליכי עומק. משתמש במילים כמו: "התבוננות", "מסע", "דפוסים", "חיבור". תגובות הביניים שלו: "אני שומע אותך", "זה נשמע משמעותי</t>
+  </si>
+  <si>
+    <t>ישירה, אנרגטית, ממוקדת תוצאות ומטרות. משתמשת במילים כמו: "חדות", "סטנדרטים", "הצלחה", "דוגרי". תגובות הביניים שלה: "מעולה, בואי נתקדם", "חשוב להיות חדים על זה</t>
+  </si>
+  <si>
+    <t>שליו, מטאפורי, מתמקד בערכים, אינטואיציה וחיבור נשמתי. משתמש במילים כמו: "הדהוד", "שיעור", "שורש", "תדר". תגובות הביניים שלו: "אני מתחבר למה שאמרת", "תודה על השיתוף העמוק</t>
+  </si>
+  <si>
+    <t>שורת פתיחה</t>
+  </si>
+  <si>
+    <t>"שלום חן 🙏
+הדרך למציאת חיבור אמיתי עוברת דרך הקשבה פנימית ודיוק. ככל שתאפשרי לעצמך לענות מהמקום הכי עמוק, פתוח ואמיתי שלך – כך נוכל למצוא אדם שהתדר והערכים שלו מהדהדים עם שלך.
+תרגישי חופשיה לזרום עם התחושות שלך. אם תרגישי צורך בהפסקה, אפשר לעצור לרגע ולהמשיך כשהלב יהיה פנוי לכך שוב.
+חשוב שתדעי שהמילים שלך קדושות עבורי; הן נשארות בינינו בלבד ולא יפורסמו. הן נועדו אך ורק כדי לעזור לי לראות את הנשמה שלך ולחבר אותה לאדם הנכון. אני כאן כדי להקשיב לך ולמהות שאת מביאה
+מוכנה להתחיל?"</t>
+  </si>
+  <si>
+    <t>"היי חן, אני המאמנת שלך למציאת זוגיות! מוכנה לצאת לדרך? 🚀
+המטרה שלנו היא למצוא לך התאמה מדויקת וחזקה, ובשביל זה אני צריכה את המידע הכי חד שיש. ככל שתהיי יותר דוגרי, מפורטת וכנה בתשובות שלך – כך נוכל להגיע לתוצאה טובה יותר ולמצוא מישהו שבאמת מתאים לסטנדרטים שלך.
+זכרי, אם השיחה מתארכת, אפשר לעצור הכל ולהמשיך בזמן אחר. אנחנו כאן כדי לעבוד בשבילך.
+מבחינת פרטיות – הכל נשאר 'בחדר האימונים' שלנו. התשובות שלך לא עוברות לפרופיל הציבורי, הן רק הכלי שלי לנתח את הנתונים ולעשות לך את המאץ' המושלם.
+יוצאות לדרך?"</t>
+  </si>
+  <si>
+    <t>"היי חן, אני שמח ללוות אותך בתהליך הזה. 😊
+כדי שאוכל להבין באמת מי את ומה הלב שלך מחפש, אנחנו צריכים רגע לצלול פנימה ולהכיר לעומק. ככל שתשתפי ביותר פתיחות וכנות, כך נוכל לבנות תמונה מלאה ודיוק רגשי שיוביל אותנו לאדם הנכון עבורך.
+אם תרגישי שזה עמוס מדי, תמיד תוכלי לקחת נשימה, לעצור ולהמשיך כשיהיה לך נוח.
+חשוב שתדעי – השיחה הזו היא מרחב בטוח ופרטי לגמרי. התשובות שלך לא יפורסמו בשום מקום; הן נועדו רק כדי שאוכל להבין את הדפוסים והצרכים שלך ולמצוא לך חיבור אמיתי.
+מרגישה בנוח להתחיל?"</t>
+  </si>
+  <si>
+    <t>ניתוח לפי אקסל תכונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סוכן משוחח </t>
+  </si>
+  <si>
+    <t>שיחה ראשונית שוטפת</t>
+  </si>
+  <si>
+    <t>כרטיס התאמה</t>
+  </si>
+  <si>
+    <t>בחירת מלווה</t>
+  </si>
+  <si>
+    <t>אחרי MVP:</t>
+  </si>
+  <si>
+    <t>מעבר לג'מיני או מודל אחר</t>
+  </si>
+  <si>
+    <t>מודל משוחח</t>
+  </si>
+  <si>
+    <t>שואל את אותה שאלה לפעמים בחזרה לשיחה</t>
+  </si>
+  <si>
+    <t>חזרה לשיחה</t>
+  </si>
+  <si>
+    <t>לבחור שוב מלווה, ולהתנהג בהתאם - אם חדש -שיחה חדשה, אם ישן - כיף שחזרת ולהמשיך..</t>
+  </si>
+  <si>
+    <t>לסדר אלגוריתם חישוב חיצוני ובהתאם מודל מנתח</t>
+  </si>
+  <si>
+    <t>לעדכן אפיון של המודלים</t>
+  </si>
+  <si>
+    <t>אפיון</t>
+  </si>
+  <si>
+    <t>מנתח</t>
+  </si>
+  <si>
+    <t>אלגוריתם ומשוחח</t>
+  </si>
+  <si>
+    <t>לסדר ציון לשידוך ולוודא שהמשוחח עובד איתו</t>
+  </si>
+  <si>
+    <t>לעשות שאלת טיפוסים</t>
+  </si>
+  <si>
+    <t>משוחח</t>
+  </si>
+  <si>
+    <t>להוסיף דיל ברייקרס נוספים - חרדי, ערבי, דרוזי. מה עוד?</t>
+  </si>
+  <si>
+    <t>להוסיף תכונות חדשות, תכונות מודלים ולסדר משקלים וודאויות</t>
+  </si>
+  <si>
+    <t>קלסטרים של טיפוסים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חלוקה לפרופילים כפי שהגדרתי </t>
+  </si>
+  <si>
+    <t>תכונות מורכבות - סחיות, עממיות.. מה עוד?</t>
+  </si>
+  <si>
+    <t>לסיים בכללי</t>
+  </si>
+  <si>
+    <t>להגיע לפרסום של שלב א'.</t>
+  </si>
+  <si>
+    <t>לתת שורת סיכום טובה</t>
+  </si>
+  <si>
+    <t>יכולת ניסוח</t>
+  </si>
+  <si>
     <t>זיהוי דיל ברייקרס פוטנציאליים
 .
  מאפיינים משמעותיים אצל המשתמש שעלולים להוות דיל ברייקר עבור חלק מהאנשים — לצורך התאמה טובה יותר והימנעות מחוסר התאמה.
@@ -3719,6 +4081,8 @@
 - smoker (מעשנ/ת)
 - polyamorous (פוליאמורי/ת)
 - open_relationship (בזוגיות פתוחה)
+-arab (ערבי)
+-orthodox (חרדי)
 חוקים:
 -אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
 - אם אין אינדיקציה ברורה → להחזיר ריק</t>
@@ -3740,6 +4104,8 @@
 smoker (מעשנ/ת)
 polyamorous (פוליאמורי/ת)
 open_relationship (בזוגיות פתוחה)
+-arab (ערבי)
+-orthodox (חרדי)
 חוקים:
 - אם זוהה מאפיין אחד מהרשימה באופן ברור → יש להחזיר אותו (גם אם זה היחיד)
 - אין צורך ביותר ממאפיין אחד — גם אחד מספיק
@@ -3747,363 +4113,31 @@
 - אין להחזיר ערכים על בסיס השערה</t>
   </si>
   <si>
-    <t>קונפורמיות</t>
-  </si>
-  <si>
-    <t>Conformity</t>
-  </si>
-  <si>
-    <t>נטייה למיינסטרים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת מידת מיינסטרים
-הגדרה:
-סחיות = שילוב של מיינסטרים + קונפורמיות + גישה נורמטיבית לחיים
-עד כמה המשתמש נוטה למיינסטרים, לנורמות מקובלות ולגישה "רגילה" לחיים, לעומת ייחודיות, פתיחות וסטייה מהנורמה.
-חוקים:
-- יש להעריך לפי הקשר תרבותי ישראלי
-- אם המשתמש מבטא משיכה לשונה, חריג או לא שגרתי → הורד ציון
-חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש! </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת קונפורמיות
-עד כמה המשתמש נוטה לנורמות מקובלות ולגישה "רגילה" לחיים לעומת פתיחות וסטייה מהנורמה. 
-ככל שהמשתמש יותר קונפורמיסט - העלה ציון
-- אם המשתמש מציג חשיבה עצמאית או חריגה → הורד ציון
-חובה לנסות לתת ציון פה גם אם אין ראיות - תנחש לפי הוייב וסגנון הדיבור של המשתמש!
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- עד כמה תחומי העניין שלו מיינסטרים או שגרתיים
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- עד כמה הדעות שלו נפוצות ונורמטיביות
-- עד כמה הוא "זורם עם מה שמקובל" לעומת חשיבה עצמאית
-- עד כמה הוא פתוח לסגנונות חיים לא שגרתיים (זוגיות, קריירה, אורח חיים)</t>
-  </si>
-  <si>
-    <t>Oriental</t>
-  </si>
-  <si>
-    <t>מזרחיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת סגנון מזרחי (עממיות תרבותית־סגנונית)
-.
-ציון גבוה = סגנון מזרחי מובהק  
-ציון נמוך = סגנון פחות מזרחי / יותר סלקטיבי או נישתי
-עד כמה המשתמש משדר סגנון תרבותי־מזרחי בווייב, בטעם ובסגנון האישי — לעומת סגנון יותר אשכנזי
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">עד כמה המשתמש בסגנון עממי
-.
-ציון גבוה = עממי מאוד
-ציון נמוך = סגנון יותר סלקטיבי או נישתי
-עד כמה המשתמש משדר סגנון תרבותי־עממי בוייב, בטעם ובסגנון האישי — לעומת סגנון פחות עממי ויותר נישתי או מובחן
-חוקים:
-- אם המשתמש משדר סגנון עממי, פתוח, מחובר לתרבות פופולרית → העלה ציון
-- אם המשתמש משדר סגנון נישתי, סלקטיבי או מובחן → הורד ציון
-חובה לנסות לתת ציון פה גם אם אין אינדיקציה ברורה - תנחש לפי הוייב וסגנון הדיבור של המשתמש! לא לתת סתם ציון ממוצע. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">:
-- סגנון שפה (ישיר, עממי, יומיומי לעומת מובחן יותר)
-- וייב כללי של חום, פתיחות ונגישות
-- חיבור לתרבות פופולרית רחבה
-- תחושת "מסתדר עם כולם" לעומת סלקטיביות חברתית
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- טעם מוזיקלי 
-- סגנון שפה 
-- סגנון אישי ותרבותי שמזוהה עם וייב מזרחי
-- זהות מוצהרת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מוצא  ≠ סגנון.
-המטרה לא לזהות האם המשתמש מזרחי או אשכנזי. אם זיהית שהוא מזרחי לפי צבע עור או הצהרה ברורה - זה יכול מעט מאוד להעלות ציון אבל הציון מדבר על הסגנון, לא על קביעת העדה. </t>
-  </si>
-  <si>
-    <t>broad_appeal</t>
-  </si>
-  <si>
-    <t>קרבה למשפחת המוצא</t>
-  </si>
-  <si>
-    <t>family_of_origin_closeness</t>
-  </si>
-  <si>
-    <t>serious_relationship_intent</t>
-  </si>
-  <si>
-    <t>מחפש קשר רציני</t>
-  </si>
-  <si>
-    <t>עד כמה המשתמש מחפש קשר רציני.
-אם מחפש סטוצים בלבד -&gt; הורד ציון.</t>
-  </si>
-  <si>
-    <t>emotional_expressiveness</t>
-  </si>
-  <si>
-    <t>עד כמה המשתמש עסוק ברגשות ונוטה לשיח רגשי.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת רמת דתיות
-עד כמה המשתמש דתי או חילוני, כלומר עד כמה הדת והמסורת מהוות חלק מרכזי באורח החיים, באמונות ובהתנהלות היומיומית שלו.
- יש להעריך את הרצף בין חילוני, מסורתי ודתי
-ככל שמידת הדתיות גבוהה יותר - נגדיר ציון גבוה יותר
-אם המשתמש לא מדבר כלל על הדת אין להניח שהוא בהכרח חילוני, ניתן לתת ציון נמוך בסביבות ה40. </t>
-  </si>
-  <si>
-    <t>דרמטיות/תיאטרליות</t>
-  </si>
-  <si>
-    <t>ימין פוליטי</t>
-  </si>
-  <si>
-    <t>שמאל פוליטי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- הבעת תמיכה בממשלה
-- רמזים עקיפים אך ברורים לעמדות פוליטיות</t>
-  </si>
-  <si>
-    <t>הערכת נטייה פוליטית שמאלנית
-עד כמה המשתמש נוטה לדעות פוליטיות שמאלניות.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערכת נטייה פוליטית ימנית
-עד כמה המשתמש נוטה לדעות פוליטיות ימניות (ביבי, בן גביר וכו'). . </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- ביקורת על הממשלה
-- הפגנות וחברות בארגונים המזוהים עם השמאל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- תשובות מופרכות
-- תשובות לא קשורות ומתחכמות</t>
-  </si>
-  <si>
-    <t>נושא השאלה</t>
-  </si>
-  <si>
-    <t>ה"אנטי" מאץ'</t>
-  </si>
-  <si>
-    <t>"בואי ננסה תרגיל של התבוננות הפוכה: תתארי לי את הדמות שתרגישי איתה הכי פחות בנוח. מה בווייב שלו או באמונות שלו פשוט לא עובר אצלך?"</t>
-  </si>
-  <si>
-    <t>"בואי נהיה רגע חדות – מי הבחור שהכי לא מתאים לך? מה הדעות והאמונות שלו שפוסלות אותו על הסף?"</t>
-  </si>
-  <si>
-    <t>"לפעמים הדיוק מגיע דווקא מהמקום שלא מהדהד איתנו. תתארי לי אדם שהאנרגיה והאמונות שלו מרגישים לך הכי רחוקים מהשורש שלך. מי הוא היה?"</t>
-  </si>
-  <si>
-    <t>קשר אחרון</t>
-  </si>
-  <si>
-    <t>"ספרי לי קצת על הקשר האחרון שלך. מה הרגשת שעבד שם מבחינת החיבור, ואיפה הרגשת שזה כבר לא היה נכון עבורך?"</t>
-  </si>
-  <si>
-    <t>"בואי נלמד מהעבר – מה קרה במערכת היחסים האחרונה שלך? מה עבד בשטח ומה הייתה הנקודה שבה זה הפסיק לעבוד?"</t>
-  </si>
-  <si>
-    <t>"איזה שיעור הביא איתו הקשר האחרון שהיה לך? מה שם הרגיש זורם ובאיזה שלב הרגשת שהחיבור כבר לא מזין אתכם?"</t>
-  </si>
-  <si>
-    <t>מראה עצמי</t>
-  </si>
-  <si>
-    <t>"איך את תופסת את המראה שלך?"</t>
-  </si>
-  <si>
-    <t>"בואי נדבר על המראה שלך, איך היית מתארת אותו?"</t>
-  </si>
-  <si>
-    <t>"איך את מתארת את המעטפת החיצונית שלך, המראה שלך?"</t>
-  </si>
-  <si>
-    <t>מראה - העדפה</t>
-  </si>
-  <si>
-    <t>"וחשוב לי להבין – אילו איכויות חיצוניות בבן זוג גורמות לך להרגיש משיכה או קרבה?"</t>
-  </si>
-  <si>
-    <t>"מה הסטנדרטים שלך לגבי המראה של הצד השני? מה חייב להיות שם?"</t>
-  </si>
-  <si>
-    <t>"ואילו מאפיינים פיזיים בבן זוג מרגישים לך נכונים ומזמינים?"</t>
-  </si>
-  <si>
-    <t>זהות/דיל ברייקר</t>
-  </si>
-  <si>
-    <t>"האם יש משהו מהותי בזהות שלך, או פרט חשוב עלייך, שאת מרגישה שחשוב שאדע לפני שאני מחבר אותך למישהו?"</t>
-  </si>
-  <si>
-    <t>"יש משהו מהותי בזהות שלך או פרט קריטי שחובה לדעת עלייך לפני שאנחנו יוצאים לדרך עם התאמות?"</t>
-  </si>
-  <si>
-    <t>"האם יש משהו בזהות העמוקה שלך, או פרט מהותי עלייך, שחשוב שיקבל ביטוי לפני שאני מחבר בין הנשמה שלך לאחרת?"</t>
-  </si>
-  <si>
-    <t>מיליון דולר</t>
-  </si>
-  <si>
-    <t>"דמייני שמחר את זוכה במיליון דולר. מה הדבר הראשון שתעשי עם הכוח הזה?"</t>
-  </si>
-  <si>
-    <t>"בונוס רציני: זכית במיליון דולר. מה את עושה עם הכסף הזה מחר בבוקר?"</t>
-  </si>
-  <si>
-    <t>"זרימה של שפע הגיעה אליך – מיליון דולר. איך היית משתמשת בהם כדי להיטיב עם חייך?"</t>
-  </si>
-  <si>
-    <t>קוגניציה (קנאה)</t>
-  </si>
-  <si>
-    <t>"שאלה קצת אחרת: דמייני אדם שמעולם לא חווה את הרגש שקוראים לו 'קנאה'. איך היית מסבירה לו את המנגנון הזה, בלי להשתמש במילה עצמה?"</t>
-  </si>
-  <si>
-    <t>"אתגר קטן: תסבירי לי איך המנגנון של 'קנאה' עובד, אבל בלי להשתמש במילה 'קנאה'. איך היית מתארת את התהליך הזה למישהו שלא מכיר אותו?"</t>
-  </si>
-  <si>
-    <t>"בואי ננסה להעמיק במשהו אנושי: איך היית מתארת את התנועה הפנימית שקורה לנו כשאנחנו 'מקנאים', למישהו שמעולם לא הרגיש את זה? (בלי להשתמש במילה המפורשת)."</t>
-  </si>
-  <si>
-    <t>הפסיכולוג</t>
-  </si>
-  <si>
-    <t>הקואצ'רית</t>
-  </si>
-  <si>
-    <t>המנטור הרוחני</t>
-  </si>
-  <si>
-    <t>זהות כללית</t>
-  </si>
-  <si>
-    <t>אמפתי, רפלקטיבי, מתמקד בדפוסים רגשיים ובתהליכי עומק. משתמש במילים כמו: "התבוננות", "מסע", "דפוסים", "חיבור". תגובות הביניים שלו: "אני שומע אותך", "זה נשמע משמעותי</t>
-  </si>
-  <si>
-    <t>ישירה, אנרגטית, ממוקדת תוצאות ומטרות. משתמשת במילים כמו: "חדות", "סטנדרטים", "הצלחה", "דוגרי". תגובות הביניים שלה: "מעולה, בואי נתקדם", "חשוב להיות חדים על זה</t>
-  </si>
-  <si>
-    <t>שליו, מטאפורי, מתמקד בערכים, אינטואיציה וחיבור נשמתי. משתמש במילים כמו: "הדהוד", "שיעור", "שורש", "תדר". תגובות הביניים שלו: "אני מתחבר למה שאמרת", "תודה על השיתוף העמוק</t>
-  </si>
-  <si>
-    <t>שורת פתיחה</t>
-  </si>
-  <si>
-    <t>"שלום חן 🙏
-הדרך למציאת חיבור אמיתי עוברת דרך הקשבה פנימית ודיוק. ככל שתאפשרי לעצמך לענות מהמקום הכי עמוק, פתוח ואמיתי שלך – כך נוכל למצוא אדם שהתדר והערכים שלו מהדהדים עם שלך.
-תרגישי חופשיה לזרום עם התחושות שלך. אם תרגישי צורך בהפסקה, אפשר לעצור לרגע ולהמשיך כשהלב יהיה פנוי לכך שוב.
-חשוב שתדעי שהמילים שלך קדושות עבורי; הן נשארות בינינו בלבד ולא יפורסמו. הן נועדו אך ורק כדי לעזור לי לראות את הנשמה שלך ולחבר אותה לאדם הנכון. אני כאן כדי להקשיב לך ולמהות שאת מביאה
-מוכנה להתחיל?"</t>
-  </si>
-  <si>
-    <t>"היי חן, אני המאמנת שלך למציאת זוגיות! מוכנה לצאת לדרך? 🚀
-המטרה שלנו היא למצוא לך התאמה מדויקת וחזקה, ובשביל זה אני צריכה את המידע הכי חד שיש. ככל שתהיי יותר דוגרי, מפורטת וכנה בתשובות שלך – כך נוכל להגיע לתוצאה טובה יותר ולמצוא מישהו שבאמת מתאים לסטנדרטים שלך.
-זכרי, אם השיחה מתארכת, אפשר לעצור הכל ולהמשיך בזמן אחר. אנחנו כאן כדי לעבוד בשבילך.
-מבחינת פרטיות – הכל נשאר 'בחדר האימונים' שלנו. התשובות שלך לא עוברות לפרופיל הציבורי, הן רק הכלי שלי לנתח את הנתונים ולעשות לך את המאץ' המושלם.
-יוצאות לדרך?"</t>
-  </si>
-  <si>
-    <t>"היי חן, אני שמח ללוות אותך בתהליך הזה. 😊
-כדי שאוכל להבין באמת מי את ומה הלב שלך מחפש, אנחנו צריכים רגע לצלול פנימה ולהכיר לעומק. ככל שתשתפי ביותר פתיחות וכנות, כך נוכל לבנות תמונה מלאה ודיוק רגשי שיוביל אותנו לאדם הנכון עבורך.
-אם תרגישי שזה עמוס מדי, תמיד תוכלי לקחת נשימה, לעצור ולהמשיך כשיהיה לך נוח.
-חשוב שתדעי – השיחה הזו היא מרחב בטוח ופרטי לגמרי. התשובות שלך לא יפורסמו בשום מקום; הן נועדו רק כדי שאוכל להבין את הדפוסים והצרכים שלך ולמצוא לך חיבור אמיתי.
-מרגישה בנוח להתחיל?"</t>
-  </si>
-  <si>
-    <t>ניתוח לפי אקסל תכונות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סוכן משוחח </t>
-  </si>
-  <si>
-    <t>שיחה ראשונית שוטפת</t>
-  </si>
-  <si>
-    <t>כרטיס התאמה</t>
-  </si>
-  <si>
-    <t>בחירת מלווה</t>
-  </si>
-  <si>
-    <t>אחרי MVP:</t>
-  </si>
-  <si>
-    <t>מעבר לג'מיני או מודל אחר</t>
-  </si>
-  <si>
-    <t>מודל משוחח</t>
-  </si>
-  <si>
-    <t>שואל את אותה שאלה לפעמים בחזרה לשיחה</t>
-  </si>
-  <si>
-    <t>חזרה לשיחה</t>
-  </si>
-  <si>
-    <t>לבחור שוב מלווה, ולהתנהג בהתאם - אם חדש -שיחה חדשה, אם ישן - כיף שחזרת ולהמשיך..</t>
-  </si>
-  <si>
-    <t>לסדר אלגוריתם חישוב חיצוני ובהתאם מודל מנתח</t>
-  </si>
-  <si>
-    <t>לעדכן אפיון של המודלים</t>
-  </si>
-  <si>
-    <t>אפיון</t>
-  </si>
-  <si>
-    <t>מנתח</t>
-  </si>
-  <si>
-    <t>אלגוריתם ומשוחח</t>
-  </si>
-  <si>
-    <t>לסדר ציון לשידוך ולוודא שהמשוחח עובד איתו</t>
-  </si>
-  <si>
-    <t>לעשות שאלת טיפוסים</t>
-  </si>
-  <si>
-    <t>משוחח</t>
-  </si>
-  <si>
-    <t>להוסיף דיל ברייקרס נוספים - חרדי, ערבי, דרוזי. מה עוד?</t>
-  </si>
-  <si>
-    <t>להוסיף תכונות חדשות, תכונות מודלים ולסדר משקלים וודאויות</t>
-  </si>
-  <si>
-    <t>קלסטרים של טיפוסים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חלוקה לפרופילים כפי שהגדרתי </t>
-  </si>
-  <si>
-    <t>תכונות מורכבות - סחיות, עממיות.. מה עוד?</t>
-  </si>
-  <si>
-    <t>לסיים בכללי</t>
-  </si>
-  <si>
-    <t>להגיע לפרסום של שלב א'.</t>
-  </si>
-  <si>
-    <t>לתת שורת סיכום טובה</t>
+    <t>קלילות</t>
+  </si>
+  <si>
+    <t>ציניות</t>
+  </si>
+  <si>
+    <t>חמידות /  טוב -לב</t>
+  </si>
+  <si>
+    <t>מצפוניות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נעימות </t>
+  </si>
+  <si>
+    <t>שאר הביג פייב</t>
+  </si>
+  <si>
+    <t>כל מה שקשור בערכים של שוורץ</t>
+  </si>
+  <si>
+    <t>כל מה שקשור בmbti</t>
+  </si>
+  <si>
+    <t>עוד תכונות שיסגרו את החלק הקוגנטיבי</t>
   </si>
 </sst>
 </file>
@@ -4876,7 +4910,7 @@
         <v>421</v>
       </c>
       <c r="B12" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C12" t="s">
         <v>411</v>
@@ -4884,10 +4918,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C13" t="s">
         <v>405</v>
@@ -4895,7 +4929,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4933,7 +4967,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B18" t="s">
         <v>503</v>
@@ -4985,12 +5019,12 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -5953,142 +5987,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.6" thickBot="1">
       <c r="A1" s="54" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B1" s="54" t="s">
+        <v>660</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>661</v>
+      </c>
+      <c r="D1" s="54" t="s">
         <v>662</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>663</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="54" thickBot="1">
       <c r="A2" s="54" t="s">
+        <v>663</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>664</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>665</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="D2" s="53" t="s">
         <v>666</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>667</v>
-      </c>
-      <c r="D2" s="53" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="172.8" thickBot="1">
       <c r="A3" s="54" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>670</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>669</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>672</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>671</v>
-      </c>
       <c r="D3" s="53" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A4" s="53" t="s">
+        <v>632</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>633</v>
+      </c>
+      <c r="C4" s="53" t="s">
         <v>634</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="D4" s="53" t="s">
         <v>635</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>636</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A5" s="53" t="s">
+        <v>636</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>637</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>638</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="D5" s="53" t="s">
         <v>639</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>640</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.6" thickBot="1">
       <c r="A6" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>641</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>642</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="D6" s="53" t="s">
         <v>643</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>644</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.6" thickBot="1">
       <c r="A7" s="53" t="s">
+        <v>644</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>645</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>646</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="D7" s="53" t="s">
         <v>647</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>648</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.6" thickBot="1">
       <c r="A8" s="53" t="s">
+        <v>648</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>649</v>
+      </c>
+      <c r="C8" s="53" t="s">
         <v>650</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="D8" s="53" t="s">
         <v>651</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>652</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.6" thickBot="1">
       <c r="A9" s="53" t="s">
+        <v>652</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>653</v>
+      </c>
+      <c r="C9" s="53" t="s">
         <v>654</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="D9" s="53" t="s">
         <v>655</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>656</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A10" s="53" t="s">
+        <v>656</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>657</v>
+      </c>
+      <c r="C10" s="53" t="s">
         <v>658</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="D10" s="53" t="s">
         <v>659</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>660</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -6122,10 +6156,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C2" t="s">
         <v>411</v>
@@ -6133,66 +6167,66 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B7" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B9" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6200,7 +6234,7 @@
         <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6208,7 +6242,7 @@
         <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6216,15 +6250,15 @@
         <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B14" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6232,7 +6266,7 @@
         <v>415</v>
       </c>
       <c r="B15" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -7958,7 +7992,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="38" customWidth="1"/>
@@ -8139,13 +8173,13 @@
         <v>434</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>605</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>607</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -8167,19 +8201,19 @@
     </row>
     <row r="9" spans="1:14" ht="151.80000000000001">
       <c r="A9" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>434</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>606</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>608</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -8227,22 +8261,22 @@
     </row>
     <row r="11" spans="1:14" ht="138">
       <c r="A11" s="52" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>434</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="2">
@@ -8257,7 +8291,7 @@
     </row>
     <row r="12" spans="1:14" ht="220.8">
       <c r="A12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>434</v>
@@ -8266,10 +8300,10 @@
         <v>393</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="3"/>
@@ -8449,7 +8483,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="3"/>
@@ -8475,7 +8509,7 @@
     </row>
     <row r="19" spans="1:14" ht="43.2">
       <c r="A19" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>435</v>
@@ -8484,7 +8518,7 @@
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="3"/>
@@ -8502,13 +8536,13 @@
     </row>
     <row r="20" spans="1:14" ht="110.4">
       <c r="A20" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>436</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>572</v>
@@ -8538,16 +8572,16 @@
     </row>
     <row r="21" spans="1:14" ht="43.2">
       <c r="A21" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>436</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
@@ -8724,13 +8758,13 @@
         <v>438</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E27" s="33" t="s">
         <v>626</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>628</v>
       </c>
       <c r="F27" s="33"/>
       <c r="G27" s="3"/>
@@ -8749,13 +8783,13 @@
         <v>438</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="33" t="s">
         <v>629</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>631</v>
       </c>
       <c r="F28" s="33"/>
       <c r="G28" s="3"/>
@@ -9144,7 +9178,7 @@
         <v>592</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F42" s="33" t="s">
         <v>564</v>
@@ -9193,7 +9227,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="400.2">
+    <row r="44" spans="1:14" ht="409.6">
       <c r="A44" s="40" t="s">
         <v>275</v>
       </c>
@@ -9204,7 +9238,7 @@
         <v>274</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>600</v>
+        <v>699</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="33" t="s">
@@ -9223,7 +9257,7 @@
       </c>
       <c r="N44" s="34"/>
     </row>
-    <row r="45" spans="1:14" ht="388.8">
+    <row r="45" spans="1:14" ht="409.6">
       <c r="B45" s="2" t="s">
         <v>439</v>
       </c>
@@ -9231,7 +9265,7 @@
         <v>478</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>601</v>
+        <v>700</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>527</v>
@@ -9484,8 +9518,8 @@
       <c r="B56" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>625</v>
+      <c r="C56" s="17" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="110.4">
@@ -9519,6 +9553,54 @@
       </c>
       <c r="K57" s="2"/>
       <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="C58" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="C59" s="3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="C60" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="27.6">
+      <c r="C61" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="C62" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="C63" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="41.4">
+      <c r="C64" s="3" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" ht="27.6">
+      <c r="C65" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" ht="55.2">
+      <c r="C66" s="3" t="s">
+        <v>709</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2522F8B-BB10-43B0-8D0B-5368C395BEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA3D979-4615-4F8F-B582-D01139380743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="718">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -4007,12 +4007,6 @@
     <t>שואל את אותה שאלה לפעמים בחזרה לשיחה</t>
   </si>
   <si>
-    <t>חזרה לשיחה</t>
-  </si>
-  <si>
-    <t>לבחור שוב מלווה, ולהתנהג בהתאם - אם חדש -שיחה חדשה, אם ישן - כיף שחזרת ולהמשיך..</t>
-  </si>
-  <si>
     <t>לסדר אלגוריתם חישוב חיצוני ובהתאם מודל מנתח</t>
   </si>
   <si>
@@ -4138,6 +4132,36 @@
   </si>
   <si>
     <t>עוד תכונות שיסגרו את החלק הקוגנטיבי</t>
+  </si>
+  <si>
+    <t>פסיכולוג</t>
+  </si>
+  <si>
+    <t>לוודא שעושה סיום טוב. לוודא שעובד אחרי החלוקה לסטייג'ס. להוסיף גם סטייג'ים של שיחות שניה-שלישית. לוודא שהניתוח רץ אחרי שיחה</t>
+  </si>
+  <si>
+    <t>מראיין</t>
+  </si>
+  <si>
+    <t>לעדכן בהתאם - להוריד שאלות אישיות, להוריד פניות למנתח, להגביר שאלות סיטואציוניות וכיפיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לעשות גם את החלק של בדיקת הטעם - כרגע לא חובה לחבר למנתח </t>
+  </si>
+  <si>
+    <t>בדיקת טעם</t>
+  </si>
+  <si>
+    <t xml:space="preserve">להעביר למובייל וללטש חווית משתמש: ניסוחים, הסברים, עיצוב, הצגת פרטים למעלה וכו'. </t>
+  </si>
+  <si>
+    <t>סידור ציונים ובר התקדמות</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>להפריד שאלות לדוגמה לסטייג'ס</t>
   </si>
 </sst>
 </file>
@@ -6132,7 +6156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C1EE30-A7E2-4C7A-8C61-FDFDE8F0687C}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -6159,7 +6183,7 @@
         <v>678</v>
       </c>
       <c r="B2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C2" t="s">
         <v>411</v>
@@ -6175,7 +6199,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B4" t="s">
         <v>681</v>
@@ -6183,31 +6207,31 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>684</v>
+      </c>
+      <c r="B6" t="s">
         <v>685</v>
-      </c>
-      <c r="B6" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>687</v>
+      </c>
+      <c r="B7" t="s">
         <v>686</v>
-      </c>
-      <c r="B7" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B8" t="s">
         <v>688</v>
@@ -6215,18 +6239,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>685</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6234,7 +6258,7 @@
         <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6242,12 +6266,12 @@
         <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>682</v>
       </c>
       <c r="B13" t="s">
         <v>693</v>
@@ -6255,18 +6279,55 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>684</v>
+        <v>415</v>
       </c>
       <c r="B14" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>708</v>
+      </c>
+      <c r="B16" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>710</v>
+      </c>
+      <c r="B18" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>716</v>
+      </c>
+      <c r="B19" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>713</v>
+      </c>
+      <c r="B20" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>415</v>
       </c>
-      <c r="B15" t="s">
-        <v>696</v>
+      <c r="B21" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -9238,7 +9299,7 @@
         <v>274</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="33" t="s">
@@ -9265,7 +9326,7 @@
         <v>478</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>527</v>
@@ -9556,50 +9617,50 @@
     </row>
     <row r="58" spans="1:13">
       <c r="C58" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="C59" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="C60" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="27.6">
       <c r="C61" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="C62" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="C63" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="41.4">
       <c r="C64" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="65" spans="3:3" ht="27.6">
       <c r="C65" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="66" spans="3:3" ht="55.2">
       <c r="C66" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA3D979-4615-4F8F-B582-D01139380743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFC3382-B59F-4EC5-9C43-108C845F3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="723">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -4162,6 +4162,21 @@
   </si>
   <si>
     <t>להפריד שאלות לדוגמה לסטייג'ס</t>
+  </si>
+  <si>
+    <t>responsibilty</t>
+  </si>
+  <si>
+    <t>כולל התאמה לאייפון אנדרואיד וכו'</t>
+  </si>
+  <si>
+    <t>יש הצפנות דרך railway, אבל צריך להפריד טבלאות כך שגם אם ייפרץ - יתן כמה שפחות מידע: להימנע משמירת מידע מיותר ולהפריד מידע מפרטים אישיים של המשתמש. לחשוב מה עוד</t>
+  </si>
+  <si>
+    <t>לוודא שאכן הוא יכול לדבר רק דרך פלט בטוח ואין לו גישה לנתונים רגישים שנותחו.  לעשות דשבורד למשתמשים שיוכלו לראות איזה פרטים עליהם הם בטוחים כדי להציג בכרטיס התאמה אולי.</t>
+  </si>
+  <si>
+    <t>קיים בrailway, מורכב של postgreSQL</t>
   </si>
 </sst>
 </file>
@@ -4872,6 +4887,9 @@
       <c r="C6" t="s">
         <v>405</v>
       </c>
+      <c r="D6" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
@@ -4981,15 +4999,18 @@
         <v>502</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>415</v>
       </c>
       <c r="B17" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="D17" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>674</v>
       </c>
@@ -4997,7 +5018,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>415</v>
       </c>
@@ -5005,7 +5026,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>415</v>
       </c>
@@ -5013,7 +5034,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>506</v>
       </c>
@@ -5021,32 +5042,38 @@
         <v>507</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="D23" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="D24" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>677</v>
       </c>
@@ -8053,7 +8080,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="38" customWidth="1"/>
@@ -8063,24 +8090,24 @@
     <col min="5" max="5" width="35.6640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="29.5546875" style="5" customWidth="1"/>
     <col min="7" max="7" width="59" style="5" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" customWidth="1"/>
-    <col min="11" max="11" width="17.77734375" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" customWidth="1"/>
-    <col min="14" max="14" width="40.6640625" customWidth="1"/>
+    <col min="10" max="11" width="12.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="C1" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="C2" s="28" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="27.6">
+    <row r="4" spans="1:15" ht="27.6">
       <c r="A4" s="39" t="s">
         <v>6</v>
       </c>
@@ -8112,19 +8139,22 @@
         <v>62</v>
       </c>
       <c r="K4" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="110.4">
+    <row r="5" spans="1:15" ht="110.4">
       <c r="A5" s="47" t="s">
         <v>426</v>
       </c>
@@ -8149,20 +8179,21 @@
       <c r="J5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="43"/>
+      <c r="L5" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="42">
+      <c r="M5" s="42">
         <v>20</v>
       </c>
-      <c r="M5" s="42" t="s">
+      <c r="N5" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="O5" s="44" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="55.2">
+    <row r="6" spans="1:15" ht="55.2">
       <c r="A6" s="49" t="s">
         <v>441</v>
       </c>
@@ -8189,12 +8220,15 @@
       <c r="J6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="2"/>
+      <c r="K6" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L6" s="3"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="21"/>
-    </row>
-    <row r="7" spans="1:14" ht="317.39999999999998">
+      <c r="N6" s="2"/>
+      <c r="O6" s="21"/>
+    </row>
+    <row r="7" spans="1:15" ht="317.39999999999998">
       <c r="A7" s="40"/>
       <c r="B7" s="2" t="s">
         <v>434</v>
@@ -8219,14 +8253,17 @@
       <c r="J7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
+      <c r="K7" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="N7" s="21"/>
-    </row>
-    <row r="8" spans="1:14" ht="220.8">
+      <c r="O7" s="21"/>
+    </row>
+    <row r="8" spans="1:15" ht="220.8">
       <c r="A8" s="2" t="s">
         <v>440</v>
       </c>
@@ -8254,13 +8291,16 @@
         <v>8</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="151.80000000000001">
+    <row r="9" spans="1:15" ht="151.80000000000001">
       <c r="A9" s="2" t="s">
         <v>601</v>
       </c>
@@ -8285,10 +8325,13 @@
         <v>5</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" ht="96.6">
+      <c r="K9" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="96.6">
       <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
@@ -8315,12 +8358,13 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="138">
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" ht="138">
       <c r="A11" s="52" t="s">
         <v>607</v>
       </c>
@@ -8348,9 +8392,10 @@
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="220.8">
+      <c r="L11" s="3"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" ht="220.8">
       <c r="A12" t="s">
         <v>614</v>
       </c>
@@ -8377,8 +8422,9 @@
       <c r="J12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="138">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" ht="138">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -8405,15 +8451,18 @@
       <c r="J13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="M13" s="2" t="s">
+      <c r="K13" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="N13" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="110.4">
+    <row r="14" spans="1:15" ht="110.4">
       <c r="A14" s="40"/>
       <c r="B14" s="2" t="s">
         <v>424</v>
@@ -8430,10 +8479,13 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="138">
+      <c r="K14" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" ht="138">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -8461,13 +8513,16 @@
         <v>8</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="193.2">
+    <row r="16" spans="1:15" ht="193.2">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -8496,10 +8551,13 @@
       <c r="J16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" ht="110.4">
+      <c r="K16" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" ht="110.4">
       <c r="A17" s="2" t="s">
         <v>429</v>
       </c>
@@ -8529,11 +8587,14 @@
         <v>8</v>
       </c>
       <c r="K17" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" ht="165.6">
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" ht="165.6">
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
@@ -8559,16 +8620,19 @@
         <v>8</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="N18" s="5" t="s">
+      <c r="O18" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="43.2">
+    <row r="19" spans="1:15" ht="43.2">
       <c r="A19" s="2" t="s">
         <v>620</v>
       </c>
@@ -8591,11 +8655,14 @@
         <v>6</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="1:14" ht="110.4">
+      <c r="K19" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" ht="110.4">
       <c r="A20" s="2" t="s">
         <v>616</v>
       </c>
@@ -8625,13 +8692,16 @@
         <v>14</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="43.2">
+    <row r="21" spans="1:15" ht="43.2">
       <c r="A21" s="2" t="s">
         <v>617</v>
       </c>
@@ -8650,10 +8720,13 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="2"/>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="248.4">
+      <c r="K21" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" ht="248.4">
       <c r="A22" s="49" t="s">
         <v>47</v>
       </c>
@@ -8680,10 +8753,11 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="2"/>
-      <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" ht="207">
+      <c r="K22" s="3"/>
+      <c r="L22" s="2"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" ht="207">
       <c r="A23" s="2" t="s">
         <v>347</v>
       </c>
@@ -8713,11 +8787,14 @@
         <v>8</v>
       </c>
       <c r="K23" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" ht="82.8">
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" ht="82.8">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -8742,12 +8819,13 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="3"/>
+      <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" ht="124.2">
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" ht="124.2">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -8775,11 +8853,14 @@
         <v>8</v>
       </c>
       <c r="K25" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:14" ht="193.2">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" ht="193.2">
       <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
@@ -8806,15 +8887,16 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="K26" s="3"/>
+      <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" t="s">
+      <c r="N26" s="2"/>
+      <c r="O26" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="55.2">
+    <row r="27" spans="1:15" ht="55.2">
       <c r="B27" s="2" t="s">
         <v>438</v>
       </c>
@@ -8838,8 +8920,9 @@
       <c r="J27" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="55.2">
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:15" ht="55.2">
       <c r="B28" s="2" t="s">
         <v>438</v>
       </c>
@@ -8861,8 +8944,9 @@
         <v>3</v>
       </c>
       <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:14" ht="124.2">
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" ht="124.2">
       <c r="A29" s="49" t="s">
         <v>40</v>
       </c>
@@ -8887,10 +8971,13 @@
       <c r="J29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K29" s="2"/>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="1:14" ht="82.8">
+      <c r="K29" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" ht="82.8">
       <c r="A30" s="2" t="s">
         <v>41</v>
       </c>
@@ -8917,10 +9004,11 @@
       <c r="J30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K30" s="2"/>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" ht="138">
+      <c r="K30" s="3"/>
+      <c r="L30" s="2"/>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" ht="138">
       <c r="A31" s="2" t="s">
         <v>43</v>
       </c>
@@ -8949,10 +9037,11 @@
       <c r="J31" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K31" s="2"/>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" ht="151.80000000000001">
+      <c r="K31" s="3"/>
+      <c r="L31" s="2"/>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" ht="151.80000000000001">
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
@@ -8981,14 +9070,15 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="K32" s="3"/>
+      <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="262.2">
+    <row r="33" spans="1:15" ht="262.2">
       <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
@@ -9013,10 +9103,11 @@
       <c r="J33" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:14" ht="193.2">
+      <c r="K33" s="3"/>
+      <c r="L33" s="2"/>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" ht="193.2">
       <c r="B34" s="2" t="s">
         <v>436</v>
       </c>
@@ -9038,8 +9129,9 @@
       <c r="J34" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="207">
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:15" ht="207">
       <c r="B35" s="2" t="s">
         <v>438</v>
       </c>
@@ -9063,8 +9155,9 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="207">
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:15" ht="207">
       <c r="A36" s="2" t="s">
         <v>53</v>
       </c>
@@ -9087,12 +9180,13 @@
       <c r="J36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="3"/>
+      <c r="L36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="1:14" ht="124.2">
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:15" ht="124.2">
       <c r="B37" s="2" t="s">
         <v>434</v>
       </c>
@@ -9116,8 +9210,9 @@
       <c r="J37" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="151.80000000000001">
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:15" ht="151.80000000000001">
       <c r="B38" s="2" t="s">
         <v>434</v>
       </c>
@@ -9141,8 +9236,9 @@
       <c r="J38" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="165.6">
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:15" ht="165.6">
       <c r="B39" s="2" t="s">
         <v>434</v>
       </c>
@@ -9166,8 +9262,9 @@
       <c r="J39" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="179.4">
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="1:15" ht="179.4">
       <c r="A40" s="51"/>
       <c r="B40" s="41" t="s">
         <v>434</v>
@@ -9192,8 +9289,9 @@
       <c r="J40" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="248.4">
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:15" ht="248.4">
       <c r="A41" s="2" t="s">
         <v>60</v>
       </c>
@@ -9220,12 +9318,13 @@
       <c r="J41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="K41" s="3"/>
+      <c r="L41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="1:14" ht="110.4">
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="1:15" ht="110.4">
       <c r="A42" s="2" t="s">
         <v>120</v>
       </c>
@@ -9252,11 +9351,12 @@
       <c r="J42" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="K42" s="3"/>
+      <c r="L42" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="138">
+    <row r="43" spans="1:15" ht="138">
       <c r="A43" s="2" t="s">
         <v>277</v>
       </c>
@@ -9281,14 +9381,17 @@
         <v>9</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="M43" s="19"/>
-      <c r="N43" s="3" t="s">
+      <c r="N43" s="19"/>
+      <c r="O43" s="3" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="409.6">
+    <row r="44" spans="1:15" ht="409.6">
       <c r="A44" s="40" t="s">
         <v>275</v>
       </c>
@@ -9314,11 +9417,14 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="N44" s="34"/>
-    </row>
-    <row r="45" spans="1:14" ht="409.6">
+      <c r="O44" s="34"/>
+    </row>
+    <row r="45" spans="1:15" ht="409.6">
       <c r="B45" s="2" t="s">
         <v>439</v>
       </c>
@@ -9340,326 +9446,341 @@
       <c r="J45" t="s">
         <v>14</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
-      <c r="C47" s="36" t="s">
+    <row r="46" spans="1:15">
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="H46" s="2"/>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="C67" s="36" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="69">
-      <c r="A48" s="40" t="s">
+    <row r="68" spans="1:15" ht="69">
+      <c r="A68" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="3" t="s">
+      <c r="B68" s="2"/>
+      <c r="C68" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="2">
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="2">
         <v>0.7</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I68" s="2">
         <v>8</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="K68" s="3"/>
+      <c r="L68" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="M68" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="N68" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O68" s="3" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="27.6">
-      <c r="A49" s="40" t="s">
+    <row r="69" spans="1:15" ht="27.6">
+      <c r="A69" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="3" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="2">
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="2">
         <v>0.5</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I69" s="2">
         <v>5</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K69" s="3"/>
+      <c r="L69" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="55.2">
-      <c r="A50" s="40" t="s">
+    <row r="70" spans="1:15" ht="55.2">
+      <c r="A70" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="3" t="s">
+      <c r="B70" s="2"/>
+      <c r="C70" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="2">
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="2">
         <v>0.6</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I70" s="2">
         <v>5</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="K70" s="3"/>
+      <c r="L70" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M50" s="2"/>
-    </row>
-    <row r="51" spans="1:13" ht="41.4">
-      <c r="A51" s="40" t="s">
+      <c r="N70" s="2"/>
+    </row>
+    <row r="71" spans="1:15" ht="41.4">
+      <c r="A71" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="2">
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="2">
         <v>0.5</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I71" s="2">
         <v>4</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J71" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="K71" s="3"/>
+      <c r="L71" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M51" s="2"/>
-    </row>
-    <row r="52" spans="1:13" ht="27.6">
-      <c r="A52" s="40" t="s">
+      <c r="N71" s="2"/>
+    </row>
+    <row r="72" spans="1:15" ht="27.6">
+      <c r="A72" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="2">
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="2">
         <v>0.3</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I72" s="2">
         <v>4</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:13" ht="151.80000000000001">
-      <c r="B53" s="2" t="s">
+      <c r="K72" s="3"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:15" ht="151.80000000000001">
+      <c r="B73" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E53" s="33" t="s">
+      <c r="E73" s="33" t="s">
         <v>552</v>
       </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="2">
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="2">
         <v>0.2</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I73" s="2">
         <v>2</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J73" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="165.6">
-      <c r="B54" s="2" t="s">
+      <c r="K73" s="3"/>
+    </row>
+    <row r="74" spans="1:15" ht="165.6">
+      <c r="B74" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E54" s="33" t="s">
+      <c r="E74" s="33" t="s">
         <v>556</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F74" s="33" t="s">
         <v>557</v>
       </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="2">
+      <c r="G74" s="3"/>
+      <c r="H74" s="2">
         <v>0.2</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I74" s="2">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="82.8">
-      <c r="B55" s="2" t="s">
+      <c r="K74" s="3"/>
+    </row>
+    <row r="75" spans="1:15" ht="82.8">
+      <c r="B75" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="2">
+      <c r="G75" s="3"/>
+      <c r="H75" s="2">
         <v>0.2</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I75" s="2">
         <v>3</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J75" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M55" s="2"/>
-    </row>
-    <row r="56" spans="1:13" ht="27.6">
-      <c r="B56" s="2" t="s">
+      <c r="K75" s="3"/>
+      <c r="N75" s="2"/>
+    </row>
+    <row r="76" spans="1:15" ht="27.6">
+      <c r="B76" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C76" s="17" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="110.4">
-      <c r="A57" s="2" t="s">
+    <row r="77" spans="1:15" ht="110.4">
+      <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="E57" s="33" t="s">
+      <c r="E77" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="F57" s="33" t="s">
+      <c r="F77" s="33" t="s">
         <v>577</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="2">
+      <c r="G77" s="3"/>
+      <c r="H77" s="2">
         <v>0.6</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I77" s="2">
         <v>4</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J77" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="2"/>
-      <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="C58" s="3" t="s">
+      <c r="K77" s="3"/>
+      <c r="L77" s="2"/>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="C78" s="3" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
-      <c r="C59" s="3" t="s">
+    <row r="79" spans="1:15">
+      <c r="C79" s="3" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
-      <c r="C60" s="3" t="s">
+    <row r="80" spans="1:15">
+      <c r="C80" s="3" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="27.6">
-      <c r="C61" s="3" t="s">
+    <row r="81" spans="3:4" ht="27.6">
+      <c r="C81" s="3" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
-      <c r="C62" s="3" t="s">
+    <row r="82" spans="3:4">
+      <c r="C82" s="3" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
-      <c r="C63" s="3" t="s">
+    <row r="83" spans="3:4">
+      <c r="C83" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D83" s="5" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="41.4">
-      <c r="C64" s="3" t="s">
+    <row r="84" spans="3:4" ht="41.4">
+      <c r="C84" s="3" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="65" spans="3:3" ht="27.6">
-      <c r="C65" s="3" t="s">
+    <row r="85" spans="3:4" ht="27.6">
+      <c r="C85" s="3" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="66" spans="3:3" ht="55.2">
-      <c r="C66" s="3" t="s">
+    <row r="86" spans="3:4" ht="55.2">
+      <c r="C86" s="3" t="s">
         <v>707</v>
       </c>
     </row>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFC3382-B59F-4EC5-9C43-108C845F3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F3FB5B-31B6-4A8A-99F6-CBA9FD61CA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="747">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -4177,6 +4177,78 @@
   </si>
   <si>
     <t>קיים בrailway, מורכב של postgreSQL</t>
+  </si>
+  <si>
+    <t>Emotional Intensity</t>
+  </si>
+  <si>
+    <t>Communication Softness</t>
+  </si>
+  <si>
+    <t>Tonal Balance</t>
+  </si>
+  <si>
+    <t>שילוב</t>
+  </si>
+  <si>
+    <t>Tonal Stability</t>
+  </si>
+  <si>
+    <t>Depth Authenticity</t>
+  </si>
+  <si>
+    <t>Cliché Density</t>
+  </si>
+  <si>
+    <t>Authenticity</t>
+  </si>
+  <si>
+    <t>Communication Style</t>
+  </si>
+  <si>
+    <t>לא ברור מה הרמות פה</t>
+  </si>
+  <si>
+    <t>Refinement Level</t>
+  </si>
+  <si>
+    <t>Cognitive Signal in Humor</t>
+  </si>
+  <si>
+    <t>Humor Depth</t>
+  </si>
+  <si>
+    <t>Signal Coherence</t>
+  </si>
+  <si>
+    <t>Verbal Precision</t>
+  </si>
+  <si>
+    <t>Depth of Expression</t>
+  </si>
+  <si>
+    <t>Emotional Authenticity</t>
+  </si>
+  <si>
+    <t>Multi-Dimensionality</t>
+  </si>
+  <si>
+    <t>Intent Expression Style</t>
+  </si>
+  <si>
+    <t>Communication Clarity</t>
+  </si>
+  <si>
+    <t>Communication Structure</t>
+  </si>
+  <si>
+    <t>Communication Refinement</t>
+  </si>
+  <si>
+    <t>Cultural / Style Signal</t>
+  </si>
+  <si>
+    <t>גם כאן לא ברור מה הרמות</t>
   </si>
 </sst>
 </file>
@@ -8080,7 +8152,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="38" customWidth="1"/>
@@ -9751,17 +9823,17 @@
         <v>700</v>
       </c>
     </row>
-    <row r="81" spans="3:4" ht="27.6">
+    <row r="81" spans="3:5" ht="27.6">
       <c r="C81" s="3" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="82" spans="3:4">
+    <row r="82" spans="3:5">
       <c r="C82" s="3" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="83" spans="3:4">
+    <row r="83" spans="3:5">
       <c r="C83" s="3" t="s">
         <v>703</v>
       </c>
@@ -9769,19 +9841,138 @@
         <v>704</v>
       </c>
     </row>
-    <row r="84" spans="3:4" ht="41.4">
+    <row r="84" spans="3:5" ht="41.4">
       <c r="C84" s="3" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="85" spans="3:4" ht="27.6">
+    <row r="85" spans="3:5" ht="27.6">
       <c r="C85" s="3" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="86" spans="3:4" ht="55.2">
+    <row r="86" spans="3:5" ht="55.2">
       <c r="C86" s="3" t="s">
         <v>707</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5">
+      <c r="D87" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5">
+      <c r="D88" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5">
+      <c r="D89" t="s">
+        <v>725</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5">
+      <c r="D90" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5">
+      <c r="D91" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5">
+      <c r="D92" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5">
+      <c r="D93" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5">
+      <c r="D94" t="s">
+        <v>731</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5">
+      <c r="D95" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5">
+      <c r="D96" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="97" spans="4:5">
+      <c r="D97" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="98" spans="4:5">
+      <c r="D98" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="99" spans="4:5">
+      <c r="D99" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="100" spans="4:5">
+      <c r="D100" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="101" spans="4:5">
+      <c r="D101" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="102" spans="4:5">
+      <c r="D102" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="103" spans="4:5">
+      <c r="D103" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="104" spans="4:5">
+      <c r="D104" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="105" spans="4:5">
+      <c r="D105" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="106" spans="4:5">
+      <c r="D106" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="107" spans="4:5">
+      <c r="D107" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="108" spans="4:5">
+      <c r="D108" t="s">
+        <v>745</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>746</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F3FB5B-31B6-4A8A-99F6-CBA9FD61CA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49427923-2CF7-4FC1-B07C-426E088E056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="749">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -4249,6 +4249,12 @@
   </si>
   <si>
     <t>גם כאן לא ברור מה הרמות</t>
+  </si>
+  <si>
+    <t>גיבויים אוטומטים</t>
+  </si>
+  <si>
+    <t>הפרדה בין טסט לפרוד</t>
   </si>
 </sst>
 </file>
@@ -4876,7 +4882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -5140,13 +5146,23 @@
         <v>512</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>677</v>
       </c>
     </row>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC5BE17-AEB0-4852-AFCB-9947326E2580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5207FE-9385-4B26-B01B-82819AC295A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="815">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3033,6 +3033,9 @@
 - low self-awareness
 - impression management
 - or limited introspection</t>
+  </si>
+  <si>
+    <t>מידת חילוניות</t>
   </si>
 </sst>
 </file>
@@ -5759,7 +5762,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -6866,19 +6869,16 @@
         <v>799</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="69">
+    <row r="60" spans="1:11">
       <c r="A60" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="C60" s="38"/>
-      <c r="D60" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>792</v>
+      <c r="C60" s="2"/>
+      <c r="D60" s="17" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="69">
@@ -6890,13 +6890,13 @@
       </c>
       <c r="C61" s="38"/>
       <c r="D61" s="3" t="s">
-        <v>422</v>
+        <v>383</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="27.6">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="69">
       <c r="A62" s="2" t="s">
         <v>425</v>
       </c>
@@ -6905,38 +6905,39 @@
       </c>
       <c r="C62" s="38"/>
       <c r="D62" s="3" t="s">
-        <v>334</v>
+        <v>422</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="82.8">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="27.6">
       <c r="A63" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="D63" s="33" t="s">
+      <c r="C63" s="38"/>
+      <c r="D63" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="82.8">
+      <c r="A64" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="D64" s="33" t="s">
         <v>387</v>
       </c>
-      <c r="E63" s="33" t="s">
+      <c r="E64" s="33" t="s">
         <v>795</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -6946,25 +6947,25 @@
       <c r="B65" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="C65" t="s">
-        <v>801</v>
-      </c>
-      <c r="D65" s="56" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="28.8">
+      <c r="C65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>561</v>
+      <c r="C66" t="s">
+        <v>801</v>
+      </c>
+      <c r="D66" s="56" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8">
@@ -6975,16 +6976,13 @@
         <v>800</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>48</v>
+        <v>560</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="82.8">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="28.8">
       <c r="A68" s="2" t="s">
         <v>430</v>
       </c>
@@ -6992,16 +6990,16 @@
         <v>800</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>802</v>
+        <v>48</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="69">
+        <v>49</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="82.8">
       <c r="A69" s="2" t="s">
         <v>430</v>
       </c>
@@ -7009,16 +7007,16 @@
         <v>800</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="55.2">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="69">
       <c r="A70" s="2" t="s">
         <v>430</v>
       </c>
@@ -7026,16 +7024,16 @@
         <v>800</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>541</v>
+        <v>114</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="409.6">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="55.2">
       <c r="A71" s="2" t="s">
         <v>430</v>
       </c>
@@ -7043,12 +7041,29 @@
         <v>800</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="409.6">
+      <c r="A72" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>700</v>
       </c>
     </row>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5207FE-9385-4B26-B01B-82819AC295A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EFD0DB-0246-4060-9A44-E66728482D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,6 @@
     <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="808">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -2814,45 +2813,15 @@
     <t>רוחניות</t>
   </si>
   <si>
-    <t>Analytical Thinking</t>
-  </si>
-  <si>
     <t>Abstract Thinking</t>
   </si>
   <si>
     <t>Cognitive Flexibility</t>
   </si>
   <si>
-    <t>Verbal Reasoning</t>
-  </si>
-  <si>
-    <t>Depth of Thought</t>
-  </si>
-  <si>
-    <t>Intellectual Openness</t>
-  </si>
-  <si>
-    <t>Conceptual Clarity</t>
-  </si>
-  <si>
-    <t>Pattern Recognition</t>
-  </si>
-  <si>
-    <t>זיהוי דפוסים</t>
-  </si>
-  <si>
     <t>בהירות מושגית</t>
   </si>
   <si>
-    <t>פתיחות אינטלקטואלית</t>
-  </si>
-  <si>
-    <t>עומק מחשבתי</t>
-  </si>
-  <si>
-    <t>הסקה מילולית</t>
-  </si>
-  <si>
     <t>גמישות מחשבתית</t>
   </si>
   <si>
@@ -2866,9 +2835,6 @@
   </si>
   <si>
     <t>Intellectualism</t>
-  </si>
-  <si>
-    <t>Verbal Expression Ability</t>
   </si>
   <si>
     <t>Directness</t>
@@ -3015,17 +2981,6 @@
 - indirect expression (e.g. sarcasm)</t>
   </si>
   <si>
-    <t>Analytical Thinking should be based on evidence of structured reasoning:
-- breaking down situations into components
-- explaining cause and effect
-- identifying mechanisms or underlying structure
-Do NOT base this trait on:
-- general clarity
-- emotional understanding
-- social reasoning
-- politeness or balanced answers</t>
-  </si>
-  <si>
     <t>Self-awareness is indicated by the ability to recognize and articulate one's own weaknesses, emotional patterns, and internal conflicts.
 Users who openly describe their own flaws, reactivity, or emotional struggles should be scored higher in self-awareness.
 Do NOT assume that a user who presents only positive, balanced, or socially desirable responses has high self-awareness.
@@ -3036,6 +2991,21 @@
   </si>
   <si>
     <t>מידת חילוניות</t>
+  </si>
+  <si>
+    <t>Analytical Reasoning</t>
+  </si>
+  <si>
+    <t>Conceptual Precision</t>
+  </si>
+  <si>
+    <t>Verbal Articulation</t>
+  </si>
+  <si>
+    <t>אינטיליגנציה חברתית-אינטואיטיבית</t>
+  </si>
+  <si>
+    <t>פרופיל אנליטי</t>
   </si>
 </sst>
 </file>
@@ -3242,7 +3212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3389,7 +3359,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5762,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -5798,7 +5767,7 @@
         <v>413</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>6</v>
@@ -5810,7 +5779,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>3</v>
@@ -5837,22 +5806,20 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="151.80000000000001">
+    <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="2" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="C5" t="s">
-        <v>753</v>
+        <v>803</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>812</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -5862,16 +5829,16 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="C6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -5883,16 +5850,16 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="2" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="C7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -5904,16 +5871,16 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="C8" t="s">
-        <v>756</v>
+        <v>804</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -5923,16 +5890,16 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="2" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C9" t="s">
-        <v>757</v>
+        <v>767</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>764</v>
+        <v>639</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -5944,14 +5911,10 @@
       <c r="A10" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C10" t="s">
-        <v>758</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="3" t="s">
-        <v>763</v>
+        <v>806</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -5964,13 +5927,13 @@
         <v>715</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C11" t="s">
-        <v>759</v>
+        <v>767</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>760</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>762</v>
+        <v>435</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -5978,37 +5941,40 @@
       <c r="H11" s="3"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="28.8">
+    <row r="12" spans="1:14" ht="331.2">
       <c r="A12" s="2" t="s">
         <v>715</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C12" t="s">
-        <v>760</v>
+        <v>767</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>759</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>436</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>798</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="2"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>778</v>
+        <v>763</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>435</v>
+        <v>665</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>764</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -6016,18 +5982,18 @@
       <c r="H13" s="3"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="28.8">
+    <row r="14" spans="1:14" ht="27.6">
       <c r="A14" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>778</v>
+        <v>763</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>639</v>
+        <v>768</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -6035,135 +6001,132 @@
       <c r="H14" s="3"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:14" ht="28.8">
+    <row r="15" spans="1:14" ht="27.6">
       <c r="A15" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>778</v>
+        <v>763</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>765</v>
       </c>
       <c r="C15" t="s">
-        <v>683</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>711</v>
+        <v>761</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="331.2">
+    <row r="16" spans="1:14" ht="27.6">
       <c r="A16" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C16" t="s">
+        <v>666</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>809</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="28.8">
+    </row>
+    <row r="17" spans="1:11" ht="27.6">
       <c r="A17" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D17" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C17" t="s">
+        <v>671</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>775</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="2"/>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:11" ht="27.6">
       <c r="A18" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>704</v>
+        <v>765</v>
+      </c>
+      <c r="C18" t="s">
+        <v>785</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>701</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="J18" s="2"/>
+      <c r="K18" s="34"/>
     </row>
     <row r="19" spans="1:11" ht="27.6">
       <c r="A19" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="C19" t="s">
-        <v>772</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>773</v>
+        <v>786</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>702</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="K19" s="34"/>
     </row>
     <row r="20" spans="1:11" ht="27.6">
       <c r="A20" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="C20" t="s">
-        <v>666</v>
+        <v>787</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>707</v>
+        <v>22</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="27.6">
+      <c r="H20" s="3"/>
+      <c r="K20" s="34"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>774</v>
+        <v>693</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C21" t="s">
-        <v>671</v>
+        <v>769</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>786</v>
+        <v>697</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -6171,75 +6134,79 @@
       <c r="H21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="27.6">
+    <row r="22" spans="1:11" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>774</v>
+        <v>693</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C22" t="s">
-        <v>796</v>
+        <v>769</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>701</v>
+        <v>643</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="K22" s="34"/>
-    </row>
-    <row r="23" spans="1:11" ht="27.6">
+      <c r="H22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
-        <v>774</v>
+        <v>693</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C23" t="s">
-        <v>797</v>
+        <v>716</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>702</v>
+        <v>644</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="K23" s="34"/>
-    </row>
-    <row r="24" spans="1:11" ht="27.6">
+      <c r="H23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
-        <v>774</v>
+        <v>693</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C24" t="s">
-        <v>798</v>
+        <v>718</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>22</v>
+        <v>719</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="K24" s="34"/>
+      <c r="H24" s="2"/>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>696</v>
+        <v>769</v>
+      </c>
+      <c r="C25" t="s">
+        <v>720</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -6247,823 +6214,743 @@
       <c r="H25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="28.8">
+    <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+        <v>770</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>723</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>731</v>
+      </c>
+      <c r="F26" s="56" t="s">
+        <v>425</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>716</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
-        <v>426</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E27" s="56" t="s">
+        <v>730</v>
+      </c>
+      <c r="F27" s="56"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="2"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3" t="s">
-        <v>426</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>729</v>
+      </c>
+      <c r="F28" s="56"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+        <v>734</v>
+      </c>
+      <c r="E29" s="56" t="s">
+        <v>737</v>
+      </c>
+      <c r="F29" s="56"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="2"/>
-      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>723</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E30" s="57" t="s">
-        <v>731</v>
-      </c>
-      <c r="F30" s="57" t="s">
-        <v>425</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>733</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>736</v>
+      </c>
+      <c r="F30" s="56"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="2"/>
-      <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>725</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="E31" s="57" t="s">
-        <v>730</v>
-      </c>
-      <c r="F31" s="57"/>
+        <v>770</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>738</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>739</v>
+      </c>
+      <c r="F31" s="56"/>
       <c r="G31" s="3"/>
-      <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>727</v>
+        <v>770</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>544</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>729</v>
-      </c>
-      <c r="F32" s="57"/>
+        <v>543</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>740</v>
+      </c>
+      <c r="F32" s="56"/>
       <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C33" s="57" t="s">
-        <v>732</v>
+        <v>770</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>743</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="E33" s="57" t="s">
-        <v>737</v>
-      </c>
-      <c r="F33" s="57"/>
+        <v>742</v>
+      </c>
+      <c r="E33" s="56" t="s">
+        <v>741</v>
+      </c>
+      <c r="F33" s="56"/>
       <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>733</v>
+        <v>770</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>744</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="E34" s="57" t="s">
-        <v>736</v>
-      </c>
-      <c r="F34" s="57"/>
+        <v>745</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>748</v>
+      </c>
+      <c r="F34" s="56"/>
       <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C35" s="57" t="s">
-        <v>738</v>
+        <v>770</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>746</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="E35" s="57" t="s">
-        <v>739</v>
-      </c>
-      <c r="F35" s="57"/>
+        <v>747</v>
+      </c>
+      <c r="E35" s="56" t="s">
+        <v>749</v>
+      </c>
+      <c r="F35" s="56"/>
       <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C36" s="57" t="s">
-        <v>544</v>
+        <v>770</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>751</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="E36" s="57" t="s">
-        <v>740</v>
-      </c>
-      <c r="F36" s="57"/>
+        <v>752</v>
+      </c>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:11">
+    </row>
+    <row r="37" spans="1:11" ht="28.8">
       <c r="A37" s="2" t="s">
-        <v>782</v>
+        <v>426</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C37" s="57" t="s">
-        <v>743</v>
+        <v>772</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>432</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="E37" s="57" t="s">
-        <v>741</v>
-      </c>
-      <c r="F37" s="57"/>
+        <v>414</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" ht="220.8">
       <c r="A38" s="2" t="s">
-        <v>782</v>
+        <v>426</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C38" s="57" t="s">
-        <v>744</v>
+        <v>772</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="E38" s="57" t="s">
-        <v>748</v>
-      </c>
-      <c r="F38" s="57"/>
+        <v>29</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" ht="28.8">
       <c r="A39" s="2" t="s">
-        <v>782</v>
+        <v>426</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>746</v>
+        <v>772</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="E39" s="57" t="s">
-        <v>749</v>
-      </c>
-      <c r="F39" s="57"/>
+        <v>57</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="H39" s="3"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>782</v>
+        <v>426</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C40" s="57" t="s">
-        <v>751</v>
+        <v>772</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>752</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:11" ht="28.8">
       <c r="A41" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="C41" s="49" t="s">
-        <v>432</v>
+        <v>772</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>414</v>
+        <v>39</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:11" ht="220.8">
+      <c r="H41" s="3"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" ht="28.8">
       <c r="A42" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>772</v>
+      </c>
+      <c r="C42" t="s">
+        <v>664</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>813</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" ht="28.8">
-      <c r="A43" s="2" t="s">
+      <c r="H42" s="3"/>
+      <c r="K42" s="34"/>
+    </row>
+    <row r="43" spans="1:11" ht="179.4">
+      <c r="A43" s="40" t="s">
         <v>426</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>564</v>
+      <c r="B43" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>799</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>800</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" ht="28.8">
+      <c r="K43" s="34"/>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+        <v>776</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>545</v>
+      </c>
+      <c r="E44" s="17"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:11" ht="28.8">
+    <row r="45" spans="1:11">
       <c r="A45" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>38</v>
+        <v>776</v>
+      </c>
+      <c r="C45" s="49" t="s">
+        <v>550</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="1:11" ht="28.8">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="C46" t="s">
-        <v>664</v>
+        <v>557</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="K46" s="34"/>
-    </row>
-    <row r="47" spans="1:11" ht="179.4">
-      <c r="A47" s="40" t="s">
-        <v>426</v>
-      </c>
-      <c r="B47" s="37" t="s">
-        <v>783</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>810</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>811</v>
-      </c>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="K47" s="34"/>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="48" spans="1:11" ht="28.8">
       <c r="A48" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C48" s="49" t="s">
-        <v>431</v>
-      </c>
-      <c r="D48" s="48" t="s">
-        <v>545</v>
-      </c>
-      <c r="E48" s="17"/>
+        <v>776</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>550</v>
+        <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>43</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C50" t="s">
-        <v>557</v>
+        <v>776</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>32</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>44</v>
+        <v>777</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>350</v>
+        <v>567</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="17"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="1:11" ht="28.8">
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>559</v>
+        <v>778</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:11">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>42</v>
+        <v>774</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:11">
+        <v>16</v>
+      </c>
+      <c r="D54" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:11">
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>776</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="17" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="69">
       <c r="A57" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C57" s="49" t="s">
-        <v>785</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="C57" s="38"/>
       <c r="D57" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>383</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="69">
       <c r="A58" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="56" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>776</v>
+      </c>
+      <c r="C58" s="38"/>
+      <c r="D58" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27.6">
       <c r="A59" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="C59" s="38"/>
       <c r="D59" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>334</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="82.8">
       <c r="A60" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="17" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="69">
+        <v>776</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C61" s="38"/>
+        <v>789</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="D61" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="69">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C62" s="38"/>
-      <c r="D62" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="27.6">
+        <v>789</v>
+      </c>
+      <c r="C62" t="s">
+        <v>790</v>
+      </c>
+      <c r="D62" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="28.8">
       <c r="A63" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="C63" s="38"/>
+        <v>789</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>560</v>
+      </c>
       <c r="D63" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="82.8">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="D64" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="E64" s="33" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>789</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="82.8">
       <c r="A65" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>46</v>
+        <v>791</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>56</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="69">
       <c r="A66" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C66" t="s">
-        <v>801</v>
-      </c>
-      <c r="D66" s="56" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="28.8">
+        <v>789</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="55.2">
       <c r="A67" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>560</v>
+        <v>796</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="28.8">
+        <v>541</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="409.6">
       <c r="A68" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>48</v>
+        <v>797</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="82.8">
-      <c r="A69" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="69">
-      <c r="A70" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="55.2">
-      <c r="A71" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="409.6">
-      <c r="A72" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="D72" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7378,7 +7265,7 @@
       <c r="K11" s="3"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="220.8">
+    <row r="12" spans="1:14" ht="207">
       <c r="A12" s="2" t="s">
         <v>425</v>
       </c>
@@ -7915,7 +7802,7 @@
         <v>429</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>35</v>
@@ -8217,7 +8104,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="193.2">
+    <row r="40" spans="1:14" ht="179.4">
       <c r="A40" s="41" t="s">
         <v>425</v>
       </c>
@@ -8458,7 +8345,7 @@
       <c r="A55" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" t="s">
         <v>716</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -8576,13 +8463,13 @@
       <c r="A66" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B66" s="57" t="s">
+      <c r="B66" s="56" t="s">
         <v>723</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="D66" s="57" t="s">
+      <c r="D66" s="56" t="s">
         <v>731</v>
       </c>
     </row>
@@ -8590,13 +8477,13 @@
       <c r="A67" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="56" t="s">
         <v>725</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="D67" s="57" t="s">
+      <c r="D67" s="56" t="s">
         <v>730</v>
       </c>
     </row>
@@ -8604,13 +8491,13 @@
       <c r="A68" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B68" s="57" t="s">
+      <c r="B68" s="56" t="s">
         <v>727</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="D68" s="57" t="s">
+      <c r="D68" s="56" t="s">
         <v>729</v>
       </c>
     </row>
@@ -8618,13 +8505,13 @@
       <c r="A69" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B69" s="57" t="s">
+      <c r="B69" s="56" t="s">
         <v>732</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="56" t="s">
         <v>737</v>
       </c>
     </row>
@@ -8632,13 +8519,13 @@
       <c r="A70" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="56" t="s">
         <v>733</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="D70" s="57" t="s">
+      <c r="D70" s="56" t="s">
         <v>736</v>
       </c>
     </row>
@@ -8646,13 +8533,13 @@
       <c r="A71" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B71" s="57" t="s">
+      <c r="B71" s="56" t="s">
         <v>738</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="D71" s="57" t="s">
+      <c r="D71" s="56" t="s">
         <v>739</v>
       </c>
     </row>
@@ -8660,13 +8547,13 @@
       <c r="A72" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B72" s="57" t="s">
+      <c r="B72" s="56" t="s">
         <v>544</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D72" s="57" t="s">
+      <c r="D72" s="56" t="s">
         <v>740</v>
       </c>
     </row>
@@ -8674,13 +8561,13 @@
       <c r="A73" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B73" s="57" t="s">
+      <c r="B73" s="56" t="s">
         <v>743</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="56" t="s">
         <v>741</v>
       </c>
     </row>
@@ -8688,13 +8575,13 @@
       <c r="A74" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B74" s="57" t="s">
+      <c r="B74" s="56" t="s">
         <v>744</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="D74" s="57" t="s">
+      <c r="D74" s="56" t="s">
         <v>748</v>
       </c>
     </row>
@@ -8702,13 +8589,13 @@
       <c r="A75" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="56" t="s">
         <v>746</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="D75" s="57" t="s">
+      <c r="D75" s="56" t="s">
         <v>749</v>
       </c>
     </row>
@@ -8716,7 +8603,7 @@
       <c r="A76" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="56" t="s">
         <v>751</v>
       </c>
       <c r="C76" s="3" t="s">

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EFD0DB-0246-4060-9A44-E66728482D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C895B6B7-EFFD-4E38-BFF2-5B60DFD35206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
     <sheet name="Current Tasks" sheetId="16" r:id="rId2"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId3"/>
-    <sheet name="Internal Traits" sheetId="1" r:id="rId4"/>
-    <sheet name="internal traits - Old" sheetId="14" r:id="rId5"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId6"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId7"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId8"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId9"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId10"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId11"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId12"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId13"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId14"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId15"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId16"/>
+    <sheet name="Analyzer Tasks" sheetId="17" r:id="rId3"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId4"/>
+    <sheet name="Internal Traits" sheetId="1" r:id="rId5"/>
+    <sheet name="internal traits - Old" sheetId="14" r:id="rId6"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId7"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId8"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId9"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId10"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId11"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId12"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId13"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId14"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId15"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId16"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="840">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -2822,6 +2823,15 @@
     <t>בהירות מושגית</t>
   </si>
   <si>
+    <t>פתיחות אינטלקטואלית</t>
+  </si>
+  <si>
+    <t>עומק מחשבתי</t>
+  </si>
+  <si>
+    <t>הסקה מילולית</t>
+  </si>
+  <si>
     <t>גמישות מחשבתית</t>
   </si>
   <si>
@@ -3006,6 +3016,93 @@
   </si>
   <si>
     <t>פרופיל אנליטי</t>
+  </si>
+  <si>
+    <t>social_intuitive_ intelligence</t>
+  </si>
+  <si>
+    <t>התכונות לא תואמות את האקסל (למשל חסר סגנון סובייטי, היפיות וכו')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשקול לעבור לפחות כרגע - למודל ידני שבו אני כל פעם אג'נרט פרופמטים קבועים ואכניס לקלוד את כל התוצאות שיזין במערכת. זה לא אידיאלי אבל זו עבודה של 5 דקות ליוזר נגיד ותוציא לי תוצאות טובות. </t>
+  </si>
+  <si>
+    <t>לבדוק על הקטע של הקש אינפוט</t>
+  </si>
+  <si>
+    <t>5-6 פרומפטים  - כל אחד מהם - יג'ונרט לי אוטומטית על ידי המערכת כולל תמליל השיחה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכניסה לצ'אטי כל פעם פרומפט אחר  והוא מוציא לי JSON כמו עכשיו. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לוקחת את הjson ומכניסה למערכת - והציונים מתעדכנים. </t>
+  </si>
+  <si>
+    <t>תצוגה נפרדת לעלות השיחה ולעלות הניתוח</t>
+  </si>
+  <si>
+    <t>לעשות פונקציה שמחשבת את הציונים לפי הראיות</t>
+  </si>
+  <si>
+    <t>לעשות באופן זמני שהציון של הקוגנטיבי ילקח מהציון שחישבנו במקום הציונים של הניתוח (+יוקרה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אם עובד טוב - להחליף את הציונים הפרומפט לפרומפט הזה ולעדכן את הציונים במערכת בהתאם. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשמור גם כמות ראיות בחלוקה לכמות ראיות חזקות וחלשות. </t>
+  </si>
+  <si>
+    <t>ואז בהמשך שיחה - תשלח לניתוח רק המשך השיחה והראיות יחושבו בהתאם</t>
+  </si>
+  <si>
+    <t>אחרי זה לעשות את נרמול התוצאות והודאות יותר חכם, לא רק לפי מספר משפטים/מילים, אפשר גם נגיד לפי איזה שאלות ענה ואיזה נושאים דוברו בשיחה וכו'</t>
+  </si>
+  <si>
+    <t>יכול להיות שכרגע הנרמול לא יהיה טוב כי הוא ינרמל למרות שהמודל מוציא ראיות בכוח פחות או יותר באותה כמות לכל משתמש.</t>
+  </si>
+  <si>
+    <t>אולי בכל אחד מהפרומפטים האחרים - נעריך גם אינטליגנציה באופן כללי ונוסיף את זה לחישוב.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נוי </t>
+  </si>
+  <si>
+    <t>נטי</t>
+  </si>
+  <si>
+    <t>רון</t>
+  </si>
+  <si>
+    <t>חן</t>
+  </si>
+  <si>
+    <t>אנה</t>
+  </si>
+  <si>
+    <t>הגר</t>
+  </si>
+  <si>
+    <t>ערסית</t>
+  </si>
+  <si>
+    <t>נדב</t>
+  </si>
+  <si>
+    <t>לנסות את הראיות בשיטה של חובת 3 ראיות</t>
+  </si>
+  <si>
+    <t>בלי חוק ה3</t>
+  </si>
+  <si>
+    <t>חוק ה3</t>
+  </si>
+  <si>
+    <t>חוק ה3 בלי להכפיל משקל לראיה שלילית סבירה וכן הכפלת משקלים קיצונית לשליליים עם ראיה חזקה + הכפלה יותר קיצונית לחיובים חזקים (מעל 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אם אני עובדת בשיטה הזאת (כרגע על 6) - אני צריכה להתחשב בגודל הדלתאות </t>
   </si>
 </sst>
 </file>
@@ -3212,7 +3309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3360,6 +3457,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3930,6 +4030,621 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13">
+      <c r="B1" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="28.8">
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5">
+        <v>85</v>
+      </c>
+      <c r="D5" s="5">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>85</v>
+      </c>
+      <c r="G5" s="5">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="15">
+        <f>SQRT(H5*E5)</f>
+        <v>0.69282032302755092</v>
+      </c>
+      <c r="J5" s="15">
+        <f>(C5+F5)/2</f>
+        <v>85</v>
+      </c>
+      <c r="K5" s="15">
+        <f>I5*J5</f>
+        <v>58.889727457341827</v>
+      </c>
+      <c r="L5" s="5">
+        <f>100-ABS(G5-D5)</f>
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <f>L5*K5</f>
+        <v>5888.9727457341824</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5">
+        <v>60</v>
+      </c>
+      <c r="D6" s="5">
+        <v>50</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>80</v>
+      </c>
+      <c r="G6" s="5">
+        <v>60</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="15">
+        <f>SQRT(H6*E6)</f>
+        <v>0.54772255750516607</v>
+      </c>
+      <c r="J6" s="15">
+        <f>(C6+F6)/2</f>
+        <v>70</v>
+      </c>
+      <c r="K6" s="15">
+        <f>I6*J6</f>
+        <v>38.340579025361627</v>
+      </c>
+      <c r="L6" s="5">
+        <f>100-ABS(G6-D6)</f>
+        <v>90</v>
+      </c>
+      <c r="M6">
+        <f>L6*K6</f>
+        <v>3450.6521122825466</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="5">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5">
+        <v>90</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5">
+        <v>24</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="15">
+        <f>SQRT(H7*E7)</f>
+        <v>0.3872983346207417</v>
+      </c>
+      <c r="J7" s="15">
+        <f>(C7+F7)/2</f>
+        <v>25</v>
+      </c>
+      <c r="K7" s="15">
+        <f>I7*J7</f>
+        <v>9.6824583655185421</v>
+      </c>
+      <c r="L7" s="5">
+        <f>100-ABS(G7-D7)</f>
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <f>L7*K7</f>
+        <v>329.2035844276304</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="15">
+        <f>SUM(I5:I7)</f>
+        <v>1.6278412151534587</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13">
+        <f>SUM(K5:K7)/5</f>
+        <v>21.382552969644401</v>
+      </c>
+      <c r="L8" s="13">
+        <f>SUM(L5:L7)/5</f>
+        <v>44.8</v>
+      </c>
+      <c r="M8" s="14">
+        <f>SUM(M5:M7)/SUM(K5:K7)</f>
+        <v>90.436613964390943</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <f>I8/5</f>
+        <v>0.32556824303069176</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" ht="28.8">
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="5">
+        <v>70</v>
+      </c>
+      <c r="D13" s="5">
+        <v>80</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F13" s="5">
+        <v>80</v>
+      </c>
+      <c r="G13" s="5">
+        <v>72</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" ref="I13:I18" si="0">SQRT(H13*E13)</f>
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" ref="J13:J18" si="1">(C13+F13)/2</f>
+        <v>75</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" ref="K13:K18" si="2">I13*J13</f>
+        <v>67.5</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" ref="L13:L18" si="3">100-ABS(G13-D13)</f>
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M18" si="4">L13*K13</f>
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5">
+        <v>80</v>
+      </c>
+      <c r="D14" s="5">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F14" s="5">
+        <v>80</v>
+      </c>
+      <c r="G14" s="5">
+        <v>90</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>0.2449489742783178</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="2"/>
+        <v>19.595917942265423</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="4"/>
+        <v>587.87753826796268</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5">
+        <v>50</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="5">
+        <v>50</v>
+      </c>
+      <c r="G15" s="5">
+        <v>60</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>0.54772255750516607</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="2"/>
+        <v>27.386127875258303</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="4"/>
+        <v>2464.7515087732472</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="5">
+        <v>100</v>
+      </c>
+      <c r="D16" s="5">
+        <v>100</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>100</v>
+      </c>
+      <c r="G16" s="5">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="4"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="5">
+        <v>100</v>
+      </c>
+      <c r="D17" s="5">
+        <v>66</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>100</v>
+      </c>
+      <c r="G17" s="5">
+        <v>24</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>0.3872983346207417</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="2"/>
+        <v>38.729833462074168</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="4"/>
+        <v>2246.3303408003017</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="5">
+        <v>20</v>
+      </c>
+      <c r="D18" s="5">
+        <v>40</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="5">
+        <v>100</v>
+      </c>
+      <c r="G18" s="5">
+        <v>60</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>0.56568542494923812</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>33.941125496954285</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="4"/>
+        <v>2715.2900397563426</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5">
+        <f>SUM(H13:H18)/5</f>
+        <v>0.78</v>
+      </c>
+      <c r="I19" s="15">
+        <f>SUM(I13:I18)</f>
+        <v>3.6456552913534637</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="13">
+        <f>SUM(L13:L18)/5</f>
+        <v>74</v>
+      </c>
+      <c r="M19" s="14">
+        <f>SUM(M13:M18)/SUM(K13:K18)</f>
+        <v>56.500364466750881</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5">
+        <f>I19/5</f>
+        <v>0.72913105827069269</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4214,7 +4929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4436,7 +5151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4598,7 +5313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4748,7 +5463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4793,7 +5508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4872,7 +5587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5209,6 +5924,198 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50151C83-D621-46FF-871C-82BDAD5480FD}">
+  <dimension ref="B2:P22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="2:16">
+      <c r="P2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="P3" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="K9" t="s">
+        <v>837</v>
+      </c>
+      <c r="L9" t="s">
+        <v>836</v>
+      </c>
+      <c r="M9" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" t="s">
+        <v>814</v>
+      </c>
+      <c r="J10" t="s">
+        <v>827</v>
+      </c>
+      <c r="K10">
+        <v>90</v>
+      </c>
+      <c r="L10">
+        <v>68</v>
+      </c>
+      <c r="M10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="J11" t="s">
+        <v>828</v>
+      </c>
+      <c r="K11">
+        <v>58</v>
+      </c>
+      <c r="L11">
+        <v>51</v>
+      </c>
+      <c r="M11">
+        <v>80</v>
+      </c>
+      <c r="N11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="J12" t="s">
+        <v>829</v>
+      </c>
+      <c r="K12">
+        <v>81</v>
+      </c>
+      <c r="L12">
+        <v>61</v>
+      </c>
+      <c r="M12">
+        <v>65</v>
+      </c>
+      <c r="N12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="J13" t="s">
+        <v>830</v>
+      </c>
+      <c r="K13">
+        <v>93</v>
+      </c>
+      <c r="L13">
+        <v>71</v>
+      </c>
+      <c r="M13">
+        <v>87</v>
+      </c>
+      <c r="O13" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="B14" s="57" t="s">
+        <v>815</v>
+      </c>
+      <c r="J14" t="s">
+        <v>831</v>
+      </c>
+      <c r="K14">
+        <v>63</v>
+      </c>
+      <c r="L14">
+        <v>63</v>
+      </c>
+      <c r="M14">
+        <v>81</v>
+      </c>
+      <c r="O14" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="B15" t="s">
+        <v>816</v>
+      </c>
+      <c r="J15" t="s">
+        <v>832</v>
+      </c>
+      <c r="K15">
+        <v>54</v>
+      </c>
+      <c r="L15">
+        <v>38</v>
+      </c>
+      <c r="M15">
+        <v>51</v>
+      </c>
+      <c r="O15" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="B16" t="s">
+        <v>817</v>
+      </c>
+      <c r="J16" t="s">
+        <v>833</v>
+      </c>
+      <c r="L16">
+        <v>17</v>
+      </c>
+      <c r="O16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="J17" t="s">
+        <v>834</v>
+      </c>
+      <c r="L17">
+        <v>65</v>
+      </c>
+      <c r="O17" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="O18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" t="s">
+        <v>818</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="O22" t="s">
+        <v>826</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5729,9 +6636,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -5767,7 +6674,7 @@
         <v>413</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>6</v>
@@ -5779,7 +6686,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>3</v>
@@ -5808,16 +6715,16 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -5829,16 +6736,16 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C6" t="s">
         <v>753</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -5850,16 +6757,16 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C7" t="s">
         <v>754</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -5871,13 +6778,13 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C8" t="s">
         <v>807</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="C8" t="s">
-        <v>804</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>755</v>
@@ -5890,13 +6797,13 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>639</v>
@@ -5907,14 +6814,12 @@
       <c r="H9" s="3"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="28.8">
-      <c r="A10" s="2" t="s">
-        <v>715</v>
-      </c>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="3" t="s">
-        <v>806</v>
+        <v>758</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -5922,18 +6827,12 @@
       <c r="H10" s="3"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="28.8">
-      <c r="A11" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>760</v>
-      </c>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="3" t="s">
-        <v>435</v>
+        <v>757</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -5941,40 +6840,37 @@
       <c r="H11" s="3"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:14" ht="331.2">
+    <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>715</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>759</v>
+        <v>811</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>798</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>764</v>
+      <c r="D13" s="3" t="s">
+        <v>756</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -5982,75 +6878,78 @@
       <c r="H13" s="3"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:14" ht="27.6">
+    <row r="14" spans="1:14" ht="331.2">
       <c r="A14" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>765</v>
+        <v>715</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>770</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>762</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>801</v>
+      </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="27.6">
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C15" t="s">
-        <v>761</v>
+        <v>768</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>665</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="3"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:14" ht="27.6">
       <c r="A16" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C16" t="s">
-        <v>666</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>707</v>
+        <v>768</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="3"/>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:11" ht="27.6">
       <c r="A17" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="C17" t="s">
+        <v>764</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C17" t="s">
-        <v>671</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>775</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -6060,54 +6959,54 @@
     </row>
     <row r="18" spans="1:11" ht="27.6">
       <c r="A18" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C18" t="s">
-        <v>785</v>
+        <v>666</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="K18" s="34"/>
+      <c r="H18" s="2"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:11" ht="27.6">
       <c r="A19" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C19" t="s">
-        <v>786</v>
+        <v>671</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>702</v>
+        <v>778</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="K19" s="34"/>
+      <c r="H19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="27.6">
       <c r="A20" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C20" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>22</v>
+        <v>701</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -6115,82 +7014,78 @@
       <c r="H20" s="3"/>
       <c r="K20" s="34"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="27.6">
       <c r="A21" s="2" t="s">
-        <v>693</v>
+        <v>766</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>696</v>
+        <v>768</v>
+      </c>
+      <c r="C21" t="s">
+        <v>789</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="28.8">
+      <c r="H21" s="3"/>
+      <c r="K21" s="34"/>
+    </row>
+    <row r="22" spans="1:11" ht="27.6">
       <c r="A22" s="2" t="s">
-        <v>693</v>
+        <v>766</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>717</v>
+        <v>768</v>
+      </c>
+      <c r="C22" t="s">
+        <v>790</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>643</v>
+        <v>22</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="H22" s="3"/>
+      <c r="K22" s="34"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C23" t="s">
-        <v>716</v>
+        <v>772</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>644</v>
+        <v>697</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>426</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" ht="28.8">
       <c r="A24" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C24" t="s">
-        <v>718</v>
+        <v>772</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>719</v>
+        <v>643</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>426</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="2"/>
       <c r="J24" s="2"/>
@@ -6200,38 +7095,38 @@
         <v>693</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C25" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>721</v>
+        <v>644</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="2"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>771</v>
+        <v>693</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>723</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>731</v>
-      </c>
-      <c r="F26" s="56" t="s">
-        <v>425</v>
+        <v>772</v>
+      </c>
+      <c r="C26" t="s">
+        <v>718</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
@@ -6239,227 +7134,233 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
-        <v>771</v>
+        <v>693</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="C27" s="56" t="s">
-        <v>725</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="E27" s="56" t="s">
-        <v>730</v>
-      </c>
-      <c r="F27" s="56"/>
+        <v>772</v>
+      </c>
+      <c r="C27" t="s">
+        <v>720</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
+      <c r="H27" s="2"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>727</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>728</v>
+        <v>723</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>724</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>729</v>
-      </c>
-      <c r="F28" s="56"/>
+        <v>731</v>
+      </c>
+      <c r="F28" s="56" t="s">
+        <v>425</v>
+      </c>
       <c r="G28" s="3"/>
+      <c r="H28" s="2"/>
+      <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>732</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="F29" s="56"/>
       <c r="G29" s="3"/>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="F30" s="56"/>
       <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="E31" s="56" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F31" s="56"/>
       <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>544</v>
+        <v>733</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>543</v>
+        <v>735</v>
       </c>
       <c r="E32" s="56" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F32" s="56"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F33" s="56"/>
       <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>744</v>
+        <v>544</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>745</v>
+        <v>543</v>
       </c>
       <c r="E34" s="56" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="F34" s="56"/>
       <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="F35" s="56"/>
       <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C36" s="56" t="s">
+        <v>744</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>748</v>
+      </c>
+      <c r="F36" s="56"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>746</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>749</v>
+      </c>
+      <c r="F37" s="56"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C38" s="56" t="s">
         <v>751</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:11" ht="28.8">
-      <c r="A37" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>432</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:11" ht="220.8">
-      <c r="A38" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:11" ht="28.8">
@@ -6467,490 +7368,526 @@
         <v>426</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>563</v>
+        <v>775</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>432</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>564</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" ht="28.8">
+    </row>
+    <row r="40" spans="1:11" ht="220.8">
       <c r="A40" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>804</v>
+      </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:11" ht="28.8">
       <c r="A41" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>38</v>
+        <v>563</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>564</v>
+      </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="3"/>
+      <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:11" ht="28.8">
       <c r="A42" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C42" t="s">
-        <v>664</v>
+        <v>775</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>705</v>
+        <v>37</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="K42" s="34"/>
-    </row>
-    <row r="43" spans="1:11" ht="179.4">
-      <c r="A43" s="40" t="s">
+    </row>
+    <row r="43" spans="1:11" ht="28.8">
+      <c r="A43" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B43" s="37" t="s">
-        <v>772</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>799</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>800</v>
-      </c>
+      <c r="B43" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="K43" s="34"/>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="J43" s="19"/>
+      <c r="K43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>431</v>
-      </c>
-      <c r="D44" s="48" t="s">
-        <v>545</v>
-      </c>
-      <c r="E44" s="17"/>
+        <v>775</v>
+      </c>
+      <c r="C44" t="s">
+        <v>664</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>550</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>551</v>
-      </c>
+      <c r="K44" s="34"/>
+    </row>
+    <row r="45" spans="1:11" ht="179.4">
+      <c r="A45" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="B45" s="37" t="s">
+        <v>775</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>802</v>
+      </c>
+      <c r="D45" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>803</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="K45" s="34"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C46" t="s">
-        <v>557</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>384</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>545</v>
+      </c>
+      <c r="E46" s="17"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>44</v>
+        <v>779</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>550</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="1:11" ht="28.8">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>559</v>
+        <v>779</v>
+      </c>
+      <c r="C48" t="s">
+        <v>557</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:10">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>42</v>
+        <v>779</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+    </row>
+    <row r="50" spans="1:11" ht="28.8">
       <c r="A50" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>31</v>
+        <v>559</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>32</v>
+        <v>558</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10">
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
+      </c>
+      <c r="C51" s="49" t="s">
+        <v>42</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>567</v>
+        <v>43</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="17"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="2"/>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="H51" s="3"/>
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>778</v>
+        <v>31</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>32</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C53" s="49" t="s">
-        <v>774</v>
+        <v>779</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>780</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>567</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>781</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>27</v>
+        <v>779</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>777</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="17" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="69">
+        <v>779</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C57" s="38"/>
+        <v>779</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D57" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="69">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C58" s="38"/>
-      <c r="D58" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="27.6">
+        <v>779</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="17" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="69">
       <c r="A59" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C59" s="38"/>
       <c r="D59" s="3" t="s">
-        <v>334</v>
+        <v>383</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="82.8">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="69">
       <c r="A60" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D60" s="33" t="s">
+        <v>779</v>
+      </c>
+      <c r="C60" s="38"/>
+      <c r="D60" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="27.6">
+      <c r="A61" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C61" s="38"/>
+      <c r="D61" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="82.8">
+      <c r="A62" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D62" s="33" t="s">
         <v>387</v>
       </c>
-      <c r="E60" s="33" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="C62" t="s">
-        <v>790</v>
-      </c>
-      <c r="D62" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.8">
+      <c r="E62" s="33" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>560</v>
+        <v>46</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="28.8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="82.8">
+        <v>792</v>
+      </c>
+      <c r="C64" t="s">
+        <v>793</v>
+      </c>
+      <c r="D64" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="28.8">
       <c r="A65" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>791</v>
+        <v>560</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="69">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="28.8">
       <c r="A66" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>792</v>
+        <v>48</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="55.2">
+        <v>49</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="82.8">
       <c r="A67" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="409.6">
+    </row>
+    <row r="68" spans="1:5" ht="69">
       <c r="A68" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="D68" s="3" t="s">
+    </row>
+    <row r="69" spans="1:5" ht="55.2">
+      <c r="A69" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="409.6">
+      <c r="A70" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>700</v>
       </c>
     </row>
@@ -6959,7 +7896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7802,7 +8739,7 @@
         <v>429</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>35</v>
@@ -9053,7 +9990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9333,7 +10270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9630,7 +10567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9978,619 +10915,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
-  <dimension ref="B1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13">
-      <c r="B1" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="2:13" ht="28.8">
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5">
-        <v>85</v>
-      </c>
-      <c r="D5" s="5">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="5">
-        <v>85</v>
-      </c>
-      <c r="G5" s="5">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="I5" s="15">
-        <f>SQRT(H5*E5)</f>
-        <v>0.69282032302755092</v>
-      </c>
-      <c r="J5" s="15">
-        <f>(C5+F5)/2</f>
-        <v>85</v>
-      </c>
-      <c r="K5" s="15">
-        <f>I5*J5</f>
-        <v>58.889727457341827</v>
-      </c>
-      <c r="L5" s="5">
-        <f>100-ABS(G5-D5)</f>
-        <v>100</v>
-      </c>
-      <c r="M5">
-        <f>L5*K5</f>
-        <v>5888.9727457341824</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="5">
-        <v>60</v>
-      </c>
-      <c r="D6" s="5">
-        <v>50</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="5">
-        <v>80</v>
-      </c>
-      <c r="G6" s="5">
-        <v>60</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I6" s="15">
-        <f>SQRT(H6*E6)</f>
-        <v>0.54772255750516607</v>
-      </c>
-      <c r="J6" s="15">
-        <f>(C6+F6)/2</f>
-        <v>70</v>
-      </c>
-      <c r="K6" s="15">
-        <f>I6*J6</f>
-        <v>38.340579025361627</v>
-      </c>
-      <c r="L6" s="5">
-        <f>100-ABS(G6-D6)</f>
-        <v>90</v>
-      </c>
-      <c r="M6">
-        <f>L6*K6</f>
-        <v>3450.6521122825466</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5">
-        <v>30</v>
-      </c>
-      <c r="D7" s="5">
-        <v>90</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="5">
-        <v>20</v>
-      </c>
-      <c r="G7" s="5">
-        <v>24</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="15">
-        <f>SQRT(H7*E7)</f>
-        <v>0.3872983346207417</v>
-      </c>
-      <c r="J7" s="15">
-        <f>(C7+F7)/2</f>
-        <v>25</v>
-      </c>
-      <c r="K7" s="15">
-        <f>I7*J7</f>
-        <v>9.6824583655185421</v>
-      </c>
-      <c r="L7" s="5">
-        <f>100-ABS(G7-D7)</f>
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <f>L7*K7</f>
-        <v>329.2035844276304</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="15">
-        <f>SUM(I5:I7)</f>
-        <v>1.6278412151534587</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="13">
-        <f>SUM(K5:K7)/5</f>
-        <v>21.382552969644401</v>
-      </c>
-      <c r="L8" s="13">
-        <f>SUM(L5:L7)/5</f>
-        <v>44.8</v>
-      </c>
-      <c r="M8" s="14">
-        <f>SUM(M5:M7)/SUM(K5:K7)</f>
-        <v>90.436613964390943</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <f>I8/5</f>
-        <v>0.32556824303069176</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="2:13" ht="28.8">
-      <c r="B12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="5">
-        <v>70</v>
-      </c>
-      <c r="D13" s="5">
-        <v>80</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="F13" s="5">
-        <v>80</v>
-      </c>
-      <c r="G13" s="5">
-        <v>72</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="I13" s="15">
-        <f t="shared" ref="I13:I18" si="0">SQRT(H13*E13)</f>
-        <v>0.9</v>
-      </c>
-      <c r="J13" s="15">
-        <f t="shared" ref="J13:J18" si="1">(C13+F13)/2</f>
-        <v>75</v>
-      </c>
-      <c r="K13" s="15">
-        <f t="shared" ref="K13:K18" si="2">I13*J13</f>
-        <v>67.5</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" ref="L13:L18" si="3">100-ABS(G13-D13)</f>
-        <v>92</v>
-      </c>
-      <c r="M13">
-        <f t="shared" ref="M13:M18" si="4">L13*K13</f>
-        <v>6210</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5">
-        <v>80</v>
-      </c>
-      <c r="D14" s="5">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="F14" s="5">
-        <v>80</v>
-      </c>
-      <c r="G14" s="5">
-        <v>90</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>0.2449489742783178</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="K14" s="15">
-        <f t="shared" si="2"/>
-        <v>19.595917942265423</v>
-      </c>
-      <c r="L14" s="5">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="4"/>
-        <v>587.87753826796268</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="5">
-        <v>50</v>
-      </c>
-      <c r="D15" s="5">
-        <v>50</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="5">
-        <v>50</v>
-      </c>
-      <c r="G15" s="5">
-        <v>60</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>0.54772255750516607</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="K15" s="15">
-        <f t="shared" si="2"/>
-        <v>27.386127875258303</v>
-      </c>
-      <c r="L15" s="5">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="4"/>
-        <v>2464.7515087732472</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="5">
-        <v>100</v>
-      </c>
-      <c r="D16" s="5">
-        <v>100</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5">
-        <v>100</v>
-      </c>
-      <c r="G16" s="5">
-        <v>20</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="K16" s="15">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="4"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="5">
-        <v>100</v>
-      </c>
-      <c r="D17" s="5">
-        <v>66</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="F17" s="5">
-        <v>100</v>
-      </c>
-      <c r="G17" s="5">
-        <v>24</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>0.3872983346207417</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="K17" s="15">
-        <f t="shared" si="2"/>
-        <v>38.729833462074168</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="4"/>
-        <v>2246.3303408003017</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="5">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5">
-        <v>40</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="F18" s="5">
-        <v>100</v>
-      </c>
-      <c r="G18" s="5">
-        <v>60</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>0.56568542494923812</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="K18" s="15">
-        <f t="shared" si="2"/>
-        <v>33.941125496954285</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="4"/>
-        <v>2715.2900397563426</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5">
-        <f>SUM(H13:H18)/5</f>
-        <v>0.78</v>
-      </c>
-      <c r="I19" s="15">
-        <f>SUM(I13:I18)</f>
-        <v>3.6456552913534637</v>
-      </c>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="13">
-        <f>SUM(L13:L18)/5</f>
-        <v>74</v>
-      </c>
-      <c r="M19" s="14">
-        <f>SUM(M13:M18)/SUM(K13:K18)</f>
-        <v>56.500364466750881</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5">
-        <f>I19/5</f>
-        <v>0.72913105827069269</v>
-      </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C895B6B7-EFFD-4E38-BFF2-5B60DFD35206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8753B1-F447-4B61-9CD1-47686D711344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
     <sheet name="Current Tasks" sheetId="16" r:id="rId2"/>
     <sheet name="Analyzer Tasks" sheetId="17" r:id="rId3"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId4"/>
-    <sheet name="Internal Traits" sheetId="1" r:id="rId5"/>
-    <sheet name="internal traits - Old" sheetId="14" r:id="rId6"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId7"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId8"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId9"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId10"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId11"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId12"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId13"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId14"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId15"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId16"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId17"/>
+    <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId4"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId5"/>
+    <sheet name="Internal Traits" sheetId="1" r:id="rId6"/>
+    <sheet name="internal traits - Old" sheetId="14" r:id="rId7"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId8"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId9"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId10"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId11"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId12"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId13"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId14"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId15"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId16"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId17"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="928">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3096,20 +3097,369 @@
     <t>בלי חוק ה3</t>
   </si>
   <si>
-    <t>חוק ה3</t>
-  </si>
-  <si>
     <t>חוק ה3 בלי להכפיל משקל לראיה שלילית סבירה וכן הכפלת משקלים קיצונית לשליליים עם ראיה חזקה + הכפלה יותר קיצונית לחיובים חזקים (מעל 6)</t>
   </si>
   <si>
     <t xml:space="preserve">אם אני עובדת בשיטה הזאת (כרגע על 6) - אני צריכה להתחשב בגודל הדלתאות </t>
+  </si>
+  <si>
+    <t>70/80</t>
+  </si>
+  <si>
+    <t>חוק ה6 פלוס הכפלה אקספוננציאלית</t>
+  </si>
+  <si>
+    <t>60/65/54</t>
+  </si>
+  <si>
+    <t>האקספוננציליות צריכה להתחיל כבר ב1</t>
+  </si>
+  <si>
+    <t>59/58/61</t>
+  </si>
+  <si>
+    <t>70/63/72</t>
+  </si>
+  <si>
+    <t>51/56</t>
+  </si>
+  <si>
+    <t>אצלי למשל הוא פשוט נתן את אותו סט ראיות על כל התכונות באותו דירוג, התחיל טוב עם האנליטי ואז פשוט התחיל להעתיק</t>
+  </si>
+  <si>
+    <t>81/81</t>
+  </si>
+  <si>
+    <t>44/39</t>
+  </si>
+  <si>
+    <t>חוק ה3 (עם הכפלה של 1.3 לחזקות ופי 2 לשליליות)</t>
+  </si>
+  <si>
+    <t>צריך להגיד לו אולי לא להשתמש באותן ראיות, אלא אם הן ממש חזקות</t>
+  </si>
+  <si>
+    <t>אולי לחייב לתת 2 ראיות שליליות לפחות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מצב קודם + ראיות ייחודיות, הדגשת לקיחת החזקים ביותר וסולם חוזק. </t>
+  </si>
+  <si>
+    <t>ציון באינטואיטיבית</t>
+  </si>
+  <si>
+    <t>18/22/17</t>
+  </si>
+  <si>
+    <t>75/75/75</t>
+  </si>
+  <si>
+    <t>67/73/81</t>
+  </si>
+  <si>
+    <t>72/91/99</t>
+  </si>
+  <si>
+    <t>מקרה אנה 1 - נתן  את אותן 3 ראיות שליליות למרות שהן בחוזק בינוני לכל התכונות</t>
+  </si>
+  <si>
+    <t>דבר נוסף - הוא לוקח דברים רגשיים ומשליך אותם על יכולת קוגנטיבית. כמו הימנעות מעימותים וכו'. זה קשור רק לחברתי, לא לקוגנטיבי כללי</t>
+  </si>
+  <si>
+    <t>61/58</t>
+  </si>
+  <si>
+    <t>19/48</t>
+  </si>
+  <si>
+    <t>85/81</t>
+  </si>
+  <si>
+    <t>לחשוב איך ליצור את ההתאמה, אין לי עוד אלגוריתם לזה</t>
+  </si>
+  <si>
+    <t>לסדר את האפיון, את תכנית העבודה ואת כל המשימות שלי</t>
+  </si>
+  <si>
+    <t>לקרוא מאמרים שקשורים להתאמה על בסיס כל אחת מהתכונות</t>
+  </si>
+  <si>
+    <t>לדייק כל אחד מהפרופילים</t>
+  </si>
+  <si>
+    <t>MBTI Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensing </t>
+  </si>
+  <si>
+    <t>Intuition</t>
+  </si>
+  <si>
+    <t>Thinking</t>
+  </si>
+  <si>
+    <t>Feeling</t>
+  </si>
+  <si>
+    <t>Judging</t>
+  </si>
+  <si>
+    <t>Perceiving</t>
+  </si>
+  <si>
+    <t>MBTI</t>
+  </si>
+  <si>
+    <t>חושים</t>
+  </si>
+  <si>
+    <t>שיפוט</t>
+  </si>
+  <si>
+    <t>תפיסה</t>
+  </si>
+  <si>
+    <t>חשיבה</t>
+  </si>
+  <si>
+    <t>רגשות</t>
+  </si>
+  <si>
+    <t>אינטואיציה</t>
+  </si>
+  <si>
+    <t>לחשוב איך מכניסים לסוגי התאמה ולחשוב איך להשתמש בטקסט הכללי</t>
+  </si>
+  <si>
+    <t>עמדות</t>
+  </si>
+  <si>
+    <t>סוג</t>
+  </si>
+  <si>
+    <t>אינטלגנציה רגשית חברתית</t>
+  </si>
+  <si>
+    <t>אנרגיה-סגנון תקשורת</t>
+  </si>
+  <si>
+    <t>פרופיל סגנון</t>
+  </si>
+  <si>
+    <t>מאפיינים כלליים</t>
+  </si>
+  <si>
+    <t>פרומפט</t>
+  </si>
+  <si>
+    <t>חישוב פרופיל</t>
+  </si>
+  <si>
+    <t>חישוב התאמה</t>
+  </si>
+  <si>
+    <t>כרגע יש לי שתי שיטות חישוב: 1. פרומפט שמתייחס לכל התכונות הקוגנטיביות (ללא יוקרה תעסוקתית) ומוסיף גם הערכה של אינטליגנציה אינטואיטיבית (לצורך האיזון - לאפשר לAI לפרגן בדרך פחות אנליטית).   2. שיטת הראיות -  אותו הדבר רק במקום להוציא ציון - להוציא ראיות. 6 לכל תכונה עם עדיפות ל3 שליליות ו3 חיובית, וחובה לקחת את החזקות ביותר. (בפועל זה לא בהכרח קורה, והוא גם חוזר על אותם משפטים לכל התכונות  ולא עקבי).
+לשים כרגע את שיטת הראיות בצד, להמשיך לעבוד עם הפרומפט הנוכחי אבל: לעשות כפתור של הרצה נוספת שיאפשר להריץ שוב ולעדכן את הציונים לממוצע ההרצות. צריך בעצם לשמור מערך הרצות לכל משתמש של סך הציונים שקיבל. בהמשך יכול להיות שגם נשתמש בזה כדי לבדוק פערים. אם קיבלתי פער מאוד גדול - אני עולה ארצה להעלות את זה לשיפוט עצמי. 
+בנוסף - בכל אחד מהפרומפטים האחרים נבקש ציון אינטליגנציה אנליטית ואינטליגנציה אינטואיטיבית - נשמור אותם במערך סך אינטלגנציות. ובסוף נרכיב מזה ציון אחד.
+לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90</t>
+  </si>
+  <si>
+    <t>כרגע - ממוצע כל התכונות לפי אילו שמשפיעות על הפרופיל. צריך להיות: 50% ממוצע התכונות, 50% התאמה לפי ציון כולל.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כל התכונות הקוגנטיביות כולל יוקרה תעסוקתית, לא כולל אינטואיטיבית, כאשר אנליטיות מקבל משקל משולש.
+הציון מנורמל לסקאלה של 20-90.
+לשנות בהמשך את הציון בהתאם ל: מערך אינטליגנציות מכל פרומפט, הרצה משולשת של הפרומפט.
+לשקול - לבדוק אם המשתמש הוא "רוני" ואם כן - להעלות ציון. </t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">מורכב מממוצע התכונות: אינטלגנציה אינטואיטיבית, מודעות עצמית, אינטלגנציה רגשית וערך הפוך לנוירוטיות. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">לוודא.   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">לשפר. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ממוצע מרחק אוקלידי. </t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות, משותף עם הפרומפט של ערכים.   לשפר בהתאם לצורך</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אין ציון. הצגת כל אחת מהתכונות והערך שלהן. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">אין ציון. הצגת התכונות הבולטות (מעל 65 בחיובי או מתחת ל45 בשלילי - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>לוודא</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות, משותף עם הפרומפט של ביג פייב.   לשפר בהתאם לצורך</t>
+  </si>
+  <si>
+    <t>כחלק מהפרומפט של הפרופיל הרגשי.  מלבד אינטלגנציה אינטואיטיבית שמחושב בפרומפט הקוגנטיבי.</t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות בפרופיל הרגשי. לשפר בהתאם לצורך.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ממוצע כלל התכונות שתחת פרופיל רגשי מלבד אילו שהופרדו לאינטלגנציה רגשית חברתית.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>לוודא</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, לשפר</t>
+    </r>
+  </si>
+  <si>
+    <t>ממוצע מרחק אוקלידי.   
+לשקול - להתאים את המרחקים בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות. אולי חוץ מבאינטלגנציה אינטואיטיבית.</t>
+  </si>
+  <si>
+    <t>ממוצע מרחק אוקלידי. 
+לשקול - כנ"ל לסעיף הקודם, אפילו מרחק גדול יותר.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ממוצע מרחק אוקלידי. 
+</t>
+  </si>
+  <si>
+    <t>ממוצע מרחק אוקלידי.</t>
+  </si>
+  <si>
+    <t>ממוצע התכונות כאשר בחלק מהתכונות נשתמש בערך ההופכי (קשיחות, תיאטרליות וכו').  לשפר</t>
+  </si>
+  <si>
+    <t>אין ציון. הצגה של הסגנונות הבולטים (מעל 60? - לוודא).</t>
+  </si>
+  <si>
+    <t>כאן צריך להכניס מנגנון מתוחכם יותר. ככל שציון המשתמש יותר גבוה בתכונת סגנון (אולי לא כולן) - המשקל להתאמה יותר קריטי. בכללי אולי לא לכל תכונות הסגנון יש אותו משקל התאמה. 
+כמו כן - אפשר להכין קלסטרי טיפוסים שתלויים בסגנון + תכונות אחרות וליצור התאמות בהתאם.</t>
+  </si>
+  <si>
+    <t>חישוב ההתאמה בכללי מוגזם - צריך לראות איך עוברים לציונים יותר רחבים.</t>
+  </si>
+  <si>
+    <t>לכתוב לכל תכונה איזה פרומפט אחראי עליה, לאיזה פרופיל היא שייכת. (אם זה לא תואם את הקבוצה שלה)</t>
+  </si>
+  <si>
+    <t>נכניס קודם כל מרחק אוקלידי פשוט. ואז אפשר גם לחשוב על התאמת סגנונות לפי חוקי המודל (לא בטוח שכדאי, זה לא מוכח מחקרית)</t>
+  </si>
+  <si>
+    <t>אין פרומפט. מבוסס על תכונות קיימות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נציג ציון של מסורתיות שיחושב לפי דתיות, חילוניות, שמרנות וערך מסורת. (אולי להפריד את שמרנות לעמדה נפרדת שמכילה גם את הפתיחות וכו')
+נציג ציון של פוליטיות שיחושב לפי שמאל פוליטי וימין פוליטי.  אולי נחשב גם את מידת הפוליטיות הכללית.  
+לחשוב על איך לעשות את החישובים והאם יש עוד עמדות שנגזרות מכאן. </t>
+  </si>
+  <si>
+    <t>לחשוב על זה</t>
+  </si>
+  <si>
+    <t>לחשוב אם להציג בכלל בנפרד ומה נכנס כאן</t>
+  </si>
+  <si>
+    <t>אין.</t>
+  </si>
+  <si>
+    <t>לנרמל ציוני התאמה. כרגע גבוהים ומוגזמים. לבדוק שוב את החישוב שלי.</t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
+אולי להוסיף מידת הסתייגות..?</t>
+  </si>
+  <si>
+    <t>לחשב ציון התאמה לפי שילוב של גרופס + התאמה כללית בין התכונות ולשחק עם המשקלים</t>
+  </si>
+  <si>
+    <t>משימות</t>
+  </si>
+  <si>
+    <t>צריך - לעשות כפתור שמחשב רק MBTI כמו שאר הכפתורים</t>
+  </si>
+  <si>
+    <t>לבדוק מה פשר הציון של ביג פייב ערכים וסגנון בUserProfiles</t>
+  </si>
+  <si>
+    <t>אחרי שמסיים את השלב הזה של הmbti - פונקציית התאמת MBTI</t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות מלבד מוחצנות/מופנמות שכבר מחושב בביג פייב. לשפר בהתאם לצורך.  
+צריך לדייק את התכונות, למשל בין T לF - יש בעיה כשרוב השיחה היא רגשית. אולי צריך לנרמל את זה ביחס לאחרים או גם להדגיש את זה בפרומפט.
+אולי גם צריך לנרמל את ציון המוחצנות. 40=30, 60=50 או 55, ו70=80</t>
+  </si>
+  <si>
+    <t>הציון יהיה הטיפוס שנגזר מהציונים מבין 16 האישיות.
+עבור T/F - מוסיפים 20 נקודות לT לפני החישוב</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3261,6 +3611,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3309,7 +3673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3458,7 +3822,16 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4030,6 +4403,356 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" customWidth="1"/>
+    <col min="12" max="12" width="37.33203125" customWidth="1"/>
+    <col min="13" max="13" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="K2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6">
+      <c r="A3" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="K3" t="s">
+        <v>310</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="28.8">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D12" si="0">MIN(A4 * 5, 100)</f>
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E12" si="1">MAX(0, 100 - B4 * 10)</f>
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F12" si="2">MAX(0, 100 - C4 * 10)</f>
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G12" si="3">0.4*D4+0.2*E4+0.4*F4</f>
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>307</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.8">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>312</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.8">
+      <c r="A8">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="K8" t="s">
+        <v>316</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="27">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.8">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>40</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4644,7 +5367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4929,7 +5652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5151,7 +5874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5313,7 +6036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5463,7 +6186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5508,7 +6231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5587,7 +6310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5925,41 +6648,82 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50151C83-D621-46FF-871C-82BDAD5480FD}">
-  <dimension ref="B2:P22"/>
+  <dimension ref="B2:T31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:16">
-      <c r="P2" t="s">
+    <row r="2" spans="2:20">
+      <c r="B2" t="s">
+        <v>912</v>
+      </c>
+      <c r="R2" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="3" spans="2:16">
-      <c r="P3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16">
+    <row r="3" spans="2:20">
+      <c r="B3" t="s">
+        <v>864</v>
+      </c>
+      <c r="R3" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20">
       <c r="B4" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="5" spans="2:20">
+      <c r="B5" t="s">
+        <v>911</v>
+      </c>
+      <c r="R5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20">
+      <c r="R6" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20">
       <c r="B7" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="9" spans="2:16">
-      <c r="K9" t="s">
-        <v>837</v>
+      <c r="R7" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20">
+      <c r="R8" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="72.599999999999994">
+      <c r="K9" s="60" t="s">
+        <v>849</v>
       </c>
       <c r="L9" t="s">
         <v>836</v>
       </c>
-      <c r="M9" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16">
+      <c r="M9" s="59" t="s">
+        <v>837</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="O9" s="59" t="s">
+        <v>852</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20">
       <c r="B10" t="s">
         <v>814</v>
       </c>
@@ -5975,8 +6739,17 @@
       <c r="M10">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="2:16">
+      <c r="N10" s="58" t="s">
+        <v>844</v>
+      </c>
+      <c r="O10" t="s">
+        <v>856</v>
+      </c>
+      <c r="P10" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20">
       <c r="J11" t="s">
         <v>828</v>
       </c>
@@ -5986,14 +6759,23 @@
       <c r="L11">
         <v>51</v>
       </c>
-      <c r="M11">
-        <v>80</v>
-      </c>
-      <c r="N11">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16">
+      <c r="M11" s="57" t="s">
+        <v>839</v>
+      </c>
+      <c r="N11" s="57" t="s">
+        <v>841</v>
+      </c>
+      <c r="O11" t="s">
+        <v>854</v>
+      </c>
+      <c r="P11" t="s">
+        <v>855</v>
+      </c>
+      <c r="T11" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20">
       <c r="J12" t="s">
         <v>829</v>
       </c>
@@ -6006,11 +6788,20 @@
       <c r="M12">
         <v>65</v>
       </c>
-      <c r="N12">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16">
+      <c r="N12" s="58" t="s">
+        <v>845</v>
+      </c>
+      <c r="O12" t="s">
+        <v>860</v>
+      </c>
+      <c r="P12">
+        <v>48</v>
+      </c>
+      <c r="T12" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20">
       <c r="J13" t="s">
         <v>830</v>
       </c>
@@ -6023,12 +6814,18 @@
       <c r="M13">
         <v>87</v>
       </c>
+      <c r="N13" s="58" t="s">
+        <v>847</v>
+      </c>
       <c r="O13" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16">
-      <c r="B14" s="57" t="s">
+        <v>862</v>
+      </c>
+      <c r="P13">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="B14" s="58" t="s">
         <v>815</v>
       </c>
       <c r="J14" t="s">
@@ -6043,11 +6840,17 @@
       <c r="M14">
         <v>81</v>
       </c>
+      <c r="N14" s="57" t="s">
+        <v>843</v>
+      </c>
       <c r="O14" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16">
+        <v>861</v>
+      </c>
+      <c r="P14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20">
       <c r="B15" t="s">
         <v>816</v>
       </c>
@@ -6063,11 +6866,11 @@
       <c r="M15">
         <v>51</v>
       </c>
-      <c r="O15" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16">
+      <c r="N15" s="58" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20">
       <c r="B16" t="s">
         <v>817</v>
       </c>
@@ -6076,9 +6879,6 @@
       </c>
       <c r="L16">
         <v>17</v>
-      </c>
-      <c r="O16" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -6088,25 +6888,49 @@
       <c r="L17">
         <v>65</v>
       </c>
-      <c r="O17" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="O18" t="s">
-        <v>824</v>
-      </c>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" t="s">
         <v>818</v>
       </c>
-      <c r="O20" s="14" t="s">
-        <v>825</v>
-      </c>
     </row>
     <row r="22" spans="2:15">
       <c r="O22" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="O23" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="O24" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="O25" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="O26" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="O27" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="O29" s="14" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="O31" t="s">
         <v>826</v>
       </c>
     </row>
@@ -6116,6 +6940,253 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890832A-DBF2-45FA-8E41-3FB9FF4AFB94}">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="96.21875" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" customWidth="1"/>
+    <col min="4" max="5" width="40.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>883</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>888</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>889</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="158.4">
+      <c r="A2" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="100.8">
+      <c r="A3" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="B3" t="s">
+        <v>901</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" ht="57.6">
+      <c r="A4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8">
+      <c r="A5" t="s">
+        <v>693</v>
+      </c>
+      <c r="B5" t="s">
+        <v>897</v>
+      </c>
+      <c r="C5" t="s">
+        <v>898</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>900</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="D6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="43.2">
+      <c r="A7" t="s">
+        <v>885</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="86.4">
+      <c r="A8" t="s">
+        <v>886</v>
+      </c>
+      <c r="B8" t="s">
+        <v>894</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="72">
+      <c r="A9" s="58" t="s">
+        <v>874</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="100.8">
+      <c r="A10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B10" t="s">
+        <v>914</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>914</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12" t="s">
+        <v>914</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>887</v>
+      </c>
+      <c r="B13" t="s">
+        <v>881</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" t="s">
+        <v>863</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="14" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="14" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="14" t="s">
+        <v>924</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6636,9 +7707,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -7766,98 +8837,89 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>45</v>
+        <v>867</v>
+      </c>
+      <c r="C63" t="s">
+        <v>868</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>792</v>
+        <v>867</v>
       </c>
       <c r="C64" t="s">
-        <v>793</v>
-      </c>
-      <c r="D64" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="28.8">
+        <v>869</v>
+      </c>
+      <c r="D64" s="38" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="28.8">
+        <v>867</v>
+      </c>
+      <c r="C65" t="s">
+        <v>870</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="82.8">
+        <v>867</v>
+      </c>
+      <c r="C66" t="s">
+        <v>871</v>
+      </c>
+      <c r="D66" s="38" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="69">
+        <v>867</v>
+      </c>
+      <c r="C67" t="s">
+        <v>872</v>
+      </c>
+      <c r="D67" s="38" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>430</v>
+        <v>874</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="55.2">
+        <v>867</v>
+      </c>
+      <c r="C68" t="s">
+        <v>873</v>
+      </c>
+      <c r="D68" s="38" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
         <v>430</v>
       </c>
@@ -7865,29 +8927,122 @@
         <v>792</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>799</v>
+        <v>46</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="409.6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" t="s">
+        <v>793</v>
+      </c>
+      <c r="D70" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="28.8">
+      <c r="A71" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="28.8">
+      <c r="A72" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="82.8">
+      <c r="A73" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="69">
+      <c r="A74" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="55.2">
+      <c r="A75" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="409.6">
+      <c r="A76" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7896,7 +9051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9990,7 +11145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10270,7 +11425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10565,354 +11720,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" customWidth="1"/>
-    <col min="12" max="12" width="37.33203125" customWidth="1"/>
-    <col min="13" max="13" width="35" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="K2" t="s">
-        <v>305</v>
-      </c>
-      <c r="L2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="57.6">
-      <c r="A3" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="K3" t="s">
-        <v>310</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="28.8">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D12" si="0">MIN(A4 * 5, 100)</f>
-        <v>35</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E12" si="1">MAX(0, 100 - B4 * 10)</f>
-        <v>50</v>
-      </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F12" si="2">MAX(0, 100 - C4 * 10)</f>
-        <v>80</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4:G12" si="3">0.4*D4+0.2*E4+0.4*F4</f>
-        <v>56</v>
-      </c>
-      <c r="K4" t="s">
-        <v>307</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.8">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="3"/>
-        <v>56</v>
-      </c>
-      <c r="K6" t="s">
-        <v>312</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.8">
-      <c r="A8">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="3"/>
-        <v>64</v>
-      </c>
-      <c r="K8" t="s">
-        <v>316</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="27">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>40</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.8">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11">
-        <v>40</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <v>40</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8753B1-F447-4B61-9CD1-47686D711344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7F8CD2-2C72-4A31-B8B5-B3791579FE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="926">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3265,9 +3265,6 @@
 לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90</t>
   </si>
   <si>
-    <t>כרגע - ממוצע כל התכונות לפי אילו שמשפיעות על הפרופיל. צריך להיות: 50% ממוצע התכונות, 50% התאמה לפי ציון כולל.</t>
-  </si>
-  <si>
     <t xml:space="preserve">כל התכונות הקוגנטיביות כולל יוקרה תעסוקתית, לא כולל אינטואיטיבית, כאשר אנליטיות מקבל משקל משולש.
 הציון מנורמל לסקאלה של 20-90.
 לשנות בהמשך את הציון בהתאם ל: מערך אינטליגנציות מכל פרומפט, הרצה משולשת של הפרומפט.
@@ -3404,9 +3401,6 @@
     <t>לכתוב לכל תכונה איזה פרומפט אחראי עליה, לאיזה פרופיל היא שייכת. (אם זה לא תואם את הקבוצה שלה)</t>
   </si>
   <si>
-    <t>נכניס קודם כל מרחק אוקלידי פשוט. ואז אפשר גם לחשוב על התאמת סגנונות לפי חוקי המודל (לא בטוח שכדאי, זה לא מוכח מחקרית)</t>
-  </si>
-  <si>
     <t>אין פרומפט. מבוסס על תכונות קיימות</t>
   </si>
   <si>
@@ -3437,13 +3431,7 @@
     <t>משימות</t>
   </si>
   <si>
-    <t>צריך - לעשות כפתור שמחשב רק MBTI כמו שאר הכפתורים</t>
-  </si>
-  <si>
     <t>לבדוק מה פשר הציון של ביג פייב ערכים וסגנון בUserProfiles</t>
-  </si>
-  <si>
-    <t>אחרי שמסיים את השלב הזה של הmbti - פונקציית התאמת MBTI</t>
   </si>
   <si>
     <t>פרומפט נפרד לכל התכונות הקשורות מלבד מוחצנות/מופנמות שכבר מחושב בביג פייב. לשפר בהתאם לצורך.  
@@ -3453,6 +3441,13 @@
   <si>
     <t>הציון יהיה הטיפוס שנגזר מהציונים מבין 16 האישיות.
 עבור T/F - מוסיפים 20 נקודות לT לפני החישוב</t>
+  </si>
+  <si>
+    <t>נכניס קודם כל מרחק אוקלידי פשוט. ואז אפשר גם לחשוב על התאמת סגנונות לפי חוקי המודל (לא בטוח שכדאי, זה לא מוכח מחקרית). כן כדאי להתאים בין אותו טיפוס. לתת ציון אקסטרה אם הם אותו הטיפוס הסופי.</t>
+  </si>
+  <si>
+    <t>כרגע - ממוצע כל התכונות לפי אילו שמשפיעות על הפרופיל. צריך להיות: 50% ממוצע התכונות, 50% התאמה לפי ציון כולל.
+הפרופיל הקוגנטיבי גם מסנן התאמות במרחק 7 נקודות.</t>
   </si>
 </sst>
 </file>
@@ -6658,7 +6653,7 @@
   <sheetData>
     <row r="2" spans="2:20">
       <c r="B2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="R2" t="s">
         <v>835</v>
@@ -6679,7 +6674,7 @@
     </row>
     <row r="5" spans="2:20">
       <c r="B5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="R5" t="s">
         <v>842</v>
@@ -6941,7 +6936,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890832A-DBF2-45FA-8E41-3FB9FF4AFB94}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -6972,10 +6967,10 @@
         <v>891</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>892</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="100.8">
@@ -6983,13 +6978,13 @@
         <v>884</v>
       </c>
       <c r="B3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G3" s="14"/>
     </row>
@@ -6998,13 +6993,13 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>903</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8">
@@ -7012,13 +7007,13 @@
         <v>693</v>
       </c>
       <c r="B5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C5" t="s">
         <v>897</v>
       </c>
-      <c r="C5" t="s">
-        <v>898</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8">
@@ -7026,13 +7021,13 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
@@ -7040,13 +7035,13 @@
         <v>885</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="86.4">
@@ -7054,13 +7049,13 @@
         <v>886</v>
       </c>
       <c r="B8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>909</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72">
@@ -7068,13 +7063,13 @@
         <v>874</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="100.8">
@@ -7082,13 +7077,13 @@
         <v>882</v>
       </c>
       <c r="B10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7096,10 +7091,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7107,7 +7102,7 @@
         <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>260</v>
@@ -7121,10 +7116,10 @@
         <v>881</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7135,7 +7130,7 @@
         <v>863</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>260</v>
@@ -7143,7 +7138,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="14" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -7158,28 +7153,21 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="14" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>925</v>
-      </c>
-    </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="14" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="14" t="s">
-        <v>924</v>
-      </c>
+      <c r="A23" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7F8CD2-2C72-4A31-B8B5-B3791579FE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA97791-DDA3-4215-939B-C7C27A3BBCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="928">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3259,12 +3259,6 @@
     <t>חישוב התאמה</t>
   </si>
   <si>
-    <t>כרגע יש לי שתי שיטות חישוב: 1. פרומפט שמתייחס לכל התכונות הקוגנטיביות (ללא יוקרה תעסוקתית) ומוסיף גם הערכה של אינטליגנציה אינטואיטיבית (לצורך האיזון - לאפשר לAI לפרגן בדרך פחות אנליטית).   2. שיטת הראיות -  אותו הדבר רק במקום להוציא ציון - להוציא ראיות. 6 לכל תכונה עם עדיפות ל3 שליליות ו3 חיובית, וחובה לקחת את החזקות ביותר. (בפועל זה לא בהכרח קורה, והוא גם חוזר על אותם משפטים לכל התכונות  ולא עקבי).
-לשים כרגע את שיטת הראיות בצד, להמשיך לעבוד עם הפרומפט הנוכחי אבל: לעשות כפתור של הרצה נוספת שיאפשר להריץ שוב ולעדכן את הציונים לממוצע ההרצות. צריך בעצם לשמור מערך הרצות לכל משתמש של סך הציונים שקיבל. בהמשך יכול להיות שגם נשתמש בזה כדי לבדוק פערים. אם קיבלתי פער מאוד גדול - אני עולה ארצה להעלות את זה לשיפוט עצמי. 
-בנוסף - בכל אחד מהפרומפטים האחרים נבקש ציון אינטליגנציה אנליטית ואינטליגנציה אינטואיטיבית - נשמור אותם במערך סך אינטלגנציות. ובסוף נרכיב מזה ציון אחד.
-לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90</t>
-  </si>
-  <si>
     <t xml:space="preserve">כל התכונות הקוגנטיביות כולל יוקרה תעסוקתית, לא כולל אינטואיטיבית, כאשר אנליטיות מקבל משקל משולש.
 הציון מנורמל לסקאלה של 20-90.
 לשנות בהמשך את הציון בהתאם ל: מערך אינטליגנציות מכל פרומפט, הרצה משולשת של הפרומפט.
@@ -3370,14 +3364,6 @@
     </r>
   </si>
   <si>
-    <t>ממוצע מרחק אוקלידי.   
-לשקול - להתאים את המרחקים בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות. אולי חוץ מבאינטלגנציה אינטואיטיבית.</t>
-  </si>
-  <si>
-    <t>ממוצע מרחק אוקלידי. 
-לשקול - כנ"ל לסעיף הקודם, אפילו מרחק גדול יותר.</t>
-  </si>
-  <si>
     <t xml:space="preserve">ממוצע מרחק אוקלידי. 
 </t>
   </si>
@@ -3448,6 +3434,29 @@
   <si>
     <t>כרגע - ממוצע כל התכונות לפי אילו שמשפיעות על הפרופיל. צריך להיות: 50% ממוצע התכונות, 50% התאמה לפי ציון כולל.
 הפרופיל הקוגנטיבי גם מסנן התאמות במרחק 7 נקודות.</t>
+  </si>
+  <si>
+    <t>חישוב ציונים כללי</t>
+  </si>
+  <si>
+    <t>ממוצע מרחק אוקלידי. 
+לשקול - כנ"ל לסעיף הקודם, תיקון ל10 נקודות לטובת האישה.</t>
+  </si>
+  <si>
+    <t>כרגע חישוב הציונים נעשה לפי מרחק אוקלידי בין כל התכונות. שיניתי כך שיתאים לפערים הנוכחיים: עד 5 - התאמה טובה, 15 - התאמה לא טובה.  צריך לדייק את זה פר תכונה וגם להתחשב עבור כל תכונה בטווח האמיתי (שהAI נותן בפועל, כמו שעשינו בקוגנטיבי). 
+הציון הסופי מורכב מסך הציונים, כאשר לתכונות עם ודאות נמוכה יותר - יש פחות משקל בציון הסופי.
+בתוך כל פרופיל - מחושב באותו אופן עם דקויות של הפרופיל שמתוארות למעלה.
+לעבור לחישוב לפי פרופילים + אולי גם אחוז  מסוים לחישוב הכללי. כרגע ציון הפרופילים הוא ממוצע ציוני הפרופיל כאשר הפרופיל הקוגנטיבי מקבל משקל כפול. סחיות, עממיות ומידע כללי לא נכנסים</t>
+  </si>
+  <si>
+    <t>50% ממוצע מרחק אוקלידי.   
+50%- התאמה לפי ציון פרופיל עם התאמה של בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות.  תיקון ל4 נקודות לטובת האישה.</t>
+  </si>
+  <si>
+    <t>כרגע יש לי שתי שיטות חישוב: 1. פרומפט שמתייחס לכל התכונות הקוגנטיביות (ללא יוקרה תעסוקתית) ומוסיף גם הערכה של אינטליגנציה אינטואיטיבית (לצורך האיזון - לאפשר לAI לפרגן בדרך פחות אנליטית).   2. שיטת הראיות -  אותו הדבר רק במקום להוציא ציון - להוציא ראיות. 6 לכל תכונה עם עדיפות ל3 שליליות ו3 חיובית, וחובה לקחת את החזקות ביותר. (בפועל זה לא בהכרח קורה, והוא גם חוזר על אותם משפטים לכל התכונות  ולא עקבי).
+לשים כרגע את שיטת הראיות בצד, להמשיך לעבוד עם הפרומפט הנוכחי אבל: לעשות כפתור של הרצה נוספת שיאפשר להריץ שוב ולעדכן את הציונים לממוצע ההרצות. צריך בעצם לשמור מערך הרצות לכל משתמש של סך הציונים שקיבל. בהמשך יכול להיות שגם נשתמש בזה כדי לבדוק פערים. אם קיבלתי פער מאוד גדול - אני עולה ארצה להעלות את זה לשיפוט עצמי. 
+בנוסף - בכל אחד מהפרומפטים האחרים נבקש ציון אינטליגנציה אנליטית ואינטליגנציה אינטואיטיבית - נשמור אותם במערך סך אינטלגנציות. ובסוף נרכיב מזה ציון אחד (לא בטוחה לגבי זה, אולי זה לא ידייק וסתם יתן רעש).
+לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90</t>
   </si>
 </sst>
 </file>
@@ -3668,7 +3677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3827,6 +3836,9 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6653,7 +6665,7 @@
   <sheetData>
     <row r="2" spans="2:20">
       <c r="B2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="R2" t="s">
         <v>835</v>
@@ -6674,7 +6686,7 @@
     </row>
     <row r="5" spans="2:20">
       <c r="B5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="R5" t="s">
         <v>842</v>
@@ -6936,7 +6948,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890832A-DBF2-45FA-8E41-3FB9FF4AFB94}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -6964,27 +6976,27 @@
         <v>415</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>892</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="100.8">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="86.4">
       <c r="A3" s="5" t="s">
         <v>884</v>
       </c>
       <c r="B3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>894</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>903</v>
+        <v>893</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>926</v>
       </c>
       <c r="G3" s="14"/>
     </row>
@@ -6993,13 +7005,13 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
+        <v>900</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>902</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8">
@@ -7007,13 +7019,13 @@
         <v>693</v>
       </c>
       <c r="B5" t="s">
+        <v>895</v>
+      </c>
+      <c r="C5" t="s">
         <v>896</v>
       </c>
-      <c r="C5" t="s">
-        <v>897</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8">
@@ -7021,13 +7033,13 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
@@ -7035,13 +7047,13 @@
         <v>885</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="86.4">
@@ -7049,13 +7061,13 @@
         <v>886</v>
       </c>
       <c r="B8" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72">
@@ -7063,13 +7075,13 @@
         <v>874</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="100.8">
@@ -7077,13 +7089,13 @@
         <v>882</v>
       </c>
       <c r="B10" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7091,10 +7103,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>909</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>912</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7102,7 +7114,7 @@
         <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>260</v>
@@ -7116,10 +7128,10 @@
         <v>881</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7130,44 +7142,52 @@
         <v>863</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="14" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="18" spans="1:2" ht="115.2">
+      <c r="A18" t="s">
+        <v>923</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="14"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="14" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="14"/>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="14" t="s">
+        <v>918</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA97791-DDA3-4215-939B-C7C27A3BBCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECB2BEB-B87D-427A-B99B-B58A9271D2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
     <sheet name="Current Tasks" sheetId="16" r:id="rId2"/>
     <sheet name="Analyzer Tasks" sheetId="17" r:id="rId3"/>
     <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId4"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId5"/>
-    <sheet name="Internal Traits" sheetId="1" r:id="rId6"/>
-    <sheet name="internal traits - Old" sheetId="14" r:id="rId7"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId8"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId9"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId10"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId11"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId12"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId13"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId14"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId15"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId16"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId17"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId18"/>
+    <sheet name="external traits analyze" sheetId="19" r:id="rId5"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId6"/>
+    <sheet name="Internal Traits" sheetId="1" r:id="rId7"/>
+    <sheet name="internal traits - Old" sheetId="14" r:id="rId8"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId9"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId10"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId11"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId12"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId13"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId14"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId15"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId16"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId17"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId18"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1024">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -2848,12 +2849,6 @@
     <t>Intellectualism</t>
   </si>
   <si>
-    <t>Directness</t>
-  </si>
-  <si>
-    <t>ישירות</t>
-  </si>
-  <si>
     <t>עדינות</t>
   </si>
   <si>
@@ -2869,9 +2864,6 @@
     <t>Cognitive Profile</t>
   </si>
   <si>
-    <t>Harsh talk</t>
-  </si>
-  <si>
     <t>Big Five</t>
   </si>
   <si>
@@ -2888,9 +2880,6 @@
   </si>
   <si>
     <t>social_activism</t>
-  </si>
-  <si>
-    <t>אותנטיות</t>
   </si>
   <si>
     <t>Personal Style</t>
@@ -2925,13 +2914,7 @@
 </t>
   </si>
   <si>
-    <t>Dramatic Intensity</t>
-  </si>
-  <si>
     <t>Theatricality</t>
-  </si>
-  <si>
-    <t>Energy Level</t>
   </si>
   <si>
     <t>מידת דתיות</t>
@@ -3175,9 +3158,6 @@
     <t>85/81</t>
   </si>
   <si>
-    <t>לחשוב איך ליצור את ההתאמה, אין לי עוד אלגוריתם לזה</t>
-  </si>
-  <si>
     <t>לסדר את האפיון, את תכנית העבודה ואת כל המשימות שלי</t>
   </si>
   <si>
@@ -3257,12 +3237,6 @@
   </si>
   <si>
     <t>חישוב התאמה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כל התכונות הקוגנטיביות כולל יוקרה תעסוקתית, לא כולל אינטואיטיבית, כאשר אנליטיות מקבל משקל משולש.
-הציון מנורמל לסקאלה של 20-90.
-לשנות בהמשך את הציון בהתאם ל: מערך אינטליגנציות מכל פרומפט, הרצה משולשת של הפרומפט.
-לשקול - לבדוק אם המשתמש הוא "רוני" ואם כן - להעלות ציון. </t>
   </si>
   <si>
     <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך</t>
@@ -3390,11 +3364,6 @@
     <t>אין פרומפט. מבוסס על תכונות קיימות</t>
   </si>
   <si>
-    <t xml:space="preserve">נציג ציון של מסורתיות שיחושב לפי דתיות, חילוניות, שמרנות וערך מסורת. (אולי להפריד את שמרנות לעמדה נפרדת שמכילה גם את הפתיחות וכו')
-נציג ציון של פוליטיות שיחושב לפי שמאל פוליטי וימין פוליטי.  אולי נחשב גם את מידת הפוליטיות הכללית.  
-לחשוב על איך לעשות את החישובים והאם יש עוד עמדות שנגזרות מכאן. </t>
-  </si>
-  <si>
     <t>לחשוב על זה</t>
   </si>
   <si>
@@ -3405,10 +3374,6 @@
   </si>
   <si>
     <t>לנרמל ציוני התאמה. כרגע גבוהים ומוגזמים. לבדוק שוב את החישוב שלי.</t>
-  </si>
-  <si>
-    <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
-אולי להוסיף מידת הסתייגות..?</t>
   </si>
   <si>
     <t>לחשב ציון התאמה לפי שילוב של גרופס + התאמה כללית בין התכונות ולשחק עם המשקלים</t>
@@ -3429,9 +3394,6 @@
 עבור T/F - מוסיפים 20 נקודות לT לפני החישוב</t>
   </si>
   <si>
-    <t>נכניס קודם כל מרחק אוקלידי פשוט. ואז אפשר גם לחשוב על התאמת סגנונות לפי חוקי המודל (לא בטוח שכדאי, זה לא מוכח מחקרית). כן כדאי להתאים בין אותו טיפוס. לתת ציון אקסטרה אם הם אותו הטיפוס הסופי.</t>
-  </si>
-  <si>
     <t>כרגע - ממוצע כל התכונות לפי אילו שמשפיעות על הפרופיל. צריך להיות: 50% ממוצע התכונות, 50% התאמה לפי ציון כולל.
 הפרופיל הקוגנטיבי גם מסנן התאמות במרחק 7 נקודות.</t>
   </si>
@@ -3441,22 +3403,358 @@
   <si>
     <t>ממוצע מרחק אוקלידי. 
 לשקול - כנ"ל לסעיף הקודם, תיקון ל10 נקודות לטובת האישה.</t>
+  </si>
+  <si>
+    <t>50% ממוצע מרחק אוקלידי.   
+50%- התאמה לפי ציון פרופיל עם התאמה של בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות.  תיקון ל4 נקודות לטובת האישה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
+להוסיף אולי מידת הסתייגות.. ובכללי לקרוא על הנושא כדי לפתח את זה נכון יותר. </t>
+  </si>
+  <si>
+    <t>קטגוריה</t>
+  </si>
+  <si>
+    <t>תיאור</t>
+  </si>
+  <si>
+    <t>Visual Appeal Band</t>
+  </si>
+  <si>
+    <t>רמת אטרקטיביות כללית (פנימי בלבד)</t>
+  </si>
+  <si>
+    <t>1 Very Low / 2 Low / 3 Moderate / 4 High / 5 Very High</t>
+  </si>
+  <si>
+    <t>Body Type</t>
+  </si>
+  <si>
+    <t>מבנה גוף כללי</t>
+  </si>
+  <si>
+    <t>Slim / Fit / Average / Curvy / Heavyset</t>
+  </si>
+  <si>
+    <t>Fit</t>
+  </si>
+  <si>
+    <t>Fitness Signal</t>
+  </si>
+  <si>
+    <t>עד כמה נראה פעיל/חטוב</t>
+  </si>
+  <si>
+    <t>Low / Moderate / High</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Grooming Level</t>
+  </si>
+  <si>
+    <t>רמת טיפוח והשקעה</t>
+  </si>
+  <si>
+    <t>Minimal / Moderate / High</t>
+  </si>
+  <si>
+    <t>Style Category</t>
+  </si>
+  <si>
+    <t>סגנון חיצוני</t>
+  </si>
+  <si>
+    <t>Natural / Casual / Polished / Elegant / Glamorous / Alternative</t>
+  </si>
+  <si>
+    <t>Polished</t>
+  </si>
+  <si>
+    <t>Facial Structure</t>
+  </si>
+  <si>
+    <t>מבנה פנים</t>
+  </si>
+  <si>
+    <t>Soft / Balanced / Sharp / Strong-featured / Delicate</t>
+  </si>
+  <si>
+    <t>Sharp</t>
+  </si>
+  <si>
+    <t>Facial Archetype</t>
+  </si>
+  <si>
+    <t>vibe כללי של הפנים</t>
+  </si>
+  <si>
+    <t>Warm / Elegant / Glamorous / Natural / Intellectual / Edgy / Youthful / Mature</t>
+  </si>
+  <si>
+    <t>Warm + Elegant</t>
+  </si>
+  <si>
+    <t>Energy Projection</t>
+  </si>
+  <si>
+    <t>אנרגיה כללית</t>
+  </si>
+  <si>
+    <t>Soft / Feminine / Masculine / Dominant / Playful / Reserved</t>
+  </si>
+  <si>
+    <t>Soft</t>
+  </si>
+  <si>
+    <t>Skin Tone Range</t>
+  </si>
+  <si>
+    <t>טווח גוון חזותי כללי (לא אתני)</t>
+  </si>
+  <si>
+    <t>Fair / Light-Medium / Medium / Olive / Deep</t>
+  </si>
+  <si>
+    <t>Olive</t>
+  </si>
+  <si>
+    <t>Contrast Level</t>
+  </si>
+  <si>
+    <t>ניגודיות כללית (שיער/עור/תווי פנים)</t>
+  </si>
+  <si>
+    <t>Low / Medium / High</t>
+  </si>
+  <si>
+    <t>Overall Presentation</t>
+  </si>
+  <si>
+    <t>רושם כללי</t>
+  </si>
+  <si>
+    <t>Understated / Balanced / Striking</t>
+  </si>
+  <si>
+    <t>Striking</t>
+  </si>
+  <si>
+    <t>Visual Appeal Band – 20%</t>
+  </si>
+  <si>
+    <t>• Body Type/Fitness – 25%</t>
+  </si>
+  <si>
+    <t>• Style/Grooming – 20%</t>
+  </si>
+  <si>
+    <t>• Facial Archetype – 25%</t>
+  </si>
+  <si>
+    <t>• Presentation/Energy – 10%</t>
+  </si>
+  <si>
+    <t>אפשר לשמור גם כסקאלה (לדוגמה)</t>
+  </si>
+  <si>
+    <t>אורית</t>
+  </si>
+  <si>
+    <t>4 או 5</t>
+  </si>
+  <si>
+    <t>Average/curvery</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Natural/casutal/soft polished</t>
+  </si>
+  <si>
+    <t>soft/balanced</t>
+  </si>
+  <si>
+    <t>warm/feminin/natural</t>
+  </si>
+  <si>
+    <t>soft/warm/maternal</t>
+  </si>
+  <si>
+    <t>Light Medium/olive</t>
+  </si>
+  <si>
+    <t>Appeal</t>
+  </si>
+  <si>
+    <t>warmth</t>
+  </si>
+  <si>
+    <t>Glamour</t>
+  </si>
+  <si>
+    <t>Naturalness</t>
+  </si>
+  <si>
+    <t>Fitness aesthetic</t>
+  </si>
+  <si>
+    <t>Style polish</t>
+  </si>
+  <si>
+    <t>• Softness</t>
+  </si>
+  <si>
+    <t>• Sharpness</t>
+  </si>
+  <si>
+    <t>• Dominance</t>
+  </si>
+  <si>
+    <t>• Approachability</t>
+  </si>
+  <si>
+    <t>• Trendiness</t>
+  </si>
+  <si>
+    <t>• Elegance</t>
+  </si>
+  <si>
+    <t>• Distinctiveness</t>
+  </si>
+  <si>
+    <t>נוי</t>
+  </si>
+  <si>
+    <t>Femininity/Masculinity</t>
+  </si>
+  <si>
+    <t>אמיר</t>
+  </si>
+  <si>
+    <t>לי</t>
+  </si>
+  <si>
+    <t>מירה</t>
+  </si>
+  <si>
+    <t>ציון מינימום בפועל</t>
+  </si>
+  <si>
+    <t>1–15 = very fair</t>
+  </si>
+  <si>
+    <t>• 16–30 = fair/light</t>
+  </si>
+  <si>
+    <t>• 31–50 = light-medium</t>
+  </si>
+  <si>
+    <t>• 51–70 = medium/olive</t>
+  </si>
+  <si>
+    <t>• 71–85 = deeper olive/tan</t>
+  </si>
+  <si>
+    <t>• 86–100 = deep/dark</t>
+  </si>
+  <si>
+    <t>טווח skine tone</t>
+  </si>
+  <si>
+    <t>הזנת התכונות באופן ידני / על ידי AI בהתאם ל3 התמונות שישלחו (להדגיש למשתמשים שכדאי תמונות ברורות ותמונות גוף מלא, אם זה סבבה לבקש...)</t>
+  </si>
+  <si>
+    <t>בהעלאת תמונה - אישור ניתוח על ידי AI (ביומטרי). אם מסמנים לא - אישור ניתוח ידני. אם מסמנים לא - הבהרה שלא יהיה לנו ניתוח מראה והמשתמשים יוצגו בלי קשר למראה חיצוני (ובמאגר נפרד, צריך לחשוב אם ואיך להסביר את זה. לא ברור אם צריך לגמרי מאגר נפרד או פשוט ציון התאמה חיצוני  = 0 שישפיע על האפשרויות)</t>
+  </si>
+  <si>
+    <t>לומר למשתמשים שהם יכולים לשנות את ההסכמה בכל עת וגם לדון על זה בצ'אט ( הצ'אט צריך להיות מסוגל לספר להם למה צריך כל דבר ומה המשמעויות)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שילוב של הציונים מהAI + שיעור אישור שמחושב על ידי המערכת.  כרגע מתייחסים רק לציונים מהAI שהם בעצם ידניים כרגע. </t>
+  </si>
+  <si>
+    <t>להוסיף! אבל לחשוב איך להשתמש בזה</t>
+  </si>
+  <si>
+    <t>יכול להשפיע על העממיות אולי, לבדוק אם זה קונסיסטנט</t>
+  </si>
+  <si>
+    <t>נחלק לשתי קטגוריות של תכונות: הראשונה - 6 שהAI מנתח (או ניתוח ידני) עם ציון בכל תכונה (כולל מידת אטרקטיביות כללית, גבריות/נשיות, מבנה גוף וצבע עור, רק במונחים יותר עדינים ופוליטיקלי קורקט).  השניה - תכונות יבשות כמו גובה, צבע שיער עיניים וכו' (חלק מהם גם הAI ינתח). + שיעור אישור.  צריך לחשוב על פרומפט טוב לנושא, וצריך להתכסות מבחינה משפטית, אנושית ושקיפות למשתמש ככל הניתן. 
+הAppeal צריך לשמש גם כמסנן ראשוני במקרים קיצוניים כמו שיעור האישור (אולי במקומו). בנוסף עבור משתמשים שביקשו מפורשות גם המבנה גוף צריך להיות מסנן (אבל עם טווח רחב יחסית, או לפחות בהתחשב בודאות)
+*כל עוד אני עושה ניתוח ידני אני צריכה סקאלות ברורות כמו שאני  נותנת לAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נכניס קודם כל מרחק אוקלידי פשוט. ואז אפשר גם לחשוב על התאמת סגנונות לפי חוקי המודל (לא בטוח שכדאי, זה לא מוכח מחקרית). כן כדאי להתאים בין אותו טיפוס. לתת ציון אקסטרה אם הם אותו הטיפוס הסופי.
+לפי המודל - הדמיון הכי קריטי הוא בציר הN/S מעבר לזה - דמיון הוא לא תמיד רצוי. התאמה טובה תהיה שני צירים זהים ו2 שונים, אבל לא בטוח שנרצה את זה במקרה שלנו. צריך לחשוב איך לחשב. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נציג ציון של מסורתיות שיחושב לפי דתיות, חילוניות, שמרנות וערך מסורת. (אולי להפריד את שמרנות לעמדה נפרדת שמכילה גם את הפתיחות וכו')
+נציג ציון של פוליטיות שיחושב לפי שמאל פוליטי וימין פוליטי.  אולי נחשב גם את מידת הפוליטיות הכללית.  
+לחשוב על איך לעשות את החישובים והאם יש עוד עמדות שנגזרות מכאן. 
+אחרי הרכבת העמדות - להוציא אותן מהסגנון </t>
+  </si>
+  <si>
+    <t>כרגע מרחק רגיל בין הציונים. צריך - להתאים לטווחים האמיתיים, להוסיף התייחסות לשיעור אישור ולהתאים לבקשות המשתמש הספציפי. 
+חישוב המראה צריך להיות שונה אצל גייז, בעיקר במובן של נשיות/גבריות אבל גם לשים לב שזה משפיע על הציון הכללי.  כמו כן - אולי כדאי להתייחס אחרת אצל אנשים שבאמת לא רגישים למראה באופן מפורש.
+אולי צריך להתייחס שונה לאישור של הצד האטרקטיבי יותר. לחשוב על זה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כרגע יש לי שתי שיטות חישוב: 1. פרומפט שמתייחס לכל התכונות הקוגנטיביות (ללא יוקרה תעסוקתית) ומוסיף גם הערכה של אינטליגנציה אינטואיטיבית (לצורך האיזון - לאפשר לAI לפרגן בדרך פחות אנליטית).   2. שיטת הראיות -  אותו הדבר רק במקום להוציא ציון - להוציא ראיות. 6 לכל תכונה עם עדיפות ל3 שליליות ו3 חיובית, וחובה לקחת את החזקות ביותר. (בפועל זה לא בהכרח קורה, והוא גם חוזר על אותם משפטים לכל התכונות  ולא עקבי).
+לשים כרגע את שיטת הראיות בצד, להמשיך לעבוד עם הפרומפט הנוכחי אבל: לעשות כפתור של הרצה נוספת שיאפשר להריץ שוב ולעדכן את הציונים לממוצע ההרצות. צריך בעצם לשמור מערך הרצות לכל משתמש של סך הציונים שקיבל. בהמשך יכול להיות שגם נשתמש בזה כדי לבדוק פערים. אם קיבלתי פער מאוד גדול - אני עולה ארצה להעלות את זה לשיפוט עצמי. 
+בנוסף - בכל אחד מהפרומפטים האחרים נבקש ציון אינטליגנציה אנליטית ואינטליגנציה אינטואיטיבית - נשמור אותם במערך סך אינטלגנציות. ובסוף נרכיב מזה ציון אחד (לא בטוחה לגבי זה, אולי זה לא ידייק וסתם יתן רעש).
+לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90  (נראה לי שכבר עשיתתי את זה)
+המשוחח חייב לשאול את המשתמשים על השכלה וכו' כדי לדייק את הפרופיל הקוגנטיבי. וגם לשאול מה למדו/עשו בעבר. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כל התכונות הקוגנטיביות כולל יוקרה תעסוקתית, לא כולל אינטואיטיבית, כאשר אנליטיות מקבל משקל משולש.
+הציון מנורמל לסקאלה של 20-90.
+לשנות בהמשך את הציון בהתאם ל: מערך אינטליגנציות מכל פרומפט, הרצה משולשת של הפרומפט.
+לשקול - לבדוק אם המשתמש הוא "רוני" ואם כן - להעלות ציון. 
+יכול להיות שצריך להתייחס למצב שבו הפער בין הפרופיל הקוגנטיבי לאינטואיטיבי הוא גדול. </t>
+  </si>
+  <si>
+    <t>energetic_intensity</t>
+  </si>
+  <si>
+    <t>assertiveness_forcefulness</t>
+  </si>
+  <si>
+    <t>אסרטיביות</t>
+  </si>
+  <si>
+    <t>charismatic_presence</t>
+  </si>
+  <si>
+    <t>נוכחות כריזמתית</t>
+  </si>
+  <si>
+    <t>softness_sharpness_balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hesitation </t>
+  </si>
+  <si>
+    <t>מידת הסתייגות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אולי כדאי לשקול שינוי במשקלים של התכונות. נגיד אנרגיה ורמה קוגנטיבית כבסיס ואז את השאר...  בטוח צריך לתת משקלים גבוהים יותר בהתאם לרמת הציונים בחלק מהתכונות כמו נהנתנות, סגנונות וערכים מסוימים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בכל חישובי הציונים - גם ברמת התכונה וגם ברמת הפרופיל צריך להתאים לטווחים בפועל. </t>
   </si>
   <si>
     <t>כרגע חישוב הציונים נעשה לפי מרחק אוקלידי בין כל התכונות. שיניתי כך שיתאים לפערים הנוכחיים: עד 5 - התאמה טובה, 15 - התאמה לא טובה.  צריך לדייק את זה פר תכונה וגם להתחשב עבור כל תכונה בטווח האמיתי (שהAI נותן בפועל, כמו שעשינו בקוגנטיבי). 
 הציון הסופי מורכב מסך הציונים, כאשר לתכונות עם ודאות נמוכה יותר - יש פחות משקל בציון הסופי.
 בתוך כל פרופיל - מחושב באותו אופן עם דקויות של הפרופיל שמתוארות למעלה.
-לעבור לחישוב לפי פרופילים + אולי גם אחוז  מסוים לחישוב הכללי. כרגע ציון הפרופילים הוא ממוצע ציוני הפרופיל כאשר הפרופיל הקוגנטיבי מקבל משקל כפול. סחיות, עממיות ומידע כללי לא נכנסים</t>
-  </si>
-  <si>
-    <t>50% ממוצע מרחק אוקלידי.   
-50%- התאמה לפי ציון פרופיל עם התאמה של בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות.  תיקון ל4 נקודות לטובת האישה.</t>
-  </si>
-  <si>
-    <t>כרגע יש לי שתי שיטות חישוב: 1. פרומפט שמתייחס לכל התכונות הקוגנטיביות (ללא יוקרה תעסוקתית) ומוסיף גם הערכה של אינטליגנציה אינטואיטיבית (לצורך האיזון - לאפשר לAI לפרגן בדרך פחות אנליטית).   2. שיטת הראיות -  אותו הדבר רק במקום להוציא ציון - להוציא ראיות. 6 לכל תכונה עם עדיפות ל3 שליליות ו3 חיובית, וחובה לקחת את החזקות ביותר. (בפועל זה לא בהכרח קורה, והוא גם חוזר על אותם משפטים לכל התכונות  ולא עקבי).
-לשים כרגע את שיטת הראיות בצד, להמשיך לעבוד עם הפרומפט הנוכחי אבל: לעשות כפתור של הרצה נוספת שיאפשר להריץ שוב ולעדכן את הציונים לממוצע ההרצות. צריך בעצם לשמור מערך הרצות לכל משתמש של סך הציונים שקיבל. בהמשך יכול להיות שגם נשתמש בזה כדי לבדוק פערים. אם קיבלתי פער מאוד גדול - אני עולה ארצה להעלות את זה לשיפוט עצמי. 
-בנוסף - בכל אחד מהפרומפטים האחרים נבקש ציון אינטליגנציה אנליטית ואינטליגנציה אינטואיטיבית - נשמור אותם במערך סך אינטלגנציות. ובסוף נרכיב מזה ציון אחד (לא בטוחה לגבי זה, אולי זה לא ידייק וסתם יתן רעש).
-לנרמל את הציון הקוגנטיבי בהנתן שהציונים בפועל נעים בין 20 ל90</t>
+לעבור לחישוב לפי פרופילים + אולי גם אחוז  מסוים לחישוב הכללי. כרגע ציון הפרופילים הוא ממוצע ציוני הפרופיל כאשר הפרופיל הקוגנטיבי מקבל משקל כפול. סחיות, עממיות ומידע כללי לא נכנסים.
+לגבי המראה כרגע הוא נכנס לחישוב הכללי כ30 אחוז או 35 למשתמשים רגישים (ציון 70 ומעלה בודאות 0.7 ומעלה), ולחישוב הפרופילים נכנס כפרופיל נוסף עם משקל כפול.  לחשוב על זה, כי מצד אחד אני רוצה שברושם הראשוני אני אציג משתמשים שקשורים מבחינת מראה, מצד שני - אני רוצה לתת משקל מהותי יותר לאישיות, והמראה הוא רק מסנן. בסופו של דבר - בחירת המשתמש תחליף (או תשנה משמעותית) את הציון לפי מראה, ואז להחליט איזה משקל לתת לזה.   לקחת בחשבון גם שהתמונות יכולות להטעות, בעיקר את הAI, כמו במקרה אורית/הילה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בחישוב לפי פרופילים שיחקתי קצת עם המשקלים, בגדול כדי להתאים יותר לנוי ורון אז צריך לראות שזה באמת אמין. </t>
   </si>
 </sst>
 </file>
@@ -3677,7 +3975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3839,6 +4137,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4410,6 +4720,303 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="16.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.44140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="27.6">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.8">
+      <c r="C5" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="41.4">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.2">
+      <c r="C10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.6">
+      <c r="A13" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="19"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="B28"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="B29"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="B32"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33"/>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="14"/>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="I39"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="I41"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4759,7 +5366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5374,7 +5981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5659,7 +6266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5881,7 +6488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6043,7 +6650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6193,7 +6800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6238,7 +6845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6317,7 +6924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6665,77 +7272,77 @@
   <sheetData>
     <row r="2" spans="2:20">
       <c r="B2" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="R2" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3" spans="2:20">
       <c r="B3" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="R3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
     </row>
     <row r="4" spans="2:20">
       <c r="B4" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="2:20">
       <c r="B5" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="R5" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="2:20">
       <c r="R6" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="2:20">
       <c r="B7" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="R7" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="2:20">
       <c r="R8" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="72.599999999999994">
       <c r="K9" s="60" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="L9" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="M9" s="59" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="O9" s="59" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" spans="2:20">
       <c r="B10" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="J10" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="K10">
         <v>90</v>
@@ -6747,18 +7354,18 @@
         <v>82</v>
       </c>
       <c r="N10" s="58" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="O10" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="P10" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="2:20">
       <c r="J11" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="K11">
         <v>58</v>
@@ -6767,24 +7374,24 @@
         <v>51</v>
       </c>
       <c r="M11" s="57" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="N11" s="57" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="O11" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="P11" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="T11" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="2:20">
       <c r="J12" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="K12">
         <v>81</v>
@@ -6796,21 +7403,21 @@
         <v>65</v>
       </c>
       <c r="N12" s="58" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="O12" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="P12">
         <v>48</v>
       </c>
       <c r="T12" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="2:20">
       <c r="J13" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="K13">
         <v>93</v>
@@ -6822,10 +7429,10 @@
         <v>87</v>
       </c>
       <c r="N13" s="58" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="O13" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="P13">
         <v>75</v>
@@ -6833,10 +7440,10 @@
     </row>
     <row r="14" spans="2:20">
       <c r="B14" s="58" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="J14" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="K14">
         <v>63</v>
@@ -6848,10 +7455,10 @@
         <v>81</v>
       </c>
       <c r="N14" s="57" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="O14" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="P14">
         <v>45</v>
@@ -6859,10 +7466,10 @@
     </row>
     <row r="15" spans="2:20">
       <c r="B15" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="J15" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="K15">
         <v>54</v>
@@ -6874,15 +7481,15 @@
         <v>51</v>
       </c>
       <c r="N15" s="58" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="16" spans="2:20">
       <c r="B16" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="J16" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="L16">
         <v>17</v>
@@ -6890,7 +7497,7 @@
     </row>
     <row r="17" spans="2:15">
       <c r="J17" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="L17">
         <v>65</v>
@@ -6898,47 +7505,47 @@
     </row>
     <row r="20" spans="2:15">
       <c r="B20" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="22" spans="2:15">
       <c r="O22" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="O23" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
     </row>
     <row r="24" spans="2:15">
       <c r="O24" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="25" spans="2:15">
       <c r="O25" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
     </row>
     <row r="26" spans="2:15">
       <c r="O26" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
     </row>
     <row r="27" spans="2:15">
       <c r="O27" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
     </row>
     <row r="29" spans="2:15">
       <c r="O29" s="14" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="31" spans="2:15">
       <c r="O31" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -6959,44 +7566,44 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="14" t="s">
+        <v>876</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>882</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>883</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>888</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>889</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="158.4">
+    </row>
+    <row r="2" spans="1:7" ht="187.2">
       <c r="A2" s="5" t="s">
         <v>415</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>927</v>
+        <v>1010</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>891</v>
+        <v>1011</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="86.4">
       <c r="A3" s="5" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B3" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="G3" s="14"/>
     </row>
@@ -7005,13 +7612,13 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8">
@@ -7019,13 +7626,13 @@
         <v>693</v>
       </c>
       <c r="B5" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="C5" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8">
@@ -7033,69 +7640,69 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="D6" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
       <c r="A7" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>915</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="86.4">
       <c r="A8" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="B8" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="144">
       <c r="A9" s="58" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="100.8">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="115.2">
       <c r="A10" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="B10" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>910</v>
+        <v>1008</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7103,10 +7710,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7114,7 +7721,7 @@
         <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>260</v>
@@ -7122,38 +7729,53 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="B13" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="158.4">
       <c r="A14" t="s">
         <v>438</v>
       </c>
-      <c r="B14" t="s">
-        <v>863</v>
+      <c r="B14" s="5" t="s">
+        <v>1006</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>911</v>
+        <v>1003</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="115.2">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="201.6">
       <c r="A18" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>925</v>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="28.8">
+      <c r="B19" s="5" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7161,32 +7783,32 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="14" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="14" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -7195,6 +7817,659 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DB26E2-2FEB-428C-8A2B-44341C3C4297}">
+  <dimension ref="B1:P37"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" customWidth="1"/>
+    <col min="5" max="5" width="38.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16">
+      <c r="B1" s="62" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>917</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="62" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="28.8">
+      <c r="B2" s="63" t="s">
+        <v>918</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>919</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>920</v>
+      </c>
+      <c r="E2" s="63">
+        <v>4</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="28.8">
+      <c r="B3" s="63" t="s">
+        <v>921</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>922</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="28.8">
+      <c r="B4" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>927</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="28.8">
+      <c r="B5" s="63" t="s">
+        <v>929</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>930</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>931</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="57.6">
+      <c r="B6" s="63" t="s">
+        <v>932</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>933</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>934</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>935</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="28.8">
+      <c r="B7" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>937</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>938</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>939</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="43.2">
+      <c r="B8" s="63" t="s">
+        <v>940</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>941</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>942</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>943</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="43.2">
+      <c r="B9" s="63" t="s">
+        <v>944</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>945</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>946</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>947</v>
+      </c>
+      <c r="G9" s="63" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="43.2">
+      <c r="B10" s="63" t="s">
+        <v>948</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>949</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>950</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>951</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="28.8">
+      <c r="B11" s="63" t="s">
+        <v>952</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>953</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>954</v>
+      </c>
+      <c r="E11" s="63" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="28.8">
+      <c r="B12" s="63" t="s">
+        <v>955</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>956</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>957</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="F14" t="s">
+        <v>965</v>
+      </c>
+      <c r="G14" t="s">
+        <v>987</v>
+      </c>
+      <c r="H14" t="s">
+        <v>823</v>
+      </c>
+      <c r="I14" t="s">
+        <v>989</v>
+      </c>
+      <c r="J14" t="s">
+        <v>822</v>
+      </c>
+      <c r="K14" t="s">
+        <v>990</v>
+      </c>
+      <c r="L14" t="s">
+        <v>991</v>
+      </c>
+      <c r="M14" t="s">
+        <v>824</v>
+      </c>
+      <c r="N14" t="s">
+        <v>828</v>
+      </c>
+      <c r="P14" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="B15" s="64" t="s">
+        <v>964</v>
+      </c>
+      <c r="D15">
+        <v>80</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>974</v>
+      </c>
+      <c r="F15" s="14">
+        <v>78</v>
+      </c>
+      <c r="G15" s="14">
+        <v>94</v>
+      </c>
+      <c r="H15" s="14">
+        <v>91</v>
+      </c>
+      <c r="I15" s="14">
+        <v>84</v>
+      </c>
+      <c r="J15" s="14">
+        <v>86</v>
+      </c>
+      <c r="K15" s="14">
+        <v>79</v>
+      </c>
+      <c r="L15" s="14">
+        <v>66</v>
+      </c>
+      <c r="M15" s="14">
+        <v>80</v>
+      </c>
+      <c r="N15" s="14">
+        <v>74</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="C16" t="s">
+        <v>959</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>975</v>
+      </c>
+      <c r="F16">
+        <v>92</v>
+      </c>
+      <c r="G16">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>68</v>
+      </c>
+      <c r="I16">
+        <v>90</v>
+      </c>
+      <c r="J16">
+        <v>94</v>
+      </c>
+      <c r="K16">
+        <v>82</v>
+      </c>
+      <c r="L16">
+        <v>74</v>
+      </c>
+      <c r="M16">
+        <v>96</v>
+      </c>
+      <c r="N16">
+        <v>78</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="3:16">
+      <c r="C17" t="s">
+        <v>960</v>
+      </c>
+      <c r="D17">
+        <v>84</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>988</v>
+      </c>
+      <c r="F17" s="14">
+        <v>84</v>
+      </c>
+      <c r="G17" s="14">
+        <v>95</v>
+      </c>
+      <c r="H17" s="14">
+        <v>94</v>
+      </c>
+      <c r="I17" s="14">
+        <v>82</v>
+      </c>
+      <c r="J17" s="14">
+        <v>82</v>
+      </c>
+      <c r="K17" s="14">
+        <v>58</v>
+      </c>
+      <c r="L17" s="14">
+        <v>72</v>
+      </c>
+      <c r="M17" s="14">
+        <v>84</v>
+      </c>
+      <c r="N17" s="14">
+        <v>76</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16">
+      <c r="C18" t="s">
+        <v>961</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>976</v>
+      </c>
+      <c r="F18">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>93</v>
+      </c>
+      <c r="H18">
+        <v>88</v>
+      </c>
+      <c r="I18">
+        <v>68</v>
+      </c>
+      <c r="J18">
+        <v>58</v>
+      </c>
+      <c r="K18">
+        <v>48</v>
+      </c>
+      <c r="L18">
+        <v>42</v>
+      </c>
+      <c r="M18">
+        <v>46</v>
+      </c>
+      <c r="N18">
+        <v>52</v>
+      </c>
+      <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16">
+      <c r="C19" t="s">
+        <v>962</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>977</v>
+      </c>
+      <c r="F19">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>78</v>
+      </c>
+      <c r="H19">
+        <v>74</v>
+      </c>
+      <c r="I19">
+        <v>92</v>
+      </c>
+      <c r="J19">
+        <v>95</v>
+      </c>
+      <c r="K19">
+        <v>93</v>
+      </c>
+      <c r="L19">
+        <v>88</v>
+      </c>
+      <c r="M19">
+        <v>97</v>
+      </c>
+      <c r="N19">
+        <v>88</v>
+      </c>
+      <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16">
+      <c r="C20" t="s">
+        <v>963</v>
+      </c>
+      <c r="D20">
+        <v>72</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>978</v>
+      </c>
+      <c r="F20" s="14">
+        <v>58</v>
+      </c>
+      <c r="G20" s="14">
+        <v>90</v>
+      </c>
+      <c r="H20" s="14">
+        <v>89</v>
+      </c>
+      <c r="I20" s="14">
+        <v>83</v>
+      </c>
+      <c r="J20" s="14">
+        <v>76</v>
+      </c>
+      <c r="K20" s="14">
+        <v>84</v>
+      </c>
+      <c r="L20" s="14">
+        <v>58</v>
+      </c>
+      <c r="M20" s="14">
+        <v>72</v>
+      </c>
+      <c r="N20" s="14">
+        <v>62</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16">
+      <c r="E21" s="63" t="s">
+        <v>979</v>
+      </c>
+      <c r="F21">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>96</v>
+      </c>
+      <c r="H21">
+        <v>90</v>
+      </c>
+      <c r="I21">
+        <v>72</v>
+      </c>
+      <c r="J21">
+        <v>66</v>
+      </c>
+      <c r="K21">
+        <v>74</v>
+      </c>
+      <c r="L21">
+        <v>54</v>
+      </c>
+      <c r="M21">
+        <v>58</v>
+      </c>
+      <c r="N21">
+        <v>68</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16">
+      <c r="E22" s="63" t="s">
+        <v>948</v>
+      </c>
+      <c r="F22">
+        <v>38</v>
+      </c>
+      <c r="G22">
+        <v>42</v>
+      </c>
+      <c r="H22">
+        <v>58</v>
+      </c>
+      <c r="I22">
+        <v>72</v>
+      </c>
+      <c r="J22">
+        <v>48</v>
+      </c>
+      <c r="K22">
+        <v>22</v>
+      </c>
+      <c r="L22">
+        <v>36</v>
+      </c>
+      <c r="M22">
+        <v>42</v>
+      </c>
+      <c r="N22">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16">
+      <c r="E24" t="s">
+        <v>980</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16">
+      <c r="E25" t="s">
+        <v>981</v>
+      </c>
+      <c r="N25" t="s">
+        <v>993</v>
+      </c>
+      <c r="O25" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16">
+      <c r="E26" t="s">
+        <v>982</v>
+      </c>
+      <c r="N26" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16">
+      <c r="E27" t="s">
+        <v>983</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N27" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16">
+      <c r="E28" t="s">
+        <v>984</v>
+      </c>
+      <c r="N28" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16">
+      <c r="E29" t="s">
+        <v>985</v>
+      </c>
+      <c r="N29" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16">
+      <c r="E30" t="s">
+        <v>986</v>
+      </c>
+      <c r="N30" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7715,9 +8990,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
@@ -7753,7 +9028,7 @@
         <v>413</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>6</v>
@@ -7765,7 +9040,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>3</v>
@@ -7794,13 +9069,13 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C5" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>761</v>
@@ -7815,10 +9090,10 @@
     </row>
     <row r="6" spans="1:14" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C6" t="s">
         <v>753</v>
@@ -7836,10 +9111,10 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C7" t="s">
         <v>754</v>
@@ -7857,13 +9132,13 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C8" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>755</v>
@@ -7876,13 +9151,13 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>639</v>
@@ -7924,13 +9199,13 @@
         <v>715</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -7943,7 +9218,7 @@
         <v>715</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>763</v>
@@ -7962,7 +9237,7 @@
         <v>715</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>762</v>
@@ -7971,7 +9246,7 @@
         <v>436</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -7981,16 +9256,16 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>768</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>665</v>
+        <v>1017</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -7998,18 +9273,18 @@
       <c r="H15" s="3"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:14" ht="27.6">
+    <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>768</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>771</v>
+        <v>1013</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>704</v>
+        <v>1014</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -8019,16 +9294,16 @@
     </row>
     <row r="17" spans="1:11" ht="27.6">
       <c r="A17" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>768</v>
-      </c>
       <c r="C17" t="s">
-        <v>764</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>765</v>
+        <v>1016</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -8038,16 +9313,16 @@
     </row>
     <row r="18" spans="1:11" ht="27.6">
       <c r="A18" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>768</v>
-      </c>
       <c r="C18" t="s">
-        <v>666</v>
+        <v>1018</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>707</v>
+        <v>1019</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -8055,37 +9330,37 @@
       <c r="H18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="27.6">
+    <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C19" t="s">
-        <v>671</v>
+        <v>784</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>778</v>
+        <v>702</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="K19" s="34"/>
     </row>
     <row r="20" spans="1:11" ht="27.6">
       <c r="A20" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>768</v>
-      </c>
       <c r="C20" t="s">
-        <v>788</v>
+        <v>1012</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>701</v>
+        <v>22</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -8093,78 +9368,82 @@
       <c r="H20" s="3"/>
       <c r="K20" s="34"/>
     </row>
-    <row r="21" spans="1:11" ht="27.6">
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>766</v>
+        <v>693</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C21" t="s">
-        <v>789</v>
+        <v>769</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="K21" s="34"/>
-    </row>
-    <row r="22" spans="1:11" ht="27.6">
+      <c r="H21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>766</v>
+        <v>693</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C22" t="s">
-        <v>790</v>
+        <v>769</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>22</v>
+        <v>643</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="K22" s="34"/>
+      <c r="H22" s="2"/>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>696</v>
+        <v>769</v>
+      </c>
+      <c r="C23" t="s">
+        <v>716</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>697</v>
+        <v>644</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="28.8">
+    <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>717</v>
+        <v>769</v>
+      </c>
+      <c r="C24" t="s">
+        <v>718</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>643</v>
+        <v>719</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="2"/>
       <c r="J24" s="2"/>
@@ -8174,38 +9453,38 @@
         <v>693</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C25" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>644</v>
+        <v>721</v>
       </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>426</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="2"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C26" t="s">
-        <v>718</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>426</v>
+        <v>770</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>723</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>731</v>
+      </c>
+      <c r="F26" s="56" t="s">
+        <v>425</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
@@ -8213,233 +9492,227 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C27" t="s">
-        <v>720</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+        <v>770</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>725</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E27" s="56" t="s">
+        <v>730</v>
+      </c>
+      <c r="F27" s="56"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="2"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>723</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>728</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>731</v>
-      </c>
-      <c r="F28" s="56" t="s">
-        <v>425</v>
-      </c>
+        <v>729</v>
+      </c>
+      <c r="F28" s="56"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>725</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>726</v>
+        <v>732</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>734</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="F29" s="56"/>
       <c r="G29" s="3"/>
-      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="F30" s="56"/>
       <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="E31" s="56" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F31" s="56"/>
       <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>733</v>
+        <v>544</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>735</v>
+        <v>543</v>
       </c>
       <c r="E32" s="56" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F32" s="56"/>
       <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F33" s="56"/>
       <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>544</v>
+        <v>744</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>543</v>
+        <v>745</v>
       </c>
       <c r="E34" s="56" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="F34" s="56"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="F35" s="56"/>
       <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C36" s="56" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="E36" s="56" t="s">
-        <v>748</v>
-      </c>
-      <c r="F36" s="56"/>
+        <v>752</v>
+      </c>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" ht="28.8">
       <c r="A37" s="2" t="s">
-        <v>774</v>
+        <v>426</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>746</v>
+        <v>772</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>432</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="E37" s="56" t="s">
-        <v>749</v>
-      </c>
-      <c r="F37" s="56"/>
+        <v>414</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" ht="220.8">
       <c r="A38" s="2" t="s">
-        <v>774</v>
+        <v>426</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>751</v>
+        <v>772</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>752</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:11" ht="28.8">
@@ -8447,610 +9720,574 @@
         <v>426</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C39" s="49" t="s">
-        <v>432</v>
+        <v>772</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E39" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>564</v>
+      </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:11" ht="220.8">
+      <c r="H39" s="3"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>804</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:11" ht="28.8">
       <c r="A41" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>563</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>564</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="J41" s="2"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="3"/>
     </row>
     <row r="42" spans="1:11" ht="28.8">
       <c r="A42" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>36</v>
+        <v>772</v>
+      </c>
+      <c r="C42" t="s">
+        <v>664</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>37</v>
+        <v>705</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" ht="28.8">
-      <c r="A43" s="2" t="s">
+      <c r="K42" s="34"/>
+    </row>
+    <row r="43" spans="1:11" ht="179.4">
+      <c r="A43" s="40" t="s">
         <v>426</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E43" s="3"/>
+      <c r="B43" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>796</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>797</v>
+      </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="1:11" ht="28.8">
+      <c r="K43" s="34"/>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="C44" t="s">
-        <v>664</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="C44" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>545</v>
+      </c>
+      <c r="E44" s="17"/>
       <c r="H44" s="3"/>
-      <c r="K44" s="34"/>
-    </row>
-    <row r="45" spans="1:11" ht="179.4">
-      <c r="A45" s="40" t="s">
-        <v>426</v>
-      </c>
-      <c r="B45" s="37" t="s">
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="C45" s="38" t="s">
-        <v>802</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>803</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="K45" s="34"/>
+      <c r="C45" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C46" s="49" t="s">
-        <v>431</v>
-      </c>
-      <c r="D46" s="48" t="s">
-        <v>545</v>
-      </c>
-      <c r="E46" s="17"/>
-      <c r="H46" s="3"/>
+        <v>775</v>
+      </c>
+      <c r="C46" t="s">
+        <v>557</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C47" s="49" t="s">
-        <v>550</v>
+        <v>775</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>350</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="48" spans="1:11" ht="28.8">
       <c r="A48" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C48" t="s">
-        <v>557</v>
+        <v>775</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>558</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>44</v>
+        <v>775</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="1:11" ht="28.8">
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>559</v>
+        <v>31</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>558</v>
+        <v>32</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C51" s="49" t="s">
-        <v>42</v>
+        <v>775</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>776</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>43</v>
+        <v>567</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="17"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>31</v>
+        <v>777</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:11">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>780</v>
+        <v>775</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>774</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>16</v>
+      </c>
+      <c r="D54" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C55" s="49" t="s">
-        <v>777</v>
+        <v>775</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>775</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="17" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="69">
       <c r="A57" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>775</v>
+      </c>
+      <c r="C57" s="38"/>
       <c r="D57" s="3" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>383</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="69">
       <c r="A58" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="17" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="69">
+        <v>775</v>
+      </c>
+      <c r="C58" s="38"/>
+      <c r="D58" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27.6">
       <c r="A59" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C59" s="38"/>
       <c r="D59" s="3" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="69">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="82.8">
       <c r="A60" s="2" t="s">
         <v>425</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C60" s="38"/>
-      <c r="D60" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="27.6">
+        <v>775</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>425</v>
+        <v>867</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="82.8">
+        <v>860</v>
+      </c>
+      <c r="C61" t="s">
+        <v>861</v>
+      </c>
+      <c r="D61" s="38" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
-        <v>425</v>
+        <v>867</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="D62" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="E62" s="33" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>860</v>
+      </c>
+      <c r="C62" t="s">
+        <v>862</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="C63" t="s">
+        <v>863</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="C63" t="s">
-        <v>868</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="2" t="s">
-        <v>874</v>
-      </c>
       <c r="B64" s="3" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C64" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C65" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C66" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>874</v>
+        <v>430</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="C67" t="s">
-        <v>872</v>
-      </c>
-      <c r="D67" s="38" t="s">
-        <v>876</v>
+        <v>786</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>874</v>
+        <v>430</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>867</v>
+        <v>786</v>
       </c>
       <c r="C68" t="s">
-        <v>873</v>
-      </c>
-      <c r="D68" s="38" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>787</v>
+      </c>
+      <c r="D68" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>46</v>
+        <v>560</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="28.8">
       <c r="A70" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C70" t="s">
-        <v>793</v>
-      </c>
-      <c r="D70" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="28.8">
+        <v>786</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="82.8">
       <c r="A71" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>560</v>
+        <v>788</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="28.8">
+        <v>56</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="69">
       <c r="A72" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>48</v>
+        <v>789</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="82.8">
+        <v>114</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="55.2">
       <c r="A73" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="69">
+    </row>
+    <row r="74" spans="1:5" ht="409.6">
       <c r="A74" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>114</v>
+        <v>699</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="55.2">
-      <c r="A75" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="409.6">
-      <c r="A76" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="E76" s="3" t="s">
         <v>700</v>
       </c>
     </row>
@@ -9059,7 +10296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9902,7 +11139,7 @@
         <v>429</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>35</v>
@@ -11153,7 +12390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11431,301 +12668,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="5"/>
-    <col min="2" max="2" width="16.88671875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.44140625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="27.6">
-      <c r="A4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.8">
-      <c r="C5" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="41.4">
-      <c r="A9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9"/>
-    </row>
-    <row r="10" spans="1:10" ht="43.2">
-      <c r="C10" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.6">
-      <c r="A13" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="J14"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="J15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="19"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="B28"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="B29"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="B30"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="B31"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="B32"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33"/>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="I39"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="I41"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECB2BEB-B87D-427A-B99B-B58A9271D2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB393DB-9CF3-4554-9EFF-6E5F9F41CC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -3209,9 +3209,6 @@
     <t>אינטואיציה</t>
   </si>
   <si>
-    <t>לחשוב איך מכניסים לסוגי התאמה ולחשוב איך להשתמש בטקסט הכללי</t>
-  </si>
-  <si>
     <t>עמדות</t>
   </si>
   <si>
@@ -3237,9 +3234,6 @@
   </si>
   <si>
     <t>חישוב התאמה</t>
-  </si>
-  <si>
-    <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך</t>
   </si>
   <si>
     <r>
@@ -3755,6 +3749,14 @@
   </si>
   <si>
     <t xml:space="preserve">בחישוב לפי פרופילים שיחקתי קצת עם המשקלים, בגדול כדי להתאים יותר לנוי ורון אז צריך לראות שזה באמת אמין. </t>
+  </si>
+  <si>
+    <t>לחשוב איך מכניסים לסוגי התאמה ולחשוב איך להשתמש בטקסט הכללי (דיל ברייקרס ויתרונות אפשריים)</t>
+  </si>
+  <si>
+    <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
+פרופיל סופר קריטי. להוציא מפה כל מה שקשור לעמדות. להכניס סגנונות אפשריים - צריך לבנות את זה חכם. אולי בתגיות חופשיות (או לא חופשיות). לחשוב על זה. לצורך הבדיקה של זה אצטרך משתמשים מסגנונות שונים באמת, כרגע האוכלוסייה במערכת שלי די הומוגנית.  צריך אולי גם להיות גורם מפלטר לסגנונות לא קשורים.
+סגנונות אפשריים (לחשוב איך לעשות את זה פוליטיקלי קורקט): ערסים, נורמטיבי, עממי, סחי, קיבוצניק/מושבניק, היפי, סובייטי, גיק, תרבות גבוהה, אליטיסטי, קפליניסט. לחשוב מה עוד ואיך לנסח.</t>
   </si>
 </sst>
 </file>
@@ -7272,7 +7274,7 @@
   <sheetData>
     <row r="2" spans="2:20">
       <c r="B2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="R2" t="s">
         <v>829</v>
@@ -7293,7 +7295,7 @@
     </row>
     <row r="5" spans="2:20">
       <c r="B5" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="R5" t="s">
         <v>836</v>
@@ -7566,16 +7568,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>880</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>881</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>882</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="187.2">
@@ -7583,27 +7585,27 @@
         <v>415</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="86.4">
       <c r="A3" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G3" s="14"/>
     </row>
@@ -7612,13 +7614,13 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8">
@@ -7626,13 +7628,13 @@
         <v>693</v>
       </c>
       <c r="B5" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C5" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8">
@@ -7640,41 +7642,41 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D6" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
       <c r="A7" t="s">
+        <v>877</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="115.2">
+      <c r="A8" t="s">
         <v>878</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>896</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="86.4">
-      <c r="A8" t="s">
-        <v>879</v>
-      </c>
-      <c r="B8" t="s">
-        <v>884</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>897</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="144">
@@ -7682,27 +7684,27 @@
         <v>867</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="115.2">
       <c r="A10" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B10" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7710,10 +7712,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>901</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7721,7 +7723,7 @@
         <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>260</v>
@@ -7729,16 +7731,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B13" t="s">
-        <v>874</v>
+        <v>1022</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="158.4">
@@ -7746,36 +7748,36 @@
         <v>438</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="201.6">
       <c r="A18" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="28.8">
       <c r="B19" s="5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7783,7 +7785,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="14" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7798,17 +7800,17 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="14" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
   </sheetData>
@@ -7829,10 +7831,10 @@
   <sheetData>
     <row r="1" spans="2:16">
       <c r="B1" s="62" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>151</v>
@@ -7841,211 +7843,211 @@
         <v>213</v>
       </c>
       <c r="G1" s="62" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="2" spans="2:16" ht="28.8">
       <c r="B2" s="63" t="s">
+        <v>916</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>917</v>
+      </c>
+      <c r="D2" s="63" t="s">
         <v>918</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>919</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>920</v>
       </c>
       <c r="E2" s="63">
         <v>4</v>
       </c>
       <c r="G2" s="65" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="28.8">
       <c r="B3" s="63" t="s">
+        <v>919</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>920</v>
+      </c>
+      <c r="D3" s="63" t="s">
         <v>921</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="E3" s="63" t="s">
         <v>922</v>
       </c>
-      <c r="D3" s="63" t="s">
-        <v>923</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>924</v>
-      </c>
       <c r="G3" s="63" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="28.8">
       <c r="B4" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>925</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="E4" s="63" t="s">
         <v>926</v>
       </c>
-      <c r="D4" s="63" t="s">
-        <v>927</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>928</v>
-      </c>
       <c r="G4" s="63" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="28.8">
       <c r="B5" s="63" t="s">
+        <v>927</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="D5" s="63" t="s">
         <v>929</v>
       </c>
-      <c r="C5" s="63" t="s">
-        <v>930</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>931</v>
-      </c>
       <c r="E5" s="63" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="57.6">
       <c r="B6" s="63" t="s">
+        <v>930</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>931</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>932</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="E6" s="63" t="s">
         <v>933</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>934</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>935</v>
-      </c>
       <c r="G6" s="63" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="28.8">
       <c r="B7" s="63" t="s">
+        <v>934</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>935</v>
+      </c>
+      <c r="D7" s="63" t="s">
         <v>936</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="E7" s="63" t="s">
         <v>937</v>
       </c>
-      <c r="D7" s="63" t="s">
-        <v>938</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>939</v>
-      </c>
       <c r="G7" s="63" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="43.2">
       <c r="B8" s="63" t="s">
+        <v>938</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>939</v>
+      </c>
+      <c r="D8" s="63" t="s">
         <v>940</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="E8" s="63" t="s">
         <v>941</v>
       </c>
-      <c r="D8" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="E8" s="63" t="s">
-        <v>943</v>
-      </c>
       <c r="G8" s="63" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="43.2">
       <c r="B9" s="63" t="s">
+        <v>942</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>943</v>
+      </c>
+      <c r="D9" s="63" t="s">
         <v>944</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="E9" s="63" t="s">
         <v>945</v>
       </c>
-      <c r="D9" s="63" t="s">
-        <v>946</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>947</v>
-      </c>
       <c r="G9" s="63" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="43.2">
       <c r="B10" s="63" t="s">
+        <v>946</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>947</v>
+      </c>
+      <c r="D10" s="63" t="s">
         <v>948</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="E10" s="63" t="s">
         <v>949</v>
       </c>
-      <c r="D10" s="63" t="s">
-        <v>950</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>951</v>
-      </c>
       <c r="G10" s="63" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8">
       <c r="B11" s="63" t="s">
+        <v>950</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>951</v>
+      </c>
+      <c r="D11" s="63" t="s">
         <v>952</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>953</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>954</v>
-      </c>
       <c r="E11" s="63" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8">
       <c r="B12" s="63" t="s">
+        <v>953</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>954</v>
+      </c>
+      <c r="D12" s="63" t="s">
         <v>955</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="E12" s="63" t="s">
         <v>956</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>957</v>
-      </c>
-      <c r="E12" s="63" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="F14" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G14" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H14" t="s">
         <v>823</v>
       </c>
       <c r="I14" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="J14" t="s">
         <v>822</v>
       </c>
       <c r="K14" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="L14" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M14" t="s">
         <v>824</v>
@@ -8054,18 +8056,18 @@
         <v>828</v>
       </c>
       <c r="P14" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" s="64" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D15">
         <v>80</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F15" s="14">
         <v>78</v>
@@ -8103,10 +8105,10 @@
     </row>
     <row r="16" spans="2:16">
       <c r="C16" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E16" s="63" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="F16">
         <v>92</v>
@@ -8144,13 +8146,13 @@
     </row>
     <row r="17" spans="3:16">
       <c r="C17" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D17">
         <v>84</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F17" s="14">
         <v>84</v>
@@ -8188,10 +8190,10 @@
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E18" s="63" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F18">
         <v>52</v>
@@ -8229,10 +8231,10 @@
     </row>
     <row r="19" spans="3:16">
       <c r="C19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F19">
         <v>88</v>
@@ -8270,13 +8272,13 @@
     </row>
     <row r="20" spans="3:16">
       <c r="C20" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D20">
         <v>72</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F20" s="14">
         <v>58</v>
@@ -8314,7 +8316,7 @@
     </row>
     <row r="21" spans="3:16">
       <c r="E21" s="63" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F21">
         <v>64</v>
@@ -8352,7 +8354,7 @@
     </row>
     <row r="22" spans="3:16">
       <c r="E22" s="63" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F22">
         <v>38</v>
@@ -8384,79 +8386,79 @@
     </row>
     <row r="24" spans="3:16">
       <c r="E24" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F24" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="25" spans="3:16">
       <c r="E25" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="N25" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="O25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="26" spans="3:16">
       <c r="E26" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="N26" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="27" spans="3:16">
       <c r="E27" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F27" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="N27" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="28" spans="3:16">
       <c r="E28" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="N28" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="29" spans="3:16">
       <c r="E29" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="N29" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="30" spans="3:16">
       <c r="E30" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="N30" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -9262,7 +9264,7 @@
         <v>766</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>765</v>
@@ -9281,10 +9283,10 @@
         <v>766</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -9300,10 +9302,10 @@
         <v>766</v>
       </c>
       <c r="C17" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -9319,10 +9321,10 @@
         <v>766</v>
       </c>
       <c r="C18" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -9357,7 +9359,7 @@
         <v>766</v>
       </c>
       <c r="C20" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB393DB-9CF3-4554-9EFF-6E5F9F41CC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91FBD22-86B4-4C77-965C-E82FF7E1BC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="1026">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3236,32 +3236,6 @@
     <t>חישוב התאמה</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">מורכב מממוצע התכונות: אינטלגנציה אינטואיטיבית, מודעות עצמית, אינטלגנציה רגשית וערך הפוך לנוירוטיות. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">לוודא.   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">לשפר. </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">ממוצע מרחק אוקלידי. </t>
   </si>
   <si>
@@ -3403,10 +3377,6 @@
 50%- התאמה לפי ציון פרופיל עם התאמה של בהתאם לגבר-אישה. אחרת נשדך גברים שבממוצע יותר רגשיים לנשים שפחות.  תיקון ל4 נקודות לטובת האישה.</t>
   </si>
   <si>
-    <t xml:space="preserve">פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
-להוסיף אולי מידת הסתייגות.. ובכללי לקרוא על הנושא כדי לפתח את זה נכון יותר. </t>
-  </si>
-  <si>
     <t>קטגוריה</t>
   </si>
   <si>
@@ -3757,6 +3727,55 @@
     <t>פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
 פרופיל סופר קריטי. להוציא מפה כל מה שקשור לעמדות. להכניס סגנונות אפשריים - צריך לבנות את זה חכם. אולי בתגיות חופשיות (או לא חופשיות). לחשוב על זה. לצורך הבדיקה של זה אצטרך משתמשים מסגנונות שונים באמת, כרגע האוכלוסייה במערכת שלי די הומוגנית.  צריך אולי גם להיות גורם מפלטר לסגנונות לא קשורים.
 סגנונות אפשריים (לחשוב איך לעשות את זה פוליטיקלי קורקט): ערסים, נורמטיבי, עממי, סחי, קיבוצניק/מושבניק, היפי, סובייטי, גיק, תרבות גבוהה, אליטיסטי, קפליניסט. לחשוב מה עוד ואיך לנסח.</t>
+  </si>
+  <si>
+    <t>אימון על זוגות אמיתיים</t>
+  </si>
+  <si>
+    <t>ייעוץ משפטי וconsents על השירות</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">מורכב מממוצע התכונות: אינטלגנציה אינטואיטיבית, מודעות עצמית, אינטלגנציה רגשית וערך הפוך לנוירוטיות. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">לוודא.   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">לשפר.  לא בטוחה שנוירוטיות קשור כאן. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">פרומפט נפרד לכל התכונות הקשורות.   לשפר בהתאם לצורך.
+להוסיף אולי מידת הסתייגות.. ובכללי לקרוא על הנושא כדי לפתח את זה נכון יותר.   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>לעדכן למה שעשיתי</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4628,7 +4647,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="A17" s="14" t="s">
         <v>406</v>
       </c>
       <c r="B17" t="s">
@@ -4671,12 +4690,12 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="A22" s="14" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="A23" s="14" t="s">
         <v>465</v>
       </c>
       <c r="D23" t="s">
@@ -4692,18 +4711,28 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" t="s">
+      <c r="A25" s="14" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" t="s">
+      <c r="A26" s="14" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" t="s">
+      <c r="A27" s="14" t="s">
         <v>689</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="14" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="14" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -7274,7 +7303,7 @@
   <sheetData>
     <row r="2" spans="2:20">
       <c r="B2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R2" t="s">
         <v>829</v>
@@ -7295,7 +7324,7 @@
     </row>
     <row r="5" spans="2:20">
       <c r="B5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R5" t="s">
         <v>836</v>
@@ -7585,13 +7614,13 @@
         <v>415</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="86.4">
@@ -7599,13 +7628,13 @@
         <v>876</v>
       </c>
       <c r="B3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>883</v>
+        <v>1024</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G3" s="14"/>
     </row>
@@ -7614,13 +7643,13 @@
         <v>426</v>
       </c>
       <c r="B4" t="s">
+        <v>889</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>891</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8">
@@ -7628,13 +7657,13 @@
         <v>693</v>
       </c>
       <c r="B5" t="s">
+        <v>884</v>
+      </c>
+      <c r="C5" t="s">
         <v>885</v>
       </c>
-      <c r="C5" t="s">
-        <v>886</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8">
@@ -7642,13 +7671,13 @@
         <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2">
@@ -7656,13 +7685,13 @@
         <v>877</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>913</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="115.2">
@@ -7670,13 +7699,13 @@
         <v>878</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>895</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="144">
@@ -7684,13 +7713,13 @@
         <v>867</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>908</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="115.2">
@@ -7698,13 +7727,13 @@
         <v>874</v>
       </c>
       <c r="B10" t="s">
+        <v>898</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>899</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7712,10 +7741,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7723,7 +7752,7 @@
         <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>260</v>
@@ -7734,13 +7763,13 @@
         <v>879</v>
       </c>
       <c r="B13" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="158.4">
@@ -7748,36 +7777,36 @@
         <v>438</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="201.6">
       <c r="A18" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="28.8">
       <c r="B19" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7785,7 +7814,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="14" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7800,17 +7829,17 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="14" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -7831,10 +7860,10 @@
   <sheetData>
     <row r="1" spans="2:16">
       <c r="B1" s="62" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D1" s="62" t="s">
         <v>151</v>
@@ -7843,211 +7872,211 @@
         <v>213</v>
       </c>
       <c r="G1" s="62" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="2" spans="2:16" ht="28.8">
       <c r="B2" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>915</v>
+      </c>
+      <c r="D2" s="63" t="s">
         <v>916</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>917</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>918</v>
       </c>
       <c r="E2" s="63">
         <v>4</v>
       </c>
       <c r="G2" s="65" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="28.8">
       <c r="B3" s="63" t="s">
+        <v>917</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>918</v>
+      </c>
+      <c r="D3" s="63" t="s">
         <v>919</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="E3" s="63" t="s">
         <v>920</v>
       </c>
-      <c r="D3" s="63" t="s">
-        <v>921</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>922</v>
-      </c>
       <c r="G3" s="63" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="28.8">
       <c r="B4" s="63" t="s">
+        <v>921</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>922</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>923</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="E4" s="63" t="s">
         <v>924</v>
       </c>
-      <c r="D4" s="63" t="s">
-        <v>925</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>926</v>
-      </c>
       <c r="G4" s="63" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="28.8">
       <c r="B5" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="D5" s="63" t="s">
         <v>927</v>
       </c>
-      <c r="C5" s="63" t="s">
-        <v>928</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>929</v>
-      </c>
       <c r="E5" s="63" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="57.6">
       <c r="B6" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>929</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>930</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="E6" s="63" t="s">
         <v>931</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>932</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>933</v>
-      </c>
       <c r="G6" s="63" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="28.8">
       <c r="B7" s="63" t="s">
+        <v>932</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>933</v>
+      </c>
+      <c r="D7" s="63" t="s">
         <v>934</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="E7" s="63" t="s">
         <v>935</v>
       </c>
-      <c r="D7" s="63" t="s">
-        <v>936</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>937</v>
-      </c>
       <c r="G7" s="63" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="43.2">
       <c r="B8" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>937</v>
+      </c>
+      <c r="D8" s="63" t="s">
         <v>938</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="E8" s="63" t="s">
         <v>939</v>
       </c>
-      <c r="D8" s="63" t="s">
-        <v>940</v>
-      </c>
-      <c r="E8" s="63" t="s">
-        <v>941</v>
-      </c>
       <c r="G8" s="63" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="43.2">
       <c r="B9" s="63" t="s">
+        <v>940</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>941</v>
+      </c>
+      <c r="D9" s="63" t="s">
         <v>942</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="E9" s="63" t="s">
         <v>943</v>
       </c>
-      <c r="D9" s="63" t="s">
-        <v>944</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>945</v>
-      </c>
       <c r="G9" s="63" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="43.2">
       <c r="B10" s="63" t="s">
+        <v>944</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>945</v>
+      </c>
+      <c r="D10" s="63" t="s">
         <v>946</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="E10" s="63" t="s">
         <v>947</v>
       </c>
-      <c r="D10" s="63" t="s">
-        <v>948</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>949</v>
-      </c>
       <c r="G10" s="63" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8">
       <c r="B11" s="63" t="s">
+        <v>948</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>949</v>
+      </c>
+      <c r="D11" s="63" t="s">
         <v>950</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>951</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>952</v>
-      </c>
       <c r="E11" s="63" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8">
       <c r="B12" s="63" t="s">
+        <v>951</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>952</v>
+      </c>
+      <c r="D12" s="63" t="s">
         <v>953</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="E12" s="63" t="s">
         <v>954</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>955</v>
-      </c>
-      <c r="E12" s="63" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="F14" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G14" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H14" t="s">
         <v>823</v>
       </c>
       <c r="I14" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="J14" t="s">
         <v>822</v>
       </c>
       <c r="K14" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="L14" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M14" t="s">
         <v>824</v>
@@ -8056,18 +8085,18 @@
         <v>828</v>
       </c>
       <c r="P14" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" s="64" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D15">
         <v>80</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F15" s="14">
         <v>78</v>
@@ -8105,10 +8134,10 @@
     </row>
     <row r="16" spans="2:16">
       <c r="C16" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E16" s="63" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F16">
         <v>92</v>
@@ -8146,13 +8175,13 @@
     </row>
     <row r="17" spans="3:16">
       <c r="C17" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D17">
         <v>84</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F17" s="14">
         <v>84</v>
@@ -8190,10 +8219,10 @@
     </row>
     <row r="18" spans="3:16">
       <c r="C18" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E18" s="63" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F18">
         <v>52</v>
@@ -8231,10 +8260,10 @@
     </row>
     <row r="19" spans="3:16">
       <c r="C19" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="F19">
         <v>88</v>
@@ -8272,13 +8301,13 @@
     </row>
     <row r="20" spans="3:16">
       <c r="C20" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D20">
         <v>72</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F20" s="14">
         <v>58</v>
@@ -8316,7 +8345,7 @@
     </row>
     <row r="21" spans="3:16">
       <c r="E21" s="63" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F21">
         <v>64</v>
@@ -8354,7 +8383,7 @@
     </row>
     <row r="22" spans="3:16">
       <c r="E22" s="63" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="F22">
         <v>38</v>
@@ -8386,79 +8415,79 @@
     </row>
     <row r="24" spans="3:16">
       <c r="E24" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F24" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="3:16">
       <c r="E25" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="N25" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="O25" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="26" spans="3:16">
       <c r="E26" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="N26" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="27" spans="3:16">
       <c r="E27" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F27" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="N27" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="28" spans="3:16">
       <c r="E28" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="N28" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="29" spans="3:16">
       <c r="E29" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="N29" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="30" spans="3:16">
       <c r="E30" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="N30" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -9264,7 +9293,7 @@
         <v>766</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>765</v>
@@ -9283,10 +9312,10 @@
         <v>766</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -9302,10 +9331,10 @@
         <v>766</v>
       </c>
       <c r="C17" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -9321,10 +9350,10 @@
         <v>766</v>
       </c>
       <c r="C18" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -9359,7 +9388,7 @@
         <v>766</v>
       </c>
       <c r="C20" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>

--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -8,32 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\MatchMe\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91FBD22-86B4-4C77-965C-E82FF7E1BC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C56084-E553-4CC3-A2F7-05F2B3563458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tasks Guidline" sheetId="12" r:id="rId1"/>
-    <sheet name="Current Tasks" sheetId="16" r:id="rId2"/>
-    <sheet name="Analyzer Tasks" sheetId="17" r:id="rId3"/>
-    <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId4"/>
-    <sheet name="external traits analyze" sheetId="19" r:id="rId5"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId6"/>
-    <sheet name="Internal Traits" sheetId="1" r:id="rId7"/>
-    <sheet name="internal traits - Old" sheetId="14" r:id="rId8"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId9"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId10"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId11"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId12"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId13"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId14"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId15"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId16"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId17"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId18"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId19"/>
+    <sheet name="MVP Guidline" sheetId="20" r:id="rId1"/>
+    <sheet name="Tasks Guidline" sheetId="12" r:id="rId2"/>
+    <sheet name="Current Tasks" sheetId="16" r:id="rId3"/>
+    <sheet name="Analyzer Tasks" sheetId="17" r:id="rId4"/>
+    <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId5"/>
+    <sheet name="external traits analyze" sheetId="19" r:id="rId6"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId7"/>
+    <sheet name="Internal Traits" sheetId="1" r:id="rId8"/>
+    <sheet name="internal traits - Old" sheetId="14" r:id="rId9"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId10"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId11"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId12"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId13"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId14"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId15"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId16"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId17"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId18"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId19"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1065">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3776,6 +3778,136 @@
       </rPr>
       <t>לעדכן למה שעשיתי</t>
     </r>
+  </si>
+  <si>
+    <t>כניסה עם אוטנטיקציה</t>
+  </si>
+  <si>
+    <t>צעדים לMVP</t>
+  </si>
+  <si>
+    <t>לעשות יוזר אוטנטיקיישן</t>
+  </si>
+  <si>
+    <t>לאפשר לעצמי לשנות נתוני משתמשים - גם תכונות וגם ציוני התאמה</t>
+  </si>
+  <si>
+    <t>להכניס קונסנט וייעוץ בסיסי עם הילה</t>
+  </si>
+  <si>
+    <t>לאפשר לעצמי לאשר התאמות (ברמת הפוטנציאל הראשוני)</t>
+  </si>
+  <si>
+    <t>לסיים את חווית ההתאמה - שליחת של נוטיפיקציה, אפשרות לדירוג, כרטיס התאמה.</t>
+  </si>
+  <si>
+    <t>לסדר את הצ'אט כך שידע לדבר על ההתאמה ועל מה שקורה אחרי</t>
+  </si>
+  <si>
+    <t>בקאפס והפרדת טסט פרוד</t>
+  </si>
+  <si>
+    <t>דרך הריילווי</t>
+  </si>
+  <si>
+    <t>אוטומציה של הוספה כאפליקציה</t>
+  </si>
+  <si>
+    <t>לעשות UI מוצלח</t>
+  </si>
+  <si>
+    <t>אבטחת מידע - סגירת פינות</t>
+  </si>
+  <si>
+    <t>אפשרות לשיחה אחרי קבלת כרטיס ההתאמה</t>
+  </si>
+  <si>
+    <t>דרך ווטסאפ/הודעות/גם וגם</t>
+  </si>
+  <si>
+    <t>לחשוב על עניין העלויות - אולי לחסום צ'אט בשלב מסוים</t>
+  </si>
+  <si>
+    <t>לחשוב מה אני עושה עם זה שלא יחרוג מדי כל עוד אני לא גובה תשלום</t>
+  </si>
+  <si>
+    <t>האם להישאר עם GPT4o?</t>
+  </si>
+  <si>
+    <t>אולי כדאי לשקול מעבר לג'מיני/גרוק כדי לא להסתבך עם החסימות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בדיקות </t>
+  </si>
+  <si>
+    <t>צעדי הפצה</t>
+  </si>
+  <si>
+    <t>להתחיל פשוט - 10 משתמשים שאני מכירה שיכולים להגיד לי אם הכול תקין</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ואז - להפיץ אצל חברים וכו'.  </t>
+  </si>
+  <si>
+    <t>אחרי ותוך כדי הMVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשפר את חווית הצ'אט קודם כל </t>
+  </si>
+  <si>
+    <t>לשפר את הניתוח והאלגוריתם שיהיה אוטומטי</t>
+  </si>
+  <si>
+    <t>העלאת תמונות מסודרת כולל קונסנט על ניתוח התמונה</t>
+  </si>
+  <si>
+    <t>עם הסבר שהם לא חייבים אבל..</t>
+  </si>
+  <si>
+    <t>במסך הcandidate matches אני אוכל לשחק עם ציוני ההתאמות. וגם כפתור שבלחיצה יוצר כרטיס התאמה ומחזיר ציון התאמה מהAI שמשתלב בציון הכולל. במסך של הmatched - יהיה לי כפתור שליחה ש: 1. יציג את ההתאמה עם כרטיס ההתאמה במסך של שני המשתמשים. 2. ישלח להם ווטסאפ שאומר שיש להם התאמה.  3. בכרטיס ההתאמה יהיה כפתור "החל בשיחה" שיאפשר שליחת הודעה.  אולי עם אופציה של עבור לשיחה בווטסאפ. (צריך לוודא שיש אישור לזה. אולי אם המשתמש יבקש שיחה בווטסאפ זה בעצם ישלח מהמערכת הודעה לצד השני אם הוא רוצה להתחיל בשיחה ומשם השיחה האמיתית תתחיל)</t>
+  </si>
+  <si>
+    <t>הגבלת קצב בקשות (Rate Limiting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מסך אדמין - שיהיה פתוח רק למשתמשים שמוגדרים כאדמין. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">או רק לי. אולי לעשות מסך מסודר להרשאות. ושיעבוד שונה בלוקל ובפרוד. אפשר אולי שבכלל לא יעבוד בפרוד.  בלוקאל זה יכול להישאר עם הלינק בלבד. </t>
+  </si>
+  <si>
+    <t>חסימת "זליגת מידע" דרך ה-ID (הגנת ID enumeration).  לבדוק מה עוד צריך ואפשרי כבר עכשיו</t>
+  </si>
+  <si>
+    <t>לוודא שרואים את התפריט, שקל לנווט, לעשות לוג אאוט וכו'. לבדוק באייפון ובאנדרואיד.  אולי לעשות גם לוגו טוב</t>
+  </si>
+  <si>
+    <t>כרגע להכניס קונסנט והסבר במסך הראשי של ההסבר + כשמעלים תמונות.</t>
+  </si>
+  <si>
+    <t>תוך כדי הכול</t>
+  </si>
+  <si>
+    <t>לשלוח לזוגות בסיסיים - עדן וגל, הינדי ואלי, אלכס, דני. אולי גם ללחוץ קצת על הבנות דודות. ולשלוח לזוגות אחרים לצורך הבדיקות</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">בביצוע. להשלים את המשימות שלי. לבדוק אחר כך גם מה קורה עם משתמשים שלא רוצים להתחבר דרך גוגל/אפל ומה קורה עם משתמשים שכבר רשומים (בשתי הוריאציות). לבדוק גם באפל וגם בגלקסי.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">לפני שאני חוזרת לזה - להעתיק לקלוד את הפלט של מה שעשינו. </t>
+    </r>
+  </si>
+  <si>
+    <t>בוצע - לא עובד באנדרואיד</t>
   </si>
 </sst>
 </file>
@@ -3996,7 +4128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4171,6 +4303,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4450,299 +4583,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
-  <dimension ref="A1:D32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF54B88-E3B9-441A-8257-9C1C5A3ED25F}">
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="50.44140625" customWidth="1"/>
+    <col min="1" max="1" width="55.109375" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="35" t="s">
-        <v>389</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>390</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    <row r="1" spans="1:2">
+      <c r="A1" s="14" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="43.2">
       <c r="A2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1028</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>1036</v>
       </c>
       <c r="B3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C3" t="s">
-        <v>402</v>
-      </c>
-      <c r="D3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>1034</v>
       </c>
       <c r="B4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C4" t="s">
-        <v>405</v>
-      </c>
-      <c r="D4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>468</v>
+        <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>469</v>
-      </c>
-      <c r="C5" t="s">
-        <v>402</v>
-      </c>
-      <c r="D5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8">
       <c r="A6" t="s">
-        <v>399</v>
-      </c>
-      <c r="C6" t="s">
-        <v>396</v>
-      </c>
-      <c r="D6" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1056</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>400</v>
+        <v>1038</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
-      </c>
-      <c r="C7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>400</v>
-      </c>
-      <c r="B8" t="s">
-        <v>403</v>
-      </c>
-      <c r="C8" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B9" t="s">
-        <v>404</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4">
+        <v>1037</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>1052</v>
       </c>
       <c r="B11" t="s">
-        <v>407</v>
-      </c>
-      <c r="C11" t="s">
-        <v>402</v>
-      </c>
-      <c r="D11" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>412</v>
-      </c>
-      <c r="B12" t="s">
-        <v>614</v>
-      </c>
-      <c r="C12" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="100.8">
+      <c r="A12" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>615</v>
+        <v>1039</v>
       </c>
       <c r="B13" t="s">
-        <v>616</v>
-      </c>
-      <c r="C13" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>406</v>
-      </c>
-      <c r="B15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C15" t="s">
-        <v>402</v>
-      </c>
-      <c r="D15" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>406</v>
+        <v>1041</v>
       </c>
       <c r="B16" t="s">
-        <v>456</v>
-      </c>
-      <c r="C16" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="14" t="s">
-        <v>406</v>
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>1043</v>
       </c>
       <c r="B17" t="s">
-        <v>463</v>
-      </c>
-      <c r="D17" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>617</v>
-      </c>
-      <c r="B18" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>406</v>
-      </c>
-      <c r="B19" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>406</v>
-      </c>
-      <c r="B20" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>461</v>
-      </c>
-      <c r="B21" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="14" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="D23" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>466</v>
-      </c>
-      <c r="D24" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="14" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="14" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="14" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="14" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="14" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="14" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>620</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -4751,6 +4763,286 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" customWidth="1"/>
+    <col min="12" max="12" width="42.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="41.4">
+      <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F4">
+        <v>80</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>351</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="28.8">
+      <c r="A5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" t="s">
+        <v>290</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9">
+        <v>0.3</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10">
+        <v>0.4</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8">
+      <c r="A11" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="F11">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="L11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5047,7 +5339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5397,7 +5689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6012,7 +6304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6297,7 +6589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6519,7 +6811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6681,7 +6973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6831,7 +7123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6876,7 +7168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6955,7 +7247,313 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="50.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="35" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" t="s">
+        <v>396</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>406</v>
+      </c>
+      <c r="B11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" t="s">
+        <v>402</v>
+      </c>
+      <c r="D11" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" t="s">
+        <v>614</v>
+      </c>
+      <c r="C12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>615</v>
+      </c>
+      <c r="B13" t="s">
+        <v>616</v>
+      </c>
+      <c r="C13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" t="s">
+        <v>402</v>
+      </c>
+      <c r="D15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>406</v>
+      </c>
+      <c r="B16" t="s">
+        <v>456</v>
+      </c>
+      <c r="C16" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="B17" t="s">
+        <v>463</v>
+      </c>
+      <c r="D17" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>617</v>
+      </c>
+      <c r="B18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>406</v>
+      </c>
+      <c r="B19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>406</v>
+      </c>
+      <c r="B20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="14" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>466</v>
+      </c>
+      <c r="D24" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="14" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="14" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="66" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="14" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="14" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>620</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7110,7 +7708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C1EE30-A7E2-4C7A-8C61-FDFDE8F0687C}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7291,7 +7889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50151C83-D621-46FF-871C-82BDAD5480FD}">
   <dimension ref="B2:T31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7584,7 +8182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890832A-DBF2-45FA-8E41-3FB9FF4AFB94}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7847,7 +8445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DB26E2-2FEB-428C-8A2B-44341C3C4297}">
   <dimension ref="B1:P37"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -8500,7 +9098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9021,7 +9619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10327,7 +10925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -12419,284 +13017,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" customWidth="1"/>
-    <col min="12" max="12" width="42.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="41.4">
-      <c r="A2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3">
-        <v>90</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" t="s">
-        <v>423</v>
-      </c>
-      <c r="F4">
-        <v>80</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>351</v>
-      </c>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="28.8">
-      <c r="A5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5">
-        <v>0.5</v>
-      </c>
-      <c r="F5">
-        <v>90</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" t="s">
-        <v>290</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" t="s">
-        <v>298</v>
-      </c>
-      <c r="C8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9">
-        <v>0.3</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10">
-        <v>0.4</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" t="s">
-        <v>424</v>
-      </c>
-      <c r="E11">
-        <v>0.5</v>
-      </c>
-      <c r="F11">
-        <v>80</v>
-      </c>
-      <c r="G11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="L11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Docs/MatchMe DB.xlsx
+++ b/Docs/MatchMe DB.xlsx
@@ -1,40 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPFX\One\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E17732C-912D-44AC-A269-4E23B2A30ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860AB0F3-CCC8-4281-BC0C-66A81B0CD9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UX MVP Tasks" sheetId="22" r:id="rId1"/>
     <sheet name="MVP Guidline" sheetId="20" r:id="rId2"/>
-    <sheet name="Important details" sheetId="21" r:id="rId3"/>
-    <sheet name="Tasks Guidline" sheetId="12" r:id="rId4"/>
-    <sheet name="Current Tasks" sheetId="16" r:id="rId5"/>
-    <sheet name="Analyzer Tasks" sheetId="17" r:id="rId6"/>
-    <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId7"/>
-    <sheet name="external traits analyze" sheetId="19" r:id="rId8"/>
-    <sheet name="פרטי משתמש" sheetId="3" r:id="rId9"/>
-    <sheet name="Internal Traits" sheetId="1" r:id="rId10"/>
-    <sheet name="internal traits - Old" sheetId="14" r:id="rId11"/>
-    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId12"/>
-    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId13"/>
-    <sheet name="בניית ציונים" sheetId="9" r:id="rId14"/>
-    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId15"/>
-    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId16"/>
-    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId17"/>
-    <sheet name="טופס הזנה" sheetId="8" r:id="rId18"/>
-    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId19"/>
-    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId20"/>
-    <sheet name="בדיקות" sheetId="13" r:id="rId21"/>
-    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId22"/>
+    <sheet name="MVP Tasks" sheetId="23" r:id="rId3"/>
+    <sheet name="Users" sheetId="24" r:id="rId4"/>
+    <sheet name="Important details" sheetId="21" r:id="rId5"/>
+    <sheet name="Tasks Guidline" sheetId="12" r:id="rId6"/>
+    <sheet name="Current Tasks" sheetId="16" r:id="rId7"/>
+    <sheet name="Analyzer Tasks" sheetId="17" r:id="rId8"/>
+    <sheet name="פירוט מודל מנתח" sheetId="18" r:id="rId9"/>
+    <sheet name="external traits analyze" sheetId="19" r:id="rId10"/>
+    <sheet name="פרטי משתמש" sheetId="3" r:id="rId11"/>
+    <sheet name="Internal Traits" sheetId="1" r:id="rId12"/>
+    <sheet name="internal traits - Old" sheetId="14" r:id="rId13"/>
+    <sheet name="מאפיינים חיצוניים - כללי" sheetId="5" r:id="rId14"/>
+    <sheet name="משתמש - מאפיינים" sheetId="2" r:id="rId15"/>
+    <sheet name="בניית ציונים" sheetId="9" r:id="rId16"/>
+    <sheet name="אלגוריתם ציון פנימי" sheetId="4" r:id="rId17"/>
+    <sheet name="אלגוריתם ציון חיצוני" sheetId="6" r:id="rId18"/>
+    <sheet name="אלגוריתם שידוכים" sheetId="7" r:id="rId19"/>
+    <sheet name="טופס הזנה" sheetId="8" r:id="rId20"/>
+    <sheet name="טבלאות דאטה" sheetId="11" r:id="rId21"/>
+    <sheet name="שאלות עבור הAI" sheetId="10" r:id="rId22"/>
+    <sheet name="בדיקות" sheetId="13" r:id="rId23"/>
+    <sheet name="שאלות לפי מלווה" sheetId="15" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MVP Guidline'!$A$1:$C$42</definedName>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="1305">
   <si>
     <t>סוג חישוב</t>
   </si>
@@ -3969,12 +3971,6 @@
   </si>
   <si>
     <t xml:space="preserve">מה לגבי גיבויים?  </t>
-  </si>
-  <si>
-    <t>אני יכולה עקרונית לעשות דרך הrailway, אבל להבין איך זה עובד. וגם אולי איכשהו לשמור ידנית.</t>
-  </si>
-  <si>
-    <t>אולי גם להכניס JSON שלם ואז אוכל לתת לGPT לעשות את הניתוח</t>
   </si>
   <si>
     <t>לוודא גם שהניתוח מתבצע באמת רק פעם אחת ואחר כך זה בשליטתי בלבד. לוודא שמשתמשים נכנסים למאגר רק אחרי שאני מריצה בעצמי ניתוח ידני. לוודא גם שאין מצב שהניתוח ירוץ בלופ או משהו כזה</t>
@@ -4264,9 +4260,6 @@
     </r>
   </si>
   <si>
-    <t>לוודא שהעלאת התמונות עובדת</t>
-  </si>
-  <si>
     <t>להוסיף בצ'אט של טעם אישי: האם יש דברים שהם דיל ברייקרס מבחינתך או משפיעים משמעותית על המשיכה או החיבור? למשל - מישהו שמעשן / לא אוהב בעלי חיים / צמחונות וכדומה.. ?  
 ואז שאלה יותר רגישה של גרוש/ילדים?</t>
   </si>
@@ -4300,16 +4293,427 @@
 MBTI - הוא גם לא מנתח כל כך טוב. צריך לראות מה עושים עם המוחצנות מופנמות ומה לגבי הj הזה</t>
   </si>
   <si>
-    <t>שלב 1: להכניס תיאור של המשתמש ידני שהAI יוכל להשתמש בו וגם יופיע בתובנות. עד אז אפשר להשתמש בסיכום המשתמש הקיים. 
+    <t xml:space="preserve">דברים שעלו:  בועות שמופיעות באמצע שיחה. </t>
+  </si>
+  <si>
+    <t>לפחות של שלב 1</t>
+  </si>
+  <si>
+    <t>שלב 1: להכניס תיאור של המשתמש ידני שהAI יוכל להשתמש בו וגם יופיע בתובנות. עד אז אפשר להשתמש בסיכום המשתמש הקיים.  +  להציג הודעה שהניתוח עוד לא הושלם, ויכול להיות שהתובנות עוד לא מדויק ונעדכן כשיושלם הניתוח.   - בוצע
 שלב 2: להכניס שאלות חידוד לכל אחד מהתובנות.
 שלב 3: להביא לסגירת השיחה - אם סתם מדובר במה למדת עליי כללי- לענות, לשאול אולי שאלה שתיים מנחות ואז לסגור.  אם מדובר בחידוד תובנות - לשאול קודם כל מה הוא חושב שלא מדויק ומה דעתו על זה, להציע לעשות שאלות חידוד, לשאול אותן ואז לכתוב שננתח מחדש ולסגור את השיחה.</t>
+  </si>
+  <si>
+    <t>בוצע, לשיפור</t>
+  </si>
+  <si>
+    <t>נשאר: בדיקה כללית, לשלוח גם לעתל, אולי מיכל ואולי לליעד (???), אולי לעידו, אולי להתחיל לכתוב בכל מיני קבוצות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אולי גם להכניס JSON שלם ואז אוכל לתת לGPT לעשות את הניתוח.   
+להוסיף גם הוספת חוות דעת AI על ההתאמה שאכניס כרגע ידנית ותשפיע על הציון. </t>
+  </si>
+  <si>
+    <t>לעשות עם ג'מיני ראיון לעצמי שבו ישאל אותי שאלות על המבנה של הפרויקט שלי לוודא שאני יודעת הכול</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עטיפה עם קפסיטור - להמשיך בנפרד. </t>
+  </si>
+  <si>
+    <t>פעולות קבועות</t>
+  </si>
+  <si>
+    <t>לבדוק בresend אם יש משתמשים שניסו מג'יק לינק ולא הצליחו</t>
+  </si>
+  <si>
+    <t>לבדוק תקלות בשיחות של המשתמשים ולתקן תוך כדי</t>
+  </si>
+  <si>
+    <t>לשלוח מיילים של המשך שיחה, תובנות שהסתיימו וכו' (להגיד לכולם שזה MVP ושאנחנו אוספים משתמשים)</t>
+  </si>
+  <si>
+    <t>להכניס תובנות אישיות ולהריץ ניתוח סופי בסיום</t>
+  </si>
+  <si>
+    <t>להכניס ניתוח חיצוני למי שיש תמונות</t>
+  </si>
+  <si>
+    <t>פעולות לעכשיו</t>
+  </si>
+  <si>
+    <t>משתמש</t>
+  </si>
+  <si>
+    <t>אביב וואל</t>
+  </si>
+  <si>
+    <t>ניתוח הושלם</t>
+  </si>
+  <si>
+    <t>נתנאלה</t>
+  </si>
+  <si>
+    <t>פעולה לביצוע</t>
+  </si>
+  <si>
+    <t>קובי</t>
+  </si>
+  <si>
+    <t>סיים שיחה אבל לא נתן שום דאטה אמיתי</t>
+  </si>
+  <si>
+    <t>לידר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קיבלה מג'יק לינק ולא התחברה, כנראה היה באג. שלחתי לה מייל בנושא. </t>
+  </si>
+  <si>
+    <t>לעשות סדר בין המשתמשים בפרוד לטסט</t>
+  </si>
+  <si>
+    <t>פחות קריטי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשלוח לשני ניתוח וצילומי מסך מהמערכת  - אני צריכה לשתול שיחה של משתמש ולהציג אותו. </t>
+  </si>
+  <si>
+    <t>לעבור על השיחה של קובי ולתקן בעיות:
+* סיום השיחה בקוגנטיבי
+* להסביר שהניתוח טעם הוא לא אמיתי ואין פרופילים, רק בחינה של מה מתאים.
+* שלא יריץ ניתוח פעמיים אוטומטית</t>
+  </si>
+  <si>
+    <t>סדר עבודה</t>
+  </si>
+  <si>
+    <t>לתת להגר פוסט טוב לשתף</t>
+  </si>
+  <si>
+    <t>ממתין לשני</t>
+  </si>
+  <si>
+    <t>לראות מה עושים עם מצב שהמשתמש שולח הודעה ואז ממשיך לגבי ההודעה הקודמת אחרי שכבר יש שאלה.  (שיחה של נתנאלה לדוגמה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לסדר את התובנות </t>
+  </si>
+  <si>
+    <t>להפריד בין אקסל ניהול לאקסל אפיון</t>
+  </si>
+  <si>
+    <t>לעשות תכנית הפצה מסודרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשלוח מייל מהמערכת למשתמשים קיימים - נטי איציק שחר נדב - שישלימו את הפרופיל וכו'. </t>
+  </si>
+  <si>
+    <t>להוסיף זיקה לדת בפרטים האישיים
+להחליף את כל הקרם ללבן ולעדכן תמונה בכניסה</t>
+  </si>
+  <si>
+    <t>אנדרואיד דארק מוד - עדיין אין עיגולים וגם התובנות לא שקוף.  (צריך לעשות בהמשך אייקונים נפרדים לדארק מוד ולוגיקה שלמה לסיפור הזה...)
+רצוי גם להכניס את הלוגו האמיתי</t>
+  </si>
+  <si>
+    <t>לכתוב בקבוצות קונפשנס של האינסטגרם</t>
+  </si>
+  <si>
+    <t>שאר ענייני הMVP</t>
+  </si>
+  <si>
+    <t>הברירת מחדל של הנתונים הנוספים צריכה להיות לא ידוע - כרגע נגיד לא מעשן זו ברירת מחדל</t>
+  </si>
+  <si>
+    <t>אחר כך - ליצור מאגר מאמרים שיתויג לכל טיפוס וכו' ויוצג למשתמשים - כל פעם משהו אחר יתווסף להם לפרופיל.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פוסטים על זוגות בחתונמי </t>
+  </si>
+  <si>
+    <t>פוסט מה למדנו מדאטה של זוגות אמיתיים</t>
+  </si>
+  <si>
+    <t>להתקדם עם הקפסיטור</t>
+  </si>
+  <si>
+    <t>לעבור על השיחה של נתנאלה ושל אביב ולתקן בעיות + של המשתמשות החדשות</t>
+  </si>
+  <si>
+    <t>לסדר קצת עיצוב ותקלות שהיו (לעבור על השיחות)</t>
+  </si>
+  <si>
+    <t>לשלוח מיילים של ברוכות הבאות למשתמשות החדשות + לבדוק את המצב הresend</t>
+  </si>
+  <si>
+    <t>אחר כך - לערוך תובנות</t>
+  </si>
+  <si>
+    <t>לשלוח מיילים למשתמשים ישנים</t>
+  </si>
+  <si>
+    <t>רוני ליאור</t>
+  </si>
+  <si>
+    <t>לשלוח עוד מייל?</t>
+  </si>
+  <si>
+    <t>שיר ארז</t>
+  </si>
+  <si>
+    <t>פלג סולרסקי</t>
+  </si>
+  <si>
+    <t>יסמין כהן</t>
+  </si>
+  <si>
+    <t>אורנת</t>
+  </si>
+  <si>
+    <t>לינוי</t>
+  </si>
+  <si>
+    <t>שחר</t>
+  </si>
+  <si>
+    <t>איציק</t>
+  </si>
+  <si>
+    <t>לבדוק פרופיל ואז לשלוח מייל</t>
+  </si>
+  <si>
+    <t>לשים תובנות</t>
+  </si>
+  <si>
+    <t>נטע אזולאי</t>
+  </si>
+  <si>
+    <t>קיבלה קוד במג'יק ולא התחברה  - שלחתי מייל</t>
+  </si>
+  <si>
+    <t>התחברה ולא השלימה כלום - שלחתי מייל</t>
+  </si>
+  <si>
+    <t>לשמור שיחה</t>
+  </si>
+  <si>
+    <t>כמעט סיימה שיחה. נשלח לה מייל שתמשיך בשיחה כדי להיכנס למאגר ואחרי 4 ימים מייל על ניתוח ראשוני</t>
+  </si>
+  <si>
+    <t>עוד לא.. שבוע אחרי המייל האחרון - 21.6</t>
+  </si>
+  <si>
+    <t>אינטראקציה אחרונה</t>
+  </si>
+  <si>
+    <t>חלי</t>
+  </si>
+  <si>
+    <t>יאנה</t>
+  </si>
+  <si>
+    <t>אלמוג</t>
+  </si>
+  <si>
+    <t>סיוון</t>
+  </si>
+  <si>
+    <t>מורן</t>
+  </si>
+  <si>
+    <t>טל</t>
+  </si>
+  <si>
+    <t>ליה</t>
+  </si>
+  <si>
+    <t>דנה</t>
+  </si>
+  <si>
+    <t>אופיר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומר </t>
+  </si>
+  <si>
+    <t>עשתה רק שיחה כללית בלי סגנון קוגנטיבי וטעם אישי.  - שלחתי מייל בנושא ושמתי לה תובנות ראשונות</t>
+  </si>
+  <si>
+    <t>עשתה את ניתוח הטעם והסגנון אבל לא את הצ'אט הכללי. שמתי לה תובנות ביניים ושלחתי מייל</t>
+  </si>
+  <si>
+    <t>באגים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לא מוצגת לה בועה להמשיך.. </t>
+  </si>
+  <si>
+    <t>לא סיימה את השיחה למרות ששיטפה הרבה ולא המשיכה לאחרים.  שמתי תובנות ושלחתי מייל</t>
+  </si>
+  <si>
+    <t>לראות את מי אפשר להכניס למאגר</t>
+  </si>
+  <si>
+    <t>השלימה הכול , הזנתי תובנות ושלחתי מייל.</t>
+  </si>
+  <si>
+    <t>ניתוח חיצוני  + לשלוח מאמר  + להכניס למאגר</t>
+  </si>
+  <si>
+    <t>הילה הילל</t>
+  </si>
+  <si>
+    <t>השלים שיחה עם הצ'אט, התחיל ניתוח טעם אבל הפסיק ישר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשלוח מייל ברוך הבא עם הזמנה להמשיך. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">סיים שיחה אבל ענה במילה אחת </t>
+  </si>
+  <si>
+    <t>סתיו שמחה</t>
+  </si>
+  <si>
+    <t>התחברה והתחילה קצת את סגנון החשיבה והטעם</t>
+  </si>
+  <si>
+    <t>לבדוק שהמסך מוצג תקין למשתמשים שנכנסו</t>
+  </si>
+  <si>
+    <t>השלימה שיחה רגילה ורק התחילה קוגנטיבי</t>
+  </si>
+  <si>
+    <t>השלימה הכול חוץ מפרטים.  הזנתי תובנות ושלחתי מייל</t>
+  </si>
+  <si>
+    <t>סיימה הכול. הזנתי תובנות ושלחתי מייל</t>
+  </si>
+  <si>
+    <t>עשה רק את הצ'אט הכללי. הזנתי תובנות ושלחתי מייל</t>
+  </si>
+  <si>
+    <t>אור - orgot</t>
+  </si>
+  <si>
+    <t>בלה</t>
+  </si>
+  <si>
+    <t>dyafit6</t>
+  </si>
+  <si>
+    <t>בר - couple tester</t>
+  </si>
+  <si>
+    <t>ספיר</t>
+  </si>
+  <si>
+    <t>אור - killerorxd</t>
+  </si>
+  <si>
+    <t>ויקטוריה</t>
+  </si>
+  <si>
+    <t>עשה ניתוח טעם וצ'אט כללי. שמתי לו תובנות. אי אפשר לשלוח לו מיילים</t>
+  </si>
+  <si>
+    <t>לחשוב מה עושים עם עניין המיילים.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">התחילה את הצ'אט הכללי ולא סיימה. </t>
+  </si>
+  <si>
+    <t>אי אפשר לשלוח מיילים</t>
+  </si>
+  <si>
+    <t>נרשמ/ה ולא הוזן כלום</t>
+  </si>
+  <si>
+    <t>עשתה את הצ'אט הכללי  - הזנתי תובנות</t>
+  </si>
+  <si>
+    <t>ענת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נשאר לה רק ניתוח טעם. הכנסתי תובנות ושלחתי מייל. מאז סיימה הכול. </t>
+  </si>
+  <si>
+    <t>להזין תובנות מחדש ולהריץ שוב ניתוח. לשלוח מייל שנכנסה למאגר והניתוח שלה הושלם</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לשלוח לה מייל שנכנסה למאגר (לבדוק אם נחוץ, מה היה במייל הקודם?) עם חידוד או הודעה במסך שכדאי להשלים פרטים כדי לדייק את הסינון </t>
+  </si>
+  <si>
+    <t>השלימה די הכול פשוט לא הזינה גובה נגיד - לא קריטי</t>
+  </si>
+  <si>
+    <t>סיימה הכול!</t>
+  </si>
+  <si>
+    <t>לשלוח מייל - לבדוק אם כבר שלחתי  + להזין תובנות וכו'</t>
+  </si>
+  <si>
+    <t>אור הבן</t>
+  </si>
+  <si>
+    <t>תומר</t>
+  </si>
+  <si>
+    <t>שמתי לו הודעה במסך - 23/06 11:38</t>
+  </si>
+  <si>
+    <t>שמתי לה הודעה במסך - 23/06 11:38</t>
+  </si>
+  <si>
+    <t>סיים הכול נראה לי</t>
+  </si>
+  <si>
+    <t>חשבון נוסף בפרטנר עבור הווטסאפ העסקי - 35 שח בחודש</t>
+  </si>
+  <si>
+    <t>קיבלתי חשבונית של 35 דולר מסופאבייס - מזה??</t>
+  </si>
+  <si>
+    <t>רן כהן</t>
+  </si>
+  <si>
+    <t>ניסה להיכנס ולא הצליח</t>
+  </si>
+  <si>
+    <t>ניצן אקרמן</t>
+  </si>
+  <si>
+    <t>nimrod.harani</t>
+  </si>
+  <si>
+    <t>שלחתי מייל</t>
+  </si>
+  <si>
+    <t>סיימה הכול</t>
+  </si>
+  <si>
+    <t>להזין תובנות ולשלוח הודעה</t>
+  </si>
+  <si>
+    <t>להעביר אותה למוכנים למאגר</t>
+  </si>
+  <si>
+    <t>הגיעה לשלב לקראת כניסה למאגר</t>
+  </si>
+  <si>
+    <t>לקראת מאגר</t>
+  </si>
+  <si>
+    <t>יש לי גיבוי דרך הrailway, והסוכן שלי גם שומר את כל השיחות והתמונות כשאני מגדירה לו (בהמשך זה יהיה scedual. - רק לחשוב איפה אני מנהלת את זה)</t>
+  </si>
+  <si>
+    <t>אפל תשלום שנתי של 99 דולר.  בגוגל עשיתי תשלום חד פעמי של 25 נראה לי</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4486,6 +4890,20 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -4534,7 +4952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4711,6 +5129,12 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5008,7 +5432,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>84</v>
@@ -5025,10 +5449,10 @@
     </row>
     <row r="3" spans="1:7" ht="43.2">
       <c r="A3" s="5" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C3" t="s">
         <v>396</v>
@@ -5036,10 +5460,10 @@
     </row>
     <row r="4" spans="1:7" ht="72">
       <c r="A4" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C4" t="s">
         <v>396</v>
@@ -5048,7 +5472,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="s">
         <v>405</v>
@@ -5056,10 +5480,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B6" t="s">
         <v>1125</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1127</v>
       </c>
       <c r="C6" t="s">
         <v>396</v>
@@ -5067,10 +5491,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B7" t="s">
         <v>1143</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1145</v>
       </c>
       <c r="C7" t="s">
         <v>405</v>
@@ -5078,40 +5502,40 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="14" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8">
       <c r="A10" s="5" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B10" t="s">
         <v>396</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8">
       <c r="A11" s="5" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B11" t="s">
         <v>396</v>
       </c>
       <c r="C11" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="13" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>405</v>
       </c>
       <c r="C12" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5119,16 +5543,16 @@
     </row>
     <row r="13" spans="1:7" ht="57.6">
       <c r="A13" s="5" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B13" t="s">
         <v>396</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -5136,38 +5560,38 @@
     </row>
     <row r="14" spans="1:7" ht="86.4">
       <c r="A14" s="5" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B14" t="s">
         <v>396</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C15" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B16" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C16" t="s">
         <v>467</v>
@@ -5175,7 +5599,7 @@
     </row>
     <row r="17" spans="1:3" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B17" t="s">
         <v>396</v>
@@ -5183,7 +5607,7 @@
     </row>
     <row r="18" spans="1:3" ht="28.8">
       <c r="A18" s="13" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B18" t="s">
         <v>405</v>
@@ -5191,53 +5615,53 @@
     </row>
     <row r="19" spans="1:3" ht="28.8">
       <c r="A19" s="13" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B19" t="s">
         <v>405</v>
       </c>
       <c r="C19" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="28.8">
       <c r="A22" s="5" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
   </sheetData>
@@ -5246,6 +5670,1180 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DB26E2-2FEB-428C-8A2B-44341C3C4297}">
+  <dimension ref="B1:P37"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" customWidth="1"/>
+    <col min="5" max="5" width="38.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16">
+      <c r="B1" s="62" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>913</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="62" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="28.8">
+      <c r="B2" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>915</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>916</v>
+      </c>
+      <c r="E2" s="63">
+        <v>4</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="28.8">
+      <c r="B3" s="63" t="s">
+        <v>917</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>918</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>919</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>920</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="28.8">
+      <c r="B4" s="63" t="s">
+        <v>921</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>922</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="28.8">
+      <c r="B5" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>927</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="57.6">
+      <c r="B6" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>929</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>930</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>931</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="28.8">
+      <c r="B7" s="63" t="s">
+        <v>932</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>933</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>934</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>935</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="43.2">
+      <c r="B8" s="63" t="s">
+        <v>936</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>937</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>938</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>939</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="43.2">
+      <c r="B9" s="63" t="s">
+        <v>940</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>941</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>942</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>943</v>
+      </c>
+      <c r="G9" s="63" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="43.2">
+      <c r="B10" s="63" t="s">
+        <v>944</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>945</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>946</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>947</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="28.8">
+      <c r="B11" s="63" t="s">
+        <v>948</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>949</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>950</v>
+      </c>
+      <c r="E11" s="63" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="28.8">
+      <c r="B12" s="63" t="s">
+        <v>951</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>952</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>953</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="F14" t="s">
+        <v>961</v>
+      </c>
+      <c r="G14" t="s">
+        <v>983</v>
+      </c>
+      <c r="H14" t="s">
+        <v>823</v>
+      </c>
+      <c r="I14" t="s">
+        <v>985</v>
+      </c>
+      <c r="J14" t="s">
+        <v>822</v>
+      </c>
+      <c r="K14" t="s">
+        <v>986</v>
+      </c>
+      <c r="L14" t="s">
+        <v>987</v>
+      </c>
+      <c r="M14" t="s">
+        <v>824</v>
+      </c>
+      <c r="N14" t="s">
+        <v>828</v>
+      </c>
+      <c r="P14" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="B15" s="64" t="s">
+        <v>960</v>
+      </c>
+      <c r="D15">
+        <v>80</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>970</v>
+      </c>
+      <c r="F15" s="14">
+        <v>78</v>
+      </c>
+      <c r="G15" s="14">
+        <v>94</v>
+      </c>
+      <c r="H15" s="14">
+        <v>91</v>
+      </c>
+      <c r="I15" s="14">
+        <v>84</v>
+      </c>
+      <c r="J15" s="14">
+        <v>86</v>
+      </c>
+      <c r="K15" s="14">
+        <v>79</v>
+      </c>
+      <c r="L15" s="14">
+        <v>66</v>
+      </c>
+      <c r="M15" s="14">
+        <v>80</v>
+      </c>
+      <c r="N15" s="14">
+        <v>74</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="C16" t="s">
+        <v>955</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>971</v>
+      </c>
+      <c r="F16">
+        <v>92</v>
+      </c>
+      <c r="G16">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>68</v>
+      </c>
+      <c r="I16">
+        <v>90</v>
+      </c>
+      <c r="J16">
+        <v>94</v>
+      </c>
+      <c r="K16">
+        <v>82</v>
+      </c>
+      <c r="L16">
+        <v>74</v>
+      </c>
+      <c r="M16">
+        <v>96</v>
+      </c>
+      <c r="N16">
+        <v>78</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="3:16">
+      <c r="C17" t="s">
+        <v>956</v>
+      </c>
+      <c r="D17">
+        <v>84</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>984</v>
+      </c>
+      <c r="F17" s="14">
+        <v>84</v>
+      </c>
+      <c r="G17" s="14">
+        <v>95</v>
+      </c>
+      <c r="H17" s="14">
+        <v>94</v>
+      </c>
+      <c r="I17" s="14">
+        <v>82</v>
+      </c>
+      <c r="J17" s="14">
+        <v>82</v>
+      </c>
+      <c r="K17" s="14">
+        <v>58</v>
+      </c>
+      <c r="L17" s="14">
+        <v>72</v>
+      </c>
+      <c r="M17" s="14">
+        <v>84</v>
+      </c>
+      <c r="N17" s="14">
+        <v>76</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16">
+      <c r="C18" t="s">
+        <v>957</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>972</v>
+      </c>
+      <c r="F18">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>93</v>
+      </c>
+      <c r="H18">
+        <v>88</v>
+      </c>
+      <c r="I18">
+        <v>68</v>
+      </c>
+      <c r="J18">
+        <v>58</v>
+      </c>
+      <c r="K18">
+        <v>48</v>
+      </c>
+      <c r="L18">
+        <v>42</v>
+      </c>
+      <c r="M18">
+        <v>46</v>
+      </c>
+      <c r="N18">
+        <v>52</v>
+      </c>
+      <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16">
+      <c r="C19" t="s">
+        <v>958</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>973</v>
+      </c>
+      <c r="F19">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>78</v>
+      </c>
+      <c r="H19">
+        <v>74</v>
+      </c>
+      <c r="I19">
+        <v>92</v>
+      </c>
+      <c r="J19">
+        <v>95</v>
+      </c>
+      <c r="K19">
+        <v>93</v>
+      </c>
+      <c r="L19">
+        <v>88</v>
+      </c>
+      <c r="M19">
+        <v>97</v>
+      </c>
+      <c r="N19">
+        <v>88</v>
+      </c>
+      <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16">
+      <c r="C20" t="s">
+        <v>959</v>
+      </c>
+      <c r="D20">
+        <v>72</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>974</v>
+      </c>
+      <c r="F20" s="14">
+        <v>58</v>
+      </c>
+      <c r="G20" s="14">
+        <v>90</v>
+      </c>
+      <c r="H20" s="14">
+        <v>89</v>
+      </c>
+      <c r="I20" s="14">
+        <v>83</v>
+      </c>
+      <c r="J20" s="14">
+        <v>76</v>
+      </c>
+      <c r="K20" s="14">
+        <v>84</v>
+      </c>
+      <c r="L20" s="14">
+        <v>58</v>
+      </c>
+      <c r="M20" s="14">
+        <v>72</v>
+      </c>
+      <c r="N20" s="14">
+        <v>62</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16">
+      <c r="E21" s="63" t="s">
+        <v>975</v>
+      </c>
+      <c r="F21">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>96</v>
+      </c>
+      <c r="H21">
+        <v>90</v>
+      </c>
+      <c r="I21">
+        <v>72</v>
+      </c>
+      <c r="J21">
+        <v>66</v>
+      </c>
+      <c r="K21">
+        <v>74</v>
+      </c>
+      <c r="L21">
+        <v>54</v>
+      </c>
+      <c r="M21">
+        <v>58</v>
+      </c>
+      <c r="N21">
+        <v>68</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16">
+      <c r="E22" s="63" t="s">
+        <v>944</v>
+      </c>
+      <c r="F22">
+        <v>38</v>
+      </c>
+      <c r="G22">
+        <v>42</v>
+      </c>
+      <c r="H22">
+        <v>58</v>
+      </c>
+      <c r="I22">
+        <v>72</v>
+      </c>
+      <c r="J22">
+        <v>48</v>
+      </c>
+      <c r="K22">
+        <v>22</v>
+      </c>
+      <c r="L22">
+        <v>36</v>
+      </c>
+      <c r="M22">
+        <v>42</v>
+      </c>
+      <c r="N22">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16">
+      <c r="E24" t="s">
+        <v>976</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16">
+      <c r="E25" t="s">
+        <v>977</v>
+      </c>
+      <c r="N25" t="s">
+        <v>989</v>
+      </c>
+      <c r="O25" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16">
+      <c r="E26" t="s">
+        <v>978</v>
+      </c>
+      <c r="N26" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16">
+      <c r="E27" t="s">
+        <v>979</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1001</v>
+      </c>
+      <c r="N27" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16">
+      <c r="E28" t="s">
+        <v>980</v>
+      </c>
+      <c r="N28" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16">
+      <c r="E29" t="s">
+        <v>981</v>
+      </c>
+      <c r="N29" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16">
+      <c r="E30" t="s">
+        <v>982</v>
+      </c>
+      <c r="N30" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="39.88671875" customWidth="1"/>
+    <col min="8" max="8" width="28.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" ht="43.2">
+      <c r="A6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" ht="43.2">
+      <c r="A7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="72">
+      <c r="A8" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
+      <c r="A9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100.8">
+      <c r="A10" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="43.2">
+      <c r="A11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" ht="72">
+      <c r="A12" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="31"/>
+      <c r="I12" s="30" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="43.2">
+      <c r="A13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="115.2">
+      <c r="A14" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="28.8">
+      <c r="A15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="30" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" ht="86.4">
+      <c r="A18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="30"/>
+    </row>
+    <row r="19" spans="1:9" ht="57.6">
+      <c r="A19" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I19" s="30"/>
+    </row>
+    <row r="20" spans="1:9" ht="57.6">
+      <c r="A20" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8">
+      <c r="A23" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
+      <c r="A27" s="11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6551,7 +8149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE069491-4F9B-48D9-B01E-4A4E77F5C60E}">
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -8645,7 +10243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6089DD-60E7-435A-A2E0-E6886B132143}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -8925,7 +10523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0B4537-96F8-4545-983B-184D65EBDB8F}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9222,7 +10820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31382F6D-1248-4EE3-8D30-0A86E7B5E4BF}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -9572,7 +11170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D5149E-0B86-4D57-8B9A-686514500CE9}">
   <dimension ref="B1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10187,7 +11785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B487A18-0B10-40C8-BA24-F0DC1678FA48}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10472,7 +12070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032081D0-9A99-4BF0-86DD-30C10F371A76}">
   <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10694,7 +12292,647 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF54B88-E3B9-441A-8257-9C1C5A3ED25F}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="55.109375" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="1">
+      <c r="A2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:5" hidden="1">
+      <c r="A3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:5" ht="100.8" hidden="1">
+      <c r="A4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1">
+      <c r="A5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" hidden="1">
+      <c r="A6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" hidden="1">
+      <c r="A7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1">
+      <c r="A8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1">
+      <c r="A9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" hidden="1">
+      <c r="A10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1">
+      <c r="A11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="43.2" hidden="1">
+      <c r="A12" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1">
+      <c r="A13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.8" hidden="1">
+      <c r="A14" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1">
+      <c r="A15" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>396</v>
+      </c>
+      <c r="D15" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="100.8">
+      <c r="A16" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="43.2">
+      <c r="A19" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>405</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.8" hidden="1">
+      <c r="A20" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.8">
+      <c r="A21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C22" t="s">
+        <v>405</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1">
+      <c r="A23" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28.8">
+      <c r="A24" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C24" t="s">
+        <v>396</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1">
+      <c r="A25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>396</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1">
+      <c r="A26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C26" t="s">
+        <v>396</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28.8" hidden="1">
+      <c r="A27" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C27" t="s">
+        <v>396</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28.8" hidden="1">
+      <c r="A28" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>396</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.8" hidden="1">
+      <c r="A29" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C29" t="s">
+        <v>396</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1">
+      <c r="A30" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>396</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="43.2" hidden="1">
+      <c r="A31" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1">
+      <c r="A32" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>396</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="28.8" hidden="1">
+      <c r="A33" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1">
+      <c r="A34" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C34" t="s">
+        <v>396</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1">
+      <c r="A35" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C35" t="s">
+        <v>396</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="43.2" hidden="1">
+      <c r="A36" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1">
+      <c r="A37" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C37" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C38" t="s">
+        <v>405</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="100.8" hidden="1">
+      <c r="A39" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1"/>
+    <row r="42" spans="1:6" hidden="1">
+      <c r="A42" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="14" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="14" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="14" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C42" xr:uid="{ECF54B88-E3B9-441A-8257-9C1C5A3ED25F}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="לביצוע"/>
+        <filter val="לביצוע לקראת התאמות"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233E8F68-8BA3-48DC-98C9-B07384CDF822}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -10856,7 +13094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E73849-9796-44C6-80F8-1CA54A2F64E9}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11006,616 +13244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF54B88-E3B9-441A-8257-9C1C5A3ED25F}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F57"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="55.109375" customWidth="1"/>
-    <col min="2" max="2" width="76" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="14" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" hidden="1">
-      <c r="A2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="3" spans="1:4" hidden="1">
-      <c r="A3" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D3" s="14"/>
-    </row>
-    <row r="4" spans="1:4" ht="100.8" hidden="1">
-      <c r="A4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1">
-      <c r="A5" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.8" hidden="1">
-      <c r="A6" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" hidden="1">
-      <c r="A7" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1">
-      <c r="A8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C8" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1">
-      <c r="A9" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" hidden="1">
-      <c r="A10" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C10" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1">
-      <c r="A11" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C11" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="43.2" hidden="1">
-      <c r="A12" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C12" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1">
-      <c r="A13" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C13" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.8" hidden="1">
-      <c r="A14" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C14" t="s">
-        <v>396</v>
-      </c>
-      <c r="D14" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1">
-      <c r="A15" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>396</v>
-      </c>
-      <c r="D15" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="100.8">
-      <c r="A16" s="5" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.2">
-      <c r="A19" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C19" t="s">
-        <v>405</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28.8" hidden="1">
-      <c r="A20" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C21" t="s">
-        <v>405</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C22" t="s">
-        <v>405</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1">
-      <c r="A23" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C24" t="s">
-        <v>405</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1">
-      <c r="A25" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C25" t="s">
-        <v>396</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1">
-      <c r="A26" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C26" t="s">
-        <v>396</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.8" hidden="1">
-      <c r="A27" s="5" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C27" t="s">
-        <v>396</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.8" hidden="1">
-      <c r="A28" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C28" t="s">
-        <v>396</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.8" hidden="1">
-      <c r="A29" s="5" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C29" t="s">
-        <v>396</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1">
-      <c r="A30" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C30" t="s">
-        <v>396</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="43.2" hidden="1">
-      <c r="A31" s="14" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C31" t="s">
-        <v>396</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1">
-      <c r="A32" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C32" t="s">
-        <v>396</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="28.8" hidden="1">
-      <c r="A33" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1">
-      <c r="A34" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C34" t="s">
-        <v>396</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E35" s="14"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="43.2">
-      <c r="A37" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C37" t="s">
-        <v>402</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C38" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="14" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C39" t="s">
-        <v>405</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="86.4">
-      <c r="A40" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C40" t="s">
-        <v>405</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="14" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="14" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="14" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C42" xr:uid="{ECF54B88-E3B9-441A-8257-9C1C5A3ED25F}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="בביצוע"/>
-        <filter val="לביצוע"/>
-        <filter val="לביצוע לקראת התאמות"/>
-        <filter val="להחליט לגבי זה"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D465AB7-D7AD-4770-A1DB-A227111CD595}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11660,7 +13289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC47FA1-3DB6-4F73-94E7-2B8A7BD334E9}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11739,7 +13368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7838B-7DDE-48A8-A573-BCAB05D487CE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11895,107 +13524,335 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AAAFE0-452D-4051-B347-ABC11C3B618F}">
-  <dimension ref="B2:M23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C8906E-1C11-4B48-8F0C-8E59E3B1398D}">
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="68.21875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="5"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:13">
-      <c r="B2" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" t="s">
-        <v>1060</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" t="s">
-        <v>1071</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" t="s">
-        <v>1064</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="20.399999999999999">
-      <c r="B12" s="67" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L12" s="66" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="C15" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J15" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" t="s">
-        <v>1081</v>
+    <row r="1" spans="1:16">
+      <c r="A1" s="13" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+    </row>
+    <row r="5" spans="1:16" ht="28.8">
+      <c r="A5" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="H9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="13" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+    </row>
+    <row r="13" spans="1:16" ht="28.8">
+      <c r="A13" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+    </row>
+    <row r="14" spans="1:16" ht="57.6">
+      <c r="A14" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="5" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+    </row>
+    <row r="17" spans="1:16" ht="28.8">
+      <c r="A17" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="5" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="5" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="5" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="28.8">
+      <c r="A22" s="5" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="43.2">
+      <c r="A23" s="5" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="5" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="28.8">
+      <c r="A25" s="5" t="s">
+        <v>1209</v>
       </c>
     </row>
   </sheetData>
@@ -12004,6 +13861,753 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA8527A-E67A-4DAD-9F73-AAB853233C6F}">
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="30.109375" customWidth="1"/>
+    <col min="6" max="6" width="30.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="13" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D2" s="5">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8">
+      <c r="A3" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="5">
+        <v>21.6</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="28.8">
+      <c r="A4" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D4" s="5">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.8">
+      <c r="A5" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D5" s="5">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
+        <v>21.6</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="28.8">
+      <c r="A8" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="28.8">
+      <c r="A9" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.8">
+      <c r="A10" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.8">
+      <c r="A11" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D11" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="J14" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="J15" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="5" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="J16" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D17" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.8">
+      <c r="A18" s="5" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D18" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D19" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8">
+      <c r="A20" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D20" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.8">
+      <c r="A21" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C21" s="69" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D22" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D23" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="43.2">
+      <c r="A24" s="5" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D24" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="5" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D26" s="5">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D27" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D28" s="70">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D29" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D31" s="70">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8">
+      <c r="A32" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="68" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D33" s="70">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.8">
+      <c r="A34" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D36" s="5">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="28.8">
+      <c r="A37" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D37" s="71">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="28.8">
+      <c r="A38" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D41" s="70">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D42" s="70">
+        <v>46201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AAAFE0-452D-4051-B347-ABC11C3B618F}">
+  <dimension ref="B2:M24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="2:13">
+      <c r="B2" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="20.399999999999999">
+      <c r="B12" s="67" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L12" s="66" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="C15" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DFD5D3-52D3-4B85-A770-31E2BD7FCBB7}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -12309,7 +14913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6C1EE30-A7E2-4C7A-8C61-FDFDE8F0687C}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -12490,7 +15094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50151C83-D621-46FF-871C-82BDAD5480FD}">
   <dimension ref="B2:T31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -12783,7 +15387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890832A-DBF2-45FA-8E41-3FB9FF4AFB94}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -12962,7 +15566,7 @@
         <v>879</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>901</v>
@@ -13039,1180 +15643,6 @@
     <row r="32" spans="1:2">
       <c r="A32" s="14" t="s">
         <v>905</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DB26E2-2FEB-428C-8A2B-44341C3C4297}">
-  <dimension ref="B1:P37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" customWidth="1"/>
-    <col min="5" max="5" width="38.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:16">
-      <c r="B1" s="62" t="s">
-        <v>912</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>913</v>
-      </c>
-      <c r="D1" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" s="62" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" ht="28.8">
-      <c r="B2" s="63" t="s">
-        <v>914</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>915</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>916</v>
-      </c>
-      <c r="E2" s="63">
-        <v>4</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="28.8">
-      <c r="B3" s="63" t="s">
-        <v>917</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>918</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>919</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>920</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="28.8">
-      <c r="B4" s="63" t="s">
-        <v>921</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>922</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>923</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>924</v>
-      </c>
-      <c r="G4" s="63" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="28.8">
-      <c r="B5" s="63" t="s">
-        <v>925</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>926</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>927</v>
-      </c>
-      <c r="E5" s="63" t="s">
-        <v>924</v>
-      </c>
-      <c r="G5" s="63" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" ht="57.6">
-      <c r="B6" s="63" t="s">
-        <v>928</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>929</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>930</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>931</v>
-      </c>
-      <c r="G6" s="63" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="28.8">
-      <c r="B7" s="63" t="s">
-        <v>932</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>933</v>
-      </c>
-      <c r="D7" s="63" t="s">
-        <v>934</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>935</v>
-      </c>
-      <c r="G7" s="63" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="43.2">
-      <c r="B8" s="63" t="s">
-        <v>936</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>937</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>938</v>
-      </c>
-      <c r="E8" s="63" t="s">
-        <v>939</v>
-      </c>
-      <c r="G8" s="63" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="43.2">
-      <c r="B9" s="63" t="s">
-        <v>940</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>941</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>943</v>
-      </c>
-      <c r="G9" s="63" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="43.2">
-      <c r="B10" s="63" t="s">
-        <v>944</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>945</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>946</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>947</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="28.8">
-      <c r="B11" s="63" t="s">
-        <v>948</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>949</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>950</v>
-      </c>
-      <c r="E11" s="63" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="28.8">
-      <c r="B12" s="63" t="s">
-        <v>951</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>952</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>953</v>
-      </c>
-      <c r="E12" s="63" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16">
-      <c r="F14" t="s">
-        <v>961</v>
-      </c>
-      <c r="G14" t="s">
-        <v>983</v>
-      </c>
-      <c r="H14" t="s">
-        <v>823</v>
-      </c>
-      <c r="I14" t="s">
-        <v>985</v>
-      </c>
-      <c r="J14" t="s">
-        <v>822</v>
-      </c>
-      <c r="K14" t="s">
-        <v>986</v>
-      </c>
-      <c r="L14" t="s">
-        <v>987</v>
-      </c>
-      <c r="M14" t="s">
-        <v>824</v>
-      </c>
-      <c r="N14" t="s">
-        <v>828</v>
-      </c>
-      <c r="P14" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16">
-      <c r="B15" s="64" t="s">
-        <v>960</v>
-      </c>
-      <c r="D15">
-        <v>80</v>
-      </c>
-      <c r="E15" s="63" t="s">
-        <v>970</v>
-      </c>
-      <c r="F15" s="14">
-        <v>78</v>
-      </c>
-      <c r="G15" s="14">
-        <v>94</v>
-      </c>
-      <c r="H15" s="14">
-        <v>91</v>
-      </c>
-      <c r="I15" s="14">
-        <v>84</v>
-      </c>
-      <c r="J15" s="14">
-        <v>86</v>
-      </c>
-      <c r="K15" s="14">
-        <v>79</v>
-      </c>
-      <c r="L15" s="14">
-        <v>66</v>
-      </c>
-      <c r="M15" s="14">
-        <v>80</v>
-      </c>
-      <c r="N15" s="14">
-        <v>74</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16">
-      <c r="C16" t="s">
-        <v>955</v>
-      </c>
-      <c r="E16" s="63" t="s">
-        <v>971</v>
-      </c>
-      <c r="F16">
-        <v>92</v>
-      </c>
-      <c r="G16">
-        <v>86</v>
-      </c>
-      <c r="H16">
-        <v>68</v>
-      </c>
-      <c r="I16">
-        <v>90</v>
-      </c>
-      <c r="J16">
-        <v>94</v>
-      </c>
-      <c r="K16">
-        <v>82</v>
-      </c>
-      <c r="L16">
-        <v>74</v>
-      </c>
-      <c r="M16">
-        <v>96</v>
-      </c>
-      <c r="N16">
-        <v>78</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="3:16">
-      <c r="C17" t="s">
-        <v>956</v>
-      </c>
-      <c r="D17">
-        <v>84</v>
-      </c>
-      <c r="E17" s="63" t="s">
-        <v>984</v>
-      </c>
-      <c r="F17" s="14">
-        <v>84</v>
-      </c>
-      <c r="G17" s="14">
-        <v>95</v>
-      </c>
-      <c r="H17" s="14">
-        <v>94</v>
-      </c>
-      <c r="I17" s="14">
-        <v>82</v>
-      </c>
-      <c r="J17" s="14">
-        <v>82</v>
-      </c>
-      <c r="K17" s="14">
-        <v>58</v>
-      </c>
-      <c r="L17" s="14">
-        <v>72</v>
-      </c>
-      <c r="M17" s="14">
-        <v>84</v>
-      </c>
-      <c r="N17" s="14">
-        <v>76</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
-      <c r="P17">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16">
-      <c r="C18" t="s">
-        <v>957</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>972</v>
-      </c>
-      <c r="F18">
-        <v>52</v>
-      </c>
-      <c r="G18">
-        <v>93</v>
-      </c>
-      <c r="H18">
-        <v>88</v>
-      </c>
-      <c r="I18">
-        <v>68</v>
-      </c>
-      <c r="J18">
-        <v>58</v>
-      </c>
-      <c r="K18">
-        <v>48</v>
-      </c>
-      <c r="L18">
-        <v>42</v>
-      </c>
-      <c r="M18">
-        <v>46</v>
-      </c>
-      <c r="N18">
-        <v>52</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
-      <c r="P18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16">
-      <c r="C19" t="s">
-        <v>958</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>973</v>
-      </c>
-      <c r="F19">
-        <v>88</v>
-      </c>
-      <c r="G19">
-        <v>78</v>
-      </c>
-      <c r="H19">
-        <v>74</v>
-      </c>
-      <c r="I19">
-        <v>92</v>
-      </c>
-      <c r="J19">
-        <v>95</v>
-      </c>
-      <c r="K19">
-        <v>93</v>
-      </c>
-      <c r="L19">
-        <v>88</v>
-      </c>
-      <c r="M19">
-        <v>97</v>
-      </c>
-      <c r="N19">
-        <v>88</v>
-      </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
-      <c r="P19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="3:16">
-      <c r="C20" t="s">
-        <v>959</v>
-      </c>
-      <c r="D20">
-        <v>72</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>974</v>
-      </c>
-      <c r="F20" s="14">
-        <v>58</v>
-      </c>
-      <c r="G20" s="14">
-        <v>90</v>
-      </c>
-      <c r="H20" s="14">
-        <v>89</v>
-      </c>
-      <c r="I20" s="14">
-        <v>83</v>
-      </c>
-      <c r="J20" s="14">
-        <v>76</v>
-      </c>
-      <c r="K20" s="14">
-        <v>84</v>
-      </c>
-      <c r="L20" s="14">
-        <v>58</v>
-      </c>
-      <c r="M20" s="14">
-        <v>72</v>
-      </c>
-      <c r="N20" s="14">
-        <v>62</v>
-      </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
-      <c r="P20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16">
-      <c r="E21" s="63" t="s">
-        <v>975</v>
-      </c>
-      <c r="F21">
-        <v>64</v>
-      </c>
-      <c r="G21">
-        <v>96</v>
-      </c>
-      <c r="H21">
-        <v>90</v>
-      </c>
-      <c r="I21">
-        <v>72</v>
-      </c>
-      <c r="J21">
-        <v>66</v>
-      </c>
-      <c r="K21">
-        <v>74</v>
-      </c>
-      <c r="L21">
-        <v>54</v>
-      </c>
-      <c r="M21">
-        <v>58</v>
-      </c>
-      <c r="N21">
-        <v>68</v>
-      </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16">
-      <c r="E22" s="63" t="s">
-        <v>944</v>
-      </c>
-      <c r="F22">
-        <v>38</v>
-      </c>
-      <c r="G22">
-        <v>42</v>
-      </c>
-      <c r="H22">
-        <v>58</v>
-      </c>
-      <c r="I22">
-        <v>72</v>
-      </c>
-      <c r="J22">
-        <v>48</v>
-      </c>
-      <c r="K22">
-        <v>22</v>
-      </c>
-      <c r="L22">
-        <v>36</v>
-      </c>
-      <c r="M22">
-        <v>42</v>
-      </c>
-      <c r="N22">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16">
-      <c r="E24" t="s">
-        <v>976</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16">
-      <c r="E25" t="s">
-        <v>977</v>
-      </c>
-      <c r="N25" t="s">
-        <v>989</v>
-      </c>
-      <c r="O25" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="26" spans="3:16">
-      <c r="E26" t="s">
-        <v>978</v>
-      </c>
-      <c r="N26" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16">
-      <c r="E27" t="s">
-        <v>979</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1001</v>
-      </c>
-      <c r="N27" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16">
-      <c r="E28" t="s">
-        <v>980</v>
-      </c>
-      <c r="N28" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="29" spans="3:16">
-      <c r="E29" t="s">
-        <v>981</v>
-      </c>
-      <c r="N29" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16">
-      <c r="E30" t="s">
-        <v>982</v>
-      </c>
-      <c r="N30" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C79E50-A761-4208-AC1F-7EE61CFDD025}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="19.44140625" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" customWidth="1"/>
-    <col min="8" max="8" width="28.44140625" customWidth="1"/>
-    <col min="9" max="9" width="29.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" ht="43.2">
-      <c r="A6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="43.2">
-      <c r="A7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="72">
-      <c r="A8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="28.8">
-      <c r="A9" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="100.8">
-      <c r="A10" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="43.2">
-      <c r="A11" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="72">
-      <c r="A12" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="31"/>
-      <c r="I12" s="30" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.2">
-      <c r="A13" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" ht="115.2">
-      <c r="A14" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" ht="28.8">
-      <c r="A15" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="30" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="1:9" ht="86.4">
-      <c r="A18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="30"/>
-    </row>
-    <row r="19" spans="1:9" ht="57.6">
-      <c r="A19" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="I19" s="30"/>
-    </row>
-    <row r="20" spans="1:9" ht="57.6">
-      <c r="A20" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="28.8">
-      <c r="A27" s="11" t="s">
-        <v>349</v>
       </c>
     </row>
   </sheetData>
